--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>1467149</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>23.2700004577637</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>22.6499996185303</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>23.1100006103516</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>22.7399997711182</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1463604</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>22.8700008392334</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>22.1299991607666</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>22.5400009155273</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>22.8700008392334</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>1183409</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>23.0900001525879</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>22.7600002288818</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>22.9699993133545</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>22.9500007629395</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>1009333</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>23.1499996185303</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>22.8799991607666</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>22.9500007629395</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>23.0599994659424</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1235682</v>
+        <v>860690</v>
       </c>
       <c r="C2715" t="n">
-        <v>23.2700004577637</v>
+        <v>23.4300003051758</v>
       </c>
       <c r="D2715" t="n">
-        <v>22.9099998474121</v>
+        <v>23.0200004577637</v>
       </c>
       <c r="E2715" t="n">
-        <v>23.1499996185303</v>
+        <v>23.3700008392334</v>
       </c>
       <c r="F2715" t="n">
-        <v>23.2099990844727</v>
+        <v>23.2999992370605</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>1589868</v>
+        <v>1235682</v>
       </c>
       <c r="C2716" t="n">
-        <v>23.0900001525879</v>
+        <v>23.2700004577637</v>
       </c>
       <c r="D2716" t="n">
-        <v>22.6700000762939</v>
+        <v>22.9099998474121</v>
       </c>
       <c r="E2716" t="n">
-        <v>23.0200004577637</v>
+        <v>23.1499996185303</v>
       </c>
       <c r="F2716" t="n">
-        <v>23.0699996948242</v>
+        <v>23.2099990844727</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>1165960</v>
+        <v>1589868</v>
       </c>
       <c r="C2717" t="n">
-        <v>23.4899997711182</v>
+        <v>23.0900001525879</v>
       </c>
       <c r="D2717" t="n">
-        <v>22.8500003814697</v>
+        <v>22.6700000762939</v>
       </c>
       <c r="E2717" t="n">
-        <v>23.1299991607666</v>
+        <v>23.0200004577637</v>
       </c>
       <c r="F2717" t="n">
-        <v>22.9099998474121</v>
+        <v>23.0699996948242</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>765621</v>
+        <v>1165960</v>
       </c>
       <c r="C2718" t="n">
-        <v>23.4400005340576</v>
+        <v>23.4899997711182</v>
       </c>
       <c r="D2718" t="n">
-        <v>22.9599990844727</v>
+        <v>22.8500003814697</v>
       </c>
       <c r="E2718" t="n">
-        <v>22.9599990844727</v>
+        <v>23.1299991607666</v>
       </c>
       <c r="F2718" t="n">
-        <v>23.2600002288818</v>
+        <v>22.9099998474121</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>1467149</v>
+        <v>765621</v>
       </c>
       <c r="C2719" t="n">
-        <v>23.2700004577637</v>
+        <v>23.4400005340576</v>
       </c>
       <c r="D2719" t="n">
-        <v>22.6499996185303</v>
+        <v>22.9599990844727</v>
       </c>
       <c r="E2719" t="n">
-        <v>23.1100006103516</v>
+        <v>22.9599990844727</v>
       </c>
       <c r="F2719" t="n">
-        <v>22.7399997711182</v>
+        <v>23.2600002288818</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1463604</v>
+        <v>1467149</v>
       </c>
       <c r="C2720" t="n">
-        <v>22.8700008392334</v>
+        <v>23.2700004577637</v>
       </c>
       <c r="D2720" t="n">
-        <v>22.1299991607666</v>
+        <v>22.6499996185303</v>
       </c>
       <c r="E2720" t="n">
-        <v>22.5400009155273</v>
+        <v>23.1100006103516</v>
       </c>
       <c r="F2720" t="n">
-        <v>22.8700008392334</v>
+        <v>22.7399997711182</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1183409</v>
+        <v>1463604</v>
       </c>
       <c r="C2721" t="n">
-        <v>23.0900001525879</v>
+        <v>22.8700008392334</v>
       </c>
       <c r="D2721" t="n">
-        <v>22.7600002288818</v>
+        <v>22.1299991607666</v>
       </c>
       <c r="E2721" t="n">
-        <v>22.9699993133545</v>
+        <v>22.5400009155273</v>
       </c>
       <c r="F2721" t="n">
-        <v>22.9500007629395</v>
+        <v>22.8700008392334</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>1009333</v>
+        <v>1183409</v>
       </c>
       <c r="C2722" t="n">
-        <v>23.1499996185303</v>
+        <v>23.0900001525879</v>
       </c>
       <c r="D2722" t="n">
-        <v>22.8799991607666</v>
+        <v>22.7600002288818</v>
       </c>
       <c r="E2722" t="n">
+        <v>22.9699993133545</v>
+      </c>
+      <c r="F2722" t="n">
         <v>22.9500007629395</v>
       </c>
-      <c r="F2722" t="n">
-        <v>23.0599994659424</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>2761672</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>23.1399993896484</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>22.7199993133545</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>23.1200008392334</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>22.7900009155273</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -525,7 +525,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>5.06775999069214</v>
+        <v>5.06775951385498</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94228506088257</v>
+        <v>4.94228553771973</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G11" t="n">
-        <v>4.85863637924194</v>
+        <v>4.85863590240479</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G12" t="n">
-        <v>4.74710321426392</v>
+        <v>4.74710369110107</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>4.64254140853882</v>
+        <v>4.64254188537598</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>4.86212110519409</v>
+        <v>4.86212205886841</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G21" t="n">
-        <v>4.95622682571411</v>
+        <v>4.95622730255127</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>4.93531370162964</v>
+        <v>4.9353141784668</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>4.70876502990723</v>
+        <v>4.70876407623291</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>4.39856433868408</v>
+        <v>4.39856481552124</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>4.18246984481812</v>
+        <v>4.18247032165527</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G29" t="n">
-        <v>4.29051685333252</v>
+        <v>4.29051780700684</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G30" t="n">
-        <v>4.31839990615845</v>
+        <v>4.31840038299561</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.41250610351562</v>
+        <v>4.41250658035278</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G32" t="n">
-        <v>4.60768795013428</v>
+        <v>4.60768842697144</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G33" t="n">
-        <v>4.55889225006104</v>
+        <v>4.55889177322388</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>4.63557147979736</v>
+        <v>4.63557100296021</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G36" t="n">
-        <v>4.53798007965088</v>
+        <v>4.53798055648804</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>4.67042446136475</v>
+        <v>4.6704249382019</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.75</v>
       </c>
       <c r="G39" t="n">
-        <v>4.7052788734436</v>
+        <v>4.70527839660645</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>4.93531370162964</v>
+        <v>4.9353141784668</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>4.93531370162964</v>
+        <v>4.9353141784668</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G47" t="n">
-        <v>4.77150058746338</v>
+        <v>4.7715015411377</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>4.60420322418213</v>
+        <v>4.60420227050781</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G50" t="n">
-        <v>4.77150058746338</v>
+        <v>4.7715015411377</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>4.87954902648926</v>
+        <v>4.8795485496521</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.90046119689941</v>
+        <v>4.90046072006226</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>4.86212110519409</v>
+        <v>4.86212205886841</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>4.82029676437378</v>
+        <v>4.82029581069946</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>4.87954902648926</v>
+        <v>4.8795485496521</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>4.93531370162964</v>
+        <v>4.9353141784668</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>4.99805164337158</v>
+        <v>4.99805212020874</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.03987693786621</v>
+        <v>5.03987646102905</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>5.15838003158569</v>
+        <v>5.15837955474854</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.15838003158569</v>
+        <v>5.15837955474854</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>5.03987693786621</v>
+        <v>5.03987646102905</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.93879985809326</v>
+        <v>4.93880033493042</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G66" t="n">
-        <v>4.83423757553101</v>
+        <v>4.83423852920532</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>4.76453018188477</v>
+        <v>4.76453065872192</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>4.83772325515747</v>
+        <v>4.83772373199463</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>5.13792371749878</v>
+        <v>5.1379246711731</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G76" t="n">
-        <v>5.0403003692627</v>
+        <v>5.04029989242554</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G80" t="n">
-        <v>4.97521781921387</v>
+        <v>4.97521829605103</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>5.13430881500244</v>
+        <v>5.1343092918396</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>5.10538339614868</v>
+        <v>5.10538387298584</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>5.06922674179077</v>
+        <v>5.06922626495361</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G88" t="n">
-        <v>4.78358459472656</v>
+        <v>4.78358507156372</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G89" t="n">
-        <v>4.70765495300293</v>
+        <v>4.70765542984009</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G91" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G93" t="n">
-        <v>4.5268702507019</v>
+        <v>4.52686977386475</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G95" t="n">
-        <v>4.77996969223022</v>
+        <v>4.77997016906738</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G97" t="n">
-        <v>4.77996969223022</v>
+        <v>4.77997016906738</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G99" t="n">
-        <v>4.59918355941772</v>
+        <v>4.59918451309204</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>4.56302642822266</v>
+        <v>4.56302690505981</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.73658180236816</v>
+        <v>4.73658084869385</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>4.80166292190552</v>
+        <v>4.80166339874268</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>4.79443216323853</v>
+        <v>4.79443168640137</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>4.743812084198</v>
+        <v>4.74381256103516</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G107" t="n">
-        <v>4.76912260055542</v>
+        <v>4.7691216468811</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>4.78720092773438</v>
+        <v>4.78720045089722</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>4.743812084198</v>
+        <v>4.74381256103516</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G111" t="n">
-        <v>4.78358459472656</v>
+        <v>4.78358507156372</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G113" t="n">
-        <v>4.62449407577515</v>
+        <v>4.62449359893799</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G115" t="n">
-        <v>4.39308834075928</v>
+        <v>4.39308881759644</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G116" t="n">
-        <v>4.27738571166992</v>
+        <v>4.27738523483276</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.28461742401123</v>
+        <v>4.28461694717407</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>4.29184913635254</v>
+        <v>4.29184770584106</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40032052993774</v>
+        <v>4.40031957626343</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>4.57748985290527</v>
+        <v>4.57749032974243</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>4.6281099319458</v>
+        <v>4.62810945510864</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.625</v>
       </c>
       <c r="G123" t="n">
-        <v>4.79081678390503</v>
+        <v>4.79081630706787</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G124" t="n">
-        <v>4.32438993453979</v>
+        <v>4.32439041137695</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.5</v>
       </c>
       <c r="G125" t="n">
-        <v>3.97728180885315</v>
+        <v>3.97728157043457</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>4.23399686813354</v>
+        <v>4.2339973449707</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>4.17614507675171</v>
+        <v>4.17614555358887</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G128" t="n">
-        <v>4.23038101196289</v>
+        <v>4.23038148880005</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>4.17614507675171</v>
+        <v>4.17614555358887</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02067089080811</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G132" t="n">
-        <v>3.7314133644104</v>
+        <v>3.73141360282898</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.75</v>
       </c>
       <c r="G135" t="n">
-        <v>4.15806722640991</v>
+        <v>4.15806674957275</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G139" t="n">
-        <v>4.04598093032837</v>
+        <v>4.04597997665405</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>4.15083599090576</v>
+        <v>4.1508355140686</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.75</v>
       </c>
       <c r="G143" t="n">
-        <v>4.15806722640991</v>
+        <v>4.15806674957275</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G144" t="n">
-        <v>4.09298467636108</v>
+        <v>4.09298419952393</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08936786651611</v>
+        <v>4.08936834335327</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G146" t="n">
-        <v>4.11829519271851</v>
+        <v>4.11829423904419</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>3.94474029541016</v>
+        <v>3.94474053382874</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>3.83988380432129</v>
+        <v>3.83988475799561</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G151" t="n">
-        <v>3.69525647163391</v>
+        <v>3.69525671005249</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G152" t="n">
-        <v>3.69525647163391</v>
+        <v>3.69525671005249</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>3.79288053512573</v>
+        <v>3.79287958145142</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>3.82903718948364</v>
+        <v>3.82903742790222</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G155" t="n">
-        <v>3.78926420211792</v>
+        <v>3.78926396369934</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>3.82542181015015</v>
+        <v>3.82542204856873</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G157" t="n">
-        <v>3.81095933914185</v>
+        <v>3.81095886230469</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G158" t="n">
-        <v>3.80011177062988</v>
+        <v>3.8001115322113</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>3.85073113441467</v>
+        <v>3.85073184967041</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>3.79288053512573</v>
+        <v>3.79287958145142</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>3.6880247592926</v>
+        <v>3.68802523612976</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G162" t="n">
-        <v>3.68440961837769</v>
+        <v>3.68440866470337</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.63378882408142</v>
+        <v>3.63378858566284</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5</v>
       </c>
       <c r="G164" t="n">
-        <v>3.61571073532104</v>
+        <v>3.61571002006531</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.5</v>
       </c>
       <c r="G166" t="n">
-        <v>3.97728180885315</v>
+        <v>3.97728157043457</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>3.91943049430847</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G168" t="n">
-        <v>3.89412021636963</v>
+        <v>3.89411997795105</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>3.94112467765808</v>
+        <v>3.9411244392395</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G172" t="n">
-        <v>3.98451280593872</v>
+        <v>3.98451328277588</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G173" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>3.90496754646301</v>
+        <v>3.90496730804443</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>3.92304587364197</v>
+        <v>3.92304539680481</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327217102051</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327217102051</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>3.76757025718689</v>
+        <v>3.76757097244263</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G180" t="n">
-        <v>3.68079328536987</v>
+        <v>3.68079352378845</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G181" t="n">
-        <v>3.80011177062988</v>
+        <v>3.8001115322113</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>3.67356204986572</v>
+        <v>3.67356157302856</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.76033926010132</v>
+        <v>3.76033902168274</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G185" t="n">
-        <v>3.75672364234924</v>
+        <v>3.75672340393066</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.76757025718689</v>
+        <v>3.76757097244263</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.82542181015015</v>
+        <v>3.82542204856873</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G188" t="n">
-        <v>3.7458758354187</v>
+        <v>3.74587631225586</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66994571685791</v>
+        <v>3.66994619369507</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>3.74226021766663</v>
+        <v>3.74226069450378</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G191" t="n">
-        <v>3.75310683250427</v>
+        <v>3.75310778617859</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G192" t="n">
-        <v>3.73864555358887</v>
+        <v>3.73864459991455</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72779774665833</v>
+        <v>3.7277979850769</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.70971965789795</v>
+        <v>3.70971870422363</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.68079328536987</v>
+        <v>3.68079352378845</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G196" t="n">
-        <v>3.7458758354187</v>
+        <v>3.74587631225586</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>3.7314133644104</v>
+        <v>3.73141360282898</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>3.64825201034546</v>
+        <v>3.64825224876404</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.6229419708252</v>
+        <v>3.62294244766235</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G200" t="n">
-        <v>3.4783136844635</v>
+        <v>3.47831392288208</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G201" t="n">
-        <v>3.46240425109863</v>
+        <v>3.46240496635437</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>3.65548324584961</v>
+        <v>3.65548396110535</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>3.73864555358887</v>
+        <v>3.73864459991455</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>3.75672364234924</v>
+        <v>3.75672340393066</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G205" t="n">
-        <v>3.74226021766663</v>
+        <v>3.74226069450378</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G206" t="n">
-        <v>3.75672364234924</v>
+        <v>3.75672340393066</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>3.81457471847534</v>
+        <v>3.81457424163818</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G208" t="n">
-        <v>3.83265280723572</v>
+        <v>3.83265352249146</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G210" t="n">
-        <v>3.81819081306458</v>
+        <v>3.81819033622742</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>3.8688108921051</v>
+        <v>3.86881017684937</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.93750929832458</v>
+        <v>3.93750977516174</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.99174475669861</v>
+        <v>3.99174451828003</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G214" t="n">
-        <v>3.84711623191833</v>
+        <v>3.84711575508118</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>3.78203368186951</v>
+        <v>3.78203320503235</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G216" t="n">
-        <v>3.6880247592926</v>
+        <v>3.68802523612976</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.64463543891907</v>
+        <v>3.64463591575623</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>3.64463543891907</v>
+        <v>3.64463591575623</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>3.67356204986572</v>
+        <v>3.67356157302856</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>3.68079328536987</v>
+        <v>3.68079352378845</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G223" t="n">
-        <v>3.65186762809753</v>
+        <v>3.65186786651611</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G224" t="n">
-        <v>3.61281752586365</v>
+        <v>3.61281800270081</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G226" t="n">
-        <v>3.50579285621643</v>
+        <v>3.50579357147217</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>3.47108221054077</v>
+        <v>3.47108244895935</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>3.41323065757751</v>
+        <v>3.41323041915894</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G229" t="n">
-        <v>3.41323065757751</v>
+        <v>3.41323041915894</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G230" t="n">
-        <v>3.40744519233704</v>
+        <v>3.40744614601135</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G232" t="n">
-        <v>3.42480087280273</v>
+        <v>3.42480063438416</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G234" t="n">
-        <v>3.34236335754395</v>
+        <v>3.34236288070679</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G235" t="n">
-        <v>3.45517253875732</v>
+        <v>3.4551727771759</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>3.52893400192261</v>
+        <v>3.52893376350403</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51013207435608</v>
+        <v>3.5101318359375</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53327226638794</v>
+        <v>3.53327250480652</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G239" t="n">
-        <v>3.44504904747009</v>
+        <v>3.44504880905151</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>3.60124778747559</v>
+        <v>3.60124826431274</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.64463543891907</v>
+        <v>3.64463591575623</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>3.76033926010132</v>
+        <v>3.76033902168274</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.125</v>
       </c>
       <c r="G243" t="n">
-        <v>3.70610332489014</v>
+        <v>3.70610356330872</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>3.92304587364197</v>
+        <v>3.92304539680481</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G247" t="n">
-        <v>3.98812866210938</v>
+        <v>3.9881284236908</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>3.95197248458862</v>
+        <v>3.95197129249573</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>3.86157894134521</v>
+        <v>3.86157941818237</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>3.89050507545471</v>
+        <v>3.89050531387329</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>3.94112467765808</v>
+        <v>3.9411244392395</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G253" t="n">
-        <v>3.98451280593872</v>
+        <v>3.98451328277588</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G254" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>3.8688108921051</v>
+        <v>3.86881017684937</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327217102051</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>3.85434794425964</v>
+        <v>3.85434770584106</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>3.93750929832458</v>
+        <v>3.93750977516174</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G260" t="n">
-        <v>3.92666125297546</v>
+        <v>3.92666149139404</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>3.92304587364197</v>
+        <v>3.92304539680481</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>3.9953601360321</v>
+        <v>3.99536061286926</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>3.90496754646301</v>
+        <v>3.90496730804443</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>3.99174475669861</v>
+        <v>3.99174451828003</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G268" t="n">
-        <v>3.93389272689819</v>
+        <v>3.93389320373535</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G269" t="n">
-        <v>3.92666125297546</v>
+        <v>3.92666149139404</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.99174475669861</v>
+        <v>3.99174451828003</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G272" t="n">
-        <v>4.06405925750732</v>
+        <v>4.06405782699585</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G273" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02067089080811</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.75</v>
       </c>
       <c r="G275" t="n">
-        <v>4.15806722640991</v>
+        <v>4.15806674957275</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>4.08213710784912</v>
+        <v>4.08213663101196</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G277" t="n">
-        <v>4.11829519271851</v>
+        <v>4.11829423904419</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02067089080811</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G279" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G280" t="n">
-        <v>4.04598093032837</v>
+        <v>4.04597997665405</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>4.00620698928833</v>
+        <v>4.00620651245117</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G282" t="n">
-        <v>4.04598093032837</v>
+        <v>4.04597997665405</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G284" t="n">
-        <v>3.92666125297546</v>
+        <v>3.92666149139404</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.9736659526825</v>
+        <v>3.97366547584534</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G287" t="n">
-        <v>3.91219902038574</v>
+        <v>3.91219854354858</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.93389272689819</v>
+        <v>3.93389320373535</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.94112467765808</v>
+        <v>3.9411244392395</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.92666125297546</v>
+        <v>3.92666149139404</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>3.91943049430847</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.94112467765808</v>
+        <v>3.9411244392395</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>3.91943049430847</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>3.89050507545471</v>
+        <v>3.89050531387329</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.90496754646301</v>
+        <v>3.90496730804443</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>3.90496754646301</v>
+        <v>3.90496730804443</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G300" t="n">
-        <v>3.98089694976807</v>
+        <v>3.98089718818665</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>4.14360427856445</v>
+        <v>4.14360475540161</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>4.15083599090576</v>
+        <v>4.1508355140686</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G305" t="n">
-        <v>4.17253017425537</v>
+        <v>4.17252969741821</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>4.23038101196289</v>
+        <v>4.23038148880005</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.28100109100342</v>
+        <v>4.28100156784058</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G311" t="n">
-        <v>4.46540307998657</v>
+        <v>4.46540260314941</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>4.5485634803772</v>
+        <v>4.54856395721436</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>4.46540307998657</v>
+        <v>4.46540260314941</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G316" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.63172578811646</v>
+        <v>4.6317253112793</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G319" t="n">
-        <v>4.66065168380737</v>
+        <v>4.66065073013306</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G320" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G321" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G324" t="n">
-        <v>4.62087774276733</v>
+        <v>4.62087726593018</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.55217981338501</v>
+        <v>4.55217885971069</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G326" t="n">
-        <v>4.55217981338501</v>
+        <v>4.55217885971069</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G329" t="n">
-        <v>4.59918355941772</v>
+        <v>4.59918451309204</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.6570348739624</v>
+        <v>4.65703535079956</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G335" t="n">
-        <v>4.59918355941772</v>
+        <v>4.59918451309204</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>4.94714784622192</v>
+        <v>4.94714832305908</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G338" t="n">
-        <v>4.91310834884644</v>
+        <v>4.91310882568359</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88663339614868</v>
+        <v>4.88663291931152</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G341" t="n">
-        <v>4.97740650177002</v>
+        <v>4.97740602493286</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.91310834884644</v>
+        <v>4.91310882568359</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>5.0417046546936</v>
+        <v>5.04170370101929</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13625955581665</v>
+        <v>5.13626050949097</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.14382457733154</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G346" t="n">
-        <v>5.17786359786987</v>
+        <v>5.17786407470703</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>5.14382457733154</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>5.08709096908569</v>
+        <v>5.08709049224854</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>5.0076642036438</v>
+        <v>5.00766468048096</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>5.030357837677</v>
+        <v>5.03035736083984</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.96606016159058</v>
+        <v>4.96605968475342</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>5.07196092605591</v>
+        <v>5.07196140289307</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>5.13625955581665</v>
+        <v>5.13626050949097</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17030000686646</v>
+        <v>5.1702995300293</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>5.15138864517212</v>
+        <v>5.15138816833496</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G359" t="n">
-        <v>5.18542814254761</v>
+        <v>5.18542861938477</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>5.02657508850098</v>
+        <v>5.02657556533813</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G364" t="n">
-        <v>5.12869501113892</v>
+        <v>5.12869453430176</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.05683374404907</v>
+        <v>5.05683326721191</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>5.23838043212891</v>
+        <v>5.23837995529175</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G370" t="n">
-        <v>5.33671760559082</v>
+        <v>5.33671808242798</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>5.42370796203613</v>
+        <v>5.42370891571045</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G372" t="n">
-        <v>5.41614437103271</v>
+        <v>5.41614389419556</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>5.30267810821533</v>
+        <v>5.30267763137817</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.33293581008911</v>
+        <v>5.33293533325195</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.34806394577026</v>
+        <v>5.34806489944458</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G377" t="n">
-        <v>5.29889535903931</v>
+        <v>5.29889583587646</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G378" t="n">
-        <v>5.21190357208252</v>
+        <v>5.21190404891968</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17030000686646</v>
+        <v>5.1702995300293</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17030000686646</v>
+        <v>5.1702995300293</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.14382457733154</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G382" t="n">
-        <v>5.33671760559082</v>
+        <v>5.33671808242798</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G383" t="n">
-        <v>5.31780672073364</v>
+        <v>5.3178071975708</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G384" t="n">
-        <v>5.21190357208252</v>
+        <v>5.21190404891968</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G385" t="n">
-        <v>5.40479755401611</v>
+        <v>5.40479803085327</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>5.49935293197632</v>
+        <v>5.49935340881348</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.52204704284668</v>
+        <v>5.52204656600952</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>5.45018339157104</v>
+        <v>5.45018434524536</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G398" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640254974365</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G399" t="n">
-        <v>5.40479755401611</v>
+        <v>5.40479803085327</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49935293197632</v>
+        <v>5.49935340881348</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>5.56365060806274</v>
+        <v>5.5636510848999</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G406" t="n">
-        <v>5.62416696548462</v>
+        <v>5.62416553497314</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G408" t="n">
-        <v>5.56365060806274</v>
+        <v>5.5636510848999</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.6544246673584</v>
+        <v>5.65442419052124</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G410" t="n">
-        <v>5.7149395942688</v>
+        <v>5.71494007110596</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>5.73006820678711</v>
+        <v>5.73006868362427</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G413" t="n">
-        <v>5.58256196975708</v>
+        <v>5.58256244659424</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>5.4917893409729</v>
+        <v>5.49178886413574</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G415" t="n">
-        <v>5.57499742507935</v>
+        <v>5.57499694824219</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.375</v>
       </c>
       <c r="G418" t="n">
-        <v>5.57878017425537</v>
+        <v>5.57877969741821</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G420" t="n">
-        <v>5.47665977478027</v>
+        <v>5.47665929794312</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G421" t="n">
-        <v>5.36319303512573</v>
+        <v>5.36319351196289</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.34806394577026</v>
+        <v>5.34806489944458</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G427" t="n">
-        <v>5.45774841308594</v>
+        <v>5.4577488899231</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640254974365</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>5.36319303512573</v>
+        <v>5.36319351196289</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>5.27620124816895</v>
+        <v>5.2762017250061</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>5.25729084014893</v>
+        <v>5.25729036331177</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>5.45018339157104</v>
+        <v>5.45018434524536</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G435" t="n">
-        <v>5.53717517852783</v>
+        <v>5.53717565536499</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>5.54852247238159</v>
+        <v>5.54852199554443</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>5.58634519577026</v>
+        <v>5.58634471893311</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>5.6544246673584</v>
+        <v>5.65442419052124</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G442" t="n">
-        <v>5.69602870941162</v>
+        <v>5.69602918624878</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G443" t="n">
-        <v>5.66198921203613</v>
+        <v>5.66198873519897</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.375</v>
       </c>
       <c r="G444" t="n">
-        <v>5.57878017425537</v>
+        <v>5.57877969741821</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>5.63551378250122</v>
+        <v>5.63551330566406</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>5.62794828414917</v>
+        <v>5.62794923782349</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>5.6430778503418</v>
+        <v>5.64307737350464</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>5.51070022583008</v>
+        <v>5.51069927215576</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640254974365</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G455" t="n">
-        <v>5.43883800506592</v>
+        <v>5.43883752822876</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G457" t="n">
-        <v>5.50691747665405</v>
+        <v>5.50691795349121</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>5.56365060806274</v>
+        <v>5.5636510848999</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G460" t="n">
-        <v>5.50691747665405</v>
+        <v>5.50691795349121</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>5.53717517852783</v>
+        <v>5.53717565536499</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>5.5523042678833</v>
+        <v>5.55230474472046</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G465" t="n">
-        <v>5.88892269134521</v>
+        <v>5.8889217376709</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>5.85866403579712</v>
+        <v>5.85866451263428</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G467" t="n">
-        <v>6.02886438369751</v>
+        <v>6.02886486053467</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.0137357711792</v>
+        <v>6.01373529434204</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.03499984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>6.07803344726562</v>
+        <v>6.07803297042847</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G470" t="n">
-        <v>6.0742506980896</v>
+        <v>6.07425117492676</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G471" t="n">
-        <v>6.06668663024902</v>
+        <v>6.06668710708618</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>6.05912256240845</v>
+        <v>6.05912208557129</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G473" t="n">
-        <v>6.0250825881958</v>
+        <v>6.02508163452148</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>6.02130031585693</v>
+        <v>6.02129983901978</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>5.88892269134521</v>
+        <v>5.8889217376709</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G480" t="n">
-        <v>5.83597183227539</v>
+        <v>5.83597230911255</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>5.78680276870728</v>
+        <v>5.78680229187012</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>5.90026903152466</v>
+        <v>5.90026950836182</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G483" t="n">
-        <v>5.99482440948486</v>
+        <v>5.99482488632202</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>6.04777574539185</v>
+        <v>6.047776222229</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G485" t="n">
-        <v>6.13476705551147</v>
+        <v>6.13476657867432</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G486" t="n">
-        <v>6.13854932785034</v>
+        <v>6.13854885101318</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>6.16124296188354</v>
+        <v>6.16124248504639</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G489" t="n">
-        <v>6.13476705551147</v>
+        <v>6.13476657867432</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G490" t="n">
-        <v>6.21419429779053</v>
+        <v>6.21419382095337</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>6.34278964996338</v>
+        <v>6.34278869628906</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>6.29740285873413</v>
+        <v>6.29740190505981</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>6.39195871353149</v>
+        <v>6.39195775985718</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G497" t="n">
-        <v>6.46381950378418</v>
+        <v>6.46382093429565</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G498" t="n">
-        <v>6.57728624343872</v>
+        <v>6.57728672027588</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G499" t="n">
-        <v>6.44112730026245</v>
+        <v>6.44112682342529</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G500" t="n">
-        <v>6.53946542739868</v>
+        <v>6.53946495056152</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G502" t="n">
-        <v>6.4751672744751</v>
+        <v>6.47516632080078</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G503" t="n">
-        <v>6.44112730026245</v>
+        <v>6.44112682342529</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>6.50542545318604</v>
+        <v>6.50542497634888</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G506" t="n">
-        <v>6.51298809051514</v>
+        <v>6.51298856735229</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G507" t="n">
-        <v>6.57728624343872</v>
+        <v>6.57728672027588</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G508" t="n">
-        <v>6.60376214981079</v>
+        <v>6.60376262664795</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G509" t="n">
-        <v>6.60754442214966</v>
+        <v>6.60754346847534</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.55837535858154</v>
+        <v>6.5583758354187</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>6.39952278137207</v>
+        <v>6.39952230453491</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G514" t="n">
-        <v>6.65671443939209</v>
+        <v>6.65671396255493</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G515" t="n">
-        <v>6.73992204666138</v>
+        <v>6.73992156982422</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>7.06141138076782</v>
+        <v>7.06141185760498</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G518" t="n">
-        <v>7.12949180603027</v>
+        <v>7.12949228286743</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G520" t="n">
-        <v>7.26186943054199</v>
+        <v>7.26186990737915</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>7.27321672439575</v>
+        <v>7.27321577072144</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>7.19000673294067</v>
+        <v>7.19000720977783</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G524" t="n">
-        <v>7.32238483428955</v>
+        <v>7.32238531112671</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>7.38290166854858</v>
+        <v>7.38290023803711</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G529" t="n">
-        <v>7.5947060585022</v>
+        <v>7.59470558166504</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G531" t="n">
-        <v>7.62496137619019</v>
+        <v>7.62496328353882</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>7.49636745452881</v>
+        <v>7.49636697769165</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>7.57201194763184</v>
+        <v>7.57201099395752</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>10.0249996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>7.58335733413696</v>
+        <v>7.58335828781128</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G535" t="n">
-        <v>7.45400619506836</v>
+        <v>7.45400810241699</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.75</v>
       </c>
       <c r="G536" t="n">
-        <v>7.37533617019653</v>
+        <v>7.37533569335938</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.31799983978271</v>
       </c>
       <c r="G537" t="n">
-        <v>7.04855251312256</v>
+        <v>7.04855155944824</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G538" t="n">
-        <v>7.23009872436523</v>
+        <v>7.23009777069092</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.58800029754639</v>
       </c>
       <c r="G539" t="n">
-        <v>7.25279331207275</v>
+        <v>7.25279188156128</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9.21399974822998</v>
       </c>
       <c r="G540" t="n">
-        <v>6.96988248825073</v>
+        <v>6.96988153457642</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>9.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.99711465835571</v>
+        <v>6.99711418151855</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G542" t="n">
-        <v>6.97593402862549</v>
+        <v>6.97593259811401</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.53600025177002</v>
       </c>
       <c r="G544" t="n">
-        <v>7.21345806121826</v>
+        <v>7.2134575843811</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G545" t="n">
-        <v>7.31028127670288</v>
+        <v>7.31028079986572</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G546" t="n">
-        <v>7.31028127670288</v>
+        <v>7.31028079986572</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G547" t="n">
-        <v>7.41164588928223</v>
+        <v>7.41164636611938</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G548" t="n">
-        <v>7.48577737808228</v>
+        <v>7.48577642440796</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G549" t="n">
-        <v>7.51149606704712</v>
+        <v>7.51149654388428</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.90200042724609</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49031591415405</v>
+        <v>7.49031686782837</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.97200012207031</v>
       </c>
       <c r="G551" t="n">
-        <v>7.54326772689819</v>
+        <v>7.54326581954956</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G552" t="n">
-        <v>7.62496137619019</v>
+        <v>7.62496328353882</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G553" t="n">
-        <v>7.6552209854126</v>
+        <v>7.65521955490112</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>10.1450004577637</v>
       </c>
       <c r="G554" t="n">
-        <v>7.67413091659546</v>
+        <v>7.67413282394409</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G555" t="n">
-        <v>7.41164588928223</v>
+        <v>7.41164636611938</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G556" t="n">
-        <v>7.24220275878906</v>
+        <v>7.2422022819519</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>9.9680004119873</v>
       </c>
       <c r="G557" t="n">
-        <v>7.54024124145508</v>
+        <v>7.54024219512939</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>10.1350002288818</v>
       </c>
       <c r="G558" t="n">
-        <v>7.6665678024292</v>
+        <v>7.66656732559204</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>10.1450004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>7.67413091659546</v>
+        <v>7.67413282394409</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G561" t="n">
-        <v>7.79138088226318</v>
+        <v>7.7913818359375</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>7.64765596389771</v>
+        <v>7.64765548706055</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>10.125</v>
       </c>
       <c r="G563" t="n">
-        <v>7.65900373458862</v>
+        <v>7.65900325775146</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G564" t="n">
-        <v>7.74599409103394</v>
+        <v>7.74599313735962</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>7.64765596389771</v>
+        <v>7.64765548706055</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>7.77247047424316</v>
+        <v>7.77246952056885</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G569" t="n">
-        <v>7.57579278945923</v>
+        <v>7.57579374313354</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G570" t="n">
-        <v>7.54931783676147</v>
+        <v>7.54931735992432</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G571" t="n">
-        <v>7.41013145446777</v>
+        <v>7.41013288497925</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.81599998474121</v>
       </c>
       <c r="G572" t="n">
-        <v>7.4252610206604</v>
+        <v>7.42526149749756</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.69400024414062</v>
       </c>
       <c r="G575" t="n">
-        <v>7.33297538757324</v>
+        <v>7.3329758644104</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G576" t="n">
-        <v>7.37231159210205</v>
+        <v>7.37231063842773</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.74400043487549</v>
       </c>
       <c r="G579" t="n">
-        <v>7.37079763412476</v>
+        <v>7.37079811096191</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G580" t="n">
-        <v>7.41164588928223</v>
+        <v>7.41164636611938</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>7.31481981277466</v>
+        <v>7.31482172012329</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.62600040435791</v>
       </c>
       <c r="G582" t="n">
-        <v>7.28153705596924</v>
+        <v>7.28153800964355</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G583" t="n">
-        <v>7.31028127670288</v>
+        <v>7.31028079986572</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>7.46610832214355</v>
+        <v>7.46610879898071</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G586" t="n">
-        <v>7.54175567626953</v>
+        <v>7.54175424575806</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.96399974822998</v>
       </c>
       <c r="G587" t="n">
-        <v>7.53721618652344</v>
+        <v>7.53721475601196</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G588" t="n">
-        <v>7.5069580078125</v>
+        <v>7.50695753097534</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G589" t="n">
-        <v>7.74138021469116</v>
+        <v>7.74137926101685</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G591" t="n">
-        <v>7.7195725440979</v>
+        <v>7.71957349777222</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G592" t="n">
-        <v>7.67440176010132</v>
+        <v>7.67440319061279</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G593" t="n">
-        <v>7.67907524108887</v>
+        <v>7.67907428741455</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.9040002822876</v>
       </c>
       <c r="G594" t="n">
-        <v>7.7133412361145</v>
+        <v>7.71334218978882</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.87399959564209</v>
       </c>
       <c r="G596" t="n">
-        <v>7.68997764587402</v>
+        <v>7.68997859954834</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G598" t="n">
-        <v>7.91271734237671</v>
+        <v>7.91271829605103</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.80799961090088</v>
       </c>
       <c r="G599" t="n">
-        <v>7.6385760307312</v>
+        <v>7.63857698440552</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G600" t="n">
-        <v>7.7195725440979</v>
+        <v>7.71957349777222</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G601" t="n">
-        <v>7.57004070281982</v>
+        <v>7.57004165649414</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56848430633545</v>
+        <v>7.56848335266113</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58717489242554</v>
+        <v>7.58717393875122</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G606" t="n">
-        <v>7.14480924606323</v>
+        <v>7.14481019973755</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>8.96599960327148</v>
       </c>
       <c r="G607" t="n">
-        <v>6.98281812667847</v>
+        <v>6.98281717300415</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.89799976348877</v>
       </c>
       <c r="G608" t="n">
-        <v>6.92985820770264</v>
+        <v>6.92985916137695</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>9.1879997253418</v>
       </c>
       <c r="G609" t="n">
-        <v>7.15571260452271</v>
+        <v>7.15571308135986</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>9.1560001373291</v>
       </c>
       <c r="G610" t="n">
-        <v>7.13079214096069</v>
+        <v>7.13079261779785</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.18200016021729</v>
       </c>
       <c r="G611" t="n">
-        <v>7.15104055404663</v>
+        <v>7.15104150772095</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>8.78600025177002</v>
       </c>
       <c r="G612" t="n">
-        <v>6.84263229370117</v>
+        <v>6.84263181686401</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.95599985122681</v>
       </c>
       <c r="G614" t="n">
-        <v>6.19621896743774</v>
+        <v>6.19621849060059</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>8.4680004119873</v>
       </c>
       <c r="G615" t="n">
-        <v>6.59497022628784</v>
+        <v>6.594970703125</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>8.55399990081787</v>
       </c>
       <c r="G616" t="n">
-        <v>6.66194820404053</v>
+        <v>6.66194772720337</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.56400012969971</v>
       </c>
       <c r="G618" t="n">
-        <v>6.66973543167114</v>
+        <v>6.6697359085083</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G620" t="n">
-        <v>6.9547815322876</v>
+        <v>6.95478057861328</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.9040002822876</v>
       </c>
       <c r="G621" t="n">
-        <v>6.93453168869019</v>
+        <v>6.93453216552734</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G622" t="n">
-        <v>6.88313007354736</v>
+        <v>6.88312959671021</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.41800022125244</v>
       </c>
       <c r="G624" t="n">
-        <v>7.33483934402466</v>
+        <v>7.33484077453613</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>7.3052453994751</v>
+        <v>7.30524492263794</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G626" t="n">
-        <v>7.41895151138306</v>
+        <v>7.41895246505737</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>9.48200035095215</v>
       </c>
       <c r="G627" t="n">
-        <v>7.38468503952026</v>
+        <v>7.38468360900879</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.44400024414062</v>
       </c>
       <c r="G628" t="n">
-        <v>7.35509014129639</v>
+        <v>7.35508966445923</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G629" t="n">
-        <v>7.41895151138306</v>
+        <v>7.41895246505737</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.4220666885376</v>
+        <v>7.42206573486328</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34730100631714</v>
+        <v>7.3473014831543</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G635" t="n">
-        <v>7.37533903121948</v>
+        <v>7.37533807754517</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G641" t="n">
-        <v>7.73359155654907</v>
+        <v>7.73359251022339</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>7.65571069717407</v>
+        <v>7.65570974349976</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>9.97599983215332</v>
       </c>
       <c r="G645" t="n">
-        <v>7.76941680908203</v>
+        <v>7.76941776275635</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G647" t="n">
-        <v>7.94776439666748</v>
+        <v>7.9477653503418</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.25</v>
       </c>
       <c r="G648" t="n">
-        <v>7.98281097412109</v>
+        <v>7.98281049728394</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G649" t="n">
-        <v>7.99060010910034</v>
+        <v>7.99059915542603</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G651" t="n">
-        <v>7.9711275100708</v>
+        <v>7.97112846374512</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G652" t="n">
-        <v>7.8815655708313</v>
+        <v>7.88156461715698</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G654" t="n">
-        <v>7.94776439666748</v>
+        <v>7.9477653503418</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>10.2449998855591</v>
       </c>
       <c r="G656" t="n">
-        <v>7.97891569137573</v>
+        <v>7.97891712188721</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G657" t="n">
-        <v>7.94776439666748</v>
+        <v>7.9477653503418</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>7.94387054443359</v>
+        <v>7.94386959075928</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>10.1949996948242</v>
       </c>
       <c r="G660" t="n">
-        <v>7.93997573852539</v>
+        <v>7.93997669219971</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>9.97399997711182</v>
       </c>
       <c r="G663" t="n">
-        <v>7.76785755157471</v>
+        <v>7.76785850524902</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G665" t="n">
-        <v>7.78031969070435</v>
+        <v>7.78031873703003</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>9.9980001449585</v>
       </c>
       <c r="G667" t="n">
-        <v>7.78655004501343</v>
+        <v>7.78654909133911</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G671" t="n">
-        <v>7.94776439666748</v>
+        <v>7.9477653503418</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>8.00228118896484</v>
+        <v>8.00228023529053</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10.125</v>
       </c>
       <c r="G678" t="n">
-        <v>7.8854603767395</v>
+        <v>7.88545942306519</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>8.02564716339111</v>
+        <v>8.0256462097168</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>7.99060010910034</v>
+        <v>7.99059915542603</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>10.2650003433228</v>
       </c>
       <c r="G681" t="n">
-        <v>7.99449300765991</v>
+        <v>7.9944920539856</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G690" t="n">
-        <v>8.70710563659668</v>
+        <v>8.70710468292236</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G693" t="n">
-        <v>8.98747730255127</v>
+        <v>8.98747634887695</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97579479217529</v>
+        <v>8.97579383850098</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G695" t="n">
-        <v>8.88623046875</v>
+        <v>8.88622951507568</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>11.6450004577637</v>
       </c>
       <c r="G696" t="n">
-        <v>9.06925106048584</v>
+        <v>9.06925201416016</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G698" t="n">
-        <v>9.26006126403809</v>
+        <v>9.26006031036377</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G699" t="n">
-        <v>9.26006126403809</v>
+        <v>9.26006031036377</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>9.13155746459961</v>
+        <v>9.13155651092529</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G701" t="n">
-        <v>8.9680061340332</v>
+        <v>8.96800708770752</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G702" t="n">
-        <v>9.04978179931641</v>
+        <v>9.04978084564209</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G706" t="n">
-        <v>8.77719879150391</v>
+        <v>8.77719783782959</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>8.33327674865723</v>
+        <v>8.33327579498291</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G709" t="n">
-        <v>7.94776439666748</v>
+        <v>7.9477653503418</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G713" t="n">
-        <v>7.81926155090332</v>
+        <v>7.819260597229</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>9.68599987030029</v>
       </c>
       <c r="G714" t="n">
-        <v>7.54356288909912</v>
+        <v>7.5435619354248</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>9.23400020599365</v>
       </c>
       <c r="G715" t="n">
-        <v>7.1915397644043</v>
+        <v>7.19153928756714</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G716" t="n">
-        <v>6.98437595367432</v>
+        <v>6.98437547683716</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G717" t="n">
-        <v>6.97347211837769</v>
+        <v>6.97347259521484</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G718" t="n">
-        <v>6.89559125900269</v>
+        <v>6.89559078216553</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>8.72599983215332</v>
       </c>
       <c r="G719" t="n">
-        <v>6.79590320587158</v>
+        <v>6.79590272903442</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>8.77400016784668</v>
       </c>
       <c r="G721" t="n">
-        <v>6.83328676223755</v>
+        <v>6.83328580856323</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>9.04599952697754</v>
       </c>
       <c r="G722" t="n">
-        <v>7.04512214660645</v>
+        <v>7.04512166976929</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G723" t="n">
-        <v>7.06692886352539</v>
+        <v>7.06692981719971</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.38599967956543</v>
       </c>
       <c r="G725" t="n">
-        <v>7.30991792678833</v>
+        <v>7.30991888046265</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G726" t="n">
-        <v>7.62922954559326</v>
+        <v>7.62923049926758</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>9.60200023651123</v>
       </c>
       <c r="G728" t="n">
-        <v>7.47814130783081</v>
+        <v>7.47814226150513</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>9.87600040435791</v>
       </c>
       <c r="G730" t="n">
-        <v>7.6915340423584</v>
+        <v>7.69153594970703</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>9.90200042724609</v>
       </c>
       <c r="G731" t="n">
-        <v>7.71178483963013</v>
+        <v>7.71178579330444</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>9.82400035858154</v>
       </c>
       <c r="G732" t="n">
-        <v>7.65103721618652</v>
+        <v>7.65103816986084</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>9.7480001449585</v>
       </c>
       <c r="G734" t="n">
-        <v>7.59184741973877</v>
+        <v>7.59184837341309</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G738" t="n">
-        <v>7.47502470016479</v>
+        <v>7.47502565383911</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G742" t="n">
-        <v>7.62922954559326</v>
+        <v>7.62923049926758</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>7.40025949478149</v>
+        <v>7.40025997161865</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G746" t="n">
-        <v>7.37533903121948</v>
+        <v>7.37533807754517</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.58199977874756</v>
       </c>
       <c r="G748" t="n">
-        <v>7.46256542205811</v>
+        <v>7.46256446838379</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G749" t="n">
-        <v>7.57004070281982</v>
+        <v>7.57004165649414</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.0620002746582</v>
       </c>
       <c r="G750" t="n">
-        <v>7.05758380889893</v>
+        <v>7.05758428573608</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G751" t="n">
-        <v>7.11677312850952</v>
+        <v>7.11677265167236</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>8.93400001525879</v>
       </c>
       <c r="G752" t="n">
-        <v>6.95789527893066</v>
+        <v>6.95789623260498</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>8.96399974822998</v>
       </c>
       <c r="G753" t="n">
-        <v>6.98125982284546</v>
+        <v>6.9812593460083</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G755" t="n">
-        <v>7.21646118164062</v>
+        <v>7.21646165847778</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.14400005340576</v>
       </c>
       <c r="G756" t="n">
-        <v>7.12144613265991</v>
+        <v>7.12144660949707</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.92599964141846</v>
       </c>
       <c r="G758" t="n">
-        <v>6.95166444778442</v>
+        <v>6.95166540145874</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>9.0939998626709</v>
       </c>
       <c r="G759" t="n">
-        <v>7.08250570297241</v>
+        <v>7.0825047492981</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G762" t="n">
-        <v>6.67440843582153</v>
+        <v>6.67440795898438</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>8.77799987792969</v>
       </c>
       <c r="G763" t="n">
-        <v>6.83640146255493</v>
+        <v>6.83640098571777</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>8.75399971008301</v>
       </c>
       <c r="G764" t="n">
-        <v>6.81770944595337</v>
+        <v>6.81770896911621</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.64599990844727</v>
       </c>
       <c r="G765" t="n">
-        <v>6.73359727859497</v>
+        <v>6.73359823226929</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>6.97035646438599</v>
+        <v>6.97035789489746</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G768" t="n">
-        <v>7.30368804931641</v>
+        <v>7.30368757247925</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G769" t="n">
-        <v>7.34106969833374</v>
+        <v>7.34107065200806</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.32400035858154</v>
       </c>
       <c r="G772" t="n">
-        <v>7.26163244247437</v>
+        <v>7.26163196563721</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>9.81400012969971</v>
       </c>
       <c r="G775" t="n">
-        <v>7.64324951171875</v>
+        <v>7.64324855804443</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>9.90200042724609</v>
       </c>
       <c r="G776" t="n">
-        <v>7.71178483963013</v>
+        <v>7.71178579330444</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>9.80399990081787</v>
       </c>
       <c r="G780" t="n">
-        <v>7.6354603767395</v>
+        <v>7.63546133041382</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>9.71599960327148</v>
       </c>
       <c r="G784" t="n">
-        <v>7.56692600250244</v>
+        <v>7.56692504882812</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G786" t="n">
-        <v>7.29122734069824</v>
+        <v>7.29122686386108</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G789" t="n">
-        <v>7.72113084793091</v>
+        <v>7.72112894058228</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G790" t="n">
-        <v>7.51863861083984</v>
+        <v>7.51863956451416</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G793" t="n">
-        <v>7.70711183547974</v>
+        <v>7.70711088180542</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>10.3850002288818</v>
       </c>
       <c r="G794" t="n">
-        <v>8.08794975280762</v>
+        <v>8.08795070648193</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G795" t="n">
-        <v>7.93218898773193</v>
+        <v>7.93218803405762</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G798" t="n">
-        <v>8.07626819610596</v>
+        <v>8.07626914978027</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.2250003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>7.96333980560303</v>
+        <v>7.96334171295166</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G800" t="n">
-        <v>7.78031969070435</v>
+        <v>7.78031873703003</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.1149997711182</v>
       </c>
       <c r="G801" t="n">
-        <v>7.8776707649231</v>
+        <v>7.87766981124878</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G802" t="n">
-        <v>7.9711275100708</v>
+        <v>7.97112846374512</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>10.3249998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>8.04122257232666</v>
+        <v>8.04122161865234</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.3249998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>8.82003307342529</v>
+        <v>8.82003402709961</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G809" t="n">
-        <v>8.84729099273682</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>11.1549997329712</v>
       </c>
       <c r="G810" t="n">
-        <v>8.6876335144043</v>
+        <v>8.68763542175293</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G813" t="n">
-        <v>8.84729099273682</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>8.83950233459473</v>
+        <v>8.83950328826904</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>11.414999961853</v>
       </c>
       <c r="G815" t="n">
-        <v>8.89012432098389</v>
+        <v>8.8901252746582</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G816" t="n">
-        <v>9.00305271148682</v>
+        <v>9.00305366516113</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>8.97579479217529</v>
+        <v>8.97579383850098</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G819" t="n">
-        <v>8.97968864440918</v>
+        <v>8.97968769073486</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G821" t="n">
-        <v>8.97968864440918</v>
+        <v>8.97968769073486</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G822" t="n">
-        <v>8.83950233459473</v>
+        <v>8.83950328826904</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>8.88623046875</v>
+        <v>8.88622951507568</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G825" t="n">
-        <v>9.01862716674805</v>
+        <v>9.01862907409668</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>9.13155746459961</v>
+        <v>9.13155651092529</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G829" t="n">
-        <v>9.26006126403809</v>
+        <v>9.26006031036377</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>11.8649997711182</v>
       </c>
       <c r="G830" t="n">
-        <v>9.24059009552002</v>
+        <v>9.24059104919434</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>11.7150001525879</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12376880645752</v>
+        <v>9.1237678527832</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>12.3850002288818</v>
       </c>
       <c r="G837" t="n">
-        <v>9.6455717086792</v>
+        <v>9.64557266235352</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>12.3850002288818</v>
       </c>
       <c r="G838" t="n">
-        <v>9.6455717086792</v>
+        <v>9.64557266235352</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>12.3850002288818</v>
       </c>
       <c r="G839" t="n">
-        <v>9.6455717086792</v>
+        <v>9.64557266235352</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G841" t="n">
-        <v>9.66452980041504</v>
+        <v>9.66452789306641</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G844" t="n">
-        <v>9.61660480499268</v>
+        <v>9.61660575866699</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>11.7349996566772</v>
       </c>
       <c r="G846" t="n">
-        <v>9.3729944229126</v>
+        <v>9.37299537658691</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G848" t="n">
-        <v>9.05749893188477</v>
+        <v>9.0575008392334</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.25</v>
       </c>
       <c r="G850" t="n">
-        <v>8.18689441680908</v>
+        <v>8.18689346313477</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>9.60799980163574</v>
       </c>
       <c r="G854" t="n">
-        <v>7.67411470413208</v>
+        <v>7.6741156578064</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G855" t="n">
-        <v>7.82427406311035</v>
+        <v>7.82427501678467</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G860" t="n">
-        <v>7.90734052658081</v>
+        <v>7.90734148025513</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G862" t="n">
-        <v>7.71085548400879</v>
+        <v>7.71085643768311</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>9.5</v>
       </c>
       <c r="G865" t="n">
-        <v>7.58785390853882</v>
+        <v>7.5878529548645</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G866" t="n">
-        <v>7.38977098464966</v>
+        <v>7.38976955413818</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G867" t="n">
-        <v>7.38977098464966</v>
+        <v>7.38976955413818</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.27600002288818</v>
       </c>
       <c r="G868" t="n">
-        <v>7.40893936157227</v>
+        <v>7.40894031524658</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G870" t="n">
-        <v>7.48881149291992</v>
+        <v>7.48881244659424</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>7.42810916900635</v>
+        <v>7.42810821533203</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>9.28400039672852</v>
       </c>
       <c r="G874" t="n">
-        <v>7.41532897949219</v>
+        <v>7.4153299331665</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>9.19400024414062</v>
       </c>
       <c r="G877" t="n">
-        <v>7.34344339370728</v>
+        <v>7.34344387054443</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>9.10400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>7.27155828475952</v>
+        <v>7.27155876159668</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>9.54800033569336</v>
       </c>
       <c r="G882" t="n">
-        <v>7.62619161605835</v>
+        <v>7.62619066238403</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G883" t="n">
-        <v>7.82267713546753</v>
+        <v>7.82267618179321</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G888" t="n">
-        <v>7.83545589447021</v>
+        <v>7.83545684814453</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>7.91532850265503</v>
+        <v>7.91532945632935</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>10.375</v>
       </c>
       <c r="G891" t="n">
-        <v>8.28673267364502</v>
+        <v>8.28673362731934</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>10.7049999237061</v>
       </c>
       <c r="G892" t="n">
-        <v>8.55031108856201</v>
+        <v>8.55031204223633</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G893" t="n">
-        <v>8.53833198547363</v>
+        <v>8.53833103179932</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G894" t="n">
-        <v>8.23082447052002</v>
+        <v>8.2308235168457</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G895" t="n">
-        <v>8.07507228851318</v>
+        <v>8.0750732421875</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.2650003433228</v>
       </c>
       <c r="G897" t="n">
-        <v>8.19887542724609</v>
+        <v>8.19887447357178</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G899" t="n">
-        <v>7.99919509887695</v>
+        <v>7.99919414520264</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>9.99600028991699</v>
       </c>
       <c r="G901" t="n">
-        <v>7.98401880264282</v>
+        <v>7.98401975631714</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>9.71399974822998</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75877952575684</v>
+        <v>7.75877857208252</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>9.72599983215332</v>
       </c>
       <c r="G904" t="n">
-        <v>7.76836252212524</v>
+        <v>7.76836442947388</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G906" t="n">
-        <v>7.99919509887695</v>
+        <v>7.99919414520264</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>7.0926456451416</v>
+        <v>7.09264612197876</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.99199962615967</v>
       </c>
       <c r="G911" t="n">
-        <v>7.18210220336914</v>
+        <v>7.1821026802063</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.91199970245361</v>
       </c>
       <c r="G913" t="n">
-        <v>7.11820363998413</v>
+        <v>7.11820411682129</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.70600032806396</v>
       </c>
       <c r="G914" t="n">
-        <v>6.95366716384888</v>
+        <v>6.95366764068604</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.90200042724609</v>
       </c>
       <c r="G915" t="n">
-        <v>7.11021709442139</v>
+        <v>7.11021757125854</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>8.90799999237061</v>
       </c>
       <c r="G916" t="n">
-        <v>7.11500930786133</v>
+        <v>7.11500978469849</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>9.32199954986572</v>
       </c>
       <c r="G917" t="n">
-        <v>7.44567966461182</v>
+        <v>7.44568061828613</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>8.94400024414062</v>
       </c>
       <c r="G918" t="n">
-        <v>7.14376401901245</v>
+        <v>7.14376354217529</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>8.74199962615967</v>
       </c>
       <c r="G919" t="n">
-        <v>6.98242235183716</v>
+        <v>6.982421875</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G922" t="n">
-        <v>6.91373205184937</v>
+        <v>6.91373252868652</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G925" t="n">
-        <v>7.28433847427368</v>
+        <v>7.28433895111084</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G926" t="n">
-        <v>7.38977098464966</v>
+        <v>7.38976955413818</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G930" t="n">
-        <v>7.45207023620605</v>
+        <v>7.45207118988037</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G931" t="n">
-        <v>7.63417863845825</v>
+        <v>7.63417768478394</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>9.87399959564209</v>
       </c>
       <c r="G938" t="n">
-        <v>7.88657522201538</v>
+        <v>7.88657426834106</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G940" t="n">
-        <v>7.42810916900635</v>
+        <v>7.42810821533203</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G942" t="n">
-        <v>7.8674054145813</v>
+        <v>7.86740589141846</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G944" t="n">
-        <v>7.47603178024292</v>
+        <v>7.47603225708008</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G948" t="n">
-        <v>7.69328355789185</v>
+        <v>7.69328308105469</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G950" t="n">
-        <v>7.47603178024292</v>
+        <v>7.47603225708008</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>9.60400009155273</v>
       </c>
       <c r="G954" t="n">
-        <v>7.67091989517212</v>
+        <v>7.6709189414978</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>9.36600017547607</v>
       </c>
       <c r="G955" t="n">
-        <v>7.48082447052002</v>
+        <v>7.48082542419434</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G956" t="n">
-        <v>7.61181497573853</v>
+        <v>7.61181402206421</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>9.64599990844727</v>
       </c>
       <c r="G957" t="n">
-        <v>7.70446538925171</v>
+        <v>7.70446634292603</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>9.22799968719482</v>
       </c>
       <c r="G959" t="n">
-        <v>7.37060070037842</v>
+        <v>7.37060022354126</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G961" t="n">
-        <v>7.60382795333862</v>
+        <v>7.60382699966431</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G962" t="n">
-        <v>7.82587194442749</v>
+        <v>7.82587099075317</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>9.85599994659424</v>
       </c>
       <c r="G964" t="n">
-        <v>7.87219715118408</v>
+        <v>7.8721981048584</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G971" t="n">
-        <v>8.13497734069824</v>
+        <v>8.13497638702393</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G972" t="n">
-        <v>8.11500835418701</v>
+        <v>8.11500930786133</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.4049997329712</v>
       </c>
       <c r="G973" t="n">
-        <v>8.31069469451904</v>
+        <v>8.31069564819336</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>8.30670261383057</v>
+        <v>8.30670166015625</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G977" t="n">
-        <v>8.29072761535645</v>
+        <v>8.29072856903076</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>8.5263500213623</v>
+        <v>8.52635097503662</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>8.62619018554688</v>
+        <v>8.62618923187256</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G982" t="n">
-        <v>8.79392147064209</v>
+        <v>8.79392242431641</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.1350002288818</v>
       </c>
       <c r="G983" t="n">
-        <v>8.89376258850098</v>
+        <v>8.89376163482666</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G986" t="n">
-        <v>9.17331504821777</v>
+        <v>9.17331409454346</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G990" t="n">
-        <v>9.08146095275879</v>
+        <v>9.08146190643311</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>11.3149995803833</v>
       </c>
       <c r="G991" t="n">
-        <v>9.03753185272217</v>
+        <v>9.03753089904785</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>11.4750003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>9.16532802581787</v>
+        <v>9.16532707214355</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G993" t="n">
-        <v>9.37698936462402</v>
+        <v>9.37698841094971</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G995" t="n">
-        <v>9.21724510192871</v>
+        <v>9.21724414825439</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G997" t="n">
-        <v>8.99360179901123</v>
+        <v>8.99360275268555</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1000" t="n">
-        <v>8.99360179901123</v>
+        <v>8.99360275268555</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1003" t="n">
-        <v>8.85781955718994</v>
+        <v>8.85782051086426</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>11.2250003814697</v>
       </c>
       <c r="G1004" t="n">
-        <v>8.96564769744873</v>
+        <v>8.96564674377441</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.77794742584229</v>
+        <v>8.7779483795166</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.70606422424316</v>
+        <v>8.70606327056885</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>10.9250001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.72603034973145</v>
+        <v>8.72603130340576</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G1012" t="n">
-        <v>8.68210124969482</v>
+        <v>8.68210029602051</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>10.914999961853</v>
       </c>
       <c r="G1013" t="n">
-        <v>8.71804332733154</v>
+        <v>8.71804428100586</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G1015" t="n">
-        <v>8.53833198547363</v>
+        <v>8.53833103179932</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>11.0050001144409</v>
       </c>
       <c r="G1016" t="n">
-        <v>8.78992938995361</v>
+        <v>8.7899284362793</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1017" t="n">
-        <v>8.55430603027344</v>
+        <v>8.55430507659912</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>11.1450004577637</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.9017505645752</v>
+        <v>8.90174961090088</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.2049999237061</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.94967365264893</v>
+        <v>8.94967269897461</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.8178825378418</v>
+        <v>8.81788349151611</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.87379360198975</v>
+        <v>8.87379455566406</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.87379360198975</v>
+        <v>8.87379455566406</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>10.9849996566772</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.77395343780518</v>
+        <v>8.77395439147949</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1033" t="n">
-        <v>8.45047283172607</v>
+        <v>8.45047187805176</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>10.9849996566772</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.77395343780518</v>
+        <v>8.77395439147949</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1035" t="n">
-        <v>8.92970561981201</v>
+        <v>8.9297046661377</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.76995944976807</v>
+        <v>8.76996040344238</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.85781955718994</v>
+        <v>8.85782051086426</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>11.1850004196167</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.9336986541748</v>
+        <v>8.93369960784912</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>9.37698936462402</v>
+        <v>9.37698841094971</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>11.0249996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.80590343475342</v>
+        <v>8.8059024810791</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>10.9250001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.72603034973145</v>
+        <v>8.72603130340576</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.72203826904297</v>
+        <v>8.72203731536865</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.85781955718994</v>
+        <v>8.85782051086426</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>10.7250003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.56628608703613</v>
+        <v>8.56628704071045</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.82267713546753</v>
+        <v>7.82267618179321</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>9.49400043487549</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.58306074142456</v>
+        <v>7.5830602645874</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>9.33399963378906</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.45526552200317</v>
+        <v>7.45526456832886</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.06868410110474</v>
+        <v>7.06868457794189</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.08625507354736</v>
+        <v>7.08625555038452</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>8.97399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.16772603988647</v>
+        <v>7.16772556304932</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>8.0959997177124</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.46644735336304</v>
+        <v>6.4664478302002</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G1076" t="n">
-        <v>7.05909967422485</v>
+        <v>7.0590991973877</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>8.42199993133545</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.72683048248291</v>
+        <v>6.72683095932007</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.82906818389893</v>
+        <v>6.82906723022461</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.14855527877808</v>
+        <v>7.14855623245239</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>9.1540002822876</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.31149578094482</v>
+        <v>7.31149625778198</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>9.44400024414062</v>
       </c>
       <c r="G1085" t="n">
-        <v>7.54312562942505</v>
+        <v>7.54312372207642</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.54152631759644</v>
+        <v>7.54152774810791</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>8.70800018310547</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.95526552200317</v>
+        <v>6.95526599884033</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.94887542724609</v>
+        <v>6.94887590408325</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>8.73200035095215</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.97443580627441</v>
+        <v>6.97443532943726</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.51916313171387</v>
+        <v>6.51916360855103</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>8.75800037384033</v>
       </c>
       <c r="G1093" t="n">
-        <v>6.995201587677</v>
+        <v>6.99520206451416</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>9.21199989318848</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.35782098770142</v>
+        <v>7.35782051086426</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.15494441986084</v>
+        <v>8.15494537353516</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>8.09903430938721</v>
+        <v>8.09903526306152</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.97922563552856</v>
+        <v>7.97922515869141</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>10.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>8.38657379150391</v>
+        <v>8.38657474517822</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>9.85599994659424</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.87219715118408</v>
+        <v>7.8721981048584</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>10</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.98721361160278</v>
+        <v>7.98721313476562</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.11900234222412</v>
+        <v>8.1190013885498</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.11500835418701</v>
+        <v>8.11500930786133</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.15893936157227</v>
+        <v>8.15893840789795</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.99919509887695</v>
+        <v>7.99919414520264</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.46245384216309</v>
+        <v>8.46245288848877</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.43449783325195</v>
+        <v>8.43449878692627</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>11.0249996185303</v>
       </c>
       <c r="G1123" t="n">
-        <v>8.80590343475342</v>
+        <v>8.8059024810791</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.249192237854</v>
+        <v>9.24919319152832</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1129" t="n">
-        <v>9.249192237854</v>
+        <v>9.24919319152832</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G1135" t="n">
-        <v>9.67251682281494</v>
+        <v>9.67251586914062</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>9.90414428710938</v>
+        <v>9.90414524078369</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>12.0150003433228</v>
       </c>
       <c r="G1141" t="n">
-        <v>9.59663867950439</v>
+        <v>9.59663772583008</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>12</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.58465671539307</v>
+        <v>9.58465576171875</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.303505897522</v>
+        <v>10.3035068511963</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.0239524841309</v>
+        <v>10.0239534378052</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>12.6149997711182</v>
       </c>
       <c r="G1150" t="n">
-        <v>10.075870513916</v>
+        <v>10.0758695602417</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.0159645080566</v>
+        <v>10.0159664154053</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1153" t="n">
-        <v>10.247594833374</v>
+        <v>10.2475938796997</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1155" t="n">
-        <v>10.4313020706177</v>
+        <v>10.4313011169434</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1160" t="n">
-        <v>10.2116527557373</v>
+        <v>10.211651802063</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>12.5749998092651</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.0439205169678</v>
+        <v>10.0439214706421</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>12.7049999237061</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.1477556228638</v>
+        <v>10.1477537155151</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>12.5749998092651</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.0439205169678</v>
+        <v>10.0439214706421</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>12.7950000762939</v>
       </c>
       <c r="G1174" t="n">
-        <v>10.2196407318115</v>
+        <v>10.2196388244629</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1176" t="n">
-        <v>10.2116527557373</v>
+        <v>10.211651802063</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.3514289855957</v>
+        <v>10.3514280319214</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.4313020706177</v>
+        <v>10.4313011169434</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1182" t="n">
-        <v>10.3953580856323</v>
+        <v>10.3953590393066</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.271556854248</v>
+        <v>10.2715559005737</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1184" t="n">
-        <v>10.247594833374</v>
+        <v>10.2475938796997</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>12.75</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.1836967468262</v>
+        <v>10.1836977005005</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1188" t="n">
-        <v>9.70046997070312</v>
+        <v>9.70047092437744</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1189" t="n">
-        <v>9.70046997070312</v>
+        <v>9.70047092437744</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1190" t="n">
-        <v>10.0479145050049</v>
+        <v>10.0479135513306</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1195" t="n">
-        <v>9.81628513336182</v>
+        <v>9.81628608703613</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1196" t="n">
-        <v>9.81628513336182</v>
+        <v>9.81628608703613</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1197" t="n">
-        <v>9.66053485870361</v>
+        <v>9.66053581237793</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>11.835000038147</v>
       </c>
       <c r="G1198" t="n">
-        <v>9.45286750793457</v>
+        <v>9.45286655426025</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>11.8549995422363</v>
       </c>
       <c r="G1199" t="n">
-        <v>9.46884059906006</v>
+        <v>9.46884155273438</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1201" t="n">
-        <v>9.21724510192871</v>
+        <v>9.21724414825439</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1202" t="n">
-        <v>9.09743690490723</v>
+        <v>9.09743595123291</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>9.2052640914917</v>
+        <v>9.20526313781738</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1208" t="n">
-        <v>9.45686149597168</v>
+        <v>9.45686054229736</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1210" t="n">
-        <v>9.65654277801514</v>
+        <v>9.65654182434082</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1215" t="n">
-        <v>9.83226013183594</v>
+        <v>9.83226108551025</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>9.70446491241455</v>
+        <v>9.70446395874023</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1221" t="n">
-        <v>9.59264373779297</v>
+        <v>9.59264278411865</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G1226" t="n">
-        <v>9.18130302429199</v>
+        <v>9.18130207061768</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1227" t="n">
-        <v>9.05749893188477</v>
+        <v>9.0575008392334</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>11.75</v>
       </c>
       <c r="G1229" t="n">
-        <v>9.38497638702393</v>
+        <v>9.38497543334961</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1232" t="n">
-        <v>9.99999141693115</v>
+        <v>9.99999237060547</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>12.4750003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>9.96404933929443</v>
+        <v>9.96405029296875</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1236" t="n">
-        <v>9.61660480499268</v>
+        <v>9.61660575866699</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1237" t="n">
-        <v>9.70046997070312</v>
+        <v>9.70047092437744</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>9.83226013183594</v>
+        <v>9.83226108551025</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1241" t="n">
-        <v>9.88817119598389</v>
+        <v>9.88817024230957</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>12.5550003051758</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.0279474258423</v>
+        <v>10.027946472168</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>12.6850004196167</v>
       </c>
       <c r="G1245" t="n">
-        <v>10.131781578064</v>
+        <v>10.1317806243896</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1247" t="n">
-        <v>10.4073390960693</v>
+        <v>10.407338142395</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.3594160079956</v>
+        <v>10.3594169616699</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1252" t="n">
-        <v>10.4153270721436</v>
+        <v>10.4153261184692</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G1256" t="n">
-        <v>10.4352931976318</v>
+        <v>10.4352941513062</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1259" t="n">
-        <v>10.3514289855957</v>
+        <v>10.3514280319214</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.3953580856323</v>
+        <v>10.3953590393066</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>13.0749998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.4432802200317</v>
+        <v>10.4432821273804</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>12.7950000762939</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.2196407318115</v>
+        <v>10.2196388244629</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1270" t="n">
-        <v>10.7028656005859</v>
+        <v>10.7028646469116</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1271" t="n">
-        <v>10.9344940185547</v>
+        <v>10.934494972229</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>10.9704370498657</v>
+        <v>10.9704360961914</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1276" t="n">
-        <v>10.9704370498657</v>
+        <v>10.9704360961914</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>14</v>
       </c>
       <c r="G1277" t="n">
-        <v>11.1820993423462</v>
+        <v>11.1820983886719</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1278" t="n">
-        <v>11.0942392349243</v>
+        <v>11.0942401885986</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543050765991</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1281" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543050765991</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>13.4650001525879</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.7547826766968</v>
+        <v>10.7547817230225</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1286" t="n">
-        <v>10.4153270721436</v>
+        <v>10.4153261184692</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>13.1949996948242</v>
       </c>
       <c r="G1287" t="n">
-        <v>10.5391283035278</v>
+        <v>10.5391292572021</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>13.6149997711182</v>
       </c>
       <c r="G1293" t="n">
-        <v>10.8745899200439</v>
+        <v>10.8745908737183</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1295" t="n">
-        <v>11.6613321304321</v>
+        <v>11.6613311767578</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>15.0050001144409</v>
       </c>
       <c r="G1298" t="n">
-        <v>11.9848136901855</v>
+        <v>11.9848146438599</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>14.7849998474121</v>
       </c>
       <c r="G1299" t="n">
-        <v>11.8090944290161</v>
+        <v>11.8090953826904</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>15.1850004196167</v>
       </c>
       <c r="G1301" t="n">
-        <v>12.1285839080811</v>
+        <v>12.1285848617554</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G1302" t="n">
-        <v>12.0247497558594</v>
+        <v>12.0247507095337</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>11.861011505127</v>
+        <v>11.8610124588013</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>11.7332172393799</v>
+        <v>11.7332162857056</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>14.5349998474121</v>
       </c>
       <c r="G1307" t="n">
-        <v>11.6094150543213</v>
+        <v>11.6094160079956</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.7412042617798</v>
+        <v>11.7412033081055</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.6373701095581</v>
+        <v>11.6373691558838</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.6174011230469</v>
+        <v>11.6174020767212</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.5894479751587</v>
+        <v>11.5894470214844</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>11.5015869140625</v>
+        <v>11.5015878677368</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G1326" t="n">
-        <v>11.669319152832</v>
+        <v>11.6693181991577</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>13.9350004196167</v>
       </c>
       <c r="G1329" t="n">
-        <v>11.1301832199097</v>
+        <v>11.1301822662354</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>11.1261882781982</v>
+        <v>11.1261901855469</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>14</v>
       </c>
       <c r="G1332" t="n">
-        <v>11.1820993423462</v>
+        <v>11.1820983886719</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>13.9849996566772</v>
       </c>
       <c r="G1337" t="n">
-        <v>11.1701183319092</v>
+        <v>11.1701173782349</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>14.085000038147</v>
       </c>
       <c r="G1339" t="n">
-        <v>11.2499904632568</v>
+        <v>11.2499895095825</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>14.2250003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>11.3618106842041</v>
+        <v>11.3618125915527</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G1344" t="n">
-        <v>11.5095748901367</v>
+        <v>11.509575843811</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.0503101348877</v>
+        <v>11.0503091812134</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>14.25</v>
       </c>
       <c r="G1350" t="n">
-        <v>11.3817796707153</v>
+        <v>11.381778717041</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1353" t="n">
-        <v>11.437689781189</v>
+        <v>11.4376888275146</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>14.4849996566772</v>
       </c>
       <c r="G1354" t="n">
-        <v>11.5694770812988</v>
+        <v>11.5694789886475</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1355" t="n">
-        <v>11.2619714736938</v>
+        <v>11.2619724273682</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G1356" t="n">
-        <v>11.4336948394775</v>
+        <v>11.4336957931519</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1357" t="n">
-        <v>11.2300233840942</v>
+        <v>11.2300224304199</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1365" t="n">
-        <v>11.0503101348877</v>
+        <v>11.0503091812134</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G1367" t="n">
-        <v>10.7907266616821</v>
+        <v>10.7907257080078</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.8865718841553</v>
+        <v>10.8865728378296</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1369" t="n">
-        <v>10.990406036377</v>
+        <v>10.9904050827026</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>13.7849998474121</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.0103750228882</v>
+        <v>11.0103740692139</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1372" t="n">
-        <v>10.9424819946289</v>
+        <v>10.9424829483032</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1374" t="n">
-        <v>10.9704370498657</v>
+        <v>10.9704360961914</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.9664430618286</v>
+        <v>10.9664440155029</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.9504690170288</v>
+        <v>10.9504699707031</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>13.8549995422363</v>
       </c>
       <c r="G1377" t="n">
-        <v>11.0662832260132</v>
+        <v>11.0662841796875</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>13.8950004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.0982341766357</v>
+        <v>11.0982332229614</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>14.5</v>
       </c>
       <c r="G1390" t="n">
-        <v>11.5814599990845</v>
+        <v>11.5814590454102</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.6533441543579</v>
+        <v>11.6533432006836</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>14.7250003814697</v>
       </c>
       <c r="G1392" t="n">
-        <v>11.7611722946167</v>
+        <v>11.761173248291</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1394" t="n">
-        <v>11.7412042617798</v>
+        <v>11.7412033081055</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1395" t="n">
-        <v>11.7891273498535</v>
+        <v>11.7891283035278</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1396" t="n">
-        <v>11.7412042617798</v>
+        <v>11.7412033081055</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1398" t="n">
-        <v>11.7412042617798</v>
+        <v>11.7412033081055</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1399" t="n">
-        <v>11.8530254364014</v>
+        <v>11.8530244827271</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>11.7412042617798</v>
+        <v>11.7412033081055</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1401" t="n">
-        <v>11.7891273498535</v>
+        <v>11.7891283035278</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1402" t="n">
-        <v>11.7012672424316</v>
+        <v>11.701268196106</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>15.0450000762939</v>
       </c>
       <c r="G1404" t="n">
-        <v>12.0167627334595</v>
+        <v>12.0167617797852</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G1406" t="n">
-        <v>11.5934400558472</v>
+        <v>11.5934410095215</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.0503101348877</v>
+        <v>11.0503091812134</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543050765991</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1412" t="n">
-        <v>11.3418426513672</v>
+        <v>11.3418436050415</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>14.6149997711182</v>
       </c>
       <c r="G1414" t="n">
-        <v>11.6733121871948</v>
+        <v>11.6733112335205</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>14.7349996566772</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.7691593170166</v>
+        <v>11.7691602706909</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.8769865036011</v>
+        <v>11.8769855499268</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>15.1149997711182</v>
       </c>
       <c r="G1418" t="n">
-        <v>12.0726737976074</v>
+        <v>12.0726728439331</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1420" t="n">
-        <v>11.9129295349121</v>
+        <v>11.9129285812378</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>15.4049997329712</v>
       </c>
       <c r="G1421" t="n">
-        <v>12.3043031692505</v>
+        <v>12.3043022155762</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.4201173782349</v>
+        <v>12.4201164245605</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G1424" t="n">
-        <v>12.8873682022095</v>
+        <v>12.8873691558838</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1425" t="n">
-        <v>12.9552602767944</v>
+        <v>12.9552612304688</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1427" t="n">
-        <v>12.9712343215942</v>
+        <v>12.9712352752686</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>16.0949993133545</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.8554201126099</v>
+        <v>12.8554191589355</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>16.25</v>
       </c>
       <c r="G1431" t="n">
-        <v>12.9792222976685</v>
+        <v>12.9792213439941</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>15.9350004196167</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.7276248931885</v>
+        <v>12.7276258468628</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>15.8649997711182</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.6717147827148</v>
+        <v>12.6717138290405</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1436" t="n">
-        <v>12.7675609588623</v>
+        <v>12.767560005188</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>15.6149997711182</v>
       </c>
       <c r="G1440" t="n">
-        <v>12.4720335006714</v>
+        <v>12.4720344543457</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G1441" t="n">
-        <v>12.3881673812866</v>
+        <v>12.3881683349609</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>15.5150003433228</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.3921613693237</v>
+        <v>12.392162322998</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1446" t="n">
-        <v>12.3562202453613</v>
+        <v>12.356219291687</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1447" t="n">
-        <v>12.276346206665</v>
+        <v>12.2763471603394</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1448" t="n">
-        <v>12.1086149215698</v>
+        <v>12.1086158752441</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1450" t="n">
-        <v>12.276346206665</v>
+        <v>12.2763471603394</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>15.6450004577637</v>
       </c>
       <c r="G1451" t="n">
-        <v>12.4959955215454</v>
+        <v>12.4959945678711</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1453" t="n">
-        <v>12.6357717514038</v>
+        <v>12.6357698440552</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>15.1850004196167</v>
       </c>
       <c r="G1454" t="n">
-        <v>12.1285839080811</v>
+        <v>12.1285848617554</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>15.6149997711182</v>
       </c>
       <c r="G1455" t="n">
-        <v>12.4720335006714</v>
+        <v>12.4720344543457</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G1457" t="n">
-        <v>12.7515859603882</v>
+        <v>12.7515869140625</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>16.0450000762939</v>
       </c>
       <c r="G1459" t="n">
-        <v>12.815484046936</v>
+        <v>12.8154830932617</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>15.5249996185303</v>
       </c>
       <c r="G1461" t="n">
-        <v>12.4001474380493</v>
+        <v>12.4001493453979</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1462" t="n">
-        <v>12.5159645080566</v>
+        <v>12.5159635543823</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G1463" t="n">
-        <v>12.2963161468506</v>
+        <v>12.296314239502</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1466" t="n">
-        <v>12.5079765319824</v>
+        <v>12.5079774856567</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1467" t="n">
-        <v>12.5479135513306</v>
+        <v>12.5479125976562</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G1469" t="n">
-        <v>12.5119695663452</v>
+        <v>12.5119705200195</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1470" t="n">
-        <v>12.7156448364258</v>
+        <v>12.7156438827515</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>15.8149995803833</v>
       </c>
       <c r="G1471" t="n">
-        <v>12.6317768096924</v>
+        <v>12.6317777633667</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1472" t="n">
-        <v>13.0990304946899</v>
+        <v>13.0990295410156</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1473" t="n">
-        <v>13.2747497558594</v>
+        <v>13.2747507095337</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>16.6049995422363</v>
       </c>
       <c r="G1477" t="n">
-        <v>13.262767791748</v>
+        <v>13.2627668380737</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G1478" t="n">
-        <v>13.2867288589478</v>
+        <v>13.2867298126221</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G1480" t="n">
-        <v>13.4624481201172</v>
+        <v>13.4624471664429</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1481" t="n">
-        <v>13.122992515564</v>
+        <v>13.1229915618896</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>13.2188367843628</v>
+        <v>13.2188377380371</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1484" t="n">
-        <v>13.4864101409912</v>
+        <v>13.4864110946655</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>16.9850006103516</v>
       </c>
       <c r="G1486" t="n">
-        <v>13.5662832260132</v>
+        <v>13.5662813186646</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1487" t="n">
-        <v>13.4983911514282</v>
+        <v>13.4983892440796</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980714797974</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1491" t="n">
-        <v>13.6341743469238</v>
+        <v>13.6341753005981</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>17.2350006103516</v>
       </c>
       <c r="G1492" t="n">
-        <v>13.7659616470337</v>
+        <v>13.765962600708</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>17.3050003051758</v>
       </c>
       <c r="G1493" t="n">
-        <v>13.8218717575073</v>
+        <v>13.821873664856</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>17.25</v>
       </c>
       <c r="G1496" t="n">
-        <v>13.7779445648193</v>
+        <v>13.777943611145</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1497" t="n">
-        <v>13.6900844573975</v>
+        <v>13.6900835037231</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1500" t="n">
-        <v>13.3136920928955</v>
+        <v>13.3136911392212</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G1501" t="n">
-        <v>13.3466682434082</v>
+        <v>13.3466691970825</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>12.769603729248</v>
+        <v>12.7696046829224</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>12.9386005401611</v>
+        <v>12.9385995864868</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1509" t="n">
-        <v>13.0498914718628</v>
+        <v>13.0498924255371</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1511" t="n">
-        <v>13.1405725479126</v>
+        <v>13.1405744552612</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G1513" t="n">
-        <v>12.9221134185791</v>
+        <v>12.9221143722534</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1514" t="n">
-        <v>12.9015045166016</v>
+        <v>12.9015035629272</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G1515" t="n">
-        <v>12.9386005401611</v>
+        <v>12.9385995864868</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G1516" t="n">
-        <v>12.9468450546265</v>
+        <v>12.9468441009521</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1517" t="n">
-        <v>13.0251607894897</v>
+        <v>13.0251598358154</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>15.1450004577637</v>
       </c>
       <c r="G1520" t="n">
-        <v>12.4851942062378</v>
+        <v>12.4851932525635</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1522" t="n">
-        <v>12.4316091537476</v>
+        <v>12.4316082000732</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>15.7150001525879</v>
       </c>
       <c r="G1527" t="n">
-        <v>12.9550886154175</v>
+        <v>12.9550895690918</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1529" t="n">
-        <v>13.1776704788208</v>
+        <v>13.1776695251465</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>15.6049995422363</v>
       </c>
       <c r="G1531" t="n">
-        <v>12.864405632019</v>
+        <v>12.8644065856934</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G1534" t="n">
-        <v>13.2642297744751</v>
+        <v>13.2642307281494</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>13.3384237289429</v>
+        <v>13.3384246826172</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1538" t="n">
-        <v>12.7943363189697</v>
+        <v>12.7943353652954</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1539" t="n">
-        <v>12.547022819519</v>
+        <v>12.5470218658447</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>14.9049997329712</v>
       </c>
       <c r="G1542" t="n">
-        <v>12.2873439788818</v>
+        <v>12.2873430252075</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1543" t="n">
-        <v>11.9040079116821</v>
+        <v>11.9040069580078</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1544" t="n">
-        <v>12.0853700637817</v>
+        <v>12.0853710174561</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1545" t="n">
-        <v>12.0276651382446</v>
+        <v>12.0276641845703</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G1548" t="n">
-        <v>12.3780250549316</v>
+        <v>12.3780241012573</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1549" t="n">
-        <v>12.4233655929565</v>
+        <v>12.4233646392822</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1551" t="n">
-        <v>12.2955865859985</v>
+        <v>12.2955856323242</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1552" t="n">
-        <v>12.3739013671875</v>
+        <v>12.3739032745361</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>15.9049997329712</v>
       </c>
       <c r="G1554" t="n">
-        <v>13.1117191314697</v>
+        <v>13.111720085144</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1555" t="n">
-        <v>13.1240854263306</v>
+        <v>13.1240844726562</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G1556" t="n">
-        <v>12.9468450546265</v>
+        <v>12.9468441009521</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1557" t="n">
-        <v>12.769603729248</v>
+        <v>12.7696046829224</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>16.0949993133545</v>
       </c>
       <c r="G1558" t="n">
-        <v>13.2683515548706</v>
+        <v>13.2683506011963</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>13.1776704788208</v>
+        <v>13.1776695251465</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G1562" t="n">
-        <v>12.9138698577881</v>
+        <v>12.9138708114624</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1569" t="n">
-        <v>11.5907459259033</v>
+        <v>11.590744972229</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1571" t="n">
-        <v>10.5520286560059</v>
+        <v>10.5520296096802</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G1573" t="n">
-        <v>10.1439628601074</v>
+        <v>10.1439619064331</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>13.8149995803833</v>
       </c>
       <c r="G1577" t="n">
-        <v>11.3887720108032</v>
+        <v>11.3887710571289</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>13.8950004577637</v>
       </c>
       <c r="G1578" t="n">
-        <v>11.4547214508057</v>
+        <v>11.45472240448</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G1579" t="n">
-        <v>12.0523948669434</v>
+        <v>12.052393913269</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G1580" t="n">
-        <v>11.5454025268555</v>
+        <v>11.5454034805298</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G1582" t="n">
-        <v>11.5454025268555</v>
+        <v>11.5454034805298</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1588" t="n">
-        <v>11.8586673736572</v>
+        <v>11.8586683273315</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>13.9650001525879</v>
       </c>
       <c r="G1594" t="n">
-        <v>11.51243019104</v>
+        <v>11.5124292373657</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>14.2749996185303</v>
       </c>
       <c r="G1597" t="n">
-        <v>11.7679843902588</v>
+        <v>11.7679853439331</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G1599" t="n">
-        <v>11.4670877456665</v>
+        <v>11.4670867919922</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>14.1149997711182</v>
       </c>
       <c r="G1602" t="n">
-        <v>11.6360855102539</v>
+        <v>11.6360845565796</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G1606" t="n">
-        <v>10.8281955718994</v>
+        <v>10.8281946182251</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>13.1750001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>10.8611717224121</v>
+        <v>10.8611707687378</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1611" t="n">
-        <v>10.9559726715088</v>
+        <v>10.9559736251831</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>12.9549999237061</v>
       </c>
       <c r="G1613" t="n">
-        <v>10.6798067092896</v>
+        <v>10.6798076629639</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>11.7449998855591</v>
       </c>
       <c r="G1615" t="n">
-        <v>9.68231010437012</v>
+        <v>9.68231105804443</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>12.25</v>
       </c>
       <c r="G1617" t="n">
-        <v>10.0986213684082</v>
+        <v>10.0986204147339</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1621" t="n">
-        <v>10.4283714294434</v>
+        <v>10.4283723831177</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>10.5520286560059</v>
+        <v>10.5520296096802</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1626" t="n">
-        <v>10.7279815673828</v>
+        <v>10.7279806137085</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>13.0349998474121</v>
       </c>
       <c r="G1628" t="n">
-        <v>11.0895519256592</v>
+        <v>11.0895509719849</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1638" t="n">
-        <v>10.243052482605</v>
+        <v>10.2430534362793</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G1642" t="n">
-        <v>9.38379192352295</v>
+        <v>9.38379287719727</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>11.8450002670288</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.0771570205688</v>
+        <v>10.0771560668945</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.2260389328003</v>
+        <v>10.226037979126</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>12.1549997329712</v>
       </c>
       <c r="G1658" t="n">
-        <v>10.3408889770508</v>
+        <v>10.3408899307251</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>12.1549997329712</v>
       </c>
       <c r="G1659" t="n">
-        <v>10.3408889770508</v>
+        <v>10.3408899307251</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G1662" t="n">
-        <v>9.97506713867188</v>
+        <v>9.97506618499756</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>11.4049997329712</v>
       </c>
       <c r="G1670" t="n">
-        <v>9.70282459259033</v>
+        <v>9.70282554626465</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1678" t="n">
-        <v>10.4812622070312</v>
+        <v>10.4812631607056</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>12.3450002670288</v>
       </c>
       <c r="G1682" t="n">
-        <v>10.5025320053101</v>
+        <v>10.5025329589844</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1684" t="n">
-        <v>10.5833530426025</v>
+        <v>10.5833539962769</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G1688" t="n">
-        <v>9.77088642120361</v>
+        <v>9.7708854675293</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G1692" t="n">
-        <v>9.56670570373535</v>
+        <v>9.56670475006104</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1693" t="n">
-        <v>9.10304355621338</v>
+        <v>9.1030445098877</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G1701" t="n">
-        <v>9.24341869354248</v>
+        <v>9.2434196472168</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G1703" t="n">
-        <v>9.97506713867188</v>
+        <v>9.97506618499756</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>12.3149995803833</v>
       </c>
       <c r="G1704" t="n">
-        <v>10.4770097732544</v>
+        <v>10.4770088195801</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>12.8149995803833</v>
       </c>
       <c r="G1712" t="n">
-        <v>10.9023857116699</v>
+        <v>10.9023866653442</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1713" t="n">
-        <v>10.5323085784912</v>
+        <v>10.5323076248169</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1715" t="n">
-        <v>10.5323085784912</v>
+        <v>10.5323076248169</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G1719" t="n">
-        <v>10.7747735977173</v>
+        <v>10.774772644043</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1722" t="n">
-        <v>10.7279815673828</v>
+        <v>10.7279806137085</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1727" t="n">
-        <v>10.5833530426025</v>
+        <v>10.5833539962769</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G1729" t="n">
-        <v>10.8300724029541</v>
+        <v>10.8300714492798</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G1732" t="n">
-        <v>10.7747735977173</v>
+        <v>10.774772644043</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1741" t="n">
-        <v>11.9360485076904</v>
+        <v>11.9360475540161</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>14.3649997711182</v>
       </c>
       <c r="G1747" t="n">
-        <v>12.2210502624512</v>
+        <v>12.2210512161255</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1749" t="n">
-        <v>12.3529176712036</v>
+        <v>12.3529167175293</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>14.625</v>
       </c>
       <c r="G1750" t="n">
-        <v>12.4422454833984</v>
+        <v>12.4422464370728</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>15</v>
       </c>
       <c r="G1753" t="n">
-        <v>12.7612781524658</v>
+        <v>12.7612791061401</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>15.0349998474121</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.7910556793213</v>
+        <v>12.791054725647</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1762" t="n">
-        <v>13.1441173553467</v>
+        <v>13.1441164016724</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>15.75</v>
       </c>
       <c r="G1763" t="n">
-        <v>13.3993425369263</v>
+        <v>13.3993434906006</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1765" t="n">
-        <v>13.0505342483521</v>
+        <v>13.0505332946777</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G1766" t="n">
-        <v>13.0973262786865</v>
+        <v>13.0973253250122</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>15.7550001144409</v>
       </c>
       <c r="G1771" t="n">
-        <v>13.4035968780518</v>
+        <v>13.4035959243774</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>15.1149997711182</v>
       </c>
       <c r="G1775" t="n">
-        <v>12.8591136932373</v>
+        <v>12.8591146469116</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1776" t="n">
-        <v>13.0505342483521</v>
+        <v>13.0505332946777</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>15.375</v>
       </c>
       <c r="G1780" t="n">
-        <v>13.0803098678589</v>
+        <v>13.0803108215332</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1785" t="n">
-        <v>14.0544214248657</v>
+        <v>14.0544204711914</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1789" t="n">
-        <v>14.3181533813477</v>
+        <v>14.318154335022</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G1791" t="n">
-        <v>14.2203178405762</v>
+        <v>14.2203187942505</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>16.7450008392334</v>
       </c>
       <c r="G1793" t="n">
-        <v>14.2458410263062</v>
+        <v>14.2458400726318</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1795" t="n">
-        <v>14.0544214248657</v>
+        <v>14.0544204711914</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>16.9549999237061</v>
       </c>
       <c r="G1807" t="n">
-        <v>14.4244976043701</v>
+        <v>14.4244985580444</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1811" t="n">
-        <v>14.4542751312256</v>
+        <v>14.4542741775513</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>16.5949993133545</v>
       </c>
       <c r="G1813" t="n">
-        <v>14.1182270050049</v>
+        <v>14.1182279586792</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1814" t="n">
-        <v>14.148003578186</v>
+        <v>14.1480026245117</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.2245712280273</v>
+        <v>14.2245721817017</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>13.8549995422363</v>
       </c>
       <c r="G1833" t="n">
-        <v>11.7871675491333</v>
+        <v>11.787166595459</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>14.0950002670288</v>
       </c>
       <c r="G1834" t="n">
-        <v>11.9913482666016</v>
+        <v>11.9913473129272</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>12.0381393432617</v>
+        <v>12.0381383895874</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>14.8050003051758</v>
       </c>
       <c r="G1855" t="n">
-        <v>12.5953826904297</v>
+        <v>12.5953817367554</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1865" t="n">
-        <v>11.6808233261108</v>
+        <v>11.6808242797852</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G1866" t="n">
-        <v>11.32350730896</v>
+        <v>11.3235082626343</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1873" t="n">
-        <v>10.6258916854858</v>
+        <v>10.6258907318115</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1876" t="n">
-        <v>10.8768625259399</v>
+        <v>10.8768615722656</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>22.4500007629395</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>2173568</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>22.6399993896484</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>22.1599998474121</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>22.5100002288818</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>22.4500007629395</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>22.4500007629395</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>5.15489482879639</v>
+        <v>5.15489435195923</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12352514266968</v>
+        <v>5.12352561950684</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>4.98062419891357</v>
+        <v>4.98062515258789</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.94925594329834</v>
+        <v>4.9492564201355</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>5.06775951385498</v>
+        <v>5.06775903701782</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94228553771973</v>
+        <v>4.94228506088257</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G9" t="n">
-        <v>5.11655426025391</v>
+        <v>5.11655521392822</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G12" t="n">
-        <v>4.74710369110107</v>
+        <v>4.74710416793823</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G13" t="n">
-        <v>4.88651943206787</v>
+        <v>4.88651847839355</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G14" t="n">
-        <v>4.48569965362549</v>
+        <v>4.48569917678833</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>4.64254093170166</v>
+        <v>4.64254188537598</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>4.86560678482056</v>
+        <v>4.86560726165771</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>4.86212158203125</v>
+        <v>4.86212110519409</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97365379333496</v>
+        <v>4.97365427017212</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>4.70876359939575</v>
+        <v>4.70876407623291</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>4.61465930938721</v>
+        <v>4.61465835571289</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>4.56586265563965</v>
+        <v>4.56586360931396</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>4.3985652923584</v>
+        <v>4.39856481552124</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>4.18247032165527</v>
+        <v>4.18246984481812</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G32" t="n">
-        <v>4.60768842697144</v>
+        <v>4.60768747329712</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>4.63557052612305</v>
+        <v>4.63557100296021</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>4.59026098251343</v>
+        <v>4.59026050567627</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G36" t="n">
-        <v>4.53798007965088</v>
+        <v>4.53797960281372</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.75</v>
       </c>
       <c r="G39" t="n">
-        <v>4.70527839660645</v>
+        <v>4.7052788734436</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>4.8237829208374</v>
+        <v>4.82378196716309</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G41" t="n">
-        <v>4.90394687652588</v>
+        <v>4.90394639968872</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>4.91440200805664</v>
+        <v>4.9144024848938</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>4.98062419891357</v>
+        <v>4.98062515258789</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.97713899612427</v>
+        <v>4.97713947296143</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G47" t="n">
-        <v>4.77150106430054</v>
+        <v>4.7715015411377</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>4.66345357894897</v>
+        <v>4.66345405578613</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>4.60420227050781</v>
+        <v>4.60420274734497</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G50" t="n">
-        <v>4.77150106430054</v>
+        <v>4.7715015411377</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>4.87954902648926</v>
+        <v>4.87954807281494</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.90046167373657</v>
+        <v>4.90046072006226</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.91440200805664</v>
+        <v>4.9144024848938</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>4.86212158203125</v>
+        <v>4.86212110519409</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>4.82029724121094</v>
+        <v>4.82029676437378</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>4.80635547637939</v>
+        <v>4.80635499954224</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>4.87954902648926</v>
+        <v>4.87954807281494</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>4.98062419891357</v>
+        <v>4.98062515258789</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>5.15837955474854</v>
+        <v>5.15837907791138</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.15837955474854</v>
+        <v>5.15837907791138</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.93879985809326</v>
+        <v>4.93880033493042</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G67" t="n">
-        <v>4.79589891433716</v>
+        <v>4.79589986801147</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>4.76453113555908</v>
+        <v>4.76453065872192</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.78892803192139</v>
+        <v>4.78892707824707</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G71" t="n">
-        <v>4.72619152069092</v>
+        <v>4.7261905670166</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>4.83772373199463</v>
+        <v>4.83772420883179</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>5.13792419433594</v>
+        <v>5.13792514801025</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G76" t="n">
-        <v>5.04030084609985</v>
+        <v>5.0403003692627</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.08730411529541</v>
+        <v>5.08730506896973</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.03668451309204</v>
+        <v>5.03668546676636</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G80" t="n">
-        <v>4.97521781921387</v>
+        <v>4.97521829605103</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>5.13430976867676</v>
+        <v>5.1343092918396</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>5.10538339614868</v>
+        <v>5.10538291931152</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>5.06922626495361</v>
+        <v>5.06922674179077</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.06199502944946</v>
+        <v>5.0619945526123</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G86" t="n">
-        <v>4.870361328125</v>
+        <v>4.87036275863647</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G87" t="n">
-        <v>4.91013479232788</v>
+        <v>4.91013431549072</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G88" t="n">
-        <v>4.78358459472656</v>
+        <v>4.78358507156372</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G89" t="n">
-        <v>4.70765495300293</v>
+        <v>4.70765542984009</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>6.375</v>
       </c>
       <c r="G90" t="n">
-        <v>4.61003017425537</v>
+        <v>4.61003065109253</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G96" t="n">
-        <v>4.72211837768555</v>
+        <v>4.72211790084839</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G98" t="n">
-        <v>4.72573328018188</v>
+        <v>4.72573375701904</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G99" t="n">
-        <v>4.59918308258057</v>
+        <v>4.59918403625488</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>4.56302642822266</v>
+        <v>4.56302690505981</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>4.66426658630371</v>
+        <v>4.66426610946655</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.73658132553101</v>
+        <v>4.73658084869385</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>4.80166387557983</v>
+        <v>4.80166339874268</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>4.79443264007568</v>
+        <v>4.79443216323853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>4.743812084198</v>
+        <v>4.74381256103516</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G107" t="n">
-        <v>4.76912212371826</v>
+        <v>4.76912260055542</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>4.78720045089722</v>
+        <v>4.78719997406006</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>4.743812084198</v>
+        <v>4.74381256103516</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G111" t="n">
-        <v>4.78358459472656</v>
+        <v>4.78358507156372</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>4.69680738449097</v>
+        <v>4.69680786132812</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G113" t="n">
-        <v>4.62449359893799</v>
+        <v>4.62449407577515</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G115" t="n">
-        <v>4.39308786392212</v>
+        <v>4.39308834075928</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>4.29184818267822</v>
+        <v>4.29184913635254</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>4.57748985290527</v>
+        <v>4.57748937606812</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.55579614639282</v>
+        <v>4.55579471588135</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>4.62811040878296</v>
+        <v>4.62810945510864</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.625</v>
       </c>
       <c r="G123" t="n">
-        <v>4.79081678390503</v>
+        <v>4.79081726074219</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>4.23399686813354</v>
+        <v>4.2339973449707</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>4.17614555358887</v>
+        <v>4.17614603042603</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>4.17614555358887</v>
+        <v>4.17614603042603</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>3.94835615158081</v>
+        <v>3.94835591316223</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73141360282898</v>
+        <v>3.73141312599182</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.25</v>
       </c>
       <c r="G133" t="n">
-        <v>3.79649615287781</v>
+        <v>3.79649567604065</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G134" t="n">
-        <v>4.10744714736938</v>
+        <v>4.10744667053223</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G136" t="n">
-        <v>4.10744714736938</v>
+        <v>4.10744667053223</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>4.03513336181641</v>
+        <v>4.03513383865356</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G138" t="n">
-        <v>4.10744714736938</v>
+        <v>4.10744667053223</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G140" t="n">
-        <v>4.07852077484131</v>
+        <v>4.07852125167847</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G141" t="n">
-        <v>4.07852077484131</v>
+        <v>4.07852125167847</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>4.15083503723145</v>
+        <v>4.1508355140686</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G144" t="n">
-        <v>4.09298419952393</v>
+        <v>4.09298372268677</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08936834335327</v>
+        <v>4.08936882019043</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>3.94474053382874</v>
+        <v>3.94474029541016</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.785649061203</v>
+        <v>3.78564858436584</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>3.83988499641418</v>
+        <v>3.83988451957703</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.25</v>
       </c>
       <c r="G150" t="n">
-        <v>3.79649615287781</v>
+        <v>3.79649567604065</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G151" t="n">
-        <v>3.69525671005249</v>
+        <v>3.69525647163391</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G152" t="n">
-        <v>3.69525671005249</v>
+        <v>3.69525647163391</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>3.79288005828857</v>
+        <v>3.79288053512573</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>3.82903718948364</v>
+        <v>3.82903742790222</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G155" t="n">
-        <v>3.78926515579224</v>
+        <v>3.78926420211792</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>3.82542181015015</v>
+        <v>3.82542204856873</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G157" t="n">
-        <v>3.81095933914185</v>
+        <v>3.81095886230469</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>3.85073184967041</v>
+        <v>3.85073161125183</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>3.79288005828857</v>
+        <v>3.79288053512573</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>3.68802428245544</v>
+        <v>3.68802452087402</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5</v>
       </c>
       <c r="G164" t="n">
-        <v>3.61571049690247</v>
+        <v>3.61571097373962</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>3.91943120956421</v>
+        <v>3.91943025588989</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G168" t="n">
-        <v>3.89412045478821</v>
+        <v>3.89412069320679</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G169" t="n">
-        <v>3.86519408226013</v>
+        <v>3.86519384384155</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>3.94112396240234</v>
+        <v>3.94112348556519</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G172" t="n">
-        <v>3.98451280593872</v>
+        <v>3.98451352119446</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G173" t="n">
-        <v>3.97005033493042</v>
+        <v>3.970050573349</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.94835615158081</v>
+        <v>3.94835591316223</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>3.92304587364197</v>
+        <v>3.92304635047913</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>3.76757049560547</v>
+        <v>3.76757073402405</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G180" t="n">
-        <v>3.68079352378845</v>
+        <v>3.68079304695129</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G182" t="n">
-        <v>3.785649061203</v>
+        <v>3.78564858436584</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.7603394985199</v>
+        <v>3.76033926010132</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G185" t="n">
-        <v>3.75672340393066</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.76757049560547</v>
+        <v>3.76757073402405</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.82542181015015</v>
+        <v>3.82542204856873</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66994571685791</v>
+        <v>3.66994619369507</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>3.74226093292236</v>
+        <v>3.74226021766663</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G191" t="n">
-        <v>3.75310778617859</v>
+        <v>3.75310754776001</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G192" t="n">
-        <v>3.73864507675171</v>
+        <v>3.73864459991455</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.70971870422363</v>
+        <v>3.70971894264221</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.68079352378845</v>
+        <v>3.68079304695129</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>3.73141360282898</v>
+        <v>3.73141312599182</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>3.6482527256012</v>
+        <v>3.64825201034546</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.62294220924377</v>
+        <v>3.62294173240662</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G200" t="n">
-        <v>3.47831344604492</v>
+        <v>3.47831320762634</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G201" t="n">
-        <v>3.46240425109863</v>
+        <v>3.46240401268005</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>3.65548372268677</v>
+        <v>3.65548324584961</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>3.73864507675171</v>
+        <v>3.73864459991455</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>3.75672340393066</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G205" t="n">
-        <v>3.74226093292236</v>
+        <v>3.74226021766663</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G206" t="n">
-        <v>3.75672340393066</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>3.81457495689392</v>
+        <v>3.81457448005676</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G208" t="n">
-        <v>3.83265328407288</v>
+        <v>3.8326530456543</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>3.87604188919067</v>
+        <v>3.87604165077209</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G210" t="n">
-        <v>3.81819033622742</v>
+        <v>3.81819128990173</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.99174451828003</v>
+        <v>3.99174499511719</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G214" t="n">
-        <v>3.84711647033691</v>
+        <v>3.84711623191833</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>3.78203320503235</v>
+        <v>3.78203344345093</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68802428245544</v>
+        <v>3.68802452087402</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>3.69164085388184</v>
+        <v>3.69164061546326</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.64463663101196</v>
+        <v>3.64463591575623</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G219" t="n">
-        <v>3.66633009910583</v>
+        <v>3.66633033752441</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>3.64463663101196</v>
+        <v>3.64463591575623</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>3.68079352378845</v>
+        <v>3.68079304695129</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G223" t="n">
-        <v>3.65186738967896</v>
+        <v>3.65186810493469</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G224" t="n">
-        <v>3.61281824111938</v>
+        <v>3.61281800270081</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G226" t="n">
-        <v>3.50579285621643</v>
+        <v>3.50579237937927</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>3.47108221054077</v>
+        <v>3.47108268737793</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>3.41323089599609</v>
+        <v>3.41323065757751</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G229" t="n">
-        <v>3.41323089599609</v>
+        <v>3.41323065757751</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G230" t="n">
-        <v>3.40744614601135</v>
+        <v>3.40744566917419</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G231" t="n">
-        <v>3.41033816337585</v>
+        <v>3.41033864021301</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G232" t="n">
-        <v>3.42480134963989</v>
+        <v>3.42480111122131</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G233" t="n">
-        <v>3.46674370765686</v>
+        <v>3.46674346923828</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G234" t="n">
-        <v>3.34236335754395</v>
+        <v>3.34236311912537</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G235" t="n">
-        <v>3.45517301559448</v>
+        <v>3.4551727771759</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>3.52893352508545</v>
+        <v>3.52893376350403</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53327226638794</v>
+        <v>3.53327202796936</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>3.60124802589417</v>
+        <v>3.60124754905701</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.64463663101196</v>
+        <v>3.64463591575623</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>3.7603394985199</v>
+        <v>3.76033926010132</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.125</v>
       </c>
       <c r="G243" t="n">
-        <v>3.70610356330872</v>
+        <v>3.70610380172729</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>3.66633009910583</v>
+        <v>3.66633033752441</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.94835615158081</v>
+        <v>3.94835591316223</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>3.92304587364197</v>
+        <v>3.92304635047913</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G247" t="n">
-        <v>3.98812890052795</v>
+        <v>3.98812866210938</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>3.95197129249573</v>
+        <v>3.95197153091431</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>3.86157941818237</v>
+        <v>3.86157917976379</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>3.89050531387329</v>
+        <v>3.89050483703613</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>3.96281862258911</v>
+        <v>3.96281886100769</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>3.94112396240234</v>
+        <v>3.94112348556519</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G253" t="n">
-        <v>3.98451280593872</v>
+        <v>3.98451352119446</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G254" t="n">
-        <v>3.97005033493042</v>
+        <v>3.970050573349</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>3.85434675216675</v>
+        <v>3.85434722900391</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.97005033493042</v>
+        <v>3.970050573349</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G260" t="n">
-        <v>3.92666149139404</v>
+        <v>3.9266619682312</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>3.99897623062134</v>
+        <v>3.9989755153656</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>3.92304587364197</v>
+        <v>3.92304635047913</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.97005033493042</v>
+        <v>3.970050573349</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>3.99174451828003</v>
+        <v>3.99174499511719</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G268" t="n">
-        <v>3.93389320373535</v>
+        <v>3.93389344215393</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G269" t="n">
-        <v>3.92666149139404</v>
+        <v>3.9266619682312</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.99174451828003</v>
+        <v>3.99174499511719</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G271" t="n">
-        <v>4.02790260314941</v>
+        <v>4.02790212631226</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G273" t="n">
-        <v>3.97005033493042</v>
+        <v>3.970050573349</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G279" t="n">
-        <v>3.97005033493042</v>
+        <v>3.970050573349</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>4.00620794296265</v>
+        <v>4.00620698928833</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G283" t="n">
-        <v>3.86519408226013</v>
+        <v>3.86519384384155</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G284" t="n">
-        <v>3.92666149139404</v>
+        <v>3.9266619682312</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G285" t="n">
-        <v>3.96281862258911</v>
+        <v>3.96281886100769</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.97366547584534</v>
+        <v>3.9736659526825</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G287" t="n">
-        <v>3.91219806671143</v>
+        <v>3.91219878196716</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.93389320373535</v>
+        <v>3.93389344215393</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>3.96281862258911</v>
+        <v>3.96281886100769</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.94112396240234</v>
+        <v>3.94112348556519</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.92666149139404</v>
+        <v>3.9266619682312</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>3.91943120956421</v>
+        <v>3.91943025588989</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.94112396240234</v>
+        <v>3.94112348556519</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>3.91943120956421</v>
+        <v>3.91943025588989</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>3.89050531387329</v>
+        <v>3.89050483703613</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.87604188919067</v>
+        <v>3.87604165077209</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G300" t="n">
-        <v>3.9808976650238</v>
+        <v>3.98089694976807</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>4.03513336181641</v>
+        <v>4.03513383865356</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G302" t="n">
-        <v>4.12914180755615</v>
+        <v>4.12914133071899</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>4.14360475540161</v>
+        <v>4.14360427856445</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>4.15083503723145</v>
+        <v>4.1508355140686</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30269527435303</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>4.30269527435303</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>4.30269527435303</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.25</v>
       </c>
       <c r="G312" t="n">
-        <v>4.51963806152344</v>
+        <v>4.5196385383606</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.49794435501099</v>
+        <v>4.49794387817383</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.66426658630371</v>
+        <v>4.66426610946655</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G324" t="n">
-        <v>4.62087774276733</v>
+        <v>4.62087821960449</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.55217885971069</v>
+        <v>4.55217933654785</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G326" t="n">
-        <v>4.55217885971069</v>
+        <v>4.55217933654785</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>4.55579614639282</v>
+        <v>4.55579471588135</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G329" t="n">
-        <v>4.59918308258057</v>
+        <v>4.59918403625488</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>4.67149829864502</v>
+        <v>4.67149877548218</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>4.6425724029541</v>
+        <v>4.64257192611694</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G333" t="n">
-        <v>4.72211837768555</v>
+        <v>4.72211790084839</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.65703535079956</v>
+        <v>4.6570348739624</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G335" t="n">
-        <v>4.59918308258057</v>
+        <v>4.59918403625488</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G336" t="n">
-        <v>4.88285064697266</v>
+        <v>4.8828501701355</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>4.94714832305908</v>
+        <v>4.94714784622192</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>4.93958377838135</v>
+        <v>4.93958425521851</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G341" t="n">
-        <v>4.9774055480957</v>
+        <v>4.97740602493286</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>5.04170513153076</v>
+        <v>5.04170417785645</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.625</v>
       </c>
       <c r="G348" t="n">
-        <v>5.01144647598267</v>
+        <v>5.01144599914551</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>5.08709144592285</v>
+        <v>5.08709096908569</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>5.03035736083984</v>
+        <v>5.030357837677</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.96605968475342</v>
+        <v>4.96606016159058</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G359" t="n">
-        <v>5.18542909622192</v>
+        <v>5.18542861938477</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>5.02657508850098</v>
+        <v>5.02657556533813</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G362" t="n">
-        <v>5.06061553955078</v>
+        <v>5.06061458587646</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G363" t="n">
-        <v>5.13247776031494</v>
+        <v>5.1324782371521</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17408180236816</v>
+        <v>5.17408227920532</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>5.23837995529175</v>
+        <v>5.23837947845459</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>5.37075757980347</v>
+        <v>5.37075805664062</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>5.42370843887329</v>
+        <v>5.42370891571045</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G372" t="n">
-        <v>5.41614484786987</v>
+        <v>5.41614389419556</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G375" t="n">
-        <v>5.41236209869385</v>
+        <v>5.41236305236816</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G385" t="n">
-        <v>5.40479707717896</v>
+        <v>5.40479755401611</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>5.48044204711914</v>
+        <v>5.48044157028198</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>5.54473972320557</v>
+        <v>5.54473924636841</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>5.49935293197632</v>
+        <v>5.49935388565063</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.43127298355103</v>
+        <v>5.43127346038818</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>5.54473972320557</v>
+        <v>5.54473924636841</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>5.43127298355103</v>
+        <v>5.43127346038818</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>5.45018434524536</v>
+        <v>5.4501838684082</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.51448202133179</v>
+        <v>5.51448154449463</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G396" t="n">
-        <v>5.47287750244141</v>
+        <v>5.47287797927856</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>5.46153116226196</v>
+        <v>5.46153163909912</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G398" t="n">
-        <v>5.44640254974365</v>
+        <v>5.44640207290649</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G399" t="n">
-        <v>5.40479707717896</v>
+        <v>5.40479755401611</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49935293197632</v>
+        <v>5.49935388565063</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.55986928939819</v>
+        <v>5.55986881256104</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>5.62038421630859</v>
+        <v>5.62038469314575</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>5.60903787612915</v>
+        <v>5.60903692245483</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G410" t="n">
-        <v>5.7149395942688</v>
+        <v>5.71494007110596</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>5.73006868362427</v>
+        <v>5.73006916046143</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>5.68846368789673</v>
+        <v>5.68846416473389</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G413" t="n">
-        <v>5.58256244659424</v>
+        <v>5.58256196975708</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>5.49178838729858</v>
+        <v>5.49178886413574</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G415" t="n">
-        <v>5.57499694824219</v>
+        <v>5.57499742507935</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7.5</v>
       </c>
       <c r="G416" t="n">
-        <v>5.67333459854126</v>
+        <v>5.67333507537842</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.375</v>
       </c>
       <c r="G418" t="n">
-        <v>5.57877969741821</v>
+        <v>5.57877922058105</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G420" t="n">
-        <v>5.47665882110596</v>
+        <v>5.47665977478027</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G421" t="n">
-        <v>5.36319351196289</v>
+        <v>5.36319303512573</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.37075757980347</v>
+        <v>5.37075805664062</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.37075757980347</v>
+        <v>5.37075805664062</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>5.26485538482666</v>
+        <v>5.2648549079895</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G426" t="n">
-        <v>5.38588666915894</v>
+        <v>5.38588619232178</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>5.44640254974365</v>
+        <v>5.44640207290649</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>5.36319351196289</v>
+        <v>5.36319303512573</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>5.27620220184326</v>
+        <v>5.2762017250061</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G432" t="n">
-        <v>5.19299268722534</v>
+        <v>5.1929931640625</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>5.45018434524536</v>
+        <v>5.4501838684082</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>5.54852199554443</v>
+        <v>5.54852151870728</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>5.51826429367065</v>
+        <v>5.5182638168335</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095697402954</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>5.58634471893311</v>
+        <v>5.58634519577026</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G442" t="n">
-        <v>5.69602918624878</v>
+        <v>5.69602870941162</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G443" t="n">
-        <v>5.66198873519897</v>
+        <v>5.66198921203613</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.375</v>
       </c>
       <c r="G444" t="n">
-        <v>5.57877969741821</v>
+        <v>5.57877922058105</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>5.6355128288269</v>
+        <v>5.63551235198975</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>5.62794828414917</v>
+        <v>5.62794876098633</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.5</v>
       </c>
       <c r="G448" t="n">
-        <v>5.67333459854126</v>
+        <v>5.67333507537842</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>5.64307737350464</v>
+        <v>5.6430778503418</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>5.51069974899292</v>
+        <v>5.51069927215576</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>5.45396661758423</v>
+        <v>5.45396566390991</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>5.44640254974365</v>
+        <v>5.44640207290649</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G455" t="n">
-        <v>5.43883752822876</v>
+        <v>5.43883800506592</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095697402954</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095697402954</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>5.55230474472046</v>
+        <v>5.5523042678833</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G465" t="n">
-        <v>5.88892221450806</v>
+        <v>5.8889217376709</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>5.85866403579712</v>
+        <v>5.85866451263428</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G467" t="n">
-        <v>6.02886438369751</v>
+        <v>6.02886390686035</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.01373529434204</v>
+        <v>6.0137357711792</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G470" t="n">
-        <v>6.07425117492676</v>
+        <v>6.07425165176392</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G471" t="n">
-        <v>6.06668663024902</v>
+        <v>6.06668710708618</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>6.05912256240845</v>
+        <v>6.05912208557129</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G473" t="n">
-        <v>6.0250825881958</v>
+        <v>6.02508211135864</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>6.00617074966431</v>
+        <v>6.00617170333862</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.03264665603638</v>
+        <v>6.03264713287354</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G478" t="n">
-        <v>6.00238847732544</v>
+        <v>6.0023889541626</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>5.88892221450806</v>
+        <v>5.8889217376709</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G480" t="n">
-        <v>5.83597135543823</v>
+        <v>5.83597087860107</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>5.78680229187012</v>
+        <v>5.78680276870728</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>5.90026950836182</v>
+        <v>5.90026903152466</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G485" t="n">
-        <v>6.13476657867432</v>
+        <v>6.13476610183716</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>6.09694528579712</v>
+        <v>6.09694576263428</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>6.16124296188354</v>
+        <v>6.16124391555786</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G489" t="n">
-        <v>6.13476657867432</v>
+        <v>6.13476610183716</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G496" t="n">
-        <v>6.32009601593018</v>
+        <v>6.32009553909302</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G497" t="n">
-        <v>6.46382093429565</v>
+        <v>6.4638204574585</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G500" t="n">
-        <v>6.53946495056152</v>
+        <v>6.53946447372437</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>6.43356275558472</v>
+        <v>6.43356227874756</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G504" t="n">
-        <v>6.52811813354492</v>
+        <v>6.52811861038208</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>6.50542449951172</v>
+        <v>6.50542497634888</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G506" t="n">
-        <v>6.51298809051514</v>
+        <v>6.51298904418945</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G508" t="n">
-        <v>6.60376214981079</v>
+        <v>6.60376262664795</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.55837631225586</v>
+        <v>6.55837678909302</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G515" t="n">
-        <v>6.73992252349854</v>
+        <v>6.73992156982422</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>6.7323579788208</v>
+        <v>6.73235845565796</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G518" t="n">
-        <v>7.12949085235596</v>
+        <v>7.12949180603027</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>7.29969215393066</v>
+        <v>7.29969120025635</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G520" t="n">
-        <v>7.26187038421631</v>
+        <v>7.26186943054199</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>7.27321624755859</v>
+        <v>7.27321577072144</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G524" t="n">
-        <v>7.32238531112671</v>
+        <v>7.32238388061523</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>7.34129571914673</v>
+        <v>7.34129667282104</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>7.38290071487427</v>
+        <v>7.38290023803711</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.875</v>
       </c>
       <c r="G528" t="n">
-        <v>7.46989154815674</v>
+        <v>7.46989059448242</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G531" t="n">
-        <v>7.62496328353882</v>
+        <v>7.6249623298645</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>7.49636650085449</v>
+        <v>7.49636602401733</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>7.57201290130615</v>
+        <v>7.57201242446899</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.31799983978271</v>
       </c>
       <c r="G537" t="n">
-        <v>7.04855155944824</v>
+        <v>7.0485520362854</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9.21399974822998</v>
       </c>
       <c r="G540" t="n">
-        <v>6.96988153457642</v>
+        <v>6.9698805809021</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G542" t="n">
-        <v>6.97593259811401</v>
+        <v>6.97593307495117</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.53600025177002</v>
       </c>
       <c r="G544" t="n">
-        <v>7.21345567703247</v>
+        <v>7.21345663070679</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G545" t="n">
-        <v>7.31028175354004</v>
+        <v>7.3102822303772</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G546" t="n">
-        <v>7.31028175354004</v>
+        <v>7.3102822303772</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G547" t="n">
-        <v>7.41164541244507</v>
+        <v>7.41164636611938</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.97200012207031</v>
       </c>
       <c r="G551" t="n">
-        <v>7.54326629638672</v>
+        <v>7.54326725006104</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G552" t="n">
-        <v>7.62496328353882</v>
+        <v>7.6249623298645</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G553" t="n">
-        <v>7.65522146224976</v>
+        <v>7.65522050857544</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>10.1450004577637</v>
       </c>
       <c r="G554" t="n">
-        <v>7.67413187026978</v>
+        <v>7.67413139343262</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G555" t="n">
-        <v>7.41164541244507</v>
+        <v>7.41164636611938</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G556" t="n">
-        <v>7.24220275878906</v>
+        <v>7.24220132827759</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>9.9680004119873</v>
       </c>
       <c r="G557" t="n">
-        <v>7.54024267196655</v>
+        <v>7.54024171829224</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>10.1450004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>7.67413187026978</v>
+        <v>7.67413139343262</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G560" t="n">
-        <v>7.78381633758545</v>
+        <v>7.78381586074829</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G561" t="n">
-        <v>7.79138088226318</v>
+        <v>7.79138040542603</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>7.64765644073486</v>
+        <v>7.64765501022339</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>10.125</v>
       </c>
       <c r="G563" t="n">
-        <v>7.65900373458862</v>
+        <v>7.65900278091431</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>10.3249998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>7.81029081344604</v>
+        <v>7.81029224395752</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>7.64765644073486</v>
+        <v>7.64765501022339</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G567" t="n">
-        <v>7.84433221817017</v>
+        <v>7.84433126449585</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G569" t="n">
-        <v>7.57579326629639</v>
+        <v>7.5757942199707</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G571" t="n">
-        <v>7.41013288497925</v>
+        <v>7.41013193130493</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.81599998474121</v>
       </c>
       <c r="G572" t="n">
-        <v>7.42526149749756</v>
+        <v>7.4252610206604</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>9.72799968719482</v>
       </c>
       <c r="G573" t="n">
-        <v>7.3586950302124</v>
+        <v>7.35869455337524</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G574" t="n">
-        <v>7.38895177841187</v>
+        <v>7.38895130157471</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.69400024414062</v>
       </c>
       <c r="G575" t="n">
-        <v>7.3329758644104</v>
+        <v>7.33297538757324</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G576" t="n">
-        <v>7.37231111526489</v>
+        <v>7.37231063842773</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>10</v>
       </c>
       <c r="G577" t="n">
-        <v>7.56444692611694</v>
+        <v>7.56444787979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G578" t="n">
-        <v>7.31330823898315</v>
+        <v>7.31330919265747</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.74400043487549</v>
       </c>
       <c r="G579" t="n">
-        <v>7.37079763412476</v>
+        <v>7.37079668045044</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G580" t="n">
-        <v>7.41164541244507</v>
+        <v>7.41164636611938</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.62600040435791</v>
       </c>
       <c r="G582" t="n">
-        <v>7.28153657913208</v>
+        <v>7.2815375328064</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G583" t="n">
-        <v>7.31028175354004</v>
+        <v>7.3102822303772</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G584" t="n">
-        <v>7.38895177841187</v>
+        <v>7.38895130157471</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>7.46610927581787</v>
+        <v>7.46610975265503</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G586" t="n">
-        <v>7.5417537689209</v>
+        <v>7.54175424575806</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.96399974822998</v>
       </c>
       <c r="G587" t="n">
-        <v>7.53721475601196</v>
+        <v>7.53721570968628</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G588" t="n">
-        <v>7.50695753097534</v>
+        <v>7.50695705413818</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G589" t="n">
-        <v>7.74137830734253</v>
+        <v>7.741379737854</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G591" t="n">
-        <v>7.71957445144653</v>
+        <v>7.71957302093506</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G592" t="n">
-        <v>7.67440176010132</v>
+        <v>7.67440128326416</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G593" t="n">
-        <v>7.67907428741455</v>
+        <v>7.67907381057739</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.9040002822876</v>
       </c>
       <c r="G594" t="n">
-        <v>7.71334218978882</v>
+        <v>7.71334266662598</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.87399959564209</v>
       </c>
       <c r="G596" t="n">
-        <v>7.68997669219971</v>
+        <v>7.68997716903687</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.0749998092651</v>
       </c>
       <c r="G597" t="n">
-        <v>7.84651756286621</v>
+        <v>7.84651899337769</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G600" t="n">
-        <v>7.71957445144653</v>
+        <v>7.71957302093506</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G601" t="n">
-        <v>7.57004070281982</v>
+        <v>7.57004165649414</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56848478317261</v>
+        <v>7.56848382949829</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>9.72799968719482</v>
       </c>
       <c r="G604" t="n">
-        <v>7.57627105712891</v>
+        <v>7.57627201080322</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G605" t="n">
-        <v>7.1619439125061</v>
+        <v>7.16194438934326</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>8.96599960327148</v>
       </c>
       <c r="G607" t="n">
-        <v>6.98281669616699</v>
+        <v>6.98281764984131</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>9.1879997253418</v>
       </c>
       <c r="G609" t="n">
-        <v>7.15571308135986</v>
+        <v>7.15571355819702</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>9.1560001373291</v>
       </c>
       <c r="G610" t="n">
-        <v>7.13079214096069</v>
+        <v>7.13079166412354</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.15200042724609</v>
       </c>
       <c r="G613" t="n">
-        <v>6.3488655090332</v>
+        <v>6.34886598587036</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>8.4680004119873</v>
       </c>
       <c r="G615" t="n">
-        <v>6.59497022628784</v>
+        <v>6.594970703125</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>8.55399990081787</v>
       </c>
       <c r="G616" t="n">
-        <v>6.66194725036621</v>
+        <v>6.66194772720337</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G617" t="n">
-        <v>6.84418964385986</v>
+        <v>6.84418916702271</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.56400012969971</v>
       </c>
       <c r="G618" t="n">
-        <v>6.66973543167114</v>
+        <v>6.6697359085083</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G619" t="n">
-        <v>6.56537580490112</v>
+        <v>6.56537532806396</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G620" t="n">
-        <v>6.95478057861328</v>
+        <v>6.95478105545044</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G622" t="n">
-        <v>6.88313055038452</v>
+        <v>6.88313102722168</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.98200035095215</v>
       </c>
       <c r="G623" t="n">
-        <v>6.99527883529663</v>
+        <v>6.99527835845947</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G626" t="n">
-        <v>7.41895151138306</v>
+        <v>7.41895246505737</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.44400024414062</v>
       </c>
       <c r="G628" t="n">
-        <v>7.35508966445923</v>
+        <v>7.35508918762207</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G629" t="n">
-        <v>7.41895151138306</v>
+        <v>7.41895246505737</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>9.62199974060059</v>
       </c>
       <c r="G630" t="n">
-        <v>7.49371671676636</v>
+        <v>7.49371767044067</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.42206716537476</v>
+        <v>7.4220666885376</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G635" t="n">
-        <v>7.37533807754517</v>
+        <v>7.37533903121948</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.51799964904785</v>
       </c>
       <c r="G636" t="n">
-        <v>7.41272020339966</v>
+        <v>7.41272068023682</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.67199993133545</v>
       </c>
       <c r="G637" t="n">
-        <v>7.53265857696533</v>
+        <v>7.53265810012817</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.83199977874756</v>
       </c>
       <c r="G639" t="n">
-        <v>7.65726757049561</v>
+        <v>7.65726709365845</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.95800018310547</v>
       </c>
       <c r="G640" t="n">
-        <v>7.75539922714233</v>
+        <v>7.75539827346802</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.95800018310547</v>
       </c>
       <c r="G643" t="n">
-        <v>7.75539922714233</v>
+        <v>7.75539827346802</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.98200035095215</v>
       </c>
       <c r="G644" t="n">
-        <v>7.77408981323242</v>
+        <v>7.77408933639526</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>9.97599983215332</v>
       </c>
       <c r="G645" t="n">
-        <v>7.76941680908203</v>
+        <v>7.76941585540771</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G646" t="n">
-        <v>7.88935422897339</v>
+        <v>7.88935327529907</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G647" t="n">
-        <v>7.94776344299316</v>
+        <v>7.94776439666748</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>10.25</v>
       </c>
       <c r="G648" t="n">
-        <v>7.98281192779541</v>
+        <v>7.98281097412109</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G649" t="n">
-        <v>7.99059915542603</v>
+        <v>7.99059820175171</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G650" t="n">
-        <v>8.00617408752441</v>
+        <v>8.00617504119873</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G651" t="n">
-        <v>7.97112941741943</v>
+        <v>7.97112846374512</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G652" t="n">
-        <v>7.8815655708313</v>
+        <v>7.88156509399414</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G653" t="n">
-        <v>7.92829322814941</v>
+        <v>7.92829465866089</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G654" t="n">
-        <v>7.94776344299316</v>
+        <v>7.94776439666748</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>10.1549997329712</v>
       </c>
       <c r="G655" t="n">
-        <v>7.90882349014282</v>
+        <v>7.90882396697998</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>10.2449998855591</v>
       </c>
       <c r="G656" t="n">
-        <v>7.97891712188721</v>
+        <v>7.97891569137573</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G657" t="n">
-        <v>7.94776344299316</v>
+        <v>7.94776439666748</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>10.1949996948242</v>
       </c>
       <c r="G660" t="n">
-        <v>7.93997573852539</v>
+        <v>7.93997526168823</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.0749998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>7.84651756286621</v>
+        <v>7.84651899337769</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>9.97399997711182</v>
       </c>
       <c r="G663" t="n">
-        <v>7.76785850524902</v>
+        <v>7.7678599357605</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G664" t="n">
-        <v>7.87377691268921</v>
+        <v>7.87377595901489</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G665" t="n">
-        <v>7.78031969070435</v>
+        <v>7.78031921386719</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>10.0649995803833</v>
       </c>
       <c r="G666" t="n">
-        <v>7.83872985839844</v>
+        <v>7.8387303352356</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>9.9980001449585</v>
       </c>
       <c r="G667" t="n">
-        <v>7.78655004501343</v>
+        <v>7.78654956817627</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>10.0450000762939</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82315444946289</v>
+        <v>7.82315492630005</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>7.90492868423462</v>
+        <v>7.90492916107178</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G670" t="n">
-        <v>7.92050695419312</v>
+        <v>7.92050743103027</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G671" t="n">
-        <v>7.94776344299316</v>
+        <v>7.94776439666748</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G672" t="n">
-        <v>7.92050695419312</v>
+        <v>7.92050743103027</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>8.00228023529053</v>
+        <v>8.00228118896484</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.1549997329712</v>
       </c>
       <c r="G674" t="n">
-        <v>7.90882349014282</v>
+        <v>7.90882396697998</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>7.92440032958984</v>
+        <v>7.92439985275269</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G676" t="n">
-        <v>7.92829322814941</v>
+        <v>7.92829465866089</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>7.90492868423462</v>
+        <v>7.90492916107178</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10.125</v>
       </c>
       <c r="G678" t="n">
-        <v>7.8854603767395</v>
+        <v>7.88545942306519</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>8.02564525604248</v>
+        <v>8.0256462097168</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>7.99059915542603</v>
+        <v>7.99059820175171</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>10.2650003433228</v>
       </c>
       <c r="G681" t="n">
-        <v>7.99449300765991</v>
+        <v>7.99449348449707</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>11.0749998092651</v>
       </c>
       <c r="G688" t="n">
-        <v>8.62532901763916</v>
+        <v>8.62533092498779</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>11.1750001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>8.70320987701416</v>
+        <v>8.70321083068848</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G690" t="n">
-        <v>8.70710468292236</v>
+        <v>8.70710563659668</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97579479217529</v>
+        <v>8.97579383850098</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G695" t="n">
-        <v>8.88623046875</v>
+        <v>8.88623142242432</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>9.13155651092529</v>
+        <v>9.13155555725098</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G701" t="n">
-        <v>8.96800804138184</v>
+        <v>8.96800708770752</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>11.5</v>
       </c>
       <c r="G703" t="n">
-        <v>8.95632362365723</v>
+        <v>8.95632457733154</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G706" t="n">
-        <v>8.77719783782959</v>
+        <v>8.77719879150391</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G707" t="n">
-        <v>8.35663986206055</v>
+        <v>8.35663890838623</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G709" t="n">
-        <v>7.94776344299316</v>
+        <v>7.94776439666748</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G711" t="n">
-        <v>7.60742235183716</v>
+        <v>7.60742330551147</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>9.68599987030029</v>
       </c>
       <c r="G714" t="n">
-        <v>7.5435619354248</v>
+        <v>7.54356145858765</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G716" t="n">
-        <v>6.98437595367432</v>
+        <v>6.98437547683716</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G717" t="n">
-        <v>6.973473072052</v>
+        <v>6.97347259521484</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>8.77400016784668</v>
       </c>
       <c r="G721" t="n">
-        <v>6.83328676223755</v>
+        <v>6.83328628540039</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>9.62600040435791</v>
       </c>
       <c r="G729" t="n">
-        <v>7.49683237075806</v>
+        <v>7.49683332443237</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>9.87600040435791</v>
       </c>
       <c r="G730" t="n">
-        <v>7.69153547286987</v>
+        <v>7.69153594970703</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>9.82400035858154</v>
       </c>
       <c r="G732" t="n">
-        <v>7.651038646698</v>
+        <v>7.65103816986084</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G733" t="n">
-        <v>7.67128753662109</v>
+        <v>7.67128658294678</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>9.7480001449585</v>
       </c>
       <c r="G734" t="n">
-        <v>7.59184837341309</v>
+        <v>7.59184885025024</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>7.49215936660767</v>
+        <v>7.49215888977051</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G736" t="n">
-        <v>7.50150585174561</v>
+        <v>7.50150680541992</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G738" t="n">
-        <v>7.47502517700195</v>
+        <v>7.47502565383911</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G739" t="n">
-        <v>7.50150585174561</v>
+        <v>7.50150680541992</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G740" t="n">
-        <v>7.45633459091187</v>
+        <v>7.45633411407471</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G744" t="n">
-        <v>7.61832761764526</v>
+        <v>7.61832666397095</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G746" t="n">
-        <v>7.37533807754517</v>
+        <v>7.37533903121948</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G747" t="n">
-        <v>7.56069612503052</v>
+        <v>7.56069469451904</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G749" t="n">
-        <v>7.57004070281982</v>
+        <v>7.57004165649414</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.0620002746582</v>
       </c>
       <c r="G750" t="n">
-        <v>7.05758380889893</v>
+        <v>7.05758333206177</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G751" t="n">
-        <v>7.11677265167236</v>
+        <v>7.11677217483521</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>8.96399974822998</v>
       </c>
       <c r="G753" t="n">
-        <v>6.9812593460083</v>
+        <v>6.98125982284546</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G755" t="n">
-        <v>7.21645975112915</v>
+        <v>7.21646070480347</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.14400005340576</v>
       </c>
       <c r="G756" t="n">
-        <v>7.12144613265991</v>
+        <v>7.12144660949707</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>8.92599964141846</v>
       </c>
       <c r="G758" t="n">
-        <v>6.95166492462158</v>
+        <v>6.95166540145874</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>9.0939998626709</v>
       </c>
       <c r="G759" t="n">
-        <v>7.08250522613525</v>
+        <v>7.08250570297241</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G761" t="n">
-        <v>6.79123020172119</v>
+        <v>6.79123115539551</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>8.64599990844727</v>
       </c>
       <c r="G765" t="n">
-        <v>6.73359823226929</v>
+        <v>6.73359775543213</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>6.97035694122314</v>
+        <v>6.97035646438599</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="n">
-        <v>7.00929689407349</v>
+        <v>7.00929641723633</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G768" t="n">
-        <v>7.30368804931641</v>
+        <v>7.30368757247925</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.34200000762939</v>
       </c>
       <c r="G771" t="n">
-        <v>7.27565050125122</v>
+        <v>7.27565002441406</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G777" t="n">
-        <v>7.67128753662109</v>
+        <v>7.67128658294678</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>9.77600002288818</v>
       </c>
       <c r="G779" t="n">
-        <v>7.61365413665771</v>
+        <v>7.6136531829834</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G781" t="n">
-        <v>7.67128753662109</v>
+        <v>7.67128658294678</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>7.49994850158691</v>
+        <v>7.49994802474976</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>9.74400043487549</v>
       </c>
       <c r="G783" t="n">
-        <v>7.58873224258423</v>
+        <v>7.58873176574707</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>9.71599960327148</v>
       </c>
       <c r="G784" t="n">
-        <v>7.56692457199097</v>
+        <v>7.56692552566528</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G785" t="n">
-        <v>7.3893575668335</v>
+        <v>7.38935708999634</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G786" t="n">
-        <v>7.29122686386108</v>
+        <v>7.2912278175354</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>9.68400001525879</v>
       </c>
       <c r="G787" t="n">
-        <v>7.54200410842896</v>
+        <v>7.5420036315918</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G789" t="n">
-        <v>7.72112989425659</v>
+        <v>7.72112941741943</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G790" t="n">
-        <v>7.51863956451416</v>
+        <v>7.51864004135132</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>9.67199993133545</v>
       </c>
       <c r="G791" t="n">
-        <v>7.53265857696533</v>
+        <v>7.53265810012817</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G793" t="n">
-        <v>7.70711088180542</v>
+        <v>7.70711135864258</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>10.6049995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>8.25928783416748</v>
+        <v>8.2592887878418</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G798" t="n">
-        <v>8.07626819610596</v>
+        <v>8.07626724243164</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>10.2250003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>7.96334075927734</v>
+        <v>7.96333932876587</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G800" t="n">
-        <v>7.78031969070435</v>
+        <v>7.78031921386719</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>10.1149997711182</v>
       </c>
       <c r="G801" t="n">
-        <v>7.87767171859741</v>
+        <v>7.87767124176025</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G802" t="n">
-        <v>7.97112941741943</v>
+        <v>7.97112846374512</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G803" t="n">
-        <v>7.95555114746094</v>
+        <v>7.95555210113525</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G806" t="n">
-        <v>8.59028339385986</v>
+        <v>8.59028244018555</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G807" t="n">
-        <v>8.74604606628418</v>
+        <v>8.74604511260986</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>11.3249998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>8.82003211975098</v>
+        <v>8.82003116607666</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G809" t="n">
-        <v>8.84729099273682</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>11.1549997329712</v>
       </c>
       <c r="G810" t="n">
-        <v>8.68763542175293</v>
+        <v>8.68763446807861</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G812" t="n">
-        <v>8.94074821472168</v>
+        <v>8.94074726104736</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G813" t="n">
-        <v>8.84729099273682</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>8.83950328826904</v>
+        <v>8.83950233459473</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>11.414999961853</v>
       </c>
       <c r="G815" t="n">
-        <v>8.89012432098389</v>
+        <v>8.8901252746582</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>8.97579479217529</v>
+        <v>8.97579383850098</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G819" t="n">
-        <v>8.97968864440918</v>
+        <v>8.97968769073486</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G821" t="n">
-        <v>8.97968864440918</v>
+        <v>8.97968769073486</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G822" t="n">
-        <v>8.83950328826904</v>
+        <v>8.83950233459473</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>8.88623046875</v>
+        <v>8.88623142242432</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G825" t="n">
-        <v>9.01862907409668</v>
+        <v>9.01862812042236</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>9.13155651092529</v>
+        <v>9.13155555725098</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G827" t="n">
-        <v>9.23669624328613</v>
+        <v>9.23669528961182</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G828" t="n">
-        <v>9.0575704574585</v>
+        <v>9.05756950378418</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G831" t="n">
-        <v>9.29899978637695</v>
+        <v>9.29900074005127</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G832" t="n">
-        <v>9.21333312988281</v>
+        <v>9.21333122253418</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>11.6949996948242</v>
       </c>
       <c r="G833" t="n">
-        <v>9.10819244384766</v>
+        <v>9.10819149017334</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>11.7049999237061</v>
       </c>
       <c r="G834" t="n">
-        <v>9.11598014831543</v>
+        <v>9.11598110198975</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>12.1549997329712</v>
       </c>
       <c r="G840" t="n">
-        <v>9.46644592285156</v>
+        <v>9.46644496917725</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G841" t="n">
-        <v>9.66452884674072</v>
+        <v>9.66452789306641</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G844" t="n">
-        <v>9.61660575866699</v>
+        <v>9.61660480499268</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>11.4250001907349</v>
       </c>
       <c r="G847" t="n">
-        <v>9.12539196014404</v>
+        <v>9.12539100646973</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G848" t="n">
-        <v>9.05749988555908</v>
+        <v>9.0575008392334</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>10.25</v>
       </c>
       <c r="G850" t="n">
-        <v>8.1868953704834</v>
+        <v>8.18689441680908</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G851" t="n">
-        <v>8.13098239898682</v>
+        <v>8.13098430633545</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>9.85200023651123</v>
       </c>
       <c r="G853" t="n">
-        <v>7.86900329589844</v>
+        <v>7.8690037727356</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>9.91800022125244</v>
       </c>
       <c r="G857" t="n">
-        <v>7.92171859741211</v>
+        <v>7.92171812057495</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G858" t="n">
-        <v>7.93130445480347</v>
+        <v>7.93130350112915</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G860" t="n">
-        <v>7.90734052658081</v>
+        <v>7.90734148025513</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G861" t="n">
-        <v>7.7955207824707</v>
+        <v>7.79552030563354</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G862" t="n">
-        <v>7.71085643768311</v>
+        <v>7.71085548400879</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>9.5</v>
       </c>
       <c r="G865" t="n">
-        <v>7.58785390853882</v>
+        <v>7.5878529548645</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.27600002288818</v>
       </c>
       <c r="G868" t="n">
-        <v>7.40893840789795</v>
+        <v>7.40893888473511</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G870" t="n">
-        <v>7.48881196975708</v>
+        <v>7.48881101608276</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G871" t="n">
-        <v>7.48401975631714</v>
+        <v>7.48401880264282</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G872" t="n">
-        <v>7.42331647872925</v>
+        <v>7.42331600189209</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>9.28400039672852</v>
       </c>
       <c r="G874" t="n">
-        <v>7.41532945632935</v>
+        <v>7.41532850265503</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>9.10400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>7.271559715271</v>
+        <v>7.27155923843384</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>9.31799983978271</v>
       </c>
       <c r="G880" t="n">
-        <v>7.44248533248901</v>
+        <v>7.44248580932617</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G881" t="n">
-        <v>7.53992938995361</v>
+        <v>7.5399284362793</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>9.54800033569336</v>
       </c>
       <c r="G882" t="n">
-        <v>7.62619161605835</v>
+        <v>7.62619256973267</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G883" t="n">
-        <v>7.82267713546753</v>
+        <v>7.82267570495605</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G885" t="n">
-        <v>7.78433847427368</v>
+        <v>7.78433895111084</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G887" t="n">
-        <v>7.66772603988647</v>
+        <v>7.66772556304932</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>7.91532754898071</v>
+        <v>7.91532850265503</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>10.7049999237061</v>
       </c>
       <c r="G892" t="n">
-        <v>8.55031108856201</v>
+        <v>8.55031204223633</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.2650003433228</v>
       </c>
       <c r="G897" t="n">
-        <v>8.19887542724609</v>
+        <v>8.19887447357178</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>10.1949996948242</v>
       </c>
       <c r="G898" t="n">
-        <v>8.14296340942383</v>
+        <v>8.14296436309814</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>9.99600028991699</v>
       </c>
       <c r="G901" t="n">
-        <v>7.98401880264282</v>
+        <v>7.98401975631714</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>9.71399974822998</v>
       </c>
       <c r="G903" t="n">
-        <v>7.75877857208252</v>
+        <v>7.75877904891968</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>9.72599983215332</v>
       </c>
       <c r="G904" t="n">
-        <v>7.76836347579956</v>
+        <v>7.76836395263672</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>9.9379997253418</v>
       </c>
       <c r="G905" t="n">
-        <v>7.9376916885376</v>
+        <v>7.93769264221191</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G907" t="n">
-        <v>7.7811427116394</v>
+        <v>7.78114223480225</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.99199962615967</v>
       </c>
       <c r="G911" t="n">
-        <v>7.18210220336914</v>
+        <v>7.1821026802063</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>7.29232692718506</v>
+        <v>7.29232597351074</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.90200042724609</v>
       </c>
       <c r="G915" t="n">
-        <v>7.11021709442139</v>
+        <v>7.11021757125854</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>8.90799999237061</v>
       </c>
       <c r="G916" t="n">
-        <v>7.11500978469849</v>
+        <v>7.11501026153564</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>9.32199954986572</v>
       </c>
       <c r="G917" t="n">
-        <v>7.44568061828613</v>
+        <v>7.44568109512329</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>8.94400024414062</v>
       </c>
       <c r="G918" t="n">
-        <v>7.14376497268677</v>
+        <v>7.14376401901245</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>8.51399993896484</v>
       </c>
       <c r="G921" t="n">
-        <v>6.8003134727478</v>
+        <v>6.80031394958496</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>8.7519998550415</v>
       </c>
       <c r="G924" t="n">
-        <v>6.9904088973999</v>
+        <v>6.99040937423706</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G925" t="n">
-        <v>7.28433895111084</v>
+        <v>7.28433799743652</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G930" t="n">
-        <v>7.45207071304321</v>
+        <v>7.45207118988037</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G931" t="n">
-        <v>7.63417720794678</v>
+        <v>7.63417768478394</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G932" t="n">
-        <v>7.4904088973999</v>
+        <v>7.49040842056274</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>9.57600021362305</v>
       </c>
       <c r="G935" t="n">
-        <v>7.64855575561523</v>
+        <v>7.64855480194092</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>9.87399959564209</v>
       </c>
       <c r="G938" t="n">
-        <v>7.88657331466675</v>
+        <v>7.88657474517822</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>9.42399978637695</v>
       </c>
       <c r="G941" t="n">
-        <v>7.52715063095093</v>
+        <v>7.52715015411377</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G942" t="n">
-        <v>7.86740589141846</v>
+        <v>7.86740636825562</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>9.76399993896484</v>
       </c>
       <c r="G943" t="n">
-        <v>7.79871559143066</v>
+        <v>7.79871606826782</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>9.68400001525879</v>
       </c>
       <c r="G946" t="n">
-        <v>7.73481845855713</v>
+        <v>7.73481893539429</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>9.91800022125244</v>
       </c>
       <c r="G947" t="n">
-        <v>7.92171859741211</v>
+        <v>7.92171812057495</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>9.61800003051758</v>
       </c>
       <c r="G952" t="n">
-        <v>7.68210220336914</v>
+        <v>7.68210172653198</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G956" t="n">
-        <v>7.61181449890137</v>
+        <v>7.61181402206421</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>9.64599990844727</v>
       </c>
       <c r="G957" t="n">
-        <v>7.70446634292603</v>
+        <v>7.70446586608887</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>9.3120002746582</v>
       </c>
       <c r="G960" t="n">
-        <v>7.43769407272339</v>
+        <v>7.43769454956055</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G961" t="n">
-        <v>7.60382747650146</v>
+        <v>7.60382795333862</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G962" t="n">
-        <v>7.82587194442749</v>
+        <v>7.82587242126465</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>9.5959997177124</v>
       </c>
       <c r="G963" t="n">
-        <v>7.6645302772522</v>
+        <v>7.66452980041504</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>9.85599994659424</v>
       </c>
       <c r="G964" t="n">
-        <v>7.87219715118408</v>
+        <v>7.87219667434692</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.0550003051758</v>
       </c>
       <c r="G965" t="n">
-        <v>8.03114318847656</v>
+        <v>8.03114223480225</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>10.0550003051758</v>
       </c>
       <c r="G967" t="n">
-        <v>8.03114318847656</v>
+        <v>8.03114223480225</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G969" t="n">
-        <v>8.13098239898682</v>
+        <v>8.13098430633545</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G971" t="n">
-        <v>8.13497638702393</v>
+        <v>8.13497734069824</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G972" t="n">
-        <v>8.11500930786133</v>
+        <v>8.11501026153564</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>8.30670261383057</v>
+        <v>8.30670166015625</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G977" t="n">
-        <v>8.29072761535645</v>
+        <v>8.29072856903076</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>8.5263500213623</v>
+        <v>8.52635097503662</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G980" t="n">
-        <v>8.66612815856934</v>
+        <v>8.6661262512207</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G982" t="n">
-        <v>8.79392147064209</v>
+        <v>8.79392242431641</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>11.3649997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>9.07746887207031</v>
+        <v>9.077467918396</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G989" t="n">
-        <v>8.96964168548584</v>
+        <v>8.96963977813721</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>11.3149995803833</v>
       </c>
       <c r="G991" t="n">
-        <v>9.03753185272217</v>
+        <v>9.03753280639648</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G993" t="n">
-        <v>9.37698936462402</v>
+        <v>9.37698841094971</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>11.6949996948242</v>
       </c>
       <c r="G994" t="n">
-        <v>9.34104537963867</v>
+        <v>9.34104633331299</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G995" t="n">
-        <v>9.21724414825439</v>
+        <v>9.21724510192871</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>11.2749996185303</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.00558280944824</v>
+        <v>9.00558185577393</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.04152488708496</v>
+        <v>9.04152584075928</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>11.2250003814697</v>
       </c>
       <c r="G1004" t="n">
-        <v>8.96564865112305</v>
+        <v>8.96564769744873</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>11.1750001907349</v>
       </c>
       <c r="G1006" t="n">
-        <v>8.92571067810059</v>
+        <v>8.9257116317749</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.70606231689453</v>
+        <v>8.70606136322021</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>10.9250001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.72603130340576</v>
+        <v>8.72603034973145</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1017" t="n">
-        <v>8.55430507659912</v>
+        <v>8.55430603027344</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.4983959197998</v>
+        <v>8.49839496612549</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>11.1450004577637</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.9017505645752</v>
+        <v>8.90174961090088</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1021" t="n">
-        <v>9.23321914672852</v>
+        <v>9.2332181930542</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>11.2049999237061</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.94967269897461</v>
+        <v>8.94967174530029</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.813889503479</v>
+        <v>8.81389045715332</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.91373157501221</v>
+        <v>8.91373062133789</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.96964168548584</v>
+        <v>8.96963977813721</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.87379455566406</v>
+        <v>8.87379360198975</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>10.9949998855591</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.78194236755371</v>
+        <v>8.78194141387939</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.87379455566406</v>
+        <v>8.87379360198975</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1033" t="n">
-        <v>8.45047092437744</v>
+        <v>8.45047187805176</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>10.5749998092651</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.44647693634033</v>
+        <v>8.44647789001465</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>10.8149995803833</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.63817024230957</v>
+        <v>8.63817119598389</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1041" t="n">
-        <v>9.04152488708496</v>
+        <v>9.04152584075928</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G1042" t="n">
-        <v>9.37698936462402</v>
+        <v>9.37698841094971</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1043" t="n">
-        <v>9.32906532287598</v>
+        <v>9.32906627655029</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>11.0249996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.8059024810791</v>
+        <v>8.80590343475342</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>10.9250001907349</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.72603130340576</v>
+        <v>8.72603034973145</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.72203826904297</v>
+        <v>8.72203731536865</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>10.7250003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.56628799438477</v>
+        <v>8.56628704071045</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.82267713546753</v>
+        <v>7.82267570495605</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1055" t="n">
-        <v>7.94727659225464</v>
+        <v>7.9472770690918</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G1056" t="n">
-        <v>7.84823703765869</v>
+        <v>7.84823608398438</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>9.49400043487549</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.58306074142456</v>
+        <v>7.58306121826172</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.29232692718506</v>
+        <v>7.29232597351074</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>9.33399963378906</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.45526456832886</v>
+        <v>7.45526504516602</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.06868457794189</v>
+        <v>7.06868410110474</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.08625602722168</v>
+        <v>7.08625555038452</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>6.91800022125244</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.52555465698242</v>
+        <v>5.52555513381958</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>7.7039999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.15334892272949</v>
+        <v>6.15334939956665</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1069" t="n">
-        <v>5.90255069732666</v>
+        <v>5.90255117416382</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.00957918167114</v>
+        <v>6.0095796585083</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>7.47800016403198</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.97283792495728</v>
+        <v>5.97283840179443</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>7.47800016403198</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.97283792495728</v>
+        <v>5.97283840179443</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>8.0959997177124</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.4664478302002</v>
+        <v>6.46644830703735</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1079" t="n">
-        <v>6.62139987945557</v>
+        <v>6.62140035629272</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.14855623245239</v>
+        <v>7.14855575561523</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>9.1540002822876</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.31149578094482</v>
+        <v>7.31149530410767</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>9.3120002746582</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.43769407272339</v>
+        <v>7.43769454956055</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>9.44400024414062</v>
       </c>
       <c r="G1085" t="n">
-        <v>7.54312467575073</v>
+        <v>7.54312515258789</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.63577651977539</v>
+        <v>7.63577699661255</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>8.83399963378906</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.05590391159058</v>
+        <v>7.05590438842773</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.51916313171387</v>
+        <v>6.51916360855103</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.37858772277832</v>
+        <v>7.37858819961548</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>9.21199989318848</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.3578200340271</v>
+        <v>7.35782051086426</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>9.50399971008301</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.5910472869873</v>
+        <v>7.59104776382446</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>9.73400020599365</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.77475261688232</v>
+        <v>7.77475357055664</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.15494441986084</v>
+        <v>8.15494537353516</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>8.09903335571289</v>
+        <v>8.09903430938721</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.75398731231689</v>
+        <v>7.75398683547974</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.48401975631714</v>
+        <v>7.48401880264282</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.97922563552856</v>
+        <v>7.97922658920288</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G1108" t="n">
-        <v>7.92491245269775</v>
+        <v>7.92491292953491</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>9.85599994659424</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.87219715118408</v>
+        <v>7.87219667434692</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.11500930786133</v>
+        <v>8.11501026153564</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.46245384216309</v>
+        <v>8.46245288848877</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>10.5050001144409</v>
       </c>
       <c r="G1119" t="n">
-        <v>8.3905668258667</v>
+        <v>8.39056777954102</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.43449878692627</v>
+        <v>8.43449783325195</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>11.0249996185303</v>
       </c>
       <c r="G1123" t="n">
-        <v>8.8059024810791</v>
+        <v>8.80590343475342</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>11.2650003433228</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.99759674072266</v>
+        <v>8.99759578704834</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>11.2849998474121</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.01357078552246</v>
+        <v>9.01356983184814</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1127" t="n">
-        <v>9.32906532287598</v>
+        <v>9.32906627655029</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.32906532287598</v>
+        <v>9.32906627655029</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>12.1049995422363</v>
       </c>
       <c r="G1131" t="n">
-        <v>9.66852188110352</v>
+        <v>9.6685209274292</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>12.1049995422363</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.66852188110352</v>
+        <v>9.6685209274292</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>12.0349998474121</v>
       </c>
       <c r="G1138" t="n">
-        <v>9.61261081695557</v>
+        <v>9.61260986328125</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>12.1350002288818</v>
       </c>
       <c r="G1140" t="n">
-        <v>9.69248390197754</v>
+        <v>9.69248485565186</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>12</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.58465671539307</v>
+        <v>9.58465576171875</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1144" t="n">
-        <v>9.96804141998291</v>
+        <v>9.96804237365723</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>12.9350004196167</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.3314609527588</v>
+        <v>10.3314619064331</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.3035049438477</v>
+        <v>10.3035039901733</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>12.6149997711182</v>
       </c>
       <c r="G1150" t="n">
-        <v>10.075870513916</v>
+        <v>10.0758695602417</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1153" t="n">
-        <v>10.247594833374</v>
+        <v>10.2475938796997</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1156" t="n">
-        <v>10.3674030303955</v>
+        <v>10.3674020767212</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1157" t="n">
-        <v>10.5271472930908</v>
+        <v>10.5271482467651</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>12.9949998855591</v>
       </c>
       <c r="G1158" t="n">
-        <v>10.3793830871582</v>
+        <v>10.3793840408325</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>12.2749996185303</v>
       </c>
       <c r="G1164" t="n">
-        <v>9.8043041229248</v>
+        <v>9.80430507659912</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.0319395065308</v>
+        <v>10.0319404602051</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1171" t="n">
-        <v>10.6549434661865</v>
+        <v>10.6549425125122</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>12.7950000762939</v>
       </c>
       <c r="G1174" t="n">
-        <v>10.2196388244629</v>
+        <v>10.2196397781372</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1184" t="n">
-        <v>10.247594833374</v>
+        <v>10.2475938796997</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1186" t="n">
-        <v>10.2316207885742</v>
+        <v>10.2316217422485</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>12.75</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.1836977005005</v>
+        <v>10.1836967468262</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1190" t="n">
-        <v>10.0479154586792</v>
+        <v>10.0479145050049</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>12.3450002670288</v>
       </c>
       <c r="G1191" t="n">
-        <v>9.86021709442139</v>
+        <v>9.86021614074707</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1193" t="n">
-        <v>9.93609237670898</v>
+        <v>9.9360933303833</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>12.2849998474121</v>
       </c>
       <c r="G1194" t="n">
-        <v>9.81229114532471</v>
+        <v>9.81229209899902</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1195" t="n">
-        <v>9.81628513336182</v>
+        <v>9.81628608703613</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1196" t="n">
-        <v>9.81628513336182</v>
+        <v>9.81628608703613</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1197" t="n">
-        <v>9.66053581237793</v>
+        <v>9.6605339050293</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1201" t="n">
-        <v>9.21724414825439</v>
+        <v>9.21724510192871</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1202" t="n">
-        <v>9.09743690490723</v>
+        <v>9.09743785858154</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1203" t="n">
-        <v>9.36101531982422</v>
+        <v>9.36101341247559</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>9.2052640914917</v>
+        <v>9.20526313781738</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1205" t="n">
-        <v>9.35302829742432</v>
+        <v>9.35302734375</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>11.7550001144409</v>
       </c>
       <c r="G1207" t="n">
-        <v>9.38897037506104</v>
+        <v>9.38896942138672</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1210" t="n">
-        <v>9.65654182434082</v>
+        <v>9.6565408706665</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1212" t="n">
-        <v>9.5367317199707</v>
+        <v>9.53673267364502</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>12.25</v>
       </c>
       <c r="G1213" t="n">
-        <v>9.78433609008789</v>
+        <v>9.78433513641357</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>12.2650003433228</v>
       </c>
       <c r="G1214" t="n">
-        <v>9.7963171005249</v>
+        <v>9.79631805419922</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1217" t="n">
-        <v>9.77634906768799</v>
+        <v>9.77634811401367</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1221" t="n">
-        <v>9.59264373779297</v>
+        <v>9.59264278411865</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>9.24120426177979</v>
+        <v>9.2412052154541</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1223" t="n">
-        <v>9.24120426177979</v>
+        <v>9.2412052154541</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>9.23321914672852</v>
+        <v>9.2332181930542</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>11.2650003433228</v>
       </c>
       <c r="G1225" t="n">
-        <v>8.99759674072266</v>
+        <v>8.99759578704834</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1227" t="n">
-        <v>9.05749988555908</v>
+        <v>9.0575008392334</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>11.75</v>
       </c>
       <c r="G1229" t="n">
-        <v>9.38497734069824</v>
+        <v>9.38497638702393</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>12.4750003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>9.96404933929443</v>
+        <v>9.96404838562012</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1236" t="n">
-        <v>9.61660575866699</v>
+        <v>9.61660480499268</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G1239" t="n">
-        <v>9.75238800048828</v>
+        <v>9.7523889541626</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1241" t="n">
-        <v>9.88817119598389</v>
+        <v>9.88817024230957</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>12.6850004196167</v>
       </c>
       <c r="G1245" t="n">
-        <v>10.1317806243896</v>
+        <v>10.1317796707153</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.3594169616699</v>
+        <v>10.3594160079956</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1252" t="n">
-        <v>10.4153261184692</v>
+        <v>10.4153270721436</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1255" t="n">
-        <v>10.4951982498169</v>
+        <v>10.4951992034912</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G1256" t="n">
-        <v>10.4352941513062</v>
+        <v>10.4352931976318</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>13.0749998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.4432811737061</v>
+        <v>10.4432821273804</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>12.7950000762939</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.2196388244629</v>
+        <v>10.2196397781372</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.2316207885742</v>
+        <v>10.2316217422485</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.5710763931274</v>
+        <v>10.5710773468018</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>13.4250001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.7228336334229</v>
+        <v>10.7228345870972</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>13.3850002288818</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.6908855438232</v>
+        <v>10.6908845901489</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1270" t="n">
-        <v>10.7028656005859</v>
+        <v>10.7028665542603</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>10.7348146438599</v>
+        <v>10.7348155975342</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>10.9704370498657</v>
+        <v>10.97043800354</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1276" t="n">
-        <v>10.9704370498657</v>
+        <v>10.97043800354</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1278" t="n">
-        <v>11.0942392349243</v>
+        <v>11.0942401885986</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543031692505</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1281" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543031692505</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>13.4650001525879</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.7547826766968</v>
+        <v>10.7547836303711</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1286" t="n">
-        <v>10.4153261184692</v>
+        <v>10.4153270721436</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>13.1949996948242</v>
       </c>
       <c r="G1287" t="n">
-        <v>10.5391283035278</v>
+        <v>10.5391273498535</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>13.3850002288818</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.6908855438232</v>
+        <v>10.6908845901489</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>14.625</v>
       </c>
       <c r="G1297" t="n">
-        <v>11.6812992095947</v>
+        <v>11.681300163269</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>15.0050001144409</v>
       </c>
       <c r="G1298" t="n">
-        <v>11.9848146438599</v>
+        <v>11.9848136901855</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>14.7849998474121</v>
       </c>
       <c r="G1299" t="n">
-        <v>11.8090944290161</v>
+        <v>11.8090953826904</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>15.0649995803833</v>
       </c>
       <c r="G1300" t="n">
-        <v>12.0327377319336</v>
+        <v>12.0327386856079</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>15.1850004196167</v>
       </c>
       <c r="G1301" t="n">
-        <v>12.1285839080811</v>
+        <v>12.1285829544067</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G1302" t="n">
-        <v>12.0247507095337</v>
+        <v>12.0247497558594</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>11.9009466171265</v>
+        <v>11.9009485244751</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>11.7332172393799</v>
+        <v>11.7332162857056</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>14.875</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.8809795379639</v>
+        <v>11.8809804916382</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.6373701095581</v>
+        <v>11.6373691558838</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.8330574035645</v>
+        <v>11.8330554962158</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.6174020767212</v>
+        <v>11.6174030303955</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.5894470214844</v>
+        <v>11.5894460678101</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>14.375</v>
       </c>
       <c r="G1314" t="n">
-        <v>11.4816198348999</v>
+        <v>11.4816188812256</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>14.4449996948242</v>
       </c>
       <c r="G1315" t="n">
-        <v>11.5375299453735</v>
+        <v>11.5375289916992</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1316" t="n">
-        <v>11.8210763931274</v>
+        <v>11.8210754394531</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G1317" t="n">
-        <v>11.7132482528687</v>
+        <v>11.7132472991943</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1320" t="n">
-        <v>11.72523021698</v>
+        <v>11.7252292633057</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1322" t="n">
-        <v>11.5335369110107</v>
+        <v>11.5335359573364</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>14.625</v>
       </c>
       <c r="G1324" t="n">
-        <v>11.6812992095947</v>
+        <v>11.681300163269</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>11.5015878677368</v>
+        <v>11.5015888214111</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>14.2049999237061</v>
       </c>
       <c r="G1327" t="n">
-        <v>11.3458366394043</v>
+        <v>11.34583568573</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>14.0150003433228</v>
       </c>
       <c r="G1328" t="n">
-        <v>11.1940803527832</v>
+        <v>11.1940793991089</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1331" t="n">
-        <v>11.038330078125</v>
+        <v>11.0383291244507</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G1333" t="n">
-        <v>11.1461563110352</v>
+        <v>11.1461572647095</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G1334" t="n">
-        <v>11.1461563110352</v>
+        <v>11.1461572647095</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>13.8450002670288</v>
       </c>
       <c r="G1335" t="n">
-        <v>11.0582981109619</v>
+        <v>11.0582971572876</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>13.9849996566772</v>
       </c>
       <c r="G1337" t="n">
-        <v>11.1701183319092</v>
+        <v>11.1701173782349</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>14.085000038147</v>
       </c>
       <c r="G1339" t="n">
-        <v>11.2499914169312</v>
+        <v>11.2499895095825</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>14.2250003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>11.3618106842041</v>
+        <v>11.3618116378784</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>13.9049997329712</v>
       </c>
       <c r="G1346" t="n">
-        <v>11.1062202453613</v>
+        <v>11.1062211990356</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1347" t="n">
-        <v>11.0303421020508</v>
+        <v>11.0303430557251</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.0503101348877</v>
+        <v>11.0503091812134</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G1351" t="n">
-        <v>11.4656438827515</v>
+        <v>11.4656448364258</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G1352" t="n">
-        <v>11.4656438827515</v>
+        <v>11.4656448364258</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>13.9049997329712</v>
       </c>
       <c r="G1360" t="n">
-        <v>11.1062202453613</v>
+        <v>11.1062211990356</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1361" t="n">
-        <v>11.2220344543457</v>
+        <v>11.22203540802</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>14.1850004196167</v>
       </c>
       <c r="G1363" t="n">
-        <v>11.3298635482788</v>
+        <v>11.3298625946045</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1364" t="n">
-        <v>11.1501502990723</v>
+        <v>11.1501512527466</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1365" t="n">
-        <v>11.0503101348877</v>
+        <v>11.0503091812134</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.8865718841553</v>
+        <v>10.8865728378296</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1369" t="n">
-        <v>10.9904050827026</v>
+        <v>10.9904069900513</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>13.7849998474121</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.0103750228882</v>
+        <v>11.0103740692139</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1371" t="n">
-        <v>10.910532951355</v>
+        <v>10.9105339050293</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1372" t="n">
-        <v>10.9424829483032</v>
+        <v>10.9424819946289</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G1373" t="n">
-        <v>10.9185199737549</v>
+        <v>10.9185209274292</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1374" t="n">
-        <v>10.9704370498657</v>
+        <v>10.97043800354</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.9664430618286</v>
+        <v>10.9664440155029</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1381" t="n">
-        <v>11.1341762542725</v>
+        <v>11.1341753005981</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1383" t="n">
-        <v>11.1661243438721</v>
+        <v>11.1661233901978</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G1384" t="n">
-        <v>11.1221942901611</v>
+        <v>11.1221952438354</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1386" t="n">
-        <v>11.4896068572998</v>
+        <v>11.4896078109741</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G1388" t="n">
-        <v>11.2100534439087</v>
+        <v>11.210054397583</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>14.5</v>
       </c>
       <c r="G1390" t="n">
-        <v>11.5814599990845</v>
+        <v>11.5814590454102</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.6533441543579</v>
+        <v>11.6533451080322</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1393" t="n">
-        <v>11.8210763931274</v>
+        <v>11.8210754394531</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G1406" t="n">
-        <v>11.5934410095215</v>
+        <v>11.5934400558472</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G1408" t="n">
-        <v>11.4656438827515</v>
+        <v>11.4656448364258</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.0503101348877</v>
+        <v>11.0503091812134</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543031692505</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>14.7349996566772</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.7691593170166</v>
+        <v>11.7691583633423</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.8769865036011</v>
+        <v>11.8769874572754</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>12.2443990707397</v>
+        <v>12.2443971633911</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1419" t="n">
-        <v>11.8210763931274</v>
+        <v>11.8210754394531</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1420" t="n">
-        <v>11.9129285812378</v>
+        <v>11.9129295349121</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1425" t="n">
-        <v>12.9552593231201</v>
+        <v>12.9552602767944</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G1426" t="n">
-        <v>13.0910415649414</v>
+        <v>13.0910425186157</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1427" t="n">
-        <v>12.9712352752686</v>
+        <v>12.9712343215942</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1428" t="n">
-        <v>12.9233112335205</v>
+        <v>12.9233121871948</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>16.0949993133545</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.8554191589355</v>
+        <v>12.8554201126099</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>15.9449996948242</v>
       </c>
       <c r="G1430" t="n">
-        <v>12.7356119155884</v>
+        <v>12.7356109619141</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>16.25</v>
       </c>
       <c r="G1431" t="n">
-        <v>12.9792213439941</v>
+        <v>12.9792222976685</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>15.8950004577637</v>
       </c>
       <c r="G1435" t="n">
-        <v>12.6956768035889</v>
+        <v>12.6956777572632</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G1441" t="n">
-        <v>12.3881673812866</v>
+        <v>12.3881683349609</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>15.5150003433228</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.3921613693237</v>
+        <v>12.392162322998</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>15.3850002288818</v>
       </c>
       <c r="G1443" t="n">
-        <v>12.2883281707764</v>
+        <v>12.2883291244507</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1446" t="n">
-        <v>12.356219291687</v>
+        <v>12.3562183380127</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1448" t="n">
-        <v>12.1086149215698</v>
+        <v>12.1086158752441</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>15.2650003433228</v>
       </c>
       <c r="G1449" t="n">
-        <v>12.1924819946289</v>
+        <v>12.1924829483032</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1452" t="n">
-        <v>12.7475929260254</v>
+        <v>12.7475919723511</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>15.1850004196167</v>
       </c>
       <c r="G1454" t="n">
-        <v>12.1285839080811</v>
+        <v>12.1285829544067</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>15.6850004196167</v>
       </c>
       <c r="G1456" t="n">
-        <v>12.5279455184937</v>
+        <v>12.5279445648193</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G1457" t="n">
-        <v>12.7515869140625</v>
+        <v>12.7515859603882</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>15.6049995422363</v>
       </c>
       <c r="G1460" t="n">
-        <v>12.4640474319458</v>
+        <v>12.4640464782715</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>15.5249996185303</v>
       </c>
       <c r="G1461" t="n">
-        <v>12.4001483917236</v>
+        <v>12.4001493453979</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1462" t="n">
-        <v>12.5159645080566</v>
+        <v>12.5159635543823</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>15.2449998855591</v>
       </c>
       <c r="G1464" t="n">
-        <v>12.1765069961548</v>
+        <v>12.1765060424805</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1465" t="n">
-        <v>12.4920024871826</v>
+        <v>12.4920015335083</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>15.8050003051758</v>
       </c>
       <c r="G1468" t="n">
-        <v>12.6237916946411</v>
+        <v>12.6237907409668</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1470" t="n">
-        <v>12.7156448364258</v>
+        <v>12.7156438827515</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1474" t="n">
-        <v>13.1469526290894</v>
+        <v>13.146951675415</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G1475" t="n">
-        <v>13.0910415649414</v>
+        <v>13.0910425186157</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G1478" t="n">
-        <v>13.2867298126221</v>
+        <v>13.2867288589478</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>16.7849998474121</v>
       </c>
       <c r="G1479" t="n">
-        <v>13.4065380096436</v>
+        <v>13.4065361022949</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G1480" t="n">
-        <v>13.4624471664429</v>
+        <v>13.4624481201172</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1481" t="n">
-        <v>13.122992515564</v>
+        <v>13.1229915618896</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>13.2188377380371</v>
+        <v>13.2188367843628</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1483" t="n">
-        <v>13.1908826828003</v>
+        <v>13.1908836364746</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1484" t="n">
-        <v>13.4864101409912</v>
+        <v>13.4864110946655</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>16.9850006103516</v>
       </c>
       <c r="G1486" t="n">
-        <v>13.5662832260132</v>
+        <v>13.5662841796875</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1487" t="n">
-        <v>13.4983901977539</v>
+        <v>13.4983911514282</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980714797974</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1491" t="n">
-        <v>13.6341743469238</v>
+        <v>13.6341724395752</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>17.2350006103516</v>
       </c>
       <c r="G1492" t="n">
-        <v>13.765962600708</v>
+        <v>13.7659616470337</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>17.25</v>
       </c>
       <c r="G1496" t="n">
-        <v>13.7779426574707</v>
+        <v>13.777943611145</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1497" t="n">
-        <v>13.6900835037231</v>
+        <v>13.6900844573975</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1498" t="n">
-        <v>13.6022243499756</v>
+        <v>13.6022253036499</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>16.7049999237061</v>
       </c>
       <c r="G1499" t="n">
-        <v>13.7712211608887</v>
+        <v>13.771222114563</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1500" t="n">
-        <v>13.3136911392212</v>
+        <v>13.3136920928955</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>13.1488161087036</v>
+        <v>13.1488170623779</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>15.5550003051758</v>
       </c>
       <c r="G1504" t="n">
-        <v>12.8231887817383</v>
+        <v>12.823187828064</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>12.769603729248</v>
+        <v>12.7696027755737</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>12.9386014938354</v>
+        <v>12.9386005401611</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="n">
-        <v>12.695408821106</v>
+        <v>12.6954097747803</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>16.2450008392334</v>
       </c>
       <c r="G1510" t="n">
-        <v>13.3920087814331</v>
+        <v>13.3920097351074</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1512" t="n">
-        <v>12.950966835022</v>
+        <v>12.9509658813477</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G1513" t="n">
-        <v>12.9221143722534</v>
+        <v>12.9221134185791</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G1515" t="n">
-        <v>12.9386014938354</v>
+        <v>12.9386005401611</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G1516" t="n">
-        <v>12.9468441009521</v>
+        <v>12.9468450546265</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1519" t="n">
-        <v>12.291464805603</v>
+        <v>12.2914657592773</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1522" t="n">
-        <v>12.4316091537476</v>
+        <v>12.4316082000732</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>15.7550001144409</v>
       </c>
       <c r="G1528" t="n">
-        <v>12.9880628585815</v>
+        <v>12.9880638122559</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1529" t="n">
-        <v>13.1776695251465</v>
+        <v>13.1776704788208</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>15.4849996566772</v>
       </c>
       <c r="G1530" t="n">
-        <v>12.7654819488525</v>
+        <v>12.7654809951782</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>15.6049995422363</v>
       </c>
       <c r="G1531" t="n">
-        <v>12.8644065856934</v>
+        <v>12.8644075393677</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1532" t="n">
-        <v>12.5305337905884</v>
+        <v>12.5305328369141</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>13.3384237289429</v>
+        <v>13.3384246826172</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1540" t="n">
-        <v>12.703652381897</v>
+        <v>12.7036542892456</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1541" t="n">
-        <v>12.6459474563599</v>
+        <v>12.6459465026855</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>14.9049997329712</v>
       </c>
       <c r="G1542" t="n">
-        <v>12.2873430252075</v>
+        <v>12.2873420715332</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1543" t="n">
-        <v>11.9040079116821</v>
+        <v>11.9040069580078</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1545" t="n">
-        <v>12.0276641845703</v>
+        <v>12.0276651382446</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G1548" t="n">
-        <v>12.3780241012573</v>
+        <v>12.3780250549316</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1549" t="n">
-        <v>12.4233665466309</v>
+        <v>12.4233655929565</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G1550" t="n">
-        <v>12.2543678283691</v>
+        <v>12.2543668746948</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1551" t="n">
-        <v>12.2955856323242</v>
+        <v>12.2955865859985</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1555" t="n">
-        <v>13.1240863800049</v>
+        <v>13.1240854263306</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G1556" t="n">
-        <v>12.9468441009521</v>
+        <v>12.9468450546265</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1557" t="n">
-        <v>12.769603729248</v>
+        <v>12.7696027755737</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>13.1776695251465</v>
+        <v>13.1776704788208</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G1562" t="n">
-        <v>12.9138689041138</v>
+        <v>12.9138698577881</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>15.5550003051758</v>
       </c>
       <c r="G1563" t="n">
-        <v>12.8231887817383</v>
+        <v>12.823187828064</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>14.9250001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>12.3038301467896</v>
+        <v>12.3038311004639</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>14.0450000762939</v>
       </c>
       <c r="G1568" t="n">
-        <v>11.5783777236938</v>
+        <v>11.5783786773682</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1569" t="n">
-        <v>11.590744972229</v>
+        <v>11.5907440185547</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G1570" t="n">
-        <v>11.3970155715942</v>
+        <v>11.3970146179199</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.4695920944214</v>
+        <v>10.4695911407471</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1575" t="n">
-        <v>10.8982677459717</v>
+        <v>10.8982667922974</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>13.8950004577637</v>
       </c>
       <c r="G1578" t="n">
-        <v>11.45472240448</v>
+        <v>11.4547214508057</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1581" t="n">
-        <v>11.5660133361816</v>
+        <v>11.5660123825073</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1583" t="n">
-        <v>11.5824995040894</v>
+        <v>11.5825004577637</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1585" t="n">
-        <v>11.5824995040894</v>
+        <v>11.5825004577637</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1588" t="n">
-        <v>11.8586673736572</v>
+        <v>11.8586683273315</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G1590" t="n">
-        <v>11.3970155715942</v>
+        <v>11.3970146179199</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1592" t="n">
-        <v>11.8545446395874</v>
+        <v>11.8545436859131</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1593" t="n">
-        <v>11.8092050552368</v>
+        <v>11.8092031478882</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>13.9650001525879</v>
       </c>
       <c r="G1594" t="n">
-        <v>11.5124292373657</v>
+        <v>11.5124282836914</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G1595" t="n">
-        <v>11.677303314209</v>
+        <v>11.6773042678833</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G1596" t="n">
-        <v>11.8627891540527</v>
+        <v>11.8627901077271</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>14.2749996185303</v>
       </c>
       <c r="G1597" t="n">
-        <v>11.7679853439331</v>
+        <v>11.7679843902588</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G1598" t="n">
-        <v>11.5041856765747</v>
+        <v>11.5041847229004</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G1599" t="n">
-        <v>11.4670867919922</v>
+        <v>11.4670877456665</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>13.9049997329712</v>
       </c>
       <c r="G1600" t="n">
-        <v>11.4629650115967</v>
+        <v>11.462965965271</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1603" t="n">
-        <v>11.6237192153931</v>
+        <v>11.6237201690674</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>13.1750001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>10.8611698150635</v>
+        <v>10.8611707687378</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>10.7581233978271</v>
+        <v>10.7581243515015</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>12.9549999237061</v>
       </c>
       <c r="G1613" t="n">
-        <v>10.6798086166382</v>
+        <v>10.6798076629639</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>10.1810598373413</v>
+        <v>10.181058883667</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>12.0050001144409</v>
       </c>
       <c r="G1618" t="n">
-        <v>9.89664936065674</v>
+        <v>9.89664840698242</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>12.375</v>
       </c>
       <c r="G1619" t="n">
-        <v>10.2016696929932</v>
+        <v>10.2016687393188</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1626" t="n">
-        <v>10.7279815673828</v>
+        <v>10.7279806137085</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G1629" t="n">
-        <v>11.1150732040405</v>
+        <v>11.1150722503662</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1630" t="n">
-        <v>11.263955116272</v>
+        <v>11.2639541625977</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>13.0050001144409</v>
       </c>
       <c r="G1635" t="n">
-        <v>11.0640287399292</v>
+        <v>11.0640277862549</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1638" t="n">
-        <v>10.243052482605</v>
+        <v>10.2430534362793</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G1642" t="n">
-        <v>9.38379287719727</v>
+        <v>9.38379383087158</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G1643" t="n">
-        <v>9.09453678131104</v>
+        <v>9.09453773498535</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.2221508026123</v>
+        <v>9.22215175628662</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1646" t="n">
-        <v>9.55394458770752</v>
+        <v>9.5539436340332</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.226037979126</v>
+        <v>10.2260389328003</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G1655" t="n">
-        <v>9.84745216369629</v>
+        <v>9.84745311737061</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>11.2950000762939</v>
       </c>
       <c r="G1656" t="n">
-        <v>9.60924243927002</v>
+        <v>9.60924339294434</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G1657" t="n">
-        <v>9.83894443511963</v>
+        <v>9.83894538879395</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>11.7049999237061</v>
       </c>
       <c r="G1667" t="n">
-        <v>9.95805072784424</v>
+        <v>9.95805168151855</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>11.4250001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>9.71984004974365</v>
+        <v>9.71984100341797</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1672" t="n">
-        <v>9.6305103302002</v>
+        <v>9.63051128387451</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>12.0550003051758</v>
       </c>
       <c r="G1676" t="n">
-        <v>10.2558145523071</v>
+        <v>10.2558155059814</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1677" t="n">
-        <v>10.5918617248535</v>
+        <v>10.5918607711792</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1678" t="n">
-        <v>10.4812622070312</v>
+        <v>10.4812631607056</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1681" t="n">
-        <v>10.1664848327637</v>
+        <v>10.166485786438</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>12.3450002670288</v>
       </c>
       <c r="G1682" t="n">
-        <v>10.5025339126587</v>
+        <v>10.5025329589844</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1693" t="n">
-        <v>9.1030445098877</v>
+        <v>9.10304546356201</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>11.1450004577637</v>
       </c>
       <c r="G1698" t="n">
-        <v>9.48163032531738</v>
+        <v>9.4816312789917</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>10.8450002670288</v>
       </c>
       <c r="G1700" t="n">
-        <v>9.22640514373779</v>
+        <v>9.22640419006348</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>12.585000038147</v>
       </c>
       <c r="G1708" t="n">
-        <v>10.7067127227783</v>
+        <v>10.706711769104</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>11.9449996948242</v>
       </c>
       <c r="G1710" t="n">
-        <v>10.1622304916382</v>
+        <v>10.1622314453125</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>12.4750003814697</v>
       </c>
       <c r="G1716" t="n">
-        <v>10.613130569458</v>
+        <v>10.6131296157837</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1722" t="n">
-        <v>10.7279815673828</v>
+        <v>10.7279806137085</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1723" t="n">
-        <v>10.5408163070679</v>
+        <v>10.5408153533936</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>11.9250001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>10.1452159881592</v>
+        <v>10.1452169418335</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>12.3649997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>10.5195474624634</v>
+        <v>10.5195465087891</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G1729" t="n">
-        <v>10.8300724029541</v>
+        <v>10.8300714492798</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G1730" t="n">
-        <v>10.817310333252</v>
+        <v>10.8173093795776</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>13.1949996948242</v>
       </c>
       <c r="G1734" t="n">
-        <v>11.2256717681885</v>
+        <v>11.2256708145142</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1735" t="n">
-        <v>11.5191793441772</v>
+        <v>11.5191802978516</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1741" t="n">
-        <v>11.9360485076904</v>
+        <v>11.9360494613647</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>14.2849998474121</v>
       </c>
       <c r="G1744" t="n">
-        <v>12.1529893875122</v>
+        <v>12.1529903411865</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1749" t="n">
-        <v>12.3529167175293</v>
+        <v>12.3529176712036</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>14.625</v>
       </c>
       <c r="G1750" t="n">
-        <v>12.4422464370728</v>
+        <v>12.4422473907471</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.4720220565796</v>
+        <v>12.4720230102539</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>14.7550001144409</v>
       </c>
       <c r="G1752" t="n">
-        <v>12.5528440475464</v>
+        <v>12.5528450012207</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>15</v>
       </c>
       <c r="G1753" t="n">
-        <v>12.7612781524658</v>
+        <v>12.7612791061401</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>15.0349998474121</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.7910537719727</v>
+        <v>12.791054725647</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>12.8888912200928</v>
+        <v>12.8888921737671</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1759" t="n">
-        <v>12.9314279556274</v>
+        <v>12.9314289093018</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G1766" t="n">
-        <v>13.0973253250122</v>
+        <v>13.0973262786865</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1768" t="n">
-        <v>13.169638633728</v>
+        <v>13.1696395874023</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>14.7550001144409</v>
       </c>
       <c r="G1772" t="n">
-        <v>12.5528440475464</v>
+        <v>12.5528450012207</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>15.1149997711182</v>
       </c>
       <c r="G1775" t="n">
-        <v>12.8591136932373</v>
+        <v>12.8591146469116</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1781" t="n">
-        <v>13.3227739334106</v>
+        <v>13.322774887085</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1782" t="n">
-        <v>13.2036695480347</v>
+        <v>13.203670501709</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1784" t="n">
-        <v>13.6630764007568</v>
+        <v>13.6630754470825</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1786" t="n">
-        <v>13.9353151321411</v>
+        <v>13.9353141784668</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1790" t="n">
-        <v>14.233078956604</v>
+        <v>14.2330780029297</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1798" t="n">
-        <v>13.8077030181885</v>
+        <v>13.8077020645142</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>16.3349990844727</v>
       </c>
       <c r="G1803" t="n">
-        <v>13.8970317840576</v>
+        <v>13.8970308303833</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1804" t="n">
-        <v>13.9948701858521</v>
+        <v>13.9948692321777</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G1809" t="n">
-        <v>14.3862152099609</v>
+        <v>14.3862142562866</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1810" t="n">
-        <v>14.3053951263428</v>
+        <v>14.3053941726685</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1812" t="n">
-        <v>13.8077030181885</v>
+        <v>13.8077020645142</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.2245712280273</v>
+        <v>14.224570274353</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>13.9948701858521</v>
+        <v>13.9948692321777</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G1820" t="n">
-        <v>13.4291172027588</v>
+        <v>13.4291181564331</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>15.8050003051758</v>
       </c>
       <c r="G1822" t="n">
-        <v>13.4461345672607</v>
+        <v>13.4461336135864</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>16.0650005340576</v>
       </c>
       <c r="G1823" t="n">
-        <v>13.667329788208</v>
+        <v>13.6673288345337</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1825" t="n">
-        <v>13.6971054077148</v>
+        <v>13.6971044540405</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1826" t="n">
-        <v>13.8162107467651</v>
+        <v>13.8162097930908</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>15.5</v>
       </c>
       <c r="G1831" t="n">
-        <v>13.1866540908813</v>
+        <v>13.1866550445557</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G1832" t="n">
-        <v>12.5826206207275</v>
+        <v>12.5826215744019</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>13.2950000762939</v>
       </c>
       <c r="G1836" t="n">
-        <v>11.3107452392578</v>
+        <v>11.3107461929321</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1839" t="n">
-        <v>11.8594818115234</v>
+        <v>11.8594808578491</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>14.0550003051758</v>
       </c>
       <c r="G1840" t="n">
-        <v>11.9573173522949</v>
+        <v>11.9573183059692</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>14.414999961853</v>
       </c>
       <c r="G1846" t="n">
-        <v>12.2635879516602</v>
+        <v>12.2635889053345</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>13.914999961853</v>
       </c>
       <c r="G1848" t="n">
-        <v>11.8382120132446</v>
+        <v>11.8382129669189</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>14.2650003433228</v>
       </c>
       <c r="G1852" t="n">
-        <v>12.1359758377075</v>
+        <v>12.1359767913818</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>14.8050003051758</v>
       </c>
       <c r="G1855" t="n">
-        <v>12.5953826904297</v>
+        <v>12.5953817367554</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>14.4250001907349</v>
       </c>
       <c r="G1858" t="n">
-        <v>12.2720956802368</v>
+        <v>12.2720966339111</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1865" t="n">
-        <v>11.6808233261108</v>
+        <v>11.6808223724365</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>13.3149995803833</v>
       </c>
       <c r="G1868" t="n">
-        <v>11.3277616500854</v>
+        <v>11.3277606964111</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1870" t="n">
-        <v>11.4426136016846</v>
+        <v>11.4426126480103</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1872" t="n">
-        <v>10.6173830032349</v>
+        <v>10.6173820495605</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1877" t="n">
-        <v>10.6769361495972</v>
+        <v>10.6769351959229</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>22</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>2303421</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>22.5400009155273</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>22.0900001525879</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>22.2099990844727</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>22.1299991607666</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>22.1299991607666</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>21.6599998474121</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>21.5799999237061</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>1913321</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>22.0300006866455</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>21.8400001525879</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>21.8400001525879</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>21.7800006866455</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1873958</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>21.8099994659424</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>21.6000003814697</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>21.2399997711182</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>2022058</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>21.3799991607666</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>20.9200000762939</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>21</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>21.0200004577637</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>1675541</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>21.4599990844727</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>21.2299995422363</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>1094839</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>21.5799999237061</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>21.2399997711182</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>21.4400005340576</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>5.15489435195923</v>
+        <v>5.15489387512207</v>
       </c>
       <c r="H2" t="n">
         <v>1120023</v>
@@ -456,7 +456,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12352609634399</v>
+        <v>5.12352561950684</v>
       </c>
       <c r="H3" t="n">
         <v>1067026</v>
@@ -485,7 +485,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>4.98062515258789</v>
+        <v>4.98062419891357</v>
       </c>
       <c r="H4" t="n">
         <v>1113419</v>
@@ -543,7 +543,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>5.06775999069214</v>
+        <v>5.06775951385498</v>
       </c>
       <c r="H6" t="n">
         <v>1754689</v>
@@ -572,7 +572,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94228553771973</v>
+        <v>4.94228601455688</v>
       </c>
       <c r="H7" t="n">
         <v>1267080</v>
@@ -601,7 +601,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>5.07124519348145</v>
+        <v>5.07124471664429</v>
       </c>
       <c r="H8" t="n">
         <v>1072008</v>
@@ -630,7 +630,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G9" t="n">
-        <v>5.11655473709106</v>
+        <v>5.11655569076538</v>
       </c>
       <c r="H9" t="n">
         <v>884030</v>
@@ -659,7 +659,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G10" t="n">
-        <v>5.00153779983521</v>
+        <v>5.00153732299805</v>
       </c>
       <c r="H10" t="n">
         <v>950617</v>
@@ -688,7 +688,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G11" t="n">
-        <v>4.85863542556763</v>
+        <v>4.85863590240479</v>
       </c>
       <c r="H11" t="n">
         <v>1145452</v>
@@ -804,7 +804,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>4.64254236221313</v>
+        <v>4.64254140853882</v>
       </c>
       <c r="H15" t="n">
         <v>1328854</v>
@@ -833,7 +833,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.78195714950562</v>
+        <v>4.78195762634277</v>
       </c>
       <c r="H16" t="n">
         <v>1223809</v>
@@ -862,7 +862,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G17" t="n">
-        <v>4.78195714950562</v>
+        <v>4.78195762634277</v>
       </c>
       <c r="H17" t="n">
         <v>801131</v>
@@ -891,7 +891,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>4.86560678482056</v>
+        <v>4.8656063079834</v>
       </c>
       <c r="H18" t="n">
         <v>810566</v>
@@ -949,7 +949,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>4.86212110519409</v>
+        <v>4.86212062835693</v>
       </c>
       <c r="H20" t="n">
         <v>774619</v>
@@ -1007,7 +1007,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G22" t="n">
-        <v>4.97365379333496</v>
+        <v>4.9736533164978</v>
       </c>
       <c r="H22" t="n">
         <v>993347</v>
@@ -1036,7 +1036,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>4.9353141784668</v>
+        <v>4.93531465530396</v>
       </c>
       <c r="H23" t="n">
         <v>890820</v>
@@ -1094,7 +1094,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>4.61465883255005</v>
+        <v>4.61465835571289</v>
       </c>
       <c r="H25" t="n">
         <v>1487324</v>
@@ -1123,7 +1123,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>4.56586360931396</v>
+        <v>4.56586313247681</v>
       </c>
       <c r="H26" t="n">
         <v>807599</v>
@@ -1152,7 +1152,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>4.39856481552124</v>
+        <v>4.39856433868408</v>
       </c>
       <c r="H27" t="n">
         <v>1769827</v>
@@ -1181,7 +1181,7 @@
         <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>4.18246984481812</v>
+        <v>4.18247032165527</v>
       </c>
       <c r="H28" t="n">
         <v>4309103</v>
@@ -1210,7 +1210,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G29" t="n">
-        <v>4.29051685333252</v>
+        <v>4.29051733016968</v>
       </c>
       <c r="H29" t="n">
         <v>2729696</v>
@@ -1268,7 +1268,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G31" t="n">
-        <v>4.41250514984131</v>
+        <v>4.41250610351562</v>
       </c>
       <c r="H31" t="n">
         <v>1485710</v>
@@ -1326,7 +1326,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G33" t="n">
-        <v>4.55889225006104</v>
+        <v>4.55889272689819</v>
       </c>
       <c r="H33" t="n">
         <v>1030645</v>
@@ -1413,7 +1413,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G36" t="n">
-        <v>4.53797960281372</v>
+        <v>4.53797912597656</v>
       </c>
       <c r="H36" t="n">
         <v>826666</v>
@@ -1471,7 +1471,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>4.67042541503906</v>
+        <v>4.6704249382019</v>
       </c>
       <c r="H38" t="n">
         <v>635989</v>
@@ -1500,7 +1500,7 @@
         <v>6.75</v>
       </c>
       <c r="G39" t="n">
-        <v>4.70527839660645</v>
+        <v>4.7052788734436</v>
       </c>
       <c r="H39" t="n">
         <v>1611257</v>
@@ -1529,7 +1529,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>4.82378244400024</v>
+        <v>4.82378196716309</v>
       </c>
       <c r="H40" t="n">
         <v>1384817</v>
@@ -1558,7 +1558,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G41" t="n">
-        <v>4.90394639968872</v>
+        <v>4.9039454460144</v>
       </c>
       <c r="H41" t="n">
         <v>1286913</v>
@@ -1587,7 +1587,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>4.91440153121948</v>
+        <v>4.91440200805664</v>
       </c>
       <c r="H42" t="n">
         <v>1229361</v>
@@ -1616,7 +1616,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>4.98062515258789</v>
+        <v>4.98062419891357</v>
       </c>
       <c r="H43" t="n">
         <v>820528</v>
@@ -1645,7 +1645,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>4.9353141784668</v>
+        <v>4.93531465530396</v>
       </c>
       <c r="H44" t="n">
         <v>1499459</v>
@@ -1674,7 +1674,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.97713947296143</v>
+        <v>4.97713899612427</v>
       </c>
       <c r="H45" t="n">
         <v>1200447</v>
@@ -1703,7 +1703,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>4.9353141784668</v>
+        <v>4.93531465530396</v>
       </c>
       <c r="H46" t="n">
         <v>964840</v>
@@ -1761,7 +1761,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>4.66345405578613</v>
+        <v>4.66345453262329</v>
       </c>
       <c r="H48" t="n">
         <v>1329087</v>
@@ -1790,7 +1790,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>4.60420274734497</v>
+        <v>4.60420227050781</v>
       </c>
       <c r="H49" t="n">
         <v>1135132</v>
@@ -1848,7 +1848,7 @@
         <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>4.87954807281494</v>
+        <v>4.8795485496521</v>
       </c>
       <c r="H51" t="n">
         <v>1102638</v>
@@ -1877,7 +1877,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.90046119689941</v>
+        <v>4.90046072006226</v>
       </c>
       <c r="H52" t="n">
         <v>1406683</v>
@@ -1906,7 +1906,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.91440153121948</v>
+        <v>4.91440200805664</v>
       </c>
       <c r="H53" t="n">
         <v>813066</v>
@@ -1935,7 +1935,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>4.86212110519409</v>
+        <v>4.86212062835693</v>
       </c>
       <c r="H54" t="n">
         <v>720606</v>
@@ -1964,7 +1964,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>4.82029724121094</v>
+        <v>4.82029676437378</v>
       </c>
       <c r="H55" t="n">
         <v>882262</v>
@@ -1993,7 +1993,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>4.80635452270508</v>
+        <v>4.80635595321655</v>
       </c>
       <c r="H56" t="n">
         <v>2597623</v>
@@ -2022,7 +2022,7 @@
         <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>4.87954807281494</v>
+        <v>4.8795485496521</v>
       </c>
       <c r="H57" t="n">
         <v>1525752</v>
@@ -2051,7 +2051,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>4.9353141784668</v>
+        <v>4.93531465530396</v>
       </c>
       <c r="H58" t="n">
         <v>1306433</v>
@@ -2080,7 +2080,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>4.98062515258789</v>
+        <v>4.98062419891357</v>
       </c>
       <c r="H59" t="n">
         <v>1309079</v>
@@ -2109,7 +2109,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>4.99805164337158</v>
+        <v>4.99805212020874</v>
       </c>
       <c r="H60" t="n">
         <v>1297200</v>
@@ -2167,7 +2167,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>5.15838003158569</v>
+        <v>5.15837955474854</v>
       </c>
       <c r="H62" t="n">
         <v>3573879</v>
@@ -2196,7 +2196,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.15838003158569</v>
+        <v>5.15837955474854</v>
       </c>
       <c r="H63" t="n">
         <v>7332824</v>
@@ -2254,7 +2254,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.93879985809326</v>
+        <v>4.93880081176758</v>
       </c>
       <c r="H65" t="n">
         <v>1641462</v>
@@ -2283,7 +2283,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G66" t="n">
-        <v>4.83423709869385</v>
+        <v>4.83423805236816</v>
       </c>
       <c r="H66" t="n">
         <v>2726318</v>
@@ -2312,7 +2312,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G67" t="n">
-        <v>4.79589891433716</v>
+        <v>4.79589939117432</v>
       </c>
       <c r="H67" t="n">
         <v>1700880</v>
@@ -2370,7 +2370,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>4.76453018188477</v>
+        <v>4.76453113555908</v>
       </c>
       <c r="H69" t="n">
         <v>1610753</v>
@@ -2399,7 +2399,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.78892850875854</v>
+        <v>4.78892755508423</v>
       </c>
       <c r="H70" t="n">
         <v>1226391</v>
@@ -2457,7 +2457,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>4.83772277832031</v>
+        <v>4.83772373199463</v>
       </c>
       <c r="H72" t="n">
         <v>1303785</v>
@@ -2486,7 +2486,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G73" t="n">
-        <v>4.92485952377319</v>
+        <v>4.92485904693604</v>
       </c>
       <c r="H73" t="n">
         <v>1466819</v>
@@ -2544,7 +2544,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>5.13792419433594</v>
+        <v>5.1379246711731</v>
       </c>
       <c r="H75" t="n">
         <v>2392811</v>
@@ -2602,7 +2602,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.08730459213257</v>
+        <v>5.08730411529541</v>
       </c>
       <c r="H77" t="n">
         <v>1355061</v>
@@ -2631,7 +2631,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>5.07645750045776</v>
+        <v>5.07645797729492</v>
       </c>
       <c r="H78" t="n">
         <v>1460707</v>
@@ -2660,7 +2660,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.03668451309204</v>
+        <v>5.03668546676636</v>
       </c>
       <c r="H79" t="n">
         <v>661831</v>
@@ -2689,7 +2689,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G80" t="n">
-        <v>4.97521829605103</v>
+        <v>4.97521781921387</v>
       </c>
       <c r="H80" t="n">
         <v>902966</v>
@@ -2776,7 +2776,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G83" t="n">
-        <v>5.19216060638428</v>
+        <v>5.19216012954712</v>
       </c>
       <c r="H83" t="n">
         <v>1315384</v>
@@ -2805,7 +2805,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>5.06922674179077</v>
+        <v>5.06922578811646</v>
       </c>
       <c r="H84" t="n">
         <v>1187575</v>
@@ -2834,7 +2834,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.0619945526123</v>
+        <v>5.06199502944946</v>
       </c>
       <c r="H85" t="n">
         <v>766651</v>
@@ -2863,7 +2863,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G86" t="n">
-        <v>4.87036323547363</v>
+        <v>4.87036228179932</v>
       </c>
       <c r="H86" t="n">
         <v>1509534</v>
@@ -2892,7 +2892,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G87" t="n">
-        <v>4.91013526916504</v>
+        <v>4.91013479232788</v>
       </c>
       <c r="H87" t="n">
         <v>881025</v>
@@ -2979,7 +2979,7 @@
         <v>6.375</v>
       </c>
       <c r="G90" t="n">
-        <v>4.61003065109253</v>
+        <v>4.61003112792969</v>
       </c>
       <c r="H90" t="n">
         <v>1317961</v>
@@ -3037,7 +3037,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>4.58833599090576</v>
+        <v>4.58833646774292</v>
       </c>
       <c r="H92" t="n">
         <v>1279308</v>
@@ -3066,7 +3066,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G93" t="n">
-        <v>4.52686977386475</v>
+        <v>4.52686929702759</v>
       </c>
       <c r="H93" t="n">
         <v>1100368</v>
@@ -3124,7 +3124,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G95" t="n">
-        <v>4.77996921539307</v>
+        <v>4.77996969223022</v>
       </c>
       <c r="H95" t="n">
         <v>1736284</v>
@@ -3153,7 +3153,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G96" t="n">
-        <v>4.72211837768555</v>
+        <v>4.72211790084839</v>
       </c>
       <c r="H96" t="n">
         <v>1602098</v>
@@ -3182,7 +3182,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G97" t="n">
-        <v>4.77996921539307</v>
+        <v>4.77996969223022</v>
       </c>
       <c r="H97" t="n">
         <v>1260512</v>
@@ -3211,7 +3211,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G98" t="n">
-        <v>4.7257342338562</v>
+        <v>4.72573280334473</v>
       </c>
       <c r="H98" t="n">
         <v>764494</v>
@@ -3240,7 +3240,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G99" t="n">
-        <v>4.59918403625488</v>
+        <v>4.59918355941772</v>
       </c>
       <c r="H99" t="n">
         <v>2047704</v>
@@ -3269,7 +3269,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>4.56302738189697</v>
+        <v>4.56302642822266</v>
       </c>
       <c r="H100" t="n">
         <v>1433539</v>
@@ -3298,7 +3298,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>4.66426658630371</v>
+        <v>4.66426610946655</v>
       </c>
       <c r="H101" t="n">
         <v>1319208</v>
@@ -3414,7 +3414,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G105" t="n">
-        <v>4.83058881759644</v>
+        <v>4.83058929443359</v>
       </c>
       <c r="H105" t="n">
         <v>301436</v>
@@ -3530,7 +3530,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>4.67511415481567</v>
+        <v>4.67511367797852</v>
       </c>
       <c r="H109" t="n">
         <v>863571</v>
@@ -3617,7 +3617,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>4.69680833816528</v>
+        <v>4.69680881500244</v>
       </c>
       <c r="H112" t="n">
         <v>755214</v>
@@ -3646,7 +3646,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G113" t="n">
-        <v>4.62449407577515</v>
+        <v>4.62449359893799</v>
       </c>
       <c r="H113" t="n">
         <v>678152</v>
@@ -3704,7 +3704,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G115" t="n">
-        <v>4.39308786392212</v>
+        <v>4.39308834075928</v>
       </c>
       <c r="H115" t="n">
         <v>1453904</v>
@@ -3733,7 +3733,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G116" t="n">
-        <v>4.27738618850708</v>
+        <v>4.27738571166992</v>
       </c>
       <c r="H116" t="n">
         <v>1300109</v>
@@ -3762,7 +3762,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.28461742401123</v>
+        <v>4.28461694717407</v>
       </c>
       <c r="H117" t="n">
         <v>1066848</v>
@@ -3791,7 +3791,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>4.29184865951538</v>
+        <v>4.29184818267822</v>
       </c>
       <c r="H118" t="n">
         <v>1213762</v>
@@ -3820,7 +3820,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40031957626343</v>
+        <v>4.40032005310059</v>
       </c>
       <c r="H119" t="n">
         <v>1255915</v>
@@ -3878,7 +3878,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.55579519271851</v>
+        <v>4.55579566955566</v>
       </c>
       <c r="H121" t="n">
         <v>919785</v>
@@ -3907,7 +3907,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>4.62810945510864</v>
+        <v>4.6281099319458</v>
       </c>
       <c r="H122" t="n">
         <v>1201249</v>
@@ -3936,7 +3936,7 @@
         <v>6.625</v>
       </c>
       <c r="G123" t="n">
-        <v>4.79081630706787</v>
+        <v>4.79081678390503</v>
       </c>
       <c r="H123" t="n">
         <v>2174412</v>
@@ -3994,7 +3994,7 @@
         <v>5.5</v>
       </c>
       <c r="G125" t="n">
-        <v>3.97728133201599</v>
+        <v>3.97728180885315</v>
       </c>
       <c r="H125" t="n">
         <v>3230849</v>
@@ -4023,7 +4023,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>4.2339973449707</v>
+        <v>4.23399782180786</v>
       </c>
       <c r="H126" t="n">
         <v>1838104</v>
@@ -4139,7 +4139,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.02066993713379</v>
+        <v>4.02067041397095</v>
       </c>
       <c r="H130" t="n">
         <v>1421546</v>
@@ -4168,7 +4168,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>3.94835591316223</v>
+        <v>3.94835543632507</v>
       </c>
       <c r="H131" t="n">
         <v>845896</v>
@@ -4197,7 +4197,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73141312599182</v>
+        <v>3.73141360282898</v>
       </c>
       <c r="H132" t="n">
         <v>3993579</v>
@@ -4226,7 +4226,7 @@
         <v>5.25</v>
       </c>
       <c r="G133" t="n">
-        <v>3.79649615287781</v>
+        <v>3.79649639129639</v>
       </c>
       <c r="H133" t="n">
         <v>2105891</v>
@@ -4429,7 +4429,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G140" t="n">
-        <v>4.07852172851562</v>
+        <v>4.07852077484131</v>
       </c>
       <c r="H140" t="n">
         <v>2842855</v>
@@ -4458,7 +4458,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G141" t="n">
-        <v>4.07852172851562</v>
+        <v>4.07852077484131</v>
       </c>
       <c r="H141" t="n">
         <v>2956609</v>
@@ -4487,7 +4487,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>4.1508355140686</v>
+        <v>4.15083599090576</v>
       </c>
       <c r="H142" t="n">
         <v>2137222</v>
@@ -4632,7 +4632,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>3.944739818573</v>
+        <v>3.94474053382874</v>
       </c>
       <c r="H147" t="n">
         <v>4996048</v>
@@ -4690,7 +4690,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>3.83988499641418</v>
+        <v>3.83988475799561</v>
       </c>
       <c r="H149" t="n">
         <v>1927684</v>
@@ -4719,7 +4719,7 @@
         <v>5.25</v>
       </c>
       <c r="G150" t="n">
-        <v>3.79649615287781</v>
+        <v>3.79649639129639</v>
       </c>
       <c r="H150" t="n">
         <v>2848439</v>
@@ -4806,7 +4806,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>3.79288029670715</v>
+        <v>3.79288053512573</v>
       </c>
       <c r="H153" t="n">
         <v>2240614</v>
@@ -4835,7 +4835,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>3.82903790473938</v>
+        <v>3.8290376663208</v>
       </c>
       <c r="H154" t="n">
         <v>1283102</v>
@@ -4922,7 +4922,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G157" t="n">
-        <v>3.81095838546753</v>
+        <v>3.81095910072327</v>
       </c>
       <c r="H157" t="n">
         <v>1021306</v>
@@ -4951,7 +4951,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G158" t="n">
-        <v>3.80011224746704</v>
+        <v>3.8001115322113</v>
       </c>
       <c r="H158" t="n">
         <v>708270</v>
@@ -4980,7 +4980,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>3.85073232650757</v>
+        <v>3.85073137283325</v>
       </c>
       <c r="H159" t="n">
         <v>1359382</v>
@@ -5009,7 +5009,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>3.79288029670715</v>
+        <v>3.79288053512573</v>
       </c>
       <c r="H160" t="n">
         <v>1368032</v>
@@ -5067,7 +5067,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G162" t="n">
-        <v>3.68440866470337</v>
+        <v>3.68440890312195</v>
       </c>
       <c r="H162" t="n">
         <v>1350688</v>
@@ -5096,7 +5096,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.63378953933716</v>
+        <v>3.63378930091858</v>
       </c>
       <c r="H163" t="n">
         <v>2620713</v>
@@ -5125,7 +5125,7 @@
         <v>5</v>
       </c>
       <c r="G164" t="n">
-        <v>3.61571097373962</v>
+        <v>3.61571025848389</v>
       </c>
       <c r="H164" t="n">
         <v>1813564</v>
@@ -5154,7 +5154,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>3.90135216712952</v>
+        <v>3.90135145187378</v>
       </c>
       <c r="H165" t="n">
         <v>4871992</v>
@@ -5183,7 +5183,7 @@
         <v>5.5</v>
       </c>
       <c r="G166" t="n">
-        <v>3.97728133201599</v>
+        <v>3.97728180885315</v>
       </c>
       <c r="H166" t="n">
         <v>3532873</v>
@@ -5212,7 +5212,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>3.91942977905273</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H167" t="n">
         <v>1361661</v>
@@ -5270,7 +5270,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G169" t="n">
-        <v>3.86519432067871</v>
+        <v>3.86519455909729</v>
       </c>
       <c r="H169" t="n">
         <v>629475</v>
@@ -5357,7 +5357,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G172" t="n">
-        <v>3.98451328277588</v>
+        <v>3.9845130443573</v>
       </c>
       <c r="H172" t="n">
         <v>2769977</v>
@@ -5415,7 +5415,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.94835591316223</v>
+        <v>3.94835543632507</v>
       </c>
       <c r="H174" t="n">
         <v>1218944</v>
@@ -5444,7 +5444,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>3.90496754646301</v>
+        <v>3.90496683120728</v>
       </c>
       <c r="H175" t="n">
         <v>796583</v>
@@ -5502,7 +5502,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H177" t="n">
         <v>2745965</v>
@@ -5531,7 +5531,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H178" t="n">
         <v>1872241</v>
@@ -5560,7 +5560,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>3.76757001876831</v>
+        <v>3.76757025718689</v>
       </c>
       <c r="H179" t="n">
         <v>1730619</v>
@@ -5618,7 +5618,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G181" t="n">
-        <v>3.80011224746704</v>
+        <v>3.8001115322113</v>
       </c>
       <c r="H181" t="n">
         <v>1500707</v>
@@ -5676,7 +5676,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>3.67356157302856</v>
+        <v>3.67356181144714</v>
       </c>
       <c r="H183" t="n">
         <v>1411142</v>
@@ -5705,7 +5705,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.76033902168274</v>
+        <v>3.76033926010132</v>
       </c>
       <c r="H184" t="n">
         <v>1171746</v>
@@ -5734,7 +5734,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G185" t="n">
-        <v>3.75672292709351</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H185" t="n">
         <v>1626816</v>
@@ -5763,7 +5763,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.76757001876831</v>
+        <v>3.76757025718689</v>
       </c>
       <c r="H186" t="n">
         <v>1095288</v>
@@ -5821,7 +5821,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G188" t="n">
-        <v>3.74587607383728</v>
+        <v>3.74587559700012</v>
       </c>
       <c r="H188" t="n">
         <v>1474820</v>
@@ -5850,7 +5850,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66994619369507</v>
+        <v>3.66994595527649</v>
       </c>
       <c r="H189" t="n">
         <v>2099802</v>
@@ -5879,7 +5879,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>3.74226117134094</v>
+        <v>3.74226093292236</v>
       </c>
       <c r="H190" t="n">
         <v>3263669</v>
@@ -5937,7 +5937,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G192" t="n">
-        <v>3.73864507675171</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H192" t="n">
         <v>1453013</v>
@@ -5966,7 +5966,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72779726982117</v>
+        <v>3.72779750823975</v>
       </c>
       <c r="H193" t="n">
         <v>2119783</v>
@@ -5995,7 +5995,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.70971918106079</v>
+        <v>3.70971870422363</v>
       </c>
       <c r="H194" t="n">
         <v>1549911</v>
@@ -6053,7 +6053,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G196" t="n">
-        <v>3.74587607383728</v>
+        <v>3.74587559700012</v>
       </c>
       <c r="H196" t="n">
         <v>1713471</v>
@@ -6082,7 +6082,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>3.73141312599182</v>
+        <v>3.73141360282898</v>
       </c>
       <c r="H197" t="n">
         <v>1836123</v>
@@ -6111,7 +6111,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>3.64825201034546</v>
+        <v>3.6482515335083</v>
       </c>
       <c r="H198" t="n">
         <v>2133006</v>
@@ -6169,7 +6169,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G200" t="n">
-        <v>3.4783136844635</v>
+        <v>3.47831392288208</v>
       </c>
       <c r="H200" t="n">
         <v>6007717</v>
@@ -6256,7 +6256,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>3.73864507675171</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H203" t="n">
         <v>6162802</v>
@@ -6285,7 +6285,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>3.75672292709351</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H204" t="n">
         <v>5488683</v>
@@ -6314,7 +6314,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G205" t="n">
-        <v>3.74226117134094</v>
+        <v>3.74226093292236</v>
       </c>
       <c r="H205" t="n">
         <v>3684581</v>
@@ -6343,7 +6343,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G206" t="n">
-        <v>3.75672292709351</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H206" t="n">
         <v>2084886</v>
@@ -6401,7 +6401,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G208" t="n">
-        <v>3.83265256881714</v>
+        <v>3.83265328407288</v>
       </c>
       <c r="H208" t="n">
         <v>3501461</v>
@@ -6430,7 +6430,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>3.87604165077209</v>
+        <v>3.87604212760925</v>
       </c>
       <c r="H209" t="n">
         <v>2199321</v>
@@ -6459,7 +6459,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G210" t="n">
-        <v>3.81819009780884</v>
+        <v>3.818190574646</v>
       </c>
       <c r="H210" t="n">
         <v>2913261</v>
@@ -6488,7 +6488,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>3.86881017684937</v>
+        <v>3.86881041526794</v>
       </c>
       <c r="H211" t="n">
         <v>2192359</v>
@@ -6517,7 +6517,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.93750858306885</v>
+        <v>3.93750905990601</v>
       </c>
       <c r="H212" t="n">
         <v>2143095</v>
@@ -6546,7 +6546,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.99174404144287</v>
+        <v>3.99174451828003</v>
       </c>
       <c r="H213" t="n">
         <v>3510082</v>
@@ -6575,7 +6575,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G214" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711623191833</v>
       </c>
       <c r="H214" t="n">
         <v>2039874</v>
@@ -6604,7 +6604,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>3.78203320503235</v>
+        <v>3.78203296661377</v>
       </c>
       <c r="H215" t="n">
         <v>1276554</v>
@@ -6662,7 +6662,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>3.69164061546326</v>
+        <v>3.69163966178894</v>
       </c>
       <c r="H217" t="n">
         <v>2605202</v>
@@ -6778,7 +6778,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>3.67356157302856</v>
+        <v>3.67356181144714</v>
       </c>
       <c r="H221" t="n">
         <v>3276707</v>
@@ -6836,7 +6836,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G223" t="n">
-        <v>3.65186786651611</v>
+        <v>3.65186810493469</v>
       </c>
       <c r="H223" t="n">
         <v>2767052</v>
@@ -6894,7 +6894,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G225" t="n">
-        <v>3.5969090461731</v>
+        <v>3.59690833091736</v>
       </c>
       <c r="H225" t="n">
         <v>2042948</v>
@@ -6923,7 +6923,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G226" t="n">
-        <v>3.50579261779785</v>
+        <v>3.50579285621643</v>
       </c>
       <c r="H226" t="n">
         <v>2943006</v>
@@ -6952,7 +6952,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>3.47108268737793</v>
+        <v>3.47108197212219</v>
       </c>
       <c r="H227" t="n">
         <v>2432187</v>
@@ -7039,7 +7039,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G230" t="n">
-        <v>3.40744614601135</v>
+        <v>3.40744519233704</v>
       </c>
       <c r="H230" t="n">
         <v>2323535</v>
@@ -7068,7 +7068,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G231" t="n">
-        <v>3.41033864021301</v>
+        <v>3.41033816337585</v>
       </c>
       <c r="H231" t="n">
         <v>2268934</v>
@@ -7126,7 +7126,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G233" t="n">
-        <v>3.46674346923828</v>
+        <v>3.46674299240112</v>
       </c>
       <c r="H233" t="n">
         <v>1321400</v>
@@ -7184,7 +7184,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G235" t="n">
-        <v>3.45517325401306</v>
+        <v>3.45517301559448</v>
       </c>
       <c r="H235" t="n">
         <v>2082364</v>
@@ -7242,7 +7242,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51013231277466</v>
+        <v>3.51013255119324</v>
       </c>
       <c r="H237" t="n">
         <v>4013855</v>
@@ -7387,7 +7387,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>3.76033902168274</v>
+        <v>3.76033926010132</v>
       </c>
       <c r="H242" t="n">
         <v>3062648</v>
@@ -7416,7 +7416,7 @@
         <v>5.125</v>
       </c>
       <c r="G243" t="n">
-        <v>3.70610308647156</v>
+        <v>3.70610356330872</v>
       </c>
       <c r="H243" t="n">
         <v>2409471</v>
@@ -7474,7 +7474,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.94835591316223</v>
+        <v>3.94835543632507</v>
       </c>
       <c r="H245" t="n">
         <v>6476581</v>
@@ -7532,7 +7532,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G247" t="n">
-        <v>3.98812866210938</v>
+        <v>3.98812818527222</v>
       </c>
       <c r="H247" t="n">
         <v>3264617</v>
@@ -7561,7 +7561,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>3.95197176933289</v>
+        <v>3.95197153091431</v>
       </c>
       <c r="H248" t="n">
         <v>2687315</v>
@@ -7590,7 +7590,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>3.86157894134521</v>
+        <v>3.86157870292664</v>
       </c>
       <c r="H249" t="n">
         <v>1875617</v>
@@ -7648,7 +7648,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>3.96281909942627</v>
+        <v>3.96281886100769</v>
       </c>
       <c r="H251" t="n">
         <v>2343541</v>
@@ -7706,7 +7706,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G253" t="n">
-        <v>3.98451328277588</v>
+        <v>3.9845130443573</v>
       </c>
       <c r="H253" t="n">
         <v>1275566</v>
@@ -7764,7 +7764,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>3.86881017684937</v>
+        <v>3.86881041526794</v>
       </c>
       <c r="H255" t="n">
         <v>1417418</v>
@@ -7793,7 +7793,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H256" t="n">
         <v>989625</v>
@@ -7880,7 +7880,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>3.93750858306885</v>
+        <v>3.93750905990601</v>
       </c>
       <c r="H259" t="n">
         <v>2238448</v>
@@ -7967,7 +7967,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>3.99897599220276</v>
+        <v>3.99897646903992</v>
       </c>
       <c r="H262" t="n">
         <v>2114774</v>
@@ -8054,7 +8054,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>3.99536037445068</v>
+        <v>3.99535989761353</v>
       </c>
       <c r="H265" t="n">
         <v>1848308</v>
@@ -8083,7 +8083,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>3.90496754646301</v>
+        <v>3.90496683120728</v>
       </c>
       <c r="H266" t="n">
         <v>1253458</v>
@@ -8112,7 +8112,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>3.99174404144287</v>
+        <v>3.99174451828003</v>
       </c>
       <c r="H267" t="n">
         <v>1773147</v>
@@ -8199,7 +8199,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.99174404144287</v>
+        <v>3.99174451828003</v>
       </c>
       <c r="H270" t="n">
         <v>1825982</v>
@@ -8228,7 +8228,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G271" t="n">
-        <v>4.0279016494751</v>
+        <v>4.02790117263794</v>
       </c>
       <c r="H271" t="n">
         <v>2977261</v>
@@ -8257,7 +8257,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G272" t="n">
-        <v>4.06405830383301</v>
+        <v>4.06405878067017</v>
       </c>
       <c r="H272" t="n">
         <v>3193803</v>
@@ -8315,7 +8315,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>4.02066993713379</v>
+        <v>4.02067041397095</v>
       </c>
       <c r="H274" t="n">
         <v>2581220</v>
@@ -8431,7 +8431,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>4.02066993713379</v>
+        <v>4.02067041397095</v>
       </c>
       <c r="H278" t="n">
         <v>2796328</v>
@@ -8576,7 +8576,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G283" t="n">
-        <v>3.86519432067871</v>
+        <v>3.86519455909729</v>
       </c>
       <c r="H283" t="n">
         <v>2735014</v>
@@ -8634,7 +8634,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G285" t="n">
-        <v>3.96281909942627</v>
+        <v>3.96281886100769</v>
       </c>
       <c r="H285" t="n">
         <v>1908662</v>
@@ -8663,7 +8663,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.97366642951965</v>
+        <v>3.97366666793823</v>
       </c>
       <c r="H286" t="n">
         <v>1319086</v>
@@ -8692,7 +8692,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G287" t="n">
-        <v>3.9121994972229</v>
+        <v>3.91219830513</v>
       </c>
       <c r="H287" t="n">
         <v>1173142</v>
@@ -8750,7 +8750,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>3.96281909942627</v>
+        <v>3.96281886100769</v>
       </c>
       <c r="H289" t="n">
         <v>2102413</v>
@@ -8837,7 +8837,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>3.91942977905273</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H292" t="n">
         <v>2376919</v>
@@ -8895,7 +8895,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>3.91942977905273</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H294" t="n">
         <v>1953366</v>
@@ -8953,7 +8953,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.90496754646301</v>
+        <v>3.90496683120728</v>
       </c>
       <c r="H296" t="n">
         <v>2215104</v>
@@ -8982,7 +8982,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.87604165077209</v>
+        <v>3.87604212760925</v>
       </c>
       <c r="H297" t="n">
         <v>2992561</v>
@@ -9011,7 +9011,7 @@
         <v>5.375</v>
       </c>
       <c r="G298" t="n">
-        <v>3.8868887424469</v>
+        <v>3.88688898086548</v>
       </c>
       <c r="H298" t="n">
         <v>6414207</v>
@@ -9040,7 +9040,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>3.90496754646301</v>
+        <v>3.90496683120728</v>
       </c>
       <c r="H299" t="n">
         <v>2120956</v>
@@ -9069,7 +9069,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G300" t="n">
-        <v>3.98089671134949</v>
+        <v>3.98089718818665</v>
       </c>
       <c r="H300" t="n">
         <v>2265275</v>
@@ -9156,7 +9156,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>4.14360427856445</v>
+        <v>4.14360475540161</v>
       </c>
       <c r="H303" t="n">
         <v>2285686</v>
@@ -9185,7 +9185,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>4.1508355140686</v>
+        <v>4.15083599090576</v>
       </c>
       <c r="H304" t="n">
         <v>1601707</v>
@@ -9214,7 +9214,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G305" t="n">
-        <v>4.17252969741821</v>
+        <v>4.17253017425537</v>
       </c>
       <c r="H305" t="n">
         <v>1549143</v>
@@ -9272,7 +9272,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30269527435303</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H307" t="n">
         <v>2406004</v>
@@ -9301,7 +9301,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>4.30269527435303</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H308" t="n">
         <v>1384487</v>
@@ -9330,7 +9330,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.28100156784058</v>
+        <v>4.28100109100342</v>
       </c>
       <c r="H309" t="n">
         <v>1381742</v>
@@ -9359,7 +9359,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>4.30269527435303</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H310" t="n">
         <v>1166357</v>
@@ -9417,7 +9417,7 @@
         <v>6.25</v>
       </c>
       <c r="G312" t="n">
-        <v>4.51963806152344</v>
+        <v>4.5196385383606</v>
       </c>
       <c r="H312" t="n">
         <v>11461676</v>
@@ -9446,7 +9446,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>4.54856395721436</v>
+        <v>4.5485634803772</v>
       </c>
       <c r="H313" t="n">
         <v>2788421</v>
@@ -9504,7 +9504,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.49794435501099</v>
+        <v>4.49794387817383</v>
       </c>
       <c r="H315" t="n">
         <v>1899424</v>
@@ -9562,7 +9562,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.66426658630371</v>
+        <v>4.66426610946655</v>
       </c>
       <c r="H317" t="n">
         <v>2928708</v>
@@ -9620,7 +9620,7 @@
         <v>6.44500017166138</v>
       </c>
       <c r="G319" t="n">
-        <v>4.66065120697021</v>
+        <v>4.66065073013306</v>
       </c>
       <c r="H319" t="n">
         <v>1606012</v>
@@ -9765,7 +9765,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G324" t="n">
-        <v>4.62087774276733</v>
+        <v>4.62087821960449</v>
       </c>
       <c r="H324" t="n">
         <v>2138251</v>
@@ -9794,7 +9794,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.55218029022217</v>
+        <v>4.55217981338501</v>
       </c>
       <c r="H325" t="n">
         <v>2599522</v>
@@ -9823,7 +9823,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G326" t="n">
-        <v>4.55218029022217</v>
+        <v>4.55217981338501</v>
       </c>
       <c r="H326" t="n">
         <v>2329372</v>
@@ -9852,7 +9852,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>4.55579519271851</v>
+        <v>4.55579566955566</v>
       </c>
       <c r="H327" t="n">
         <v>2299424</v>
@@ -9910,7 +9910,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G329" t="n">
-        <v>4.59918403625488</v>
+        <v>4.59918355941772</v>
       </c>
       <c r="H329" t="n">
         <v>2211159</v>
@@ -9997,7 +9997,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>4.6425724029541</v>
+        <v>4.64257287979126</v>
       </c>
       <c r="H332" t="n">
         <v>1809308</v>
@@ -10026,7 +10026,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G333" t="n">
-        <v>4.72211837768555</v>
+        <v>4.72211790084839</v>
       </c>
       <c r="H333" t="n">
         <v>1861825</v>
@@ -10084,7 +10084,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G335" t="n">
-        <v>4.59918403625488</v>
+        <v>4.59918355941772</v>
       </c>
       <c r="H335" t="n">
         <v>3738102</v>
@@ -10113,7 +10113,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G336" t="n">
-        <v>4.88285064697266</v>
+        <v>4.88285112380981</v>
       </c>
       <c r="H336" t="n">
         <v>4467194</v>
@@ -10171,7 +10171,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G338" t="n">
-        <v>4.91310834884644</v>
+        <v>4.91310930252075</v>
       </c>
       <c r="H338" t="n">
         <v>1812525</v>
@@ -10229,7 +10229,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>4.93958425521851</v>
+        <v>4.93958473205566</v>
       </c>
       <c r="H340" t="n">
         <v>2188783</v>
@@ -10258,7 +10258,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G341" t="n">
-        <v>4.97740602493286</v>
+        <v>4.97740650177002</v>
       </c>
       <c r="H341" t="n">
         <v>1985770</v>
@@ -10287,7 +10287,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.91310834884644</v>
+        <v>4.91310930252075</v>
       </c>
       <c r="H342" t="n">
         <v>1543013</v>
@@ -10316,7 +10316,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>5.04170370101929</v>
+        <v>5.0417046546936</v>
       </c>
       <c r="H343" t="n">
         <v>3358984</v>
@@ -10345,7 +10345,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13625955581665</v>
+        <v>5.13626003265381</v>
       </c>
       <c r="H344" t="n">
         <v>2148000</v>
@@ -10374,7 +10374,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.1438250541687</v>
+        <v>5.14382457733154</v>
       </c>
       <c r="H345" t="n">
         <v>2913934</v>
@@ -10432,7 +10432,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>5.1438250541687</v>
+        <v>5.14382457733154</v>
       </c>
       <c r="H347" t="n">
         <v>2197856</v>
@@ -10461,7 +10461,7 @@
         <v>6.625</v>
       </c>
       <c r="G348" t="n">
-        <v>5.01144599914551</v>
+        <v>5.01144647598267</v>
       </c>
       <c r="H348" t="n">
         <v>2180864</v>
@@ -10490,7 +10490,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>5.08709049224854</v>
+        <v>5.08709096908569</v>
       </c>
       <c r="H349" t="n">
         <v>2037566</v>
@@ -10519,7 +10519,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>5.00766372680664</v>
+        <v>5.0076642036438</v>
       </c>
       <c r="H350" t="n">
         <v>2559502</v>
@@ -10548,7 +10548,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>5.030357837677</v>
+        <v>5.03035736083984</v>
       </c>
       <c r="H351" t="n">
         <v>2299129</v>
@@ -10606,7 +10606,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.96606016159058</v>
+        <v>4.96605968475342</v>
       </c>
       <c r="H353" t="n">
         <v>2522783</v>
@@ -10635,7 +10635,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>5.09465551376343</v>
+        <v>5.09465503692627</v>
       </c>
       <c r="H354" t="n">
         <v>2760019</v>
@@ -10693,7 +10693,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>5.13625955581665</v>
+        <v>5.13626003265381</v>
       </c>
       <c r="H356" t="n">
         <v>1253175</v>
@@ -10722,7 +10722,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>5.1702995300293</v>
+        <v>5.17030000686646</v>
       </c>
       <c r="H357" t="n">
         <v>1872012</v>
@@ -10751,7 +10751,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>5.15138864517212</v>
+        <v>5.15138912200928</v>
       </c>
       <c r="H358" t="n">
         <v>1066471</v>
@@ -10780,7 +10780,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G359" t="n">
-        <v>5.18542814254761</v>
+        <v>5.18542861938477</v>
       </c>
       <c r="H359" t="n">
         <v>1621300</v>
@@ -10838,7 +10838,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>5.02657556533813</v>
+        <v>5.02657508850098</v>
       </c>
       <c r="H361" t="n">
         <v>1407225</v>
@@ -10867,7 +10867,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G362" t="n">
-        <v>5.06061506271362</v>
+        <v>5.06061553955078</v>
       </c>
       <c r="H362" t="n">
         <v>1677680</v>
@@ -10954,7 +10954,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.05683326721191</v>
+        <v>5.05683374404907</v>
       </c>
       <c r="H365" t="n">
         <v>857551</v>
@@ -11012,7 +11012,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>5.23837995529175</v>
+        <v>5.23838043212891</v>
       </c>
       <c r="H367" t="n">
         <v>2803808</v>
@@ -11041,7 +11041,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>5.40858030319214</v>
+        <v>5.40857982635498</v>
       </c>
       <c r="H368" t="n">
         <v>3520150</v>
@@ -11070,7 +11070,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>5.37075757980347</v>
+        <v>5.37075710296631</v>
       </c>
       <c r="H369" t="n">
         <v>2325569</v>
@@ -11128,7 +11128,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>5.42370843887329</v>
+        <v>5.42370891571045</v>
       </c>
       <c r="H371" t="n">
         <v>1836918</v>
@@ -11157,7 +11157,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G372" t="n">
-        <v>5.41614437103271</v>
+        <v>5.41614484786987</v>
       </c>
       <c r="H372" t="n">
         <v>2245553</v>
@@ -11186,7 +11186,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>5.30267763137817</v>
+        <v>5.30267810821533</v>
       </c>
       <c r="H373" t="n">
         <v>1843445</v>
@@ -11215,7 +11215,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.33293533325195</v>
+        <v>5.33293485641479</v>
       </c>
       <c r="H374" t="n">
         <v>2246270</v>
@@ -11244,7 +11244,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G375" t="n">
-        <v>5.41236162185669</v>
+        <v>5.41236257553101</v>
       </c>
       <c r="H375" t="n">
         <v>1237025</v>
@@ -11273,7 +11273,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.34806442260742</v>
+        <v>5.34806489944458</v>
       </c>
       <c r="H376" t="n">
         <v>1253710</v>
@@ -11302,7 +11302,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G377" t="n">
-        <v>5.29889535903931</v>
+        <v>5.29889583587646</v>
       </c>
       <c r="H377" t="n">
         <v>1760770</v>
@@ -11331,7 +11331,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G378" t="n">
-        <v>5.21190404891968</v>
+        <v>5.21190357208252</v>
       </c>
       <c r="H378" t="n">
         <v>2634505</v>
@@ -11360,7 +11360,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>5.1702995300293</v>
+        <v>5.17030000686646</v>
       </c>
       <c r="H379" t="n">
         <v>1727362</v>
@@ -11389,7 +11389,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>5.1702995300293</v>
+        <v>5.17030000686646</v>
       </c>
       <c r="H380" t="n">
         <v>1653074</v>
@@ -11418,7 +11418,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.1438250541687</v>
+        <v>5.14382457733154</v>
       </c>
       <c r="H381" t="n">
         <v>1459321</v>
@@ -11505,7 +11505,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G384" t="n">
-        <v>5.21190404891968</v>
+        <v>5.21190357208252</v>
       </c>
       <c r="H384" t="n">
         <v>2968004</v>
@@ -11534,7 +11534,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G385" t="n">
-        <v>5.40479755401611</v>
+        <v>5.40479803085327</v>
       </c>
       <c r="H385" t="n">
         <v>2375031</v>
@@ -11563,7 +11563,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>5.48044204711914</v>
+        <v>5.48044157028198</v>
       </c>
       <c r="H386" t="n">
         <v>2718690</v>
@@ -11592,7 +11592,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>5.54473972320557</v>
+        <v>5.54473924636841</v>
       </c>
       <c r="H387" t="n">
         <v>3228470</v>
@@ -11621,7 +11621,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>5.65820646286011</v>
+        <v>5.65820693969727</v>
       </c>
       <c r="H388" t="n">
         <v>2690430</v>
@@ -11650,7 +11650,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>5.49935340881348</v>
+        <v>5.49935293197632</v>
       </c>
       <c r="H389" t="n">
         <v>2989285</v>
@@ -11708,7 +11708,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.43127346038818</v>
+        <v>5.43127298355103</v>
       </c>
       <c r="H391" t="n">
         <v>1825504</v>
@@ -11737,7 +11737,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>5.54473972320557</v>
+        <v>5.54473924636841</v>
       </c>
       <c r="H392" t="n">
         <v>1316398</v>
@@ -11766,7 +11766,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>5.43127346038818</v>
+        <v>5.43127298355103</v>
       </c>
       <c r="H393" t="n">
         <v>3118560</v>
@@ -11795,7 +11795,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>5.45018482208252</v>
+        <v>5.4501838684082</v>
       </c>
       <c r="H394" t="n">
         <v>1196170</v>
@@ -11824,7 +11824,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.51448249816895</v>
+        <v>5.51448202133179</v>
       </c>
       <c r="H395" t="n">
         <v>1573825</v>
@@ -11853,7 +11853,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G396" t="n">
-        <v>5.47287797927856</v>
+        <v>5.47287750244141</v>
       </c>
       <c r="H396" t="n">
         <v>1629912</v>
@@ -11911,7 +11911,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G398" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640159606934</v>
       </c>
       <c r="H398" t="n">
         <v>1103593</v>
@@ -11940,7 +11940,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G399" t="n">
-        <v>5.40479755401611</v>
+        <v>5.40479803085327</v>
       </c>
       <c r="H399" t="n">
         <v>1176652</v>
@@ -11969,7 +11969,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49935340881348</v>
+        <v>5.49935293197632</v>
       </c>
       <c r="H400" t="n">
         <v>1347527</v>
@@ -12027,7 +12027,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.55986833572388</v>
+        <v>5.55986881256104</v>
       </c>
       <c r="H402" t="n">
         <v>667810</v>
@@ -12114,7 +12114,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>5.60903787612915</v>
+        <v>5.60903739929199</v>
       </c>
       <c r="H405" t="n">
         <v>1635128</v>
@@ -12143,7 +12143,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G406" t="n">
-        <v>5.62416648864746</v>
+        <v>5.6241660118103</v>
       </c>
       <c r="H406" t="n">
         <v>2126217</v>
@@ -12172,7 +12172,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>5.61281967163086</v>
+        <v>5.61282014846802</v>
       </c>
       <c r="H407" t="n">
         <v>1739803</v>
@@ -12230,7 +12230,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.6544246673584</v>
+        <v>5.65442514419556</v>
       </c>
       <c r="H409" t="n">
         <v>1900336</v>
@@ -12259,7 +12259,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G410" t="n">
-        <v>5.71494007110596</v>
+        <v>5.7149395942688</v>
       </c>
       <c r="H410" t="n">
         <v>1739188</v>
@@ -12288,7 +12288,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>5.73006868362427</v>
+        <v>5.73006820678711</v>
       </c>
       <c r="H411" t="n">
         <v>1115707</v>
@@ -12317,7 +12317,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>5.6884651184082</v>
+        <v>5.68846368789673</v>
       </c>
       <c r="H412" t="n">
         <v>1193303</v>
@@ -12375,7 +12375,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>5.4917893409729</v>
+        <v>5.49178886413574</v>
       </c>
       <c r="H414" t="n">
         <v>1057522</v>
@@ -12462,7 +12462,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G417" t="n">
-        <v>5.57121515274048</v>
+        <v>5.57121562957764</v>
       </c>
       <c r="H417" t="n">
         <v>874805</v>
@@ -12491,7 +12491,7 @@
         <v>7.375</v>
       </c>
       <c r="G418" t="n">
-        <v>5.57878017425537</v>
+        <v>5.57877969741821</v>
       </c>
       <c r="H418" t="n">
         <v>1231791</v>
@@ -12520,7 +12520,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G419" t="n">
-        <v>5.49557065963745</v>
+        <v>5.49557113647461</v>
       </c>
       <c r="H419" t="n">
         <v>902775</v>
@@ -12549,7 +12549,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G420" t="n">
-        <v>5.47665977478027</v>
+        <v>5.47665929794312</v>
       </c>
       <c r="H420" t="n">
         <v>886521</v>
@@ -12607,7 +12607,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.37075757980347</v>
+        <v>5.37075710296631</v>
       </c>
       <c r="H422" t="n">
         <v>1152544</v>
@@ -12636,7 +12636,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.37075757980347</v>
+        <v>5.37075710296631</v>
       </c>
       <c r="H423" t="n">
         <v>603194</v>
@@ -12665,7 +12665,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.34806442260742</v>
+        <v>5.34806489944458</v>
       </c>
       <c r="H424" t="n">
         <v>423239</v>
@@ -12694,7 +12694,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>5.26485538482666</v>
+        <v>5.26485586166382</v>
       </c>
       <c r="H425" t="n">
         <v>1931785</v>
@@ -12752,7 +12752,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G427" t="n">
-        <v>5.45774841308594</v>
+        <v>5.4577488899231</v>
       </c>
       <c r="H427" t="n">
         <v>1656906</v>
@@ -12781,7 +12781,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640159606934</v>
       </c>
       <c r="H428" t="n">
         <v>954586</v>
@@ -12839,7 +12839,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>5.27620220184326</v>
+        <v>5.27620124816895</v>
       </c>
       <c r="H430" t="n">
         <v>1460582</v>
@@ -12868,7 +12868,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.21568584442139</v>
+        <v>5.2156867980957</v>
       </c>
       <c r="H431" t="n">
         <v>1685536</v>
@@ -12897,7 +12897,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G432" t="n">
-        <v>5.19299221038818</v>
+        <v>5.19299268722534</v>
       </c>
       <c r="H432" t="n">
         <v>2898177</v>
@@ -12926,7 +12926,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>5.25729179382324</v>
+        <v>5.25729084014893</v>
       </c>
       <c r="H433" t="n">
         <v>1634980</v>
@@ -12955,7 +12955,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>5.45018482208252</v>
+        <v>5.4501838684082</v>
       </c>
       <c r="H434" t="n">
         <v>2395140</v>
@@ -13042,7 +13042,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>5.51826429367065</v>
+        <v>5.51826477050781</v>
       </c>
       <c r="H437" t="n">
         <v>1374556</v>
@@ -13071,7 +13071,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H438" t="n">
         <v>1651810</v>
@@ -13100,7 +13100,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>5.58634471893311</v>
+        <v>5.58634424209595</v>
       </c>
       <c r="H439" t="n">
         <v>1126119</v>
@@ -13129,7 +13129,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G440" t="n">
-        <v>5.59390878677368</v>
+        <v>5.59390830993652</v>
       </c>
       <c r="H440" t="n">
         <v>833534</v>
@@ -13158,7 +13158,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>5.6544246673584</v>
+        <v>5.65442514419556</v>
       </c>
       <c r="H441" t="n">
         <v>2098893</v>
@@ -13245,7 +13245,7 @@
         <v>7.375</v>
       </c>
       <c r="G444" t="n">
-        <v>5.57878017425537</v>
+        <v>5.57877969741821</v>
       </c>
       <c r="H444" t="n">
         <v>2250625</v>
@@ -13303,7 +13303,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>5.6355128288269</v>
+        <v>5.63551330566406</v>
       </c>
       <c r="H446" t="n">
         <v>1991275</v>
@@ -13332,7 +13332,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>5.62794923782349</v>
+        <v>5.62794876098633</v>
       </c>
       <c r="H447" t="n">
         <v>1310962</v>
@@ -13448,7 +13448,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>5.51069974899292</v>
+        <v>5.51070022583008</v>
       </c>
       <c r="H451" t="n">
         <v>1897849</v>
@@ -13506,7 +13506,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>5.45396661758423</v>
+        <v>5.45396709442139</v>
       </c>
       <c r="H453" t="n">
         <v>2269990</v>
@@ -13535,7 +13535,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640159606934</v>
       </c>
       <c r="H454" t="n">
         <v>2254350</v>
@@ -13564,7 +13564,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G455" t="n">
-        <v>5.4388370513916</v>
+        <v>5.43883752822876</v>
       </c>
       <c r="H455" t="n">
         <v>2227067</v>
@@ -13593,7 +13593,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H456" t="n">
         <v>2136844</v>
@@ -13680,7 +13680,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>5.61660194396973</v>
+        <v>5.61660289764404</v>
       </c>
       <c r="H459" t="n">
         <v>1535948</v>
@@ -13738,7 +13738,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H461" t="n">
         <v>653510</v>
@@ -13825,7 +13825,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>5.5523042678833</v>
+        <v>5.55230474472046</v>
       </c>
       <c r="H464" t="n">
         <v>1035421</v>
@@ -13854,7 +13854,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G465" t="n">
-        <v>5.8889217376709</v>
+        <v>5.88892221450806</v>
       </c>
       <c r="H465" t="n">
         <v>6603368</v>
@@ -13912,7 +13912,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G467" t="n">
-        <v>6.02886390686035</v>
+        <v>6.02886438369751</v>
       </c>
       <c r="H467" t="n">
         <v>5565313</v>
@@ -13941,7 +13941,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.01373529434204</v>
+        <v>6.01373624801636</v>
       </c>
       <c r="H468" t="n">
         <v>2796505</v>
@@ -14086,7 +14086,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G473" t="n">
-        <v>6.0250825881958</v>
+        <v>6.02508211135864</v>
       </c>
       <c r="H473" t="n">
         <v>2396168</v>
@@ -14115,7 +14115,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>6.00617122650146</v>
+        <v>6.00617170333862</v>
       </c>
       <c r="H474" t="n">
         <v>1187378</v>
@@ -14173,7 +14173,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.03264665603638</v>
+        <v>6.03264617919922</v>
       </c>
       <c r="H476" t="n">
         <v>2330028</v>
@@ -14202,7 +14202,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>5.97213172912598</v>
+        <v>5.97213125228882</v>
       </c>
       <c r="H477" t="n">
         <v>1904370</v>
@@ -14231,7 +14231,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G478" t="n">
-        <v>6.00238943099976</v>
+        <v>6.0023889541626</v>
       </c>
       <c r="H478" t="n">
         <v>1479963</v>
@@ -14260,7 +14260,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>5.8889217376709</v>
+        <v>5.88892221450806</v>
       </c>
       <c r="H479" t="n">
         <v>2778926</v>
@@ -14289,7 +14289,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G480" t="n">
-        <v>5.83597087860107</v>
+        <v>5.83597135543823</v>
       </c>
       <c r="H480" t="n">
         <v>1764454</v>
@@ -14318,7 +14318,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>5.78680229187012</v>
+        <v>5.78680181503296</v>
       </c>
       <c r="H481" t="n">
         <v>2037192</v>
@@ -14347,7 +14347,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>5.90026903152466</v>
+        <v>5.90026950836182</v>
       </c>
       <c r="H482" t="n">
         <v>1721482</v>
@@ -14376,7 +14376,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G483" t="n">
-        <v>5.99482440948486</v>
+        <v>5.99482488632202</v>
       </c>
       <c r="H483" t="n">
         <v>2129837</v>
@@ -14405,7 +14405,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>6.04777526855469</v>
+        <v>6.04777479171753</v>
       </c>
       <c r="H484" t="n">
         <v>1409766</v>
@@ -14434,7 +14434,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G485" t="n">
-        <v>6.13476610183716</v>
+        <v>6.13476657867432</v>
       </c>
       <c r="H485" t="n">
         <v>1649104</v>
@@ -14521,7 +14521,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>6.16124248504639</v>
+        <v>6.16124296188354</v>
       </c>
       <c r="H488" t="n">
         <v>1807013</v>
@@ -14550,7 +14550,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G489" t="n">
-        <v>6.13476610183716</v>
+        <v>6.13476657867432</v>
       </c>
       <c r="H489" t="n">
         <v>1847566</v>
@@ -14579,7 +14579,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G490" t="n">
-        <v>6.21419334411621</v>
+        <v>6.21419382095337</v>
       </c>
       <c r="H490" t="n">
         <v>1822039</v>
@@ -14608,7 +14608,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>6.34278869628906</v>
+        <v>6.34278964996338</v>
       </c>
       <c r="H491" t="n">
         <v>3494738</v>
@@ -14637,7 +14637,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G492" t="n">
-        <v>6.4070873260498</v>
+        <v>6.40708637237549</v>
       </c>
       <c r="H492" t="n">
         <v>2493160</v>
@@ -14666,7 +14666,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>6.29740238189697</v>
+        <v>6.29740190505981</v>
       </c>
       <c r="H493" t="n">
         <v>3189474</v>
@@ -14695,7 +14695,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G494" t="n">
-        <v>6.3617000579834</v>
+        <v>6.36170053482056</v>
       </c>
       <c r="H494" t="n">
         <v>2642211</v>
@@ -14869,7 +14869,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G500" t="n">
-        <v>6.53946542739868</v>
+        <v>6.53946590423584</v>
       </c>
       <c r="H500" t="n">
         <v>2118776</v>
@@ -14898,7 +14898,7 @@
         <v>8.50500011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>6.43356227874756</v>
+        <v>6.43356275558472</v>
       </c>
       <c r="H501" t="n">
         <v>2491728</v>
@@ -14985,7 +14985,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G504" t="n">
-        <v>6.52811813354492</v>
+        <v>6.52811717987061</v>
       </c>
       <c r="H504" t="n">
         <v>1354361</v>
@@ -15043,7 +15043,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G506" t="n">
-        <v>6.51298904418945</v>
+        <v>6.51298856735229</v>
       </c>
       <c r="H506" t="n">
         <v>1451098</v>
@@ -15101,7 +15101,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G508" t="n">
-        <v>6.60376214981079</v>
+        <v>6.60376310348511</v>
       </c>
       <c r="H508" t="n">
         <v>1276865</v>
@@ -15217,7 +15217,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G512" t="n">
-        <v>6.38817548751831</v>
+        <v>6.38817501068115</v>
       </c>
       <c r="H512" t="n">
         <v>1409513</v>
@@ -15246,7 +15246,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>6.39952230453491</v>
+        <v>6.39952278137207</v>
       </c>
       <c r="H513" t="n">
         <v>2092048</v>
@@ -15275,7 +15275,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G514" t="n">
-        <v>6.65671300888062</v>
+        <v>6.65671348571777</v>
       </c>
       <c r="H514" t="n">
         <v>2595760</v>
@@ -15304,7 +15304,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G515" t="n">
-        <v>6.73992156982422</v>
+        <v>6.73992204666138</v>
       </c>
       <c r="H515" t="n">
         <v>1945979</v>
@@ -15333,7 +15333,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>6.7323579788208</v>
+        <v>6.73235845565796</v>
       </c>
       <c r="H516" t="n">
         <v>2553929</v>
@@ -15362,7 +15362,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>7.06141185760498</v>
+        <v>7.06141090393066</v>
       </c>
       <c r="H517" t="n">
         <v>3758849</v>
@@ -15391,7 +15391,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G518" t="n">
-        <v>7.12949228286743</v>
+        <v>7.12949180603027</v>
       </c>
       <c r="H518" t="n">
         <v>2703458</v>
@@ -15420,7 +15420,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>7.29969120025635</v>
+        <v>7.29969167709351</v>
       </c>
       <c r="H519" t="n">
         <v>2135357</v>
@@ -15449,7 +15449,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G520" t="n">
-        <v>7.26186990737915</v>
+        <v>7.26186895370483</v>
       </c>
       <c r="H520" t="n">
         <v>2754591</v>
@@ -15478,7 +15478,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>7.27321624755859</v>
+        <v>7.27321529388428</v>
       </c>
       <c r="H521" t="n">
         <v>1422538</v>
@@ -15507,7 +15507,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>7.19000768661499</v>
+        <v>7.19000720977783</v>
       </c>
       <c r="H522" t="n">
         <v>2491793</v>
@@ -15536,7 +15536,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>7.22026538848877</v>
+        <v>7.22026443481445</v>
       </c>
       <c r="H523" t="n">
         <v>1774616</v>
@@ -15565,7 +15565,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G524" t="n">
-        <v>7.32238435745239</v>
+        <v>7.32238578796387</v>
       </c>
       <c r="H524" t="n">
         <v>1544485</v>
@@ -15594,7 +15594,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>7.34129571914673</v>
+        <v>7.34129619598389</v>
       </c>
       <c r="H525" t="n">
         <v>2716719</v>
@@ -15623,7 +15623,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>7.38290023803711</v>
+        <v>7.38290119171143</v>
       </c>
       <c r="H526" t="n">
         <v>2937349</v>
@@ -15652,7 +15652,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>7.51527881622314</v>
+        <v>7.51527833938599</v>
       </c>
       <c r="H527" t="n">
         <v>3719053</v>
@@ -15710,7 +15710,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G529" t="n">
-        <v>7.59470462799072</v>
+        <v>7.59470510482788</v>
       </c>
       <c r="H529" t="n">
         <v>2770136</v>
@@ -15739,7 +15739,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>7.64009094238281</v>
+        <v>7.64009237289429</v>
       </c>
       <c r="H530" t="n">
         <v>1886050</v>
@@ -15768,7 +15768,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G531" t="n">
-        <v>7.6249623298645</v>
+        <v>7.62496328353882</v>
       </c>
       <c r="H531" t="n">
         <v>2724662</v>
@@ -15797,7 +15797,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>7.49636793136597</v>
+        <v>7.49636840820312</v>
       </c>
       <c r="H532" t="n">
         <v>2703227</v>
@@ -15826,7 +15826,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>7.57201099395752</v>
+        <v>7.57201194763184</v>
       </c>
       <c r="H533" t="n">
         <v>2351710</v>
@@ -15855,7 +15855,7 @@
         <v>10.0249996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>7.58335876464844</v>
+        <v>7.58335781097412</v>
       </c>
       <c r="H534" t="n">
         <v>2726639</v>
@@ -15884,7 +15884,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G535" t="n">
-        <v>7.4540057182312</v>
+        <v>7.45400667190552</v>
       </c>
       <c r="H535" t="n">
         <v>3357817</v>
@@ -15913,7 +15913,7 @@
         <v>9.75</v>
       </c>
       <c r="G536" t="n">
-        <v>7.37533617019653</v>
+        <v>7.37533569335938</v>
       </c>
       <c r="H536" t="n">
         <v>2297778</v>
@@ -15942,7 +15942,7 @@
         <v>9.31799983978271</v>
       </c>
       <c r="G537" t="n">
-        <v>7.04855155944824</v>
+        <v>7.0485520362854</v>
       </c>
       <c r="H537" t="n">
         <v>5044050</v>
@@ -15971,7 +15971,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G538" t="n">
-        <v>7.23009967803955</v>
+        <v>7.23009824752808</v>
       </c>
       <c r="H538" t="n">
         <v>4868264</v>
@@ -16000,7 +16000,7 @@
         <v>9.58800029754639</v>
       </c>
       <c r="G539" t="n">
-        <v>7.25279188156128</v>
+        <v>7.25279140472412</v>
       </c>
       <c r="H539" t="n">
         <v>3063469</v>
@@ -16087,7 +16087,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G542" t="n">
-        <v>6.97593450546265</v>
+        <v>6.97593355178833</v>
       </c>
       <c r="H542" t="n">
         <v>1859299</v>
@@ -16116,7 +16116,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G543" t="n">
-        <v>7.03039646148682</v>
+        <v>7.03039693832397</v>
       </c>
       <c r="H543" t="n">
         <v>3747691</v>
@@ -16145,7 +16145,7 @@
         <v>9.53600025177002</v>
       </c>
       <c r="G544" t="n">
-        <v>7.21345710754395</v>
+        <v>7.21345663070679</v>
       </c>
       <c r="H544" t="n">
         <v>2381962</v>
@@ -16174,7 +16174,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G545" t="n">
-        <v>7.31028270721436</v>
+        <v>7.3102822303772</v>
       </c>
       <c r="H545" t="n">
         <v>1876859</v>
@@ -16203,7 +16203,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G546" t="n">
-        <v>7.31028270721436</v>
+        <v>7.3102822303772</v>
       </c>
       <c r="H546" t="n">
         <v>1280155</v>
@@ -16232,7 +16232,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G547" t="n">
-        <v>7.41164636611938</v>
+        <v>7.41164493560791</v>
       </c>
       <c r="H547" t="n">
         <v>1795777</v>
@@ -16261,7 +16261,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G548" t="n">
-        <v>7.48577690124512</v>
+        <v>7.48577785491943</v>
       </c>
       <c r="H548" t="n">
         <v>1631990</v>
@@ -16290,7 +16290,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G549" t="n">
-        <v>7.51149654388428</v>
+        <v>7.51149749755859</v>
       </c>
       <c r="H549" t="n">
         <v>2091851</v>
@@ -16319,7 +16319,7 @@
         <v>9.90200042724609</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49031543731689</v>
+        <v>7.49031782150269</v>
       </c>
       <c r="H550" t="n">
         <v>2022903</v>
@@ -16348,7 +16348,7 @@
         <v>9.97200012207031</v>
       </c>
       <c r="G551" t="n">
-        <v>7.54326677322388</v>
+        <v>7.54326772689819</v>
       </c>
       <c r="H551" t="n">
         <v>2306092</v>
@@ -16377,7 +16377,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G552" t="n">
-        <v>7.6249623298645</v>
+        <v>7.62496328353882</v>
       </c>
       <c r="H552" t="n">
         <v>1930528</v>
@@ -16406,7 +16406,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G553" t="n">
-        <v>7.65522193908691</v>
+        <v>7.65522146224976</v>
       </c>
       <c r="H553" t="n">
         <v>2284556</v>
@@ -16435,7 +16435,7 @@
         <v>10.1450004577637</v>
       </c>
       <c r="G554" t="n">
-        <v>7.67413187026978</v>
+        <v>7.67413234710693</v>
       </c>
       <c r="H554" t="n">
         <v>2059806</v>
@@ -16464,7 +16464,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G555" t="n">
-        <v>7.41164636611938</v>
+        <v>7.41164493560791</v>
       </c>
       <c r="H555" t="n">
         <v>3047161</v>
@@ -16493,7 +16493,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G556" t="n">
-        <v>7.24220275878906</v>
+        <v>7.24220180511475</v>
       </c>
       <c r="H556" t="n">
         <v>3303724</v>
@@ -16522,7 +16522,7 @@
         <v>9.9680004119873</v>
       </c>
       <c r="G557" t="n">
-        <v>7.54024124145508</v>
+        <v>7.54024076461792</v>
       </c>
       <c r="H557" t="n">
         <v>2648397</v>
@@ -16551,7 +16551,7 @@
         <v>10.1350002288818</v>
       </c>
       <c r="G558" t="n">
-        <v>7.6665678024292</v>
+        <v>7.66656637191772</v>
       </c>
       <c r="H558" t="n">
         <v>1674650</v>
@@ -16580,7 +16580,7 @@
         <v>10.1450004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>7.67413187026978</v>
+        <v>7.67413234710693</v>
       </c>
       <c r="H559" t="n">
         <v>1864379</v>
@@ -16609,7 +16609,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G560" t="n">
-        <v>7.78381681442261</v>
+        <v>7.78381586074829</v>
       </c>
       <c r="H560" t="n">
         <v>1473972</v>
@@ -16638,7 +16638,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G561" t="n">
-        <v>7.7913818359375</v>
+        <v>7.79138088226318</v>
       </c>
       <c r="H561" t="n">
         <v>2329031</v>
@@ -16667,7 +16667,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>7.64765596389771</v>
+        <v>7.64765644073486</v>
       </c>
       <c r="H562" t="n">
         <v>1900362</v>
@@ -16696,7 +16696,7 @@
         <v>10.125</v>
       </c>
       <c r="G563" t="n">
-        <v>7.65900278091431</v>
+        <v>7.65900230407715</v>
       </c>
       <c r="H563" t="n">
         <v>1838776</v>
@@ -16725,7 +16725,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G564" t="n">
-        <v>7.74599456787109</v>
+        <v>7.74599409103394</v>
       </c>
       <c r="H564" t="n">
         <v>1632465</v>
@@ -16754,7 +16754,7 @@
         <v>10.3249998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>7.8102912902832</v>
+        <v>7.81029081344604</v>
       </c>
       <c r="H565" t="n">
         <v>3130588</v>
@@ -16783,7 +16783,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>7.64765596389771</v>
+        <v>7.64765644073486</v>
       </c>
       <c r="H566" t="n">
         <v>2427519</v>
@@ -16812,7 +16812,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G567" t="n">
-        <v>7.84433126449585</v>
+        <v>7.84433221817017</v>
       </c>
       <c r="H567" t="n">
         <v>2616314</v>
@@ -16841,7 +16841,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>7.77246999740601</v>
+        <v>7.77246904373169</v>
       </c>
       <c r="H568" t="n">
         <v>1383045</v>
@@ -16870,7 +16870,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G569" t="n">
-        <v>7.57579469680786</v>
+        <v>7.5757942199707</v>
       </c>
       <c r="H569" t="n">
         <v>2012509</v>
@@ -16899,7 +16899,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G570" t="n">
-        <v>7.54931831359863</v>
+        <v>7.54931783676147</v>
       </c>
       <c r="H570" t="n">
         <v>2525070</v>
@@ -16928,7 +16928,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G571" t="n">
-        <v>7.41013193130493</v>
+        <v>7.41013336181641</v>
       </c>
       <c r="H571" t="n">
         <v>2336239</v>
@@ -16957,7 +16957,7 @@
         <v>9.81599998474121</v>
       </c>
       <c r="G572" t="n">
-        <v>7.4252610206604</v>
+        <v>7.42526149749756</v>
       </c>
       <c r="H572" t="n">
         <v>1631785</v>
@@ -16986,7 +16986,7 @@
         <v>9.72799968719482</v>
       </c>
       <c r="G573" t="n">
-        <v>7.35869455337524</v>
+        <v>7.35869407653809</v>
       </c>
       <c r="H573" t="n">
         <v>2223477</v>
@@ -17015,7 +17015,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G574" t="n">
-        <v>7.38895225524902</v>
+        <v>7.38895177841187</v>
       </c>
       <c r="H574" t="n">
         <v>1242505</v>
@@ -17073,7 +17073,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G576" t="n">
-        <v>7.37231063842773</v>
+        <v>7.37231111526489</v>
       </c>
       <c r="H576" t="n">
         <v>2250788</v>
@@ -17102,7 +17102,7 @@
         <v>10</v>
       </c>
       <c r="G577" t="n">
-        <v>7.56444883346558</v>
+        <v>7.56444692611694</v>
       </c>
       <c r="H577" t="n">
         <v>2437053</v>
@@ -17131,7 +17131,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G578" t="n">
-        <v>7.31330823898315</v>
+        <v>7.31330728530884</v>
       </c>
       <c r="H578" t="n">
         <v>2180063</v>
@@ -17160,7 +17160,7 @@
         <v>9.74400043487549</v>
       </c>
       <c r="G579" t="n">
-        <v>7.37079668045044</v>
+        <v>7.3707971572876</v>
       </c>
       <c r="H579" t="n">
         <v>2335571</v>
@@ -17189,7 +17189,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G580" t="n">
-        <v>7.41164636611938</v>
+        <v>7.41164493560791</v>
       </c>
       <c r="H580" t="n">
         <v>1565533</v>
@@ -17218,7 +17218,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>7.31482076644897</v>
+        <v>7.31482028961182</v>
       </c>
       <c r="H581" t="n">
         <v>1968934</v>
@@ -17247,7 +17247,7 @@
         <v>9.62600040435791</v>
       </c>
       <c r="G582" t="n">
-        <v>7.2815375328064</v>
+        <v>7.28153800964355</v>
       </c>
       <c r="H582" t="n">
         <v>2457870</v>
@@ -17276,7 +17276,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G583" t="n">
-        <v>7.31028270721436</v>
+        <v>7.3102822303772</v>
       </c>
       <c r="H583" t="n">
         <v>1594651</v>
@@ -17305,7 +17305,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G584" t="n">
-        <v>7.38895225524902</v>
+        <v>7.38895177841187</v>
       </c>
       <c r="H584" t="n">
         <v>1482837</v>
@@ -17363,7 +17363,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G586" t="n">
-        <v>7.54175519943237</v>
+        <v>7.54175472259521</v>
       </c>
       <c r="H586" t="n">
         <v>1948968</v>
@@ -17392,7 +17392,7 @@
         <v>9.96399974822998</v>
       </c>
       <c r="G587" t="n">
-        <v>7.53721618652344</v>
+        <v>7.53721523284912</v>
       </c>
       <c r="H587" t="n">
         <v>1703361</v>
@@ -17421,7 +17421,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G588" t="n">
-        <v>7.50695705413818</v>
+        <v>7.5069580078125</v>
       </c>
       <c r="H588" t="n">
         <v>1885121</v>
@@ -17450,7 +17450,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G589" t="n">
-        <v>7.74137926101685</v>
+        <v>7.74137830734253</v>
       </c>
       <c r="H589" t="n">
         <v>2999699</v>
@@ -17479,7 +17479,7 @@
         <v>10</v>
       </c>
       <c r="G590" t="n">
-        <v>7.78810834884644</v>
+        <v>7.78810739517212</v>
       </c>
       <c r="H590" t="n">
         <v>2393942</v>
@@ -17537,7 +17537,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G592" t="n">
-        <v>7.67440271377563</v>
+        <v>7.67440176010132</v>
       </c>
       <c r="H592" t="n">
         <v>1682061</v>
@@ -17682,7 +17682,7 @@
         <v>10.0749998092651</v>
       </c>
       <c r="G597" t="n">
-        <v>7.84651947021484</v>
+        <v>7.84651756286621</v>
       </c>
       <c r="H597" t="n">
         <v>1772133</v>
@@ -17711,7 +17711,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G598" t="n">
-        <v>7.91271829605103</v>
+        <v>7.91271781921387</v>
       </c>
       <c r="H598" t="n">
         <v>1339035</v>
@@ -17740,7 +17740,7 @@
         <v>9.80799961090088</v>
       </c>
       <c r="G599" t="n">
-        <v>7.63857650756836</v>
+        <v>7.63857507705688</v>
       </c>
       <c r="H599" t="n">
         <v>2981084</v>
@@ -17827,7 +17827,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56848335266113</v>
+        <v>7.56848382949829</v>
       </c>
       <c r="H602" t="n">
         <v>2215103</v>
@@ -17856,7 +17856,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G603" t="n">
-        <v>7.5871729850769</v>
+        <v>7.58717441558838</v>
       </c>
       <c r="H603" t="n">
         <v>1708543</v>
@@ -17914,7 +17914,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G605" t="n">
-        <v>7.16194438934326</v>
+        <v>7.1619439125061</v>
       </c>
       <c r="H605" t="n">
         <v>4253298</v>
@@ -17943,7 +17943,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G606" t="n">
-        <v>7.14481067657471</v>
+        <v>7.14481019973755</v>
       </c>
       <c r="H606" t="n">
         <v>4059527</v>
@@ -18001,7 +18001,7 @@
         <v>8.89799976348877</v>
       </c>
       <c r="G608" t="n">
-        <v>6.92985868453979</v>
+        <v>6.92985820770264</v>
       </c>
       <c r="H608" t="n">
         <v>2087544</v>
@@ -18030,7 +18030,7 @@
         <v>9.1879997253418</v>
       </c>
       <c r="G609" t="n">
-        <v>7.15571451187134</v>
+        <v>7.15571308135986</v>
       </c>
       <c r="H609" t="n">
         <v>2450008</v>
@@ -18117,7 +18117,7 @@
         <v>8.78600025177002</v>
       </c>
       <c r="G612" t="n">
-        <v>6.84263229370117</v>
+        <v>6.84263181686401</v>
       </c>
       <c r="H612" t="n">
         <v>4006077</v>
@@ -18146,7 +18146,7 @@
         <v>8.15200042724609</v>
       </c>
       <c r="G613" t="n">
-        <v>6.34886598587036</v>
+        <v>6.34886693954468</v>
       </c>
       <c r="H613" t="n">
         <v>5791926</v>
@@ -18233,7 +18233,7 @@
         <v>8.55399990081787</v>
       </c>
       <c r="G616" t="n">
-        <v>6.66194772720337</v>
+        <v>6.66194725036621</v>
       </c>
       <c r="H616" t="n">
         <v>5399976</v>
@@ -18262,7 +18262,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G617" t="n">
-        <v>6.84418964385986</v>
+        <v>6.84419059753418</v>
       </c>
       <c r="H617" t="n">
         <v>4418459</v>
@@ -18291,7 +18291,7 @@
         <v>8.56400012969971</v>
       </c>
       <c r="G618" t="n">
-        <v>6.66973638534546</v>
+        <v>6.6697359085083</v>
       </c>
       <c r="H618" t="n">
         <v>2483270</v>
@@ -18320,7 +18320,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G619" t="n">
-        <v>6.56537485122681</v>
+        <v>6.56537532806396</v>
       </c>
       <c r="H619" t="n">
         <v>3748575</v>
@@ -18349,7 +18349,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G620" t="n">
-        <v>6.95478057861328</v>
+        <v>6.95478010177612</v>
       </c>
       <c r="H620" t="n">
         <v>4511558</v>
@@ -18407,7 +18407,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G622" t="n">
-        <v>6.88312959671021</v>
+        <v>6.88313007354736</v>
       </c>
       <c r="H622" t="n">
         <v>2212311</v>
@@ -18436,7 +18436,7 @@
         <v>8.98200035095215</v>
       </c>
       <c r="G623" t="n">
-        <v>6.99527883529663</v>
+        <v>6.99527931213379</v>
       </c>
       <c r="H623" t="n">
         <v>2980931</v>
@@ -18465,7 +18465,7 @@
         <v>9.41800022125244</v>
       </c>
       <c r="G624" t="n">
-        <v>7.33483982086182</v>
+        <v>7.3348388671875</v>
       </c>
       <c r="H624" t="n">
         <v>6835377</v>
@@ -18494,7 +18494,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>7.30524587631226</v>
+        <v>7.3052453994751</v>
       </c>
       <c r="H625" t="n">
         <v>2854136</v>
@@ -18523,7 +18523,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G626" t="n">
-        <v>7.41895246505737</v>
+        <v>7.41895198822021</v>
       </c>
       <c r="H626" t="n">
         <v>3415478</v>
@@ -18552,7 +18552,7 @@
         <v>9.48200035095215</v>
       </c>
       <c r="G627" t="n">
-        <v>7.38468456268311</v>
+        <v>7.38468503952026</v>
       </c>
       <c r="H627" t="n">
         <v>4653579</v>
@@ -18610,7 +18610,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G629" t="n">
-        <v>7.41895246505737</v>
+        <v>7.41895198822021</v>
       </c>
       <c r="H629" t="n">
         <v>2609330</v>
@@ -18668,7 +18668,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.4220666885376</v>
+        <v>7.42206716537476</v>
       </c>
       <c r="H631" t="n">
         <v>1832919</v>
@@ -18755,7 +18755,7 @@
         <v>9.51399993896484</v>
       </c>
       <c r="G634" t="n">
-        <v>7.40960550308228</v>
+        <v>7.40960597991943</v>
       </c>
       <c r="H634" t="n">
         <v>1335688</v>
@@ -18813,7 +18813,7 @@
         <v>9.51799964904785</v>
       </c>
       <c r="G636" t="n">
-        <v>7.41272068023682</v>
+        <v>7.41272163391113</v>
       </c>
       <c r="H636" t="n">
         <v>1572602</v>
@@ -18871,7 +18871,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G638" t="n">
-        <v>7.54044580459595</v>
+        <v>7.54044532775879</v>
       </c>
       <c r="H638" t="n">
         <v>1450594</v>
@@ -18900,7 +18900,7 @@
         <v>9.83199977874756</v>
       </c>
       <c r="G639" t="n">
-        <v>7.65726804733276</v>
+        <v>7.65726709365845</v>
       </c>
       <c r="H639" t="n">
         <v>2310754</v>
@@ -18929,7 +18929,7 @@
         <v>9.95800018310547</v>
       </c>
       <c r="G640" t="n">
-        <v>7.75539779663086</v>
+        <v>7.75539922714233</v>
       </c>
       <c r="H640" t="n">
         <v>1366476</v>
@@ -19016,7 +19016,7 @@
         <v>9.95800018310547</v>
       </c>
       <c r="G643" t="n">
-        <v>7.75539779663086</v>
+        <v>7.75539922714233</v>
       </c>
       <c r="H643" t="n">
         <v>1094692</v>
@@ -19045,7 +19045,7 @@
         <v>9.98200035095215</v>
       </c>
       <c r="G644" t="n">
-        <v>7.77408933639526</v>
+        <v>7.77408981323242</v>
       </c>
       <c r="H644" t="n">
         <v>1259309</v>
@@ -19074,7 +19074,7 @@
         <v>9.97599983215332</v>
       </c>
       <c r="G645" t="n">
-        <v>7.76941633224487</v>
+        <v>7.76941585540771</v>
       </c>
       <c r="H645" t="n">
         <v>1764860</v>
@@ -19103,7 +19103,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G646" t="n">
-        <v>7.88935327529907</v>
+        <v>7.88935279846191</v>
       </c>
       <c r="H646" t="n">
         <v>1558159</v>
@@ -19132,7 +19132,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G647" t="n">
-        <v>7.94776439666748</v>
+        <v>7.94776391983032</v>
       </c>
       <c r="H647" t="n">
         <v>1448602</v>
@@ -19219,7 +19219,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G650" t="n">
-        <v>8.00617599487305</v>
+        <v>8.00617504119873</v>
       </c>
       <c r="H650" t="n">
         <v>1578441</v>
@@ -19248,7 +19248,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G651" t="n">
-        <v>7.97112798690796</v>
+        <v>7.97112894058228</v>
       </c>
       <c r="H651" t="n">
         <v>1564940</v>
@@ -19277,7 +19277,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G652" t="n">
-        <v>7.88156461715698</v>
+        <v>7.88156604766846</v>
       </c>
       <c r="H652" t="n">
         <v>2800521</v>
@@ -19335,7 +19335,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G654" t="n">
-        <v>7.94776439666748</v>
+        <v>7.94776391983032</v>
       </c>
       <c r="H654" t="n">
         <v>1993070</v>
@@ -19364,7 +19364,7 @@
         <v>10.1549997329712</v>
       </c>
       <c r="G655" t="n">
-        <v>7.90882253646851</v>
+        <v>7.90882396697998</v>
       </c>
       <c r="H655" t="n">
         <v>1726917</v>
@@ -19422,7 +19422,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G657" t="n">
-        <v>7.94776439666748</v>
+        <v>7.94776391983032</v>
       </c>
       <c r="H657" t="n">
         <v>1454162</v>
@@ -19451,7 +19451,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>7.94386959075928</v>
+        <v>7.94387102127075</v>
       </c>
       <c r="H658" t="n">
         <v>1136695</v>
@@ -19480,7 +19480,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G659" t="n">
-        <v>7.82704925537109</v>
+        <v>7.82704830169678</v>
       </c>
       <c r="H659" t="n">
         <v>2131963</v>
@@ -19538,7 +19538,7 @@
         <v>10.0749998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>7.84651947021484</v>
+        <v>7.84651756286621</v>
       </c>
       <c r="H661" t="n">
         <v>2018865</v>
@@ -19567,7 +19567,7 @@
         <v>10.0550003051758</v>
       </c>
       <c r="G662" t="n">
-        <v>7.83094263076782</v>
+        <v>7.83094215393066</v>
       </c>
       <c r="H662" t="n">
         <v>1786224</v>
@@ -19654,7 +19654,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G665" t="n">
-        <v>7.78031921386719</v>
+        <v>7.78031969070435</v>
       </c>
       <c r="H665" t="n">
         <v>1671254</v>
@@ -19683,7 +19683,7 @@
         <v>10.0649995803833</v>
       </c>
       <c r="G666" t="n">
-        <v>7.8387303352356</v>
+        <v>7.83873081207275</v>
       </c>
       <c r="H666" t="n">
         <v>1430460</v>
@@ -19712,7 +19712,7 @@
         <v>9.9980001449585</v>
       </c>
       <c r="G667" t="n">
-        <v>7.78655004501343</v>
+        <v>7.78655099868774</v>
       </c>
       <c r="H667" t="n">
         <v>2346193</v>
@@ -19799,7 +19799,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G670" t="n">
-        <v>7.92050695419312</v>
+        <v>7.9205060005188</v>
       </c>
       <c r="H670" t="n">
         <v>1766590</v>
@@ -19828,7 +19828,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G671" t="n">
-        <v>7.94776439666748</v>
+        <v>7.94776391983032</v>
       </c>
       <c r="H671" t="n">
         <v>1487499</v>
@@ -19857,7 +19857,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G672" t="n">
-        <v>7.92050695419312</v>
+        <v>7.9205060005188</v>
       </c>
       <c r="H672" t="n">
         <v>1017100</v>
@@ -19915,7 +19915,7 @@
         <v>10.1549997329712</v>
       </c>
       <c r="G674" t="n">
-        <v>7.90882253646851</v>
+        <v>7.90882396697998</v>
       </c>
       <c r="H674" t="n">
         <v>1380702</v>
@@ -19944,7 +19944,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G675" t="n">
-        <v>7.92439842224121</v>
+        <v>7.92439985275269</v>
       </c>
       <c r="H675" t="n">
         <v>1019734</v>
@@ -20060,7 +20060,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>8.02564525604248</v>
+        <v>8.02564430236816</v>
       </c>
       <c r="H679" t="n">
         <v>1440548</v>
@@ -20118,7 +20118,7 @@
         <v>10.2650003433228</v>
       </c>
       <c r="G681" t="n">
-        <v>7.99449348449707</v>
+        <v>7.99449396133423</v>
       </c>
       <c r="H681" t="n">
         <v>1819523</v>
@@ -20147,7 +20147,7 @@
         <v>10.2849998474121</v>
       </c>
       <c r="G682" t="n">
-        <v>8.01006889343262</v>
+        <v>8.0100679397583</v>
       </c>
       <c r="H682" t="n">
         <v>1024986</v>
@@ -20176,7 +20176,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G683" t="n">
-        <v>8.28654861450195</v>
+        <v>8.28654670715332</v>
       </c>
       <c r="H683" t="n">
         <v>2315297</v>
@@ -20292,7 +20292,7 @@
         <v>11</v>
       </c>
       <c r="G687" t="n">
-        <v>8.56691837310791</v>
+        <v>8.56691932678223</v>
       </c>
       <c r="H687" t="n">
         <v>1662128</v>
@@ -20379,7 +20379,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G690" t="n">
-        <v>8.70710563659668</v>
+        <v>8.70710468292236</v>
       </c>
       <c r="H690" t="n">
         <v>1937510</v>
@@ -20437,7 +20437,7 @@
         <v>11.4049997329712</v>
       </c>
       <c r="G692" t="n">
-        <v>8.88233757019043</v>
+        <v>8.88233661651611</v>
       </c>
       <c r="H692" t="n">
         <v>1927177</v>
@@ -20466,7 +20466,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G693" t="n">
-        <v>8.98747730255127</v>
+        <v>8.98747634887695</v>
       </c>
       <c r="H693" t="n">
         <v>3064359</v>
@@ -20495,7 +20495,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97579479217529</v>
+        <v>8.97579383850098</v>
       </c>
       <c r="H694" t="n">
         <v>2464064</v>
@@ -20582,7 +20582,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G697" t="n">
-        <v>9.096510887146</v>
+        <v>9.09650993347168</v>
       </c>
       <c r="H697" t="n">
         <v>2058581</v>
@@ -20669,7 +20669,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>9.13155651092529</v>
+        <v>9.13155746459961</v>
       </c>
       <c r="H700" t="n">
         <v>2810250</v>
@@ -20698,7 +20698,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G701" t="n">
-        <v>8.96800804138184</v>
+        <v>8.9680061340332</v>
       </c>
       <c r="H701" t="n">
         <v>3242374</v>
@@ -20756,7 +20756,7 @@
         <v>11.5</v>
       </c>
       <c r="G703" t="n">
-        <v>8.95632362365723</v>
+        <v>8.95632457733154</v>
       </c>
       <c r="H703" t="n">
         <v>1952895</v>
@@ -20785,7 +20785,7 @@
         <v>11.4750003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>8.93685340881348</v>
+        <v>8.93685436248779</v>
       </c>
       <c r="H704" t="n">
         <v>1832941</v>
@@ -20930,7 +20930,7 @@
         <v>10.2049999237061</v>
       </c>
       <c r="G709" t="n">
-        <v>7.94776439666748</v>
+        <v>7.94776391983032</v>
       </c>
       <c r="H709" t="n">
         <v>3332680</v>
@@ -20959,7 +20959,7 @@
         <v>9.95600032806396</v>
       </c>
       <c r="G710" t="n">
-        <v>7.75384140014648</v>
+        <v>7.75384044647217</v>
       </c>
       <c r="H710" t="n">
         <v>4164604</v>
@@ -20988,7 +20988,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G711" t="n">
-        <v>7.60742330551147</v>
+        <v>7.60742378234863</v>
       </c>
       <c r="H711" t="n">
         <v>3737657</v>
@@ -21017,7 +21017,7 @@
         <v>9.75</v>
       </c>
       <c r="G712" t="n">
-        <v>7.59340572357178</v>
+        <v>7.59340476989746</v>
       </c>
       <c r="H712" t="n">
         <v>1222884</v>
@@ -21046,7 +21046,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G713" t="n">
-        <v>7.81926012039185</v>
+        <v>7.819260597229</v>
       </c>
       <c r="H713" t="n">
         <v>2218488</v>
@@ -21133,7 +21133,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G716" t="n">
-        <v>6.984375</v>
+        <v>6.98437547683716</v>
       </c>
       <c r="H716" t="n">
         <v>4261848</v>
@@ -21162,7 +21162,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G717" t="n">
-        <v>6.973473072052</v>
+        <v>6.97347259521484</v>
       </c>
       <c r="H717" t="n">
         <v>2245507</v>
@@ -21220,7 +21220,7 @@
         <v>8.72599983215332</v>
       </c>
       <c r="G719" t="n">
-        <v>6.79590272903442</v>
+        <v>6.79590320587158</v>
       </c>
       <c r="H719" t="n">
         <v>1904345</v>
@@ -21249,7 +21249,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G720" t="n">
-        <v>7.04979610443115</v>
+        <v>7.04979515075684</v>
       </c>
       <c r="H720" t="n">
         <v>3077402</v>
@@ -21278,7 +21278,7 @@
         <v>8.77400016784668</v>
       </c>
       <c r="G721" t="n">
-        <v>6.83328580856323</v>
+        <v>6.83328628540039</v>
       </c>
       <c r="H721" t="n">
         <v>2229912</v>
@@ -21336,7 +21336,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G723" t="n">
-        <v>7.06692934036255</v>
+        <v>7.06692981719971</v>
       </c>
       <c r="H723" t="n">
         <v>1554170</v>
@@ -21423,7 +21423,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G726" t="n">
-        <v>7.62923049926758</v>
+        <v>7.62923145294189</v>
       </c>
       <c r="H726" t="n">
         <v>3121627</v>
@@ -21452,7 +21452,7 @@
         <v>9.58399963378906</v>
       </c>
       <c r="G727" t="n">
-        <v>7.4641227722168</v>
+        <v>7.46412229537964</v>
       </c>
       <c r="H727" t="n">
         <v>2256475</v>
@@ -21481,7 +21481,7 @@
         <v>9.60200023651123</v>
       </c>
       <c r="G728" t="n">
-        <v>7.47814130783081</v>
+        <v>7.47814178466797</v>
       </c>
       <c r="H728" t="n">
         <v>2181089</v>
@@ -21510,7 +21510,7 @@
         <v>9.62600040435791</v>
       </c>
       <c r="G729" t="n">
-        <v>7.49683284759521</v>
+        <v>7.49683380126953</v>
       </c>
       <c r="H729" t="n">
         <v>2191642</v>
@@ -21539,7 +21539,7 @@
         <v>9.87600040435791</v>
       </c>
       <c r="G730" t="n">
-        <v>7.69153547286987</v>
+        <v>7.69153594970703</v>
       </c>
       <c r="H730" t="n">
         <v>2117523</v>
@@ -21568,7 +21568,7 @@
         <v>9.90200042724609</v>
       </c>
       <c r="G731" t="n">
-        <v>7.71178483963013</v>
+        <v>7.71178674697876</v>
       </c>
       <c r="H731" t="n">
         <v>1915905</v>
@@ -21597,7 +21597,7 @@
         <v>9.82400035858154</v>
       </c>
       <c r="G732" t="n">
-        <v>7.65103769302368</v>
+        <v>7.65103673934937</v>
       </c>
       <c r="H732" t="n">
         <v>1608151</v>
@@ -21626,7 +21626,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G733" t="n">
-        <v>7.67128562927246</v>
+        <v>7.67128658294678</v>
       </c>
       <c r="H733" t="n">
         <v>1695599</v>
@@ -21713,7 +21713,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G736" t="n">
-        <v>7.50150489807129</v>
+        <v>7.50150585174561</v>
       </c>
       <c r="H736" t="n">
         <v>1763545</v>
@@ -21742,7 +21742,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G737" t="n">
-        <v>7.54044580459595</v>
+        <v>7.54044532775879</v>
       </c>
       <c r="H737" t="n">
         <v>1242108</v>
@@ -21800,7 +21800,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G739" t="n">
-        <v>7.50150489807129</v>
+        <v>7.50150585174561</v>
       </c>
       <c r="H739" t="n">
         <v>1314109</v>
@@ -21829,7 +21829,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G740" t="n">
-        <v>7.45633411407471</v>
+        <v>7.45633459091187</v>
       </c>
       <c r="H740" t="n">
         <v>1338612</v>
@@ -21887,7 +21887,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G742" t="n">
-        <v>7.62923049926758</v>
+        <v>7.62923145294189</v>
       </c>
       <c r="H742" t="n">
         <v>1900863</v>
@@ -21945,7 +21945,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G744" t="n">
-        <v>7.61832714080811</v>
+        <v>7.61832761764526</v>
       </c>
       <c r="H744" t="n">
         <v>867162</v>
@@ -21974,7 +21974,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>7.40025901794434</v>
+        <v>7.40025949478149</v>
       </c>
       <c r="H745" t="n">
         <v>1424402</v>
@@ -22032,7 +22032,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G747" t="n">
-        <v>7.5606951713562</v>
+        <v>7.56069660186768</v>
       </c>
       <c r="H747" t="n">
         <v>1765087</v>
@@ -22061,7 +22061,7 @@
         <v>9.58199977874756</v>
       </c>
       <c r="G748" t="n">
-        <v>7.46256589889526</v>
+        <v>7.46256494522095</v>
       </c>
       <c r="H748" t="n">
         <v>1190558</v>
@@ -22148,7 +22148,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G751" t="n">
-        <v>7.11677360534668</v>
+        <v>7.11677265167236</v>
       </c>
       <c r="H751" t="n">
         <v>1246812</v>
@@ -22177,7 +22177,7 @@
         <v>8.93400001525879</v>
       </c>
       <c r="G752" t="n">
-        <v>6.95789623260498</v>
+        <v>6.95789575576782</v>
       </c>
       <c r="H752" t="n">
         <v>1417279</v>
@@ -22264,7 +22264,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G755" t="n">
-        <v>7.21646118164062</v>
+        <v>7.21646070480347</v>
       </c>
       <c r="H755" t="n">
         <v>1453615</v>
@@ -22293,7 +22293,7 @@
         <v>9.14400005340576</v>
       </c>
       <c r="G756" t="n">
-        <v>7.12144613265991</v>
+        <v>7.1214451789856</v>
       </c>
       <c r="H756" t="n">
         <v>1431356</v>
@@ -22322,7 +22322,7 @@
         <v>8.98400020599365</v>
       </c>
       <c r="G757" t="n">
-        <v>6.99683713912964</v>
+        <v>6.99683618545532</v>
       </c>
       <c r="H757" t="n">
         <v>1069839</v>
@@ -22380,7 +22380,7 @@
         <v>9.0939998626709</v>
       </c>
       <c r="G759" t="n">
-        <v>7.0825047492981</v>
+        <v>7.08250570297241</v>
       </c>
       <c r="H759" t="n">
         <v>1437335</v>
@@ -22438,7 +22438,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G761" t="n">
-        <v>6.79123067855835</v>
+        <v>6.79123115539551</v>
       </c>
       <c r="H761" t="n">
         <v>3192777</v>
@@ -22467,7 +22467,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G762" t="n">
-        <v>6.67440795898438</v>
+        <v>6.67440843582153</v>
       </c>
       <c r="H762" t="n">
         <v>1360582</v>
@@ -22583,7 +22583,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>6.97035694122314</v>
+        <v>6.97035598754883</v>
       </c>
       <c r="H766" t="n">
         <v>1340515</v>
@@ -22612,7 +22612,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="n">
-        <v>7.00929737091064</v>
+        <v>7.00929689407349</v>
       </c>
       <c r="H767" t="n">
         <v>975227</v>
@@ -22641,7 +22641,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G768" t="n">
-        <v>7.30368804931641</v>
+        <v>7.30368757247925</v>
       </c>
       <c r="H768" t="n">
         <v>2435460</v>
@@ -22728,7 +22728,7 @@
         <v>9.34200000762939</v>
       </c>
       <c r="G771" t="n">
-        <v>7.27565145492554</v>
+        <v>7.27565097808838</v>
       </c>
       <c r="H771" t="n">
         <v>745472</v>
@@ -22786,7 +22786,7 @@
         <v>9.45199966430664</v>
       </c>
       <c r="G773" t="n">
-        <v>7.36131954193115</v>
+        <v>7.36131858825684</v>
       </c>
       <c r="H773" t="n">
         <v>1035601</v>
@@ -22873,7 +22873,7 @@
         <v>9.90200042724609</v>
       </c>
       <c r="G776" t="n">
-        <v>7.71178483963013</v>
+        <v>7.71178674697876</v>
       </c>
       <c r="H776" t="n">
         <v>2662451</v>
@@ -22902,7 +22902,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G777" t="n">
-        <v>7.67128562927246</v>
+        <v>7.67128658294678</v>
       </c>
       <c r="H777" t="n">
         <v>636119</v>
@@ -22931,7 +22931,7 @@
         <v>9.75</v>
       </c>
       <c r="G778" t="n">
-        <v>7.59340572357178</v>
+        <v>7.59340476989746</v>
       </c>
       <c r="H778" t="n">
         <v>2227314</v>
@@ -22960,7 +22960,7 @@
         <v>9.77600002288818</v>
       </c>
       <c r="G779" t="n">
-        <v>7.61365604400635</v>
+        <v>7.61365509033203</v>
       </c>
       <c r="H779" t="n">
         <v>1141108</v>
@@ -23018,7 +23018,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G781" t="n">
-        <v>7.67128562927246</v>
+        <v>7.67128658294678</v>
       </c>
       <c r="H781" t="n">
         <v>1045527</v>
@@ -23076,7 +23076,7 @@
         <v>9.74400043487549</v>
       </c>
       <c r="G783" t="n">
-        <v>7.58873271942139</v>
+        <v>7.58873224258423</v>
       </c>
       <c r="H783" t="n">
         <v>1303463</v>
@@ -23105,7 +23105,7 @@
         <v>9.71599960327148</v>
       </c>
       <c r="G784" t="n">
-        <v>7.56692600250244</v>
+        <v>7.56692504882812</v>
       </c>
       <c r="H784" t="n">
         <v>1186119</v>
@@ -23221,7 +23221,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>7.63234663009644</v>
+        <v>7.63234519958496</v>
       </c>
       <c r="H788" t="n">
         <v>1925351</v>
@@ -23250,7 +23250,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G789" t="n">
-        <v>7.72112989425659</v>
+        <v>7.72113037109375</v>
       </c>
       <c r="H789" t="n">
         <v>2853647</v>
@@ -23279,7 +23279,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G790" t="n">
-        <v>7.51864004135132</v>
+        <v>7.518639087677</v>
       </c>
       <c r="H790" t="n">
         <v>1606565</v>
@@ -23337,7 +23337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>7.63234663009644</v>
+        <v>7.63234519958496</v>
       </c>
       <c r="H792" t="n">
         <v>1134194</v>
@@ -23366,7 +23366,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G793" t="n">
-        <v>7.70711183547974</v>
+        <v>7.70711231231689</v>
       </c>
       <c r="H793" t="n">
         <v>1362044</v>
@@ -23540,7 +23540,7 @@
         <v>10.2250003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>7.96334075927734</v>
+        <v>7.9633412361145</v>
       </c>
       <c r="H799" t="n">
         <v>1346337</v>
@@ -23569,7 +23569,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G800" t="n">
-        <v>7.78031921386719</v>
+        <v>7.78031969070435</v>
       </c>
       <c r="H800" t="n">
         <v>1528819</v>
@@ -23627,7 +23627,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G802" t="n">
-        <v>7.97112798690796</v>
+        <v>7.97112894058228</v>
       </c>
       <c r="H802" t="n">
         <v>895345</v>
@@ -23656,7 +23656,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G803" t="n">
-        <v>7.95555305480957</v>
+        <v>7.95555257797241</v>
       </c>
       <c r="H803" t="n">
         <v>1072121</v>
@@ -23714,7 +23714,7 @@
         <v>10.9250001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>8.50850963592529</v>
+        <v>8.50850868225098</v>
       </c>
       <c r="H805" t="n">
         <v>3610798</v>
@@ -23917,7 +23917,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G812" t="n">
-        <v>8.94074726104736</v>
+        <v>8.94074821472168</v>
       </c>
       <c r="H812" t="n">
         <v>1506561</v>
@@ -24033,7 +24033,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G816" t="n">
-        <v>9.00305271148682</v>
+        <v>9.0030517578125</v>
       </c>
       <c r="H816" t="n">
         <v>1933980</v>
@@ -24062,7 +24062,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>9.03420639038086</v>
+        <v>9.03420543670654</v>
       </c>
       <c r="H817" t="n">
         <v>1302193</v>
@@ -24091,7 +24091,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>8.97579479217529</v>
+        <v>8.97579383850098</v>
       </c>
       <c r="H818" t="n">
         <v>1515731</v>
@@ -24120,7 +24120,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G819" t="n">
-        <v>8.97968673706055</v>
+        <v>8.97968769073486</v>
       </c>
       <c r="H819" t="n">
         <v>1509775</v>
@@ -24149,7 +24149,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>9.03420639038086</v>
+        <v>9.03420543670654</v>
       </c>
       <c r="H820" t="n">
         <v>1173045</v>
@@ -24178,7 +24178,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G821" t="n">
-        <v>8.97968673706055</v>
+        <v>8.97968769073486</v>
       </c>
       <c r="H821" t="n">
         <v>1872525</v>
@@ -24265,7 +24265,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G824" t="n">
-        <v>8.9251708984375</v>
+        <v>8.92517185211182</v>
       </c>
       <c r="H824" t="n">
         <v>1643442</v>
@@ -24323,7 +24323,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>9.13155651092529</v>
+        <v>9.13155746459961</v>
       </c>
       <c r="H826" t="n">
         <v>1938732</v>
@@ -24439,7 +24439,7 @@
         <v>11.8649997711182</v>
       </c>
       <c r="G830" t="n">
-        <v>9.24059009552002</v>
+        <v>9.2405891418457</v>
       </c>
       <c r="H830" t="n">
         <v>1520646</v>
@@ -24468,7 +24468,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G831" t="n">
-        <v>9.29900169372559</v>
+        <v>9.29900074005127</v>
       </c>
       <c r="H831" t="n">
         <v>2237324</v>
@@ -24555,7 +24555,7 @@
         <v>11.7049999237061</v>
       </c>
       <c r="G834" t="n">
-        <v>9.11598014831543</v>
+        <v>9.11598205566406</v>
       </c>
       <c r="H834" t="n">
         <v>1851448</v>
@@ -24613,7 +24613,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G836" t="n">
-        <v>9.4469747543335</v>
+        <v>9.44697570800781</v>
       </c>
       <c r="H836" t="n">
         <v>3046976</v>
@@ -24816,7 +24816,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G843" t="n">
-        <v>9.43289947509766</v>
+        <v>9.43289852142334</v>
       </c>
       <c r="H843" t="n">
         <v>1259655</v>
@@ -24874,7 +24874,7 @@
         <v>11.8149995803833</v>
       </c>
       <c r="G845" t="n">
-        <v>9.43689250946045</v>
+        <v>9.43689155578613</v>
       </c>
       <c r="H845" t="n">
         <v>3023422</v>
@@ -25077,7 +25077,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G852" t="n">
-        <v>7.97123908996582</v>
+        <v>7.9712381362915</v>
       </c>
       <c r="H852" t="n">
         <v>5435251</v>
@@ -25135,7 +25135,7 @@
         <v>9.60799980163574</v>
       </c>
       <c r="G854" t="n">
-        <v>7.67411518096924</v>
+        <v>7.67411422729492</v>
       </c>
       <c r="H854" t="n">
         <v>6403338</v>
@@ -25164,7 +25164,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G855" t="n">
-        <v>7.82427406311035</v>
+        <v>7.82427501678467</v>
       </c>
       <c r="H855" t="n">
         <v>4768720</v>
@@ -25222,7 +25222,7 @@
         <v>9.91800022125244</v>
       </c>
       <c r="G857" t="n">
-        <v>7.92171859741211</v>
+        <v>7.92171955108643</v>
       </c>
       <c r="H857" t="n">
         <v>3773414</v>
@@ -25280,7 +25280,7 @@
         <v>9.78800010681152</v>
       </c>
       <c r="G859" t="n">
-        <v>7.81788492202759</v>
+        <v>7.8178858757019</v>
       </c>
       <c r="H859" t="n">
         <v>2935413</v>
@@ -25367,7 +25367,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G862" t="n">
-        <v>7.71085643768311</v>
+        <v>7.71085548400879</v>
       </c>
       <c r="H862" t="n">
         <v>4209402</v>
@@ -25396,7 +25396,7 @@
         <v>9.75</v>
       </c>
       <c r="G863" t="n">
-        <v>7.7875337600708</v>
+        <v>7.78753280639648</v>
       </c>
       <c r="H863" t="n">
         <v>2936234</v>
@@ -25454,7 +25454,7 @@
         <v>9.5</v>
       </c>
       <c r="G865" t="n">
-        <v>7.5878529548645</v>
+        <v>7.58785200119019</v>
       </c>
       <c r="H865" t="n">
         <v>41491512</v>
@@ -25483,7 +25483,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G866" t="n">
-        <v>7.38976907730103</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H866" t="n">
         <v>3383104</v>
@@ -25512,7 +25512,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G867" t="n">
-        <v>7.38976907730103</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H867" t="n">
         <v>2186192</v>
@@ -25541,7 +25541,7 @@
         <v>9.27600002288818</v>
       </c>
       <c r="G868" t="n">
-        <v>7.40893936157227</v>
+        <v>7.40893840789795</v>
       </c>
       <c r="H868" t="n">
         <v>3447972</v>
@@ -25599,7 +25599,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G870" t="n">
-        <v>7.48881149291992</v>
+        <v>7.48881244659424</v>
       </c>
       <c r="H870" t="n">
         <v>3609501</v>
@@ -25686,7 +25686,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>7.42810773849487</v>
+        <v>7.42810869216919</v>
       </c>
       <c r="H873" t="n">
         <v>2226876</v>
@@ -25715,7 +25715,7 @@
         <v>9.28400039672852</v>
       </c>
       <c r="G874" t="n">
-        <v>7.4153299331665</v>
+        <v>7.41532897949219</v>
       </c>
       <c r="H874" t="n">
         <v>1970639</v>
@@ -25802,7 +25802,7 @@
         <v>9.19400024414062</v>
       </c>
       <c r="G877" t="n">
-        <v>7.34344482421875</v>
+        <v>7.34344387054443</v>
       </c>
       <c r="H877" t="n">
         <v>1548035</v>
@@ -25918,7 +25918,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G881" t="n">
-        <v>7.53993034362793</v>
+        <v>7.53992938995361</v>
       </c>
       <c r="H881" t="n">
         <v>2730493</v>
@@ -25947,7 +25947,7 @@
         <v>9.54800033569336</v>
       </c>
       <c r="G882" t="n">
-        <v>7.62619161605835</v>
+        <v>7.62619066238403</v>
       </c>
       <c r="H882" t="n">
         <v>4544189</v>
@@ -25976,7 +25976,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G883" t="n">
-        <v>7.82267618179321</v>
+        <v>7.82267665863037</v>
       </c>
       <c r="H883" t="n">
         <v>9587699</v>
@@ -26005,7 +26005,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>7.82746982574463</v>
+        <v>7.82746887207031</v>
       </c>
       <c r="H884" t="n">
         <v>3870686</v>
@@ -26121,7 +26121,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G888" t="n">
-        <v>7.83545684814453</v>
+        <v>7.83545589447021</v>
       </c>
       <c r="H888" t="n">
         <v>2776001</v>
@@ -26179,7 +26179,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>7.91532850265503</v>
+        <v>7.91532945632935</v>
       </c>
       <c r="H890" t="n">
         <v>2445491</v>
@@ -26266,7 +26266,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G893" t="n">
-        <v>8.538330078125</v>
+        <v>8.53833103179932</v>
       </c>
       <c r="H893" t="n">
         <v>2655809</v>
@@ -26353,7 +26353,7 @@
         <v>10.3149995803833</v>
       </c>
       <c r="G896" t="n">
-        <v>8.23881149291992</v>
+        <v>8.23881053924561</v>
       </c>
       <c r="H896" t="n">
         <v>9666900</v>
@@ -26440,7 +26440,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G899" t="n">
-        <v>7.99919557571411</v>
+        <v>7.99919462203979</v>
       </c>
       <c r="H899" t="n">
         <v>4054784</v>
@@ -26585,7 +26585,7 @@
         <v>9.72599983215332</v>
       </c>
       <c r="G904" t="n">
-        <v>7.76836442947388</v>
+        <v>7.76836347579956</v>
       </c>
       <c r="H904" t="n">
         <v>2332272</v>
@@ -26643,7 +26643,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G906" t="n">
-        <v>7.99919557571411</v>
+        <v>7.99919462203979</v>
       </c>
       <c r="H906" t="n">
         <v>3450602</v>
@@ -26672,7 +26672,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G907" t="n">
-        <v>7.78114175796509</v>
+        <v>7.7811427116394</v>
       </c>
       <c r="H907" t="n">
         <v>4500422</v>
@@ -26701,7 +26701,7 @@
         <v>9.48200035095215</v>
       </c>
       <c r="G908" t="n">
-        <v>7.57347631454468</v>
+        <v>7.57347726821899</v>
       </c>
       <c r="H908" t="n">
         <v>3994996</v>
@@ -26817,7 +26817,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>7.29232549667358</v>
+        <v>7.2923264503479</v>
       </c>
       <c r="H912" t="n">
         <v>3452685</v>
@@ -26846,7 +26846,7 @@
         <v>8.91199970245361</v>
       </c>
       <c r="G913" t="n">
-        <v>7.11820363998413</v>
+        <v>7.11820411682129</v>
       </c>
       <c r="H913" t="n">
         <v>3482642</v>
@@ -26875,7 +26875,7 @@
         <v>8.70600032806396</v>
       </c>
       <c r="G914" t="n">
-        <v>6.95366859436035</v>
+        <v>6.95366907119751</v>
       </c>
       <c r="H914" t="n">
         <v>3818373</v>
@@ -26933,7 +26933,7 @@
         <v>8.90799999237061</v>
       </c>
       <c r="G916" t="n">
-        <v>7.1150107383728</v>
+        <v>7.11501026153564</v>
       </c>
       <c r="H916" t="n">
         <v>3000799</v>
@@ -26991,7 +26991,7 @@
         <v>8.94400024414062</v>
       </c>
       <c r="G918" t="n">
-        <v>7.14376449584961</v>
+        <v>7.14376354217529</v>
       </c>
       <c r="H918" t="n">
         <v>3640894</v>
@@ -27020,7 +27020,7 @@
         <v>8.74199962615967</v>
       </c>
       <c r="G919" t="n">
-        <v>6.98242139816284</v>
+        <v>6.98242092132568</v>
       </c>
       <c r="H919" t="n">
         <v>2269650</v>
@@ -27078,7 +27078,7 @@
         <v>8.51399993896484</v>
       </c>
       <c r="G921" t="n">
-        <v>6.8003134727478</v>
+        <v>6.80031394958496</v>
       </c>
       <c r="H921" t="n">
         <v>4466353</v>
@@ -27165,7 +27165,7 @@
         <v>8.7519998550415</v>
       </c>
       <c r="G924" t="n">
-        <v>6.99040937423706</v>
+        <v>6.9904088973999</v>
       </c>
       <c r="H924" t="n">
         <v>1609495</v>
@@ -27223,7 +27223,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G926" t="n">
-        <v>7.38976907730103</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H926" t="n">
         <v>3676274</v>
@@ -27252,7 +27252,7 @@
         <v>8.97599983215332</v>
       </c>
       <c r="G927" t="n">
-        <v>7.16932249069214</v>
+        <v>7.16932344436646</v>
       </c>
       <c r="H927" t="n">
         <v>2682189</v>
@@ -27339,7 +27339,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G930" t="n">
-        <v>7.45207071304321</v>
+        <v>7.4520697593689</v>
       </c>
       <c r="H930" t="n">
         <v>3565618</v>
@@ -27397,7 +27397,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G932" t="n">
-        <v>7.49040937423706</v>
+        <v>7.49040842056274</v>
       </c>
       <c r="H932" t="n">
         <v>2552791</v>
@@ -27513,7 +27513,7 @@
         <v>9.83800029754639</v>
       </c>
       <c r="G936" t="n">
-        <v>7.85782098770142</v>
+        <v>7.8578200340271</v>
       </c>
       <c r="H936" t="n">
         <v>3196132</v>
@@ -27542,7 +27542,7 @@
         <v>9.75</v>
       </c>
       <c r="G937" t="n">
-        <v>7.7875337600708</v>
+        <v>7.78753280639648</v>
       </c>
       <c r="H937" t="n">
         <v>3105529</v>
@@ -27600,7 +27600,7 @@
         <v>9.51399993896484</v>
       </c>
       <c r="G939" t="n">
-        <v>7.59903430938721</v>
+        <v>7.59903526306152</v>
       </c>
       <c r="H939" t="n">
         <v>5535766</v>
@@ -27629,7 +27629,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G940" t="n">
-        <v>7.42810773849487</v>
+        <v>7.42810869216919</v>
       </c>
       <c r="H940" t="n">
         <v>5627338</v>
@@ -27658,7 +27658,7 @@
         <v>9.42399978637695</v>
       </c>
       <c r="G941" t="n">
-        <v>7.52715015411377</v>
+        <v>7.52714920043945</v>
       </c>
       <c r="H941" t="n">
         <v>4089597</v>
@@ -27687,7 +27687,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G942" t="n">
-        <v>7.86740446090698</v>
+        <v>7.8674054145813</v>
       </c>
       <c r="H942" t="n">
         <v>4696889</v>
@@ -27774,7 +27774,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G945" t="n">
-        <v>7.50798034667969</v>
+        <v>7.507981300354</v>
       </c>
       <c r="H945" t="n">
         <v>2575989</v>
@@ -27832,7 +27832,7 @@
         <v>9.91800022125244</v>
       </c>
       <c r="G947" t="n">
-        <v>7.92171859741211</v>
+        <v>7.92171955108643</v>
       </c>
       <c r="H947" t="n">
         <v>8266753</v>
@@ -27861,7 +27861,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G948" t="n">
-        <v>7.69328355789185</v>
+        <v>7.69328451156616</v>
       </c>
       <c r="H948" t="n">
         <v>3325238</v>
@@ -27948,7 +27948,7 @@
         <v>9.47799968719482</v>
       </c>
       <c r="G951" t="n">
-        <v>7.57028007507324</v>
+        <v>7.57028102874756</v>
       </c>
       <c r="H951" t="n">
         <v>1881813</v>
@@ -28093,7 +28093,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G956" t="n">
-        <v>7.61181402206421</v>
+        <v>7.61181449890137</v>
       </c>
       <c r="H956" t="n">
         <v>3325856</v>
@@ -28122,7 +28122,7 @@
         <v>9.64599990844727</v>
       </c>
       <c r="G957" t="n">
-        <v>7.70446586608887</v>
+        <v>7.70446634292603</v>
       </c>
       <c r="H957" t="n">
         <v>2491109</v>
@@ -28296,7 +28296,7 @@
         <v>9.5959997177124</v>
       </c>
       <c r="G963" t="n">
-        <v>7.66453075408936</v>
+        <v>7.66452980041504</v>
       </c>
       <c r="H963" t="n">
         <v>2791419</v>
@@ -28383,7 +28383,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G966" t="n">
-        <v>8.03513717651367</v>
+        <v>8.03513813018799</v>
       </c>
       <c r="H966" t="n">
         <v>4312250</v>
@@ -28441,7 +28441,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G968" t="n">
-        <v>8.2428035736084</v>
+        <v>8.24280452728271</v>
       </c>
       <c r="H968" t="n">
         <v>3726083</v>
@@ -28499,7 +28499,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>8.14695739746094</v>
+        <v>8.14695835113525</v>
       </c>
       <c r="H970" t="n">
         <v>2753561</v>
@@ -28586,7 +28586,7 @@
         <v>10.4049997329712</v>
       </c>
       <c r="G973" t="n">
-        <v>8.31069469451904</v>
+        <v>8.31069564819336</v>
       </c>
       <c r="H973" t="n">
         <v>2851886</v>
@@ -28615,7 +28615,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>8.30670261383057</v>
+        <v>8.30670166015625</v>
       </c>
       <c r="H974" t="n">
         <v>2791666</v>
@@ -28644,7 +28644,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G975" t="n">
-        <v>8.16293334960938</v>
+        <v>8.16293239593506</v>
       </c>
       <c r="H975" t="n">
         <v>2456857</v>
@@ -28702,7 +28702,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G977" t="n">
-        <v>8.29072761535645</v>
+        <v>8.29072666168213</v>
       </c>
       <c r="H977" t="n">
         <v>2778678</v>
@@ -28731,7 +28731,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>8.52635097503662</v>
+        <v>8.5263500213623</v>
       </c>
       <c r="H978" t="n">
         <v>4481429</v>
@@ -28847,7 +28847,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G982" t="n">
-        <v>8.79392242431641</v>
+        <v>8.79392147064209</v>
       </c>
       <c r="H982" t="n">
         <v>3106214</v>
@@ -28876,7 +28876,7 @@
         <v>11.1350002288818</v>
       </c>
       <c r="G983" t="n">
-        <v>8.89376163482666</v>
+        <v>8.89376258850098</v>
       </c>
       <c r="H983" t="n">
         <v>2887920</v>
@@ -28905,7 +28905,7 @@
         <v>11.4350004196167</v>
       </c>
       <c r="G984" t="n">
-        <v>9.13337898254395</v>
+        <v>9.13337993621826</v>
       </c>
       <c r="H984" t="n">
         <v>4526531</v>
@@ -28934,7 +28934,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G985" t="n">
-        <v>9.18928909301758</v>
+        <v>9.18928813934326</v>
       </c>
       <c r="H985" t="n">
         <v>4781545</v>
@@ -29021,7 +29021,7 @@
         <v>11.3649997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>9.07746696472168</v>
+        <v>9.077467918396</v>
       </c>
       <c r="H988" t="n">
         <v>3944843</v>
@@ -29050,7 +29050,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G989" t="n">
-        <v>8.96964073181152</v>
+        <v>8.96964168548584</v>
       </c>
       <c r="H989" t="n">
         <v>3925640</v>
@@ -29253,7 +29253,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G996" t="n">
-        <v>9.18928909301758</v>
+        <v>9.18928813934326</v>
       </c>
       <c r="H996" t="n">
         <v>2523570</v>
@@ -29456,7 +29456,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1003" t="n">
-        <v>8.85782051086426</v>
+        <v>8.85781955718994</v>
       </c>
       <c r="H1003" t="n">
         <v>2487483</v>
@@ -29572,7 +29572,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.77794742584229</v>
+        <v>8.7779483795166</v>
       </c>
       <c r="H1007" t="n">
         <v>3734976</v>
@@ -29630,7 +29630,7 @@
         <v>11</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.78593444824219</v>
+        <v>8.7859354019165</v>
       </c>
       <c r="H1009" t="n">
         <v>2151620</v>
@@ -29804,7 +29804,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G1015" t="n">
-        <v>8.538330078125</v>
+        <v>8.53833103179932</v>
       </c>
       <c r="H1015" t="n">
         <v>1093478</v>
@@ -29891,7 +29891,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.49839687347412</v>
+        <v>8.4983959197998</v>
       </c>
       <c r="H1018" t="n">
         <v>2208761</v>
@@ -29978,7 +29978,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1021" t="n">
-        <v>9.23321914672852</v>
+        <v>9.2332181930542</v>
       </c>
       <c r="H1021" t="n">
         <v>5413395</v>
@@ -30007,7 +30007,7 @@
         <v>11.2049999237061</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.94967365264893</v>
+        <v>8.94967269897461</v>
       </c>
       <c r="H1022" t="n">
         <v>2994173</v>
@@ -30123,7 +30123,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.96964073181152</v>
+        <v>8.96964168548584</v>
       </c>
       <c r="H1026" t="n">
         <v>2056874</v>
@@ -30152,7 +30152,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.87379360198975</v>
+        <v>8.87379455566406</v>
       </c>
       <c r="H1027" t="n">
         <v>3061847</v>
@@ -30239,7 +30239,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.87379360198975</v>
+        <v>8.87379455566406</v>
       </c>
       <c r="H1030" t="n">
         <v>2515719</v>
@@ -30384,7 +30384,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1035" t="n">
-        <v>8.92970561981201</v>
+        <v>8.9297046661377</v>
       </c>
       <c r="H1035" t="n">
         <v>3264579</v>
@@ -30413,7 +30413,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.76996040344238</v>
+        <v>8.7699613571167</v>
       </c>
       <c r="H1036" t="n">
         <v>3530447</v>
@@ -30471,7 +30471,7 @@
         <v>10.8149995803833</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.63817119598389</v>
+        <v>8.63817024230957</v>
       </c>
       <c r="H1038" t="n">
         <v>1938612</v>
@@ -30500,7 +30500,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.85782051086426</v>
+        <v>8.85781955718994</v>
       </c>
       <c r="H1039" t="n">
         <v>3040168</v>
@@ -30616,7 +30616,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1043" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1043" t="n">
         <v>3510236</v>
@@ -30848,7 +30848,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.85782051086426</v>
+        <v>8.85781955718994</v>
       </c>
       <c r="H1051" t="n">
         <v>4474988</v>
@@ -30906,7 +30906,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1053" t="n">
-        <v>8.03513717651367</v>
+        <v>8.03513813018799</v>
       </c>
       <c r="H1053" t="n">
         <v>7262508</v>
@@ -30935,7 +30935,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.82267618179321</v>
+        <v>7.82267665863037</v>
       </c>
       <c r="H1054" t="n">
         <v>4733298</v>
@@ -30993,7 +30993,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G1056" t="n">
-        <v>7.84823513031006</v>
+        <v>7.84823608398438</v>
       </c>
       <c r="H1056" t="n">
         <v>5211999</v>
@@ -31022,7 +31022,7 @@
         <v>9.49400043487549</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.5830602645874</v>
+        <v>7.58306121826172</v>
       </c>
       <c r="H1057" t="n">
         <v>6625541</v>
@@ -31051,7 +31051,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.29232549667358</v>
+        <v>7.2923264503479</v>
       </c>
       <c r="H1058" t="n">
         <v>5987425</v>
@@ -31080,7 +31080,7 @@
         <v>9.33399963378906</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.4552640914917</v>
+        <v>7.45526504516602</v>
       </c>
       <c r="H1059" t="n">
         <v>6715202</v>
@@ -31109,7 +31109,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.06868410110474</v>
+        <v>7.06868457794189</v>
       </c>
       <c r="H1060" t="n">
         <v>7522341</v>
@@ -31138,7 +31138,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.08625602722168</v>
+        <v>7.08625507354736</v>
       </c>
       <c r="H1061" t="n">
         <v>6565588</v>
@@ -31225,7 +31225,7 @@
         <v>7.53599977493286</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.01916360855103</v>
+        <v>6.01916408538818</v>
       </c>
       <c r="H1064" t="n">
         <v>7546704</v>
@@ -31428,7 +31428,7 @@
         <v>7.47800016403198</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.97283840179443</v>
+        <v>5.97283887863159</v>
       </c>
       <c r="H1071" t="n">
         <v>5432734</v>
@@ -31486,7 +31486,7 @@
         <v>7.47800016403198</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.97283840179443</v>
+        <v>5.97283887863159</v>
       </c>
       <c r="H1073" t="n">
         <v>6801824</v>
@@ -31573,7 +31573,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G1076" t="n">
-        <v>7.0590991973877</v>
+        <v>7.05909967422485</v>
       </c>
       <c r="H1076" t="n">
         <v>4904120</v>
@@ -31631,7 +31631,7 @@
         <v>8.42199993133545</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.72683095932007</v>
+        <v>6.72683143615723</v>
       </c>
       <c r="H1078" t="n">
         <v>4833258</v>
@@ -31718,7 +31718,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.82906770706177</v>
+        <v>6.82906818389893</v>
       </c>
       <c r="H1081" t="n">
         <v>2997795</v>
@@ -31747,7 +31747,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.14855623245239</v>
+        <v>7.14855527877808</v>
       </c>
       <c r="H1082" t="n">
         <v>4108088</v>
@@ -31776,7 +31776,7 @@
         <v>9.1540002822876</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.31149530410767</v>
+        <v>7.31149435043335</v>
       </c>
       <c r="H1083" t="n">
         <v>3944078</v>
@@ -31863,7 +31863,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.54152727127075</v>
+        <v>7.54152822494507</v>
       </c>
       <c r="H1086" t="n">
         <v>3112691</v>
@@ -31892,7 +31892,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.63577699661255</v>
+        <v>7.63577604293823</v>
       </c>
       <c r="H1087" t="n">
         <v>3037142</v>
@@ -31921,7 +31921,7 @@
         <v>8.83399963378906</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.05590391159058</v>
+        <v>7.05590438842773</v>
       </c>
       <c r="H1088" t="n">
         <v>3989061</v>
@@ -31950,7 +31950,7 @@
         <v>8.70800018310547</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.95526599884033</v>
+        <v>6.95526552200317</v>
       </c>
       <c r="H1089" t="n">
         <v>3264928</v>
@@ -31979,7 +31979,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.94887495040894</v>
+        <v>6.94887542724609</v>
       </c>
       <c r="H1090" t="n">
         <v>2959801</v>
@@ -32008,7 +32008,7 @@
         <v>8.73200035095215</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.9744348526001</v>
+        <v>6.97443389892578</v>
       </c>
       <c r="H1091" t="n">
         <v>1843759</v>
@@ -32037,7 +32037,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.51916313171387</v>
+        <v>6.51916360855103</v>
       </c>
       <c r="H1092" t="n">
         <v>3812138</v>
@@ -32066,7 +32066,7 @@
         <v>8.75800037384033</v>
       </c>
       <c r="G1093" t="n">
-        <v>6.99520206451416</v>
+        <v>6.995201587677</v>
       </c>
       <c r="H1093" t="n">
         <v>4516225</v>
@@ -32095,7 +32095,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.37858724594116</v>
+        <v>7.37858819961548</v>
       </c>
       <c r="H1094" t="n">
         <v>3739189</v>
@@ -32153,7 +32153,7 @@
         <v>9.50399971008301</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.5910472869873</v>
+        <v>7.59104824066162</v>
       </c>
       <c r="H1096" t="n">
         <v>2859434</v>
@@ -32211,7 +32211,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.15494441986084</v>
+        <v>8.15494346618652</v>
       </c>
       <c r="H1098" t="n">
         <v>3932915</v>
@@ -32269,7 +32269,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.75398683547974</v>
+        <v>7.75398778915405</v>
       </c>
       <c r="H1100" t="n">
         <v>3245092</v>
@@ -32501,7 +32501,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G1108" t="n">
-        <v>7.92491245269775</v>
+        <v>7.92491340637207</v>
       </c>
       <c r="H1108" t="n">
         <v>3412501</v>
@@ -32530,7 +32530,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.03513717651367</v>
+        <v>8.03513813018799</v>
       </c>
       <c r="H1109" t="n">
         <v>2307002</v>
@@ -32559,7 +32559,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.17091941833496</v>
+        <v>8.17091846466064</v>
       </c>
       <c r="H1110" t="n">
         <v>2199846</v>
@@ -32617,7 +32617,7 @@
         <v>10</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.98721408843994</v>
+        <v>7.98721313476562</v>
       </c>
       <c r="H1112" t="n">
         <v>2919582</v>
@@ -32762,7 +32762,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.99919557571411</v>
+        <v>7.99919462203979</v>
       </c>
       <c r="H1117" t="n">
         <v>5418734</v>
@@ -32849,7 +32849,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.43449783325195</v>
+        <v>8.43449878692627</v>
       </c>
       <c r="H1120" t="n">
         <v>1695218</v>
@@ -32907,7 +32907,7 @@
         <v>10.8549995422363</v>
       </c>
       <c r="G1122" t="n">
-        <v>8.67012119293213</v>
+        <v>8.67012023925781</v>
       </c>
       <c r="H1122" t="n">
         <v>4731648</v>
@@ -33052,7 +33052,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1127" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1127" t="n">
         <v>6001479</v>
@@ -33139,7 +33139,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1130" t="n">
         <v>3791918</v>
@@ -33313,7 +33313,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>9.90414524078369</v>
+        <v>9.90414428710938</v>
       </c>
       <c r="H1136" t="n">
         <v>2729665</v>
@@ -33400,7 +33400,7 @@
         <v>11.8149995803833</v>
       </c>
       <c r="G1139" t="n">
-        <v>9.43689250946045</v>
+        <v>9.43689155578613</v>
       </c>
       <c r="H1139" t="n">
         <v>1809001</v>
@@ -33429,7 +33429,7 @@
         <v>12.1350002288818</v>
       </c>
       <c r="G1140" t="n">
-        <v>9.69248390197754</v>
+        <v>9.69248294830322</v>
       </c>
       <c r="H1140" t="n">
         <v>2532076</v>
@@ -33458,7 +33458,7 @@
         <v>12.0150003433228</v>
       </c>
       <c r="G1141" t="n">
-        <v>9.59663772583008</v>
+        <v>9.59663677215576</v>
       </c>
       <c r="H1141" t="n">
         <v>2925085</v>
@@ -33487,7 +33487,7 @@
         <v>12</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.58465576171875</v>
+        <v>9.58465671539307</v>
       </c>
       <c r="H1142" t="n">
         <v>2680965</v>
@@ -33516,7 +33516,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1143" t="n">
-        <v>9.97602844238281</v>
+        <v>9.97602939605713</v>
       </c>
       <c r="H1143" t="n">
         <v>3530462</v>
@@ -33574,7 +33574,7 @@
         <v>12.9350004196167</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.3314609527588</v>
+        <v>10.3314599990845</v>
       </c>
       <c r="H1145" t="n">
         <v>3020159</v>
@@ -33603,7 +33603,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.3035049438477</v>
+        <v>10.3035039901733</v>
       </c>
       <c r="H1146" t="n">
         <v>2254164</v>
@@ -33632,7 +33632,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1147" t="n">
-        <v>10.2795448303223</v>
+        <v>10.2795438766479</v>
       </c>
       <c r="H1147" t="n">
         <v>2278939</v>
@@ -33661,7 +33661,7 @@
         <v>12.4650001525879</v>
       </c>
       <c r="G1148" t="n">
-        <v>9.95606231689453</v>
+        <v>9.95606136322021</v>
       </c>
       <c r="H1148" t="n">
         <v>2497031</v>
@@ -33690,7 +33690,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.0239524841309</v>
+        <v>10.0239534378052</v>
       </c>
       <c r="H1149" t="n">
         <v>1941841</v>
@@ -33777,7 +33777,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1152" t="n">
-        <v>10.2555828094482</v>
+        <v>10.2555837631226</v>
       </c>
       <c r="H1152" t="n">
         <v>2833459</v>
@@ -33806,7 +33806,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1153" t="n">
-        <v>10.2475938796997</v>
+        <v>10.247594833374</v>
       </c>
       <c r="H1153" t="n">
         <v>1709681</v>
@@ -33835,7 +33835,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1154" t="n">
-        <v>10.2555828094482</v>
+        <v>10.2555837631226</v>
       </c>
       <c r="H1154" t="n">
         <v>2139138</v>
@@ -33893,7 +33893,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1156" t="n">
-        <v>10.3674039840698</v>
+        <v>10.3674030303955</v>
       </c>
       <c r="H1156" t="n">
         <v>3260012</v>
@@ -33922,7 +33922,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1157" t="n">
-        <v>10.5271472930908</v>
+        <v>10.5271482467651</v>
       </c>
       <c r="H1157" t="n">
         <v>2612743</v>
@@ -34096,7 +34096,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1163" t="n">
-        <v>9.72842597961426</v>
+        <v>9.72842693328857</v>
       </c>
       <c r="H1163" t="n">
         <v>3582329</v>
@@ -34154,7 +34154,7 @@
         <v>12.7049999237061</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.1477556228638</v>
+        <v>10.1477546691895</v>
       </c>
       <c r="H1165" t="n">
         <v>2727697</v>
@@ -34212,7 +34212,7 @@
         <v>12.4849996566772</v>
       </c>
       <c r="G1167" t="n">
-        <v>9.97203636169434</v>
+        <v>9.97203540802002</v>
       </c>
       <c r="H1167" t="n">
         <v>1574489</v>
@@ -34241,7 +34241,7 @@
         <v>12.335000038147</v>
       </c>
       <c r="G1168" t="n">
-        <v>9.85222816467285</v>
+        <v>9.85222911834717</v>
       </c>
       <c r="H1168" t="n">
         <v>1577674</v>
@@ -34270,7 +34270,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.0319414138794</v>
+        <v>10.0319404602051</v>
       </c>
       <c r="H1169" t="n">
         <v>1855713</v>
@@ -34328,7 +34328,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1171" t="n">
-        <v>10.6549434661865</v>
+        <v>10.6549425125122</v>
       </c>
       <c r="H1171" t="n">
         <v>4757283</v>
@@ -34357,7 +34357,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>10.4632511138916</v>
+        <v>10.4632501602173</v>
       </c>
       <c r="H1172" t="n">
         <v>2403879</v>
@@ -34415,7 +34415,7 @@
         <v>12.7950000762939</v>
       </c>
       <c r="G1174" t="n">
-        <v>10.2196388244629</v>
+        <v>10.2196407318115</v>
       </c>
       <c r="H1174" t="n">
         <v>2355822</v>
@@ -34502,7 +34502,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.3514280319214</v>
+        <v>10.3514289855957</v>
       </c>
       <c r="H1177" t="n">
         <v>1047835</v>
@@ -34560,7 +34560,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G1179" t="n">
-        <v>10.2955188751221</v>
+        <v>10.2955179214478</v>
       </c>
       <c r="H1179" t="n">
         <v>1396745</v>
@@ -34647,7 +34647,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1182" t="n">
-        <v>10.3953590393066</v>
+        <v>10.3953580856323</v>
       </c>
       <c r="H1182" t="n">
         <v>1255095</v>
@@ -34676,7 +34676,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.271556854248</v>
+        <v>10.2715559005737</v>
       </c>
       <c r="H1183" t="n">
         <v>1496652</v>
@@ -34705,7 +34705,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1184" t="n">
-        <v>10.2475938796997</v>
+        <v>10.247594833374</v>
       </c>
       <c r="H1184" t="n">
         <v>1713707</v>
@@ -34734,7 +34734,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1185" t="n">
-        <v>10.1437616348267</v>
+        <v>10.143762588501</v>
       </c>
       <c r="H1185" t="n">
         <v>1370076</v>
@@ -34763,7 +34763,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1186" t="n">
-        <v>10.2316217422485</v>
+        <v>10.2316207885742</v>
       </c>
       <c r="H1186" t="n">
         <v>1860025</v>
@@ -34908,7 +34908,7 @@
         <v>12.3450002670288</v>
       </c>
       <c r="G1191" t="n">
-        <v>9.86021614074707</v>
+        <v>9.86021518707275</v>
       </c>
       <c r="H1191" t="n">
         <v>3073555</v>
@@ -34937,7 +34937,7 @@
         <v>12.4849996566772</v>
       </c>
       <c r="G1192" t="n">
-        <v>9.97203636169434</v>
+        <v>9.97203540802002</v>
       </c>
       <c r="H1192" t="n">
         <v>1653099</v>
@@ -34995,7 +34995,7 @@
         <v>12.2849998474121</v>
       </c>
       <c r="G1194" t="n">
-        <v>9.81229209899902</v>
+        <v>9.81229114532471</v>
       </c>
       <c r="H1194" t="n">
         <v>2522094</v>
@@ -35111,7 +35111,7 @@
         <v>11.835000038147</v>
       </c>
       <c r="G1198" t="n">
-        <v>9.45286560058594</v>
+        <v>9.45286655426025</v>
       </c>
       <c r="H1198" t="n">
         <v>3900033</v>
@@ -35140,7 +35140,7 @@
         <v>11.8549995422363</v>
       </c>
       <c r="G1199" t="n">
-        <v>9.46884155273438</v>
+        <v>9.46884250640869</v>
       </c>
       <c r="H1199" t="n">
         <v>5347852</v>
@@ -35256,7 +35256,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1203" t="n">
-        <v>9.36101531982422</v>
+        <v>9.3610143661499</v>
       </c>
       <c r="H1203" t="n">
         <v>2853738</v>
@@ -35285,7 +35285,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>9.2052640914917</v>
+        <v>9.20526313781738</v>
       </c>
       <c r="H1204" t="n">
         <v>1942516</v>
@@ -35314,7 +35314,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1205" t="n">
-        <v>9.35302639007568</v>
+        <v>9.35302734375</v>
       </c>
       <c r="H1205" t="n">
         <v>1929201</v>
@@ -35372,7 +35372,7 @@
         <v>11.7550001144409</v>
       </c>
       <c r="G1207" t="n">
-        <v>9.38897037506104</v>
+        <v>9.38896942138672</v>
       </c>
       <c r="H1207" t="n">
         <v>1808298</v>
@@ -35401,7 +35401,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1208" t="n">
-        <v>9.45686149597168</v>
+        <v>9.45686054229736</v>
       </c>
       <c r="H1208" t="n">
         <v>1980347</v>
@@ -35430,7 +35430,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>9.43289947509766</v>
+        <v>9.43289852142334</v>
       </c>
       <c r="H1209" t="n">
         <v>1470610</v>
@@ -35488,7 +35488,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1211" t="n">
-        <v>9.73641204833984</v>
+        <v>9.73641300201416</v>
       </c>
       <c r="H1211" t="n">
         <v>2580855</v>
@@ -35517,7 +35517,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1212" t="n">
-        <v>9.53673362731934</v>
+        <v>9.53673267364502</v>
       </c>
       <c r="H1212" t="n">
         <v>1845468</v>
@@ -35546,7 +35546,7 @@
         <v>12.25</v>
       </c>
       <c r="G1213" t="n">
-        <v>9.78433609008789</v>
+        <v>9.78433704376221</v>
       </c>
       <c r="H1213" t="n">
         <v>1933838</v>
@@ -35633,7 +35633,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>9.70446491241455</v>
+        <v>9.70446395874023</v>
       </c>
       <c r="H1216" t="n">
         <v>1283011</v>
@@ -35778,7 +35778,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1221" t="n">
-        <v>9.59264278411865</v>
+        <v>9.59264373779297</v>
       </c>
       <c r="H1221" t="n">
         <v>1654062</v>
@@ -35865,7 +35865,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>9.23321914672852</v>
+        <v>9.2332181930542</v>
       </c>
       <c r="H1224" t="n">
         <v>1611869</v>
@@ -35923,7 +35923,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G1226" t="n">
-        <v>9.18130111694336</v>
+        <v>9.18130207061768</v>
       </c>
       <c r="H1226" t="n">
         <v>2440165</v>
@@ -36010,7 +36010,7 @@
         <v>11.75</v>
       </c>
       <c r="G1229" t="n">
-        <v>9.38497543334961</v>
+        <v>9.38497638702393</v>
       </c>
       <c r="H1229" t="n">
         <v>2210167</v>
@@ -36097,7 +36097,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1232" t="n">
-        <v>9.99999141693115</v>
+        <v>9.99999046325684</v>
       </c>
       <c r="H1232" t="n">
         <v>2555508</v>
@@ -36126,7 +36126,7 @@
         <v>12.4750003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>9.96405029296875</v>
+        <v>9.96404933929443</v>
       </c>
       <c r="H1233" t="n">
         <v>3042467</v>
@@ -36155,7 +36155,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1234" t="n">
-        <v>9.95206737518311</v>
+        <v>9.95206832885742</v>
       </c>
       <c r="H1234" t="n">
         <v>1984499</v>
@@ -36271,7 +36271,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G1238" t="n">
-        <v>9.57666873931885</v>
+        <v>9.57666969299316</v>
       </c>
       <c r="H1238" t="n">
         <v>4203286</v>
@@ -36387,7 +36387,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.1197996139526</v>
+        <v>10.119800567627</v>
       </c>
       <c r="H1242" t="n">
         <v>4296989</v>
@@ -36416,7 +36416,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1243" t="n">
-        <v>9.95206737518311</v>
+        <v>9.95206832885742</v>
       </c>
       <c r="H1243" t="n">
         <v>2113665</v>
@@ -36474,7 +36474,7 @@
         <v>12.6850004196167</v>
       </c>
       <c r="G1245" t="n">
-        <v>10.131781578064</v>
+        <v>10.1317806243896</v>
       </c>
       <c r="H1245" t="n">
         <v>2208768</v>
@@ -36503,7 +36503,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.2555828094482</v>
+        <v>10.2555837631226</v>
       </c>
       <c r="H1246" t="n">
         <v>2608186</v>
@@ -36561,7 +36561,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.3594150543213</v>
+        <v>10.3594169616699</v>
       </c>
       <c r="H1248" t="n">
         <v>4401443</v>
@@ -36648,7 +36648,7 @@
         <v>13.1850004196167</v>
       </c>
       <c r="G1251" t="n">
-        <v>10.5311422348022</v>
+        <v>10.5311412811279</v>
       </c>
       <c r="H1251" t="n">
         <v>3139294</v>
@@ -36764,7 +36764,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1255" t="n">
-        <v>10.4951992034912</v>
+        <v>10.4951982498169</v>
       </c>
       <c r="H1255" t="n">
         <v>2070881</v>
@@ -36822,7 +36822,7 @@
         <v>13.2449998855591</v>
       </c>
       <c r="G1257" t="n">
-        <v>10.579065322876</v>
+        <v>10.5790643692017</v>
       </c>
       <c r="H1257" t="n">
         <v>3081948</v>
@@ -36880,7 +36880,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1259" t="n">
-        <v>10.3514280319214</v>
+        <v>10.3514289855957</v>
       </c>
       <c r="H1259" t="n">
         <v>2657420</v>
@@ -36909,7 +36909,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G1260" t="n">
-        <v>10.4712371826172</v>
+        <v>10.4712362289429</v>
       </c>
       <c r="H1260" t="n">
         <v>2420940</v>
@@ -36938,7 +36938,7 @@
         <v>13.1850004196167</v>
       </c>
       <c r="G1261" t="n">
-        <v>10.5311422348022</v>
+        <v>10.5311412811279</v>
       </c>
       <c r="H1261" t="n">
         <v>2021242</v>
@@ -36967,7 +36967,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.3953590393066</v>
+        <v>10.3953580856323</v>
       </c>
       <c r="H1262" t="n">
         <v>2331252</v>
@@ -36996,7 +36996,7 @@
         <v>13.0749998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.4432821273804</v>
+        <v>10.4432811737061</v>
       </c>
       <c r="H1263" t="n">
         <v>1578583</v>
@@ -37025,7 +37025,7 @@
         <v>12.7950000762939</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.2196388244629</v>
+        <v>10.2196407318115</v>
       </c>
       <c r="H1264" t="n">
         <v>4986972</v>
@@ -37054,7 +37054,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.2316217422485</v>
+        <v>10.2316207885742</v>
       </c>
       <c r="H1265" t="n">
         <v>2854626</v>
@@ -37170,7 +37170,7 @@
         <v>13.3850002288818</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.6908855438232</v>
+        <v>10.6908864974976</v>
       </c>
       <c r="H1269" t="n">
         <v>1267820</v>
@@ -37257,7 +37257,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>10.7348136901855</v>
+        <v>10.7348146438599</v>
       </c>
       <c r="H1272" t="n">
         <v>2318767</v>
@@ -37315,7 +37315,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>10.97043800354</v>
+        <v>10.9704370498657</v>
       </c>
       <c r="H1274" t="n">
         <v>2651348</v>
@@ -37344,7 +37344,7 @@
         <v>13.6049995422363</v>
       </c>
       <c r="G1275" t="n">
-        <v>10.8666038513184</v>
+        <v>10.866602897644</v>
       </c>
       <c r="H1275" t="n">
         <v>1933538</v>
@@ -37373,7 +37373,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1276" t="n">
-        <v>10.97043800354</v>
+        <v>10.9704370498657</v>
       </c>
       <c r="H1276" t="n">
         <v>2545763</v>
@@ -37431,7 +37431,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1278" t="n">
-        <v>11.0942392349243</v>
+        <v>11.0942401885986</v>
       </c>
       <c r="H1278" t="n">
         <v>1878203</v>
@@ -37460,7 +37460,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543031692505</v>
       </c>
       <c r="H1279" t="n">
         <v>2276701</v>
@@ -37489,7 +37489,7 @@
         <v>13.6850004196167</v>
       </c>
       <c r="G1280" t="n">
-        <v>10.9305028915405</v>
+        <v>10.9305019378662</v>
       </c>
       <c r="H1280" t="n">
         <v>2944954</v>
@@ -37518,7 +37518,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1281" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543031692505</v>
       </c>
       <c r="H1281" t="n">
         <v>1350537</v>
@@ -37576,7 +37576,7 @@
         <v>13.4650001525879</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.7547836303711</v>
+        <v>10.7547845840454</v>
       </c>
       <c r="H1283" t="n">
         <v>1402695</v>
@@ -37721,7 +37721,7 @@
         <v>12.9549999237061</v>
       </c>
       <c r="G1288" t="n">
-        <v>10.3474359512329</v>
+        <v>10.3474349975586</v>
       </c>
       <c r="H1288" t="n">
         <v>2182575</v>
@@ -37779,7 +37779,7 @@
         <v>12.875</v>
       </c>
       <c r="G1290" t="n">
-        <v>10.2835369110107</v>
+        <v>10.2835378646851</v>
       </c>
       <c r="H1290" t="n">
         <v>1855586</v>
@@ -37808,7 +37808,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G1291" t="n">
-        <v>10.4712371826172</v>
+        <v>10.4712362289429</v>
       </c>
       <c r="H1291" t="n">
         <v>1301941</v>
@@ -37837,7 +37837,7 @@
         <v>13.3850002288818</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.6908855438232</v>
+        <v>10.6908864974976</v>
       </c>
       <c r="H1292" t="n">
         <v>2057784</v>
@@ -37895,7 +37895,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1294" t="n">
-        <v>11.5495109558105</v>
+        <v>11.5495119094849</v>
       </c>
       <c r="H1294" t="n">
         <v>4480665</v>
@@ -37982,7 +37982,7 @@
         <v>14.625</v>
       </c>
       <c r="G1297" t="n">
-        <v>11.681300163269</v>
+        <v>11.6812992095947</v>
       </c>
       <c r="H1297" t="n">
         <v>5786878</v>
@@ -38040,7 +38040,7 @@
         <v>14.7849998474121</v>
       </c>
       <c r="G1299" t="n">
-        <v>11.8090944290161</v>
+        <v>11.8090953826904</v>
       </c>
       <c r="H1299" t="n">
         <v>2016808</v>
@@ -38069,7 +38069,7 @@
         <v>15.0649995803833</v>
       </c>
       <c r="G1300" t="n">
-        <v>12.0327367782593</v>
+        <v>12.0327377319336</v>
       </c>
       <c r="H1300" t="n">
         <v>2233779</v>
@@ -38214,7 +38214,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>11.8610124588013</v>
+        <v>11.8610134124756</v>
       </c>
       <c r="H1305" t="n">
         <v>1878355</v>
@@ -38243,7 +38243,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>11.7332153320312</v>
+        <v>11.7332162857056</v>
       </c>
       <c r="H1306" t="n">
         <v>1508288</v>
@@ -38388,7 +38388,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.8330574035645</v>
+        <v>11.8330564498901</v>
       </c>
       <c r="H1311" t="n">
         <v>1577299</v>
@@ -38504,7 +38504,7 @@
         <v>14.4449996948242</v>
       </c>
       <c r="G1315" t="n">
-        <v>11.5375308990479</v>
+        <v>11.5375299453735</v>
       </c>
       <c r="H1315" t="n">
         <v>3249636</v>
@@ -38562,7 +38562,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G1317" t="n">
-        <v>11.7132482528687</v>
+        <v>11.713249206543</v>
       </c>
       <c r="H1317" t="n">
         <v>2266381</v>
@@ -38591,7 +38591,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G1318" t="n">
-        <v>11.7651653289795</v>
+        <v>11.7651662826538</v>
       </c>
       <c r="H1318" t="n">
         <v>2418327</v>
@@ -38620,7 +38620,7 @@
         <v>14.8950004577637</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.8969554901123</v>
+        <v>11.8969564437866</v>
       </c>
       <c r="H1319" t="n">
         <v>3011119</v>
@@ -38678,7 +38678,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G1321" t="n">
-        <v>11.5295419692993</v>
+        <v>11.5295429229736</v>
       </c>
       <c r="H1321" t="n">
         <v>2559551</v>
@@ -38736,7 +38736,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1323" t="n">
-        <v>11.5495109558105</v>
+        <v>11.5495119094849</v>
       </c>
       <c r="H1323" t="n">
         <v>2040470</v>
@@ -38765,7 +38765,7 @@
         <v>14.625</v>
       </c>
       <c r="G1324" t="n">
-        <v>11.681300163269</v>
+        <v>11.6812992095947</v>
       </c>
       <c r="H1324" t="n">
         <v>2036602</v>
@@ -38910,7 +38910,7 @@
         <v>13.9350004196167</v>
       </c>
       <c r="G1329" t="n">
-        <v>11.1301832199097</v>
+        <v>11.1301822662354</v>
       </c>
       <c r="H1329" t="n">
         <v>2324176</v>
@@ -38939,7 +38939,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>11.1261882781982</v>
+        <v>11.1261892318726</v>
       </c>
       <c r="H1330" t="n">
         <v>1672330</v>
@@ -39084,7 +39084,7 @@
         <v>13.8450002670288</v>
       </c>
       <c r="G1335" t="n">
-        <v>11.0582971572876</v>
+        <v>11.0582981109619</v>
       </c>
       <c r="H1335" t="n">
         <v>1961062</v>
@@ -39287,7 +39287,7 @@
         <v>14.2250003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>11.3618116378784</v>
+        <v>11.3618125915527</v>
       </c>
       <c r="H1342" t="n">
         <v>1803384</v>
@@ -39374,7 +39374,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>11.118200302124</v>
+        <v>11.1182022094727</v>
       </c>
       <c r="H1345" t="n">
         <v>2254848</v>
@@ -39432,7 +39432,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1347" t="n">
-        <v>11.0303421020508</v>
+        <v>11.0303411483765</v>
       </c>
       <c r="H1347" t="n">
         <v>1361313</v>
@@ -39461,7 +39461,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.0503091812134</v>
+        <v>11.0503101348877</v>
       </c>
       <c r="H1348" t="n">
         <v>1776773</v>
@@ -39490,7 +39490,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1349" t="n">
-        <v>11.245997428894</v>
+        <v>11.2459964752197</v>
       </c>
       <c r="H1349" t="n">
         <v>2049706</v>
@@ -39722,7 +39722,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1357" t="n">
-        <v>11.2300233840942</v>
+        <v>11.2300224304199</v>
       </c>
       <c r="H1357" t="n">
         <v>2197571</v>
@@ -39751,7 +39751,7 @@
         <v>14.1450004577637</v>
       </c>
       <c r="G1358" t="n">
-        <v>11.2979145050049</v>
+        <v>11.2979125976562</v>
       </c>
       <c r="H1358" t="n">
         <v>2141691</v>
@@ -39780,7 +39780,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1359" t="n">
-        <v>11.3098936080933</v>
+        <v>11.3098945617676</v>
       </c>
       <c r="H1359" t="n">
         <v>2759268</v>
@@ -39954,7 +39954,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1365" t="n">
-        <v>11.0503091812134</v>
+        <v>11.0503101348877</v>
       </c>
       <c r="H1365" t="n">
         <v>5330028</v>
@@ -40041,7 +40041,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.8865718841553</v>
+        <v>10.8865728378296</v>
       </c>
       <c r="H1368" t="n">
         <v>2489945</v>
@@ -40128,7 +40128,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1371" t="n">
-        <v>10.910532951355</v>
+        <v>10.9105339050293</v>
       </c>
       <c r="H1371" t="n">
         <v>1884972</v>
@@ -40157,7 +40157,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1372" t="n">
-        <v>10.9424829483032</v>
+        <v>10.9424819946289</v>
       </c>
       <c r="H1372" t="n">
         <v>3312012</v>
@@ -40186,7 +40186,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G1373" t="n">
-        <v>10.9185199737549</v>
+        <v>10.9185209274292</v>
       </c>
       <c r="H1373" t="n">
         <v>1919959</v>
@@ -40215,7 +40215,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1374" t="n">
-        <v>10.97043800354</v>
+        <v>10.9704370498657</v>
       </c>
       <c r="H1374" t="n">
         <v>1062371</v>
@@ -40360,7 +40360,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1379" t="n">
-        <v>11.245997428894</v>
+        <v>11.2459964752197</v>
       </c>
       <c r="H1379" t="n">
         <v>2432245</v>
@@ -40389,7 +40389,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1380" t="n">
-        <v>11.2140474319458</v>
+        <v>11.2140483856201</v>
       </c>
       <c r="H1380" t="n">
         <v>1937096</v>
@@ -40418,7 +40418,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1381" t="n">
-        <v>11.1341762542725</v>
+        <v>11.1341753005981</v>
       </c>
       <c r="H1381" t="n">
         <v>1518297</v>
@@ -40447,7 +40447,7 @@
         <v>13.8950004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.0982332229614</v>
+        <v>11.0982322692871</v>
       </c>
       <c r="H1382" t="n">
         <v>1378576</v>
@@ -40708,7 +40708,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.6533441543579</v>
+        <v>11.6533451080322</v>
       </c>
       <c r="H1391" t="n">
         <v>2668942</v>
@@ -40737,7 +40737,7 @@
         <v>14.7250003814697</v>
       </c>
       <c r="G1392" t="n">
-        <v>11.7611722946167</v>
+        <v>11.761173248291</v>
       </c>
       <c r="H1392" t="n">
         <v>1871889</v>
@@ -40882,7 +40882,7 @@
         <v>14.7049999237061</v>
       </c>
       <c r="G1397" t="n">
-        <v>11.7451982498169</v>
+        <v>11.7451972961426</v>
       </c>
       <c r="H1397" t="n">
         <v>2503933</v>
@@ -41027,7 +41027,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1402" t="n">
-        <v>11.701268196106</v>
+        <v>11.7012672424316</v>
       </c>
       <c r="H1402" t="n">
         <v>6079468</v>
@@ -41114,7 +41114,7 @@
         <v>14.7049999237061</v>
       </c>
       <c r="G1405" t="n">
-        <v>11.7451982498169</v>
+        <v>11.7451972961426</v>
       </c>
       <c r="H1405" t="n">
         <v>3201643</v>
@@ -41143,7 +41143,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G1406" t="n">
-        <v>11.5934410095215</v>
+        <v>11.5934419631958</v>
       </c>
       <c r="H1406" t="n">
         <v>1662545</v>
@@ -41230,7 +41230,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.0503091812134</v>
+        <v>11.0503101348877</v>
       </c>
       <c r="H1409" t="n">
         <v>2133933</v>
@@ -41259,7 +41259,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0543041229248</v>
+        <v>11.0543031692505</v>
       </c>
       <c r="H1410" t="n">
         <v>1386695</v>
@@ -41491,7 +41491,7 @@
         <v>15.1149997711182</v>
       </c>
       <c r="G1418" t="n">
-        <v>12.0726728439331</v>
+        <v>12.0726718902588</v>
       </c>
       <c r="H1418" t="n">
         <v>2580461</v>
@@ -41578,7 +41578,7 @@
         <v>15.4049997329712</v>
       </c>
       <c r="G1421" t="n">
-        <v>12.3043022155762</v>
+        <v>12.3043012619019</v>
       </c>
       <c r="H1421" t="n">
         <v>3606884</v>
@@ -41607,7 +41607,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.4201183319092</v>
+        <v>12.4201173782349</v>
       </c>
       <c r="H1422" t="n">
         <v>2549177</v>
@@ -41636,7 +41636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.7396059036255</v>
+        <v>12.7396049499512</v>
       </c>
       <c r="H1423" t="n">
         <v>2715997</v>
@@ -41665,7 +41665,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G1424" t="n">
-        <v>12.8873710632324</v>
+        <v>12.8873701095581</v>
       </c>
       <c r="H1424" t="n">
         <v>1332826</v>
@@ -41694,7 +41694,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1425" t="n">
-        <v>12.9552612304688</v>
+        <v>12.9552602767944</v>
       </c>
       <c r="H1425" t="n">
         <v>1568736</v>
@@ -41839,7 +41839,7 @@
         <v>15.9449996948242</v>
       </c>
       <c r="G1430" t="n">
-        <v>12.7356109619141</v>
+        <v>12.7356119155884</v>
       </c>
       <c r="H1430" t="n">
         <v>1600785</v>
@@ -41897,7 +41897,7 @@
         <v>15.9350004196167</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.7276248931885</v>
+        <v>12.7276258468628</v>
       </c>
       <c r="H1432" t="n">
         <v>2077557</v>
@@ -41984,7 +41984,7 @@
         <v>15.8950004577637</v>
       </c>
       <c r="G1435" t="n">
-        <v>12.6956768035889</v>
+        <v>12.6956758499146</v>
       </c>
       <c r="H1435" t="n">
         <v>1183165</v>
@@ -42013,7 +42013,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1436" t="n">
-        <v>12.767560005188</v>
+        <v>12.7675619125366</v>
       </c>
       <c r="H1436" t="n">
         <v>1011161</v>
@@ -42071,7 +42071,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G1438" t="n">
-        <v>12.7715549468994</v>
+        <v>12.7715539932251</v>
       </c>
       <c r="H1438" t="n">
         <v>908449</v>
@@ -42100,7 +42100,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G1439" t="n">
-        <v>12.7715549468994</v>
+        <v>12.7715539932251</v>
       </c>
       <c r="H1439" t="n">
         <v>546445</v>
@@ -42129,7 +42129,7 @@
         <v>15.6149997711182</v>
       </c>
       <c r="G1440" t="n">
-        <v>12.4720335006714</v>
+        <v>12.4720325469971</v>
       </c>
       <c r="H1440" t="n">
         <v>2974290</v>
@@ -42187,7 +42187,7 @@
         <v>15.5150003433228</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.3921613693237</v>
+        <v>12.392162322998</v>
       </c>
       <c r="H1442" t="n">
         <v>1547130</v>
@@ -42245,7 +42245,7 @@
         <v>15.4250001907349</v>
       </c>
       <c r="G1444" t="n">
-        <v>12.3202781677246</v>
+        <v>12.3202772140503</v>
       </c>
       <c r="H1444" t="n">
         <v>1175282</v>
@@ -42390,7 +42390,7 @@
         <v>15.2650003433228</v>
       </c>
       <c r="G1449" t="n">
-        <v>12.1924810409546</v>
+        <v>12.1924819946289</v>
       </c>
       <c r="H1449" t="n">
         <v>1028998</v>
@@ -42506,7 +42506,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1453" t="n">
-        <v>12.6357707977295</v>
+        <v>12.6357717514038</v>
       </c>
       <c r="H1453" t="n">
         <v>4244704</v>
@@ -42564,7 +42564,7 @@
         <v>15.6149997711182</v>
       </c>
       <c r="G1455" t="n">
-        <v>12.4720335006714</v>
+        <v>12.4720325469971</v>
       </c>
       <c r="H1455" t="n">
         <v>1297633</v>
@@ -42593,7 +42593,7 @@
         <v>15.6850004196167</v>
       </c>
       <c r="G1456" t="n">
-        <v>12.5279445648193</v>
+        <v>12.5279455184937</v>
       </c>
       <c r="H1456" t="n">
         <v>1260691</v>
@@ -42622,7 +42622,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G1457" t="n">
-        <v>12.7515869140625</v>
+        <v>12.7515878677368</v>
       </c>
       <c r="H1457" t="n">
         <v>1567852</v>
@@ -42651,7 +42651,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1458" t="n">
-        <v>12.7396059036255</v>
+        <v>12.7396049499512</v>
       </c>
       <c r="H1458" t="n">
         <v>1335880</v>
@@ -42767,7 +42767,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1462" t="n">
-        <v>12.5159635543823</v>
+        <v>12.515962600708</v>
       </c>
       <c r="H1462" t="n">
         <v>1816069</v>
@@ -42796,7 +42796,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G1463" t="n">
-        <v>12.2963151931763</v>
+        <v>12.2963161468506</v>
       </c>
       <c r="H1463" t="n">
         <v>1650097</v>
@@ -42854,7 +42854,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1465" t="n">
-        <v>12.4920015335083</v>
+        <v>12.4920024871826</v>
       </c>
       <c r="H1465" t="n">
         <v>1777738</v>
@@ -42883,7 +42883,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1466" t="n">
-        <v>12.5079765319824</v>
+        <v>12.5079774856567</v>
       </c>
       <c r="H1466" t="n">
         <v>1754636</v>
@@ -42912,7 +42912,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1467" t="n">
-        <v>12.5479125976562</v>
+        <v>12.5479116439819</v>
       </c>
       <c r="H1467" t="n">
         <v>1599052</v>
@@ -43028,7 +43028,7 @@
         <v>15.8149995803833</v>
       </c>
       <c r="G1471" t="n">
-        <v>12.6317777633667</v>
+        <v>12.631778717041</v>
       </c>
       <c r="H1471" t="n">
         <v>1311446</v>
@@ -43086,7 +43086,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1473" t="n">
-        <v>13.2747488021851</v>
+        <v>13.2747497558594</v>
       </c>
       <c r="H1473" t="n">
         <v>2062427</v>
@@ -43173,7 +43173,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1476" t="n">
-        <v>13.2907228469849</v>
+        <v>13.2907238006592</v>
       </c>
       <c r="H1476" t="n">
         <v>1193898</v>
@@ -43202,7 +43202,7 @@
         <v>16.6049995422363</v>
       </c>
       <c r="G1477" t="n">
-        <v>13.262767791748</v>
+        <v>13.2627658843994</v>
       </c>
       <c r="H1477" t="n">
         <v>1049924</v>
@@ -43347,7 +43347,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>13.2188367843628</v>
+        <v>13.2188358306885</v>
       </c>
       <c r="H1482" t="n">
         <v>1516881</v>
@@ -43376,7 +43376,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1483" t="n">
-        <v>13.1908826828003</v>
+        <v>13.190881729126</v>
       </c>
       <c r="H1483" t="n">
         <v>2049036</v>
@@ -43463,7 +43463,7 @@
         <v>16.9850006103516</v>
       </c>
       <c r="G1486" t="n">
-        <v>13.5662822723389</v>
+        <v>13.5662832260132</v>
       </c>
       <c r="H1486" t="n">
         <v>1958921</v>
@@ -43492,7 +43492,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1487" t="n">
-        <v>13.4983901977539</v>
+        <v>13.4983921051025</v>
       </c>
       <c r="H1487" t="n">
         <v>1790777</v>
@@ -43608,7 +43608,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1491" t="n">
-        <v>13.6341743469238</v>
+        <v>13.6341733932495</v>
       </c>
       <c r="H1491" t="n">
         <v>2128741</v>
@@ -43666,7 +43666,7 @@
         <v>17.3050003051758</v>
       </c>
       <c r="G1493" t="n">
-        <v>13.821873664856</v>
+        <v>13.8218746185303</v>
       </c>
       <c r="H1493" t="n">
         <v>1148182</v>
@@ -43724,7 +43724,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G1495" t="n">
-        <v>13.7340126037598</v>
+        <v>13.7340135574341</v>
       </c>
       <c r="H1495" t="n">
         <v>1671596</v>
@@ -43782,7 +43782,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1497" t="n">
-        <v>13.6900825500488</v>
+        <v>13.6900835037231</v>
       </c>
       <c r="H1497" t="n">
         <v>1392449</v>
@@ -43811,7 +43811,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1498" t="n">
-        <v>13.6022233963013</v>
+        <v>13.6022253036499</v>
       </c>
       <c r="H1498" t="n">
         <v>2170985</v>
@@ -43927,7 +43927,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>13.1488170623779</v>
+        <v>13.1488161087036</v>
       </c>
       <c r="H1502" t="n">
         <v>1269802</v>
@@ -43956,7 +43956,7 @@
         <v>15.5150003433228</v>
       </c>
       <c r="G1503" t="n">
-        <v>12.7902126312256</v>
+        <v>12.7902135848999</v>
       </c>
       <c r="H1503" t="n">
         <v>2565078</v>
@@ -44014,7 +44014,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>12.7696046829224</v>
+        <v>12.769603729248</v>
       </c>
       <c r="H1505" t="n">
         <v>3379076</v>
@@ -44043,7 +44043,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G1506" t="n">
-        <v>12.9385995864868</v>
+        <v>12.9386005401611</v>
       </c>
       <c r="H1506" t="n">
         <v>1845630</v>
@@ -44072,7 +44072,7 @@
         <v>15.3450002670288</v>
       </c>
       <c r="G1507" t="n">
-        <v>12.6500692367554</v>
+        <v>12.6500682830811</v>
       </c>
       <c r="H1507" t="n">
         <v>1654045</v>
@@ -44101,7 +44101,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="n">
-        <v>12.695408821106</v>
+        <v>12.6954097747803</v>
       </c>
       <c r="H1508" t="n">
         <v>1293890</v>
@@ -44159,7 +44159,7 @@
         <v>16.2450008392334</v>
       </c>
       <c r="G1510" t="n">
-        <v>13.3920097351074</v>
+        <v>13.3920087814331</v>
       </c>
       <c r="H1510" t="n">
         <v>1640760</v>
@@ -44188,7 +44188,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1511" t="n">
-        <v>13.1405735015869</v>
+        <v>13.1405725479126</v>
       </c>
       <c r="H1511" t="n">
         <v>1550516</v>
@@ -44217,7 +44217,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1512" t="n">
-        <v>12.950966835022</v>
+        <v>12.9509658813477</v>
       </c>
       <c r="H1512" t="n">
         <v>1176800</v>
@@ -44246,7 +44246,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G1513" t="n">
-        <v>12.9221143722534</v>
+        <v>12.9221134185791</v>
       </c>
       <c r="H1513" t="n">
         <v>947323</v>
@@ -44275,7 +44275,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1514" t="n">
-        <v>12.9015035629272</v>
+        <v>12.9015045166016</v>
       </c>
       <c r="H1514" t="n">
         <v>1040289</v>
@@ -44304,7 +44304,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G1515" t="n">
-        <v>12.9385995864868</v>
+        <v>12.9386005401611</v>
       </c>
       <c r="H1515" t="n">
         <v>1022511</v>
@@ -44362,7 +44362,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1517" t="n">
-        <v>13.0251617431641</v>
+        <v>13.0251607894897</v>
       </c>
       <c r="H1517" t="n">
         <v>1272662</v>
@@ -44391,7 +44391,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1518" t="n">
-        <v>12.5140466690063</v>
+        <v>12.5140476226807</v>
       </c>
       <c r="H1518" t="n">
         <v>4380917</v>
@@ -44449,7 +44449,7 @@
         <v>15.1450004577637</v>
       </c>
       <c r="G1520" t="n">
-        <v>12.4851942062378</v>
+        <v>12.4851951599121</v>
       </c>
       <c r="H1520" t="n">
         <v>1000909</v>
@@ -44536,7 +44536,7 @@
         <v>15.3450002670288</v>
       </c>
       <c r="G1523" t="n">
-        <v>12.6500692367554</v>
+        <v>12.6500682830811</v>
       </c>
       <c r="H1523" t="n">
         <v>836172</v>
@@ -44623,7 +44623,7 @@
         <v>15.4350004196167</v>
       </c>
       <c r="G1526" t="n">
-        <v>12.7242631912231</v>
+        <v>12.7242641448975</v>
       </c>
       <c r="H1526" t="n">
         <v>598379</v>
@@ -44652,7 +44652,7 @@
         <v>15.7150001525879</v>
       </c>
       <c r="G1527" t="n">
-        <v>12.9550886154175</v>
+        <v>12.9550895690918</v>
       </c>
       <c r="H1527" t="n">
         <v>1349901</v>
@@ -44681,7 +44681,7 @@
         <v>15.7550001144409</v>
       </c>
       <c r="G1528" t="n">
-        <v>12.9880628585815</v>
+        <v>12.9880638122559</v>
       </c>
       <c r="H1528" t="n">
         <v>1478008</v>
@@ -44710,7 +44710,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1529" t="n">
-        <v>13.1776695251465</v>
+        <v>13.1776714324951</v>
       </c>
       <c r="H1529" t="n">
         <v>1355812</v>
@@ -44739,7 +44739,7 @@
         <v>15.4849996566772</v>
       </c>
       <c r="G1530" t="n">
-        <v>12.7654809951782</v>
+        <v>12.7654819488525</v>
       </c>
       <c r="H1530" t="n">
         <v>2272621</v>
@@ -44826,7 +44826,7 @@
         <v>15.5150003433228</v>
       </c>
       <c r="G1533" t="n">
-        <v>12.7902126312256</v>
+        <v>12.7902135848999</v>
       </c>
       <c r="H1533" t="n">
         <v>1571174</v>
@@ -44855,7 +44855,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G1534" t="n">
-        <v>13.2642307281494</v>
+        <v>13.2642297744751</v>
       </c>
       <c r="H1534" t="n">
         <v>2695752</v>
@@ -44942,7 +44942,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1537" t="n">
-        <v>13.1075973510742</v>
+        <v>13.1075983047485</v>
       </c>
       <c r="H1537" t="n">
         <v>985261</v>
@@ -45000,7 +45000,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1539" t="n">
-        <v>12.5470218658447</v>
+        <v>12.547022819519</v>
       </c>
       <c r="H1539" t="n">
         <v>2294685</v>
@@ -45058,7 +45058,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1541" t="n">
-        <v>12.6459465026855</v>
+        <v>12.6459474563599</v>
       </c>
       <c r="H1541" t="n">
         <v>2180893</v>
@@ -45145,7 +45145,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1544" t="n">
-        <v>12.0853700637817</v>
+        <v>12.0853691101074</v>
       </c>
       <c r="H1544" t="n">
         <v>1509739</v>
@@ -45174,7 +45174,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1545" t="n">
-        <v>12.0276641845703</v>
+        <v>12.0276651382446</v>
       </c>
       <c r="H1545" t="n">
         <v>2375692</v>
@@ -45203,7 +45203,7 @@
         <v>14.585000038147</v>
       </c>
       <c r="G1546" t="n">
-        <v>12.0235433578491</v>
+        <v>12.0235424041748</v>
       </c>
       <c r="H1546" t="n">
         <v>1506097</v>
@@ -45261,7 +45261,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G1548" t="n">
-        <v>12.3780241012573</v>
+        <v>12.3780250549316</v>
       </c>
       <c r="H1548" t="n">
         <v>1831032</v>
@@ -45290,7 +45290,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1549" t="n">
-        <v>12.4233655929565</v>
+        <v>12.4233646392822</v>
       </c>
       <c r="H1549" t="n">
         <v>1472435</v>
@@ -45319,7 +45319,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G1550" t="n">
-        <v>12.2543687820435</v>
+        <v>12.2543678283691</v>
       </c>
       <c r="H1550" t="n">
         <v>1748162</v>
@@ -45348,7 +45348,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1551" t="n">
-        <v>12.2955865859985</v>
+        <v>12.2955875396729</v>
       </c>
       <c r="H1551" t="n">
         <v>2768969</v>
@@ -45435,7 +45435,7 @@
         <v>15.9049997329712</v>
       </c>
       <c r="G1554" t="n">
-        <v>13.111720085144</v>
+        <v>13.1117191314697</v>
       </c>
       <c r="H1554" t="n">
         <v>3579390</v>
@@ -45522,7 +45522,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1557" t="n">
-        <v>12.7696046829224</v>
+        <v>12.769603729248</v>
       </c>
       <c r="H1557" t="n">
         <v>2118294</v>
@@ -45580,7 +45580,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1559" t="n">
-        <v>13.1735486984253</v>
+        <v>13.173547744751</v>
       </c>
       <c r="H1559" t="n">
         <v>1914655</v>
@@ -45609,7 +45609,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1560" t="n">
-        <v>13.0416469573975</v>
+        <v>13.0416479110718</v>
       </c>
       <c r="H1560" t="n">
         <v>2268011</v>
@@ -45638,7 +45638,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>13.1776695251465</v>
+        <v>13.1776714324951</v>
       </c>
       <c r="H1561" t="n">
         <v>2426206</v>
@@ -45754,7 +45754,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1565" t="n">
-        <v>11.9699573516846</v>
+        <v>11.9699583053589</v>
       </c>
       <c r="H1565" t="n">
         <v>4647565</v>
@@ -45783,7 +45783,7 @@
         <v>14.8549995422363</v>
       </c>
       <c r="G1566" t="n">
-        <v>12.2461233139038</v>
+        <v>12.2461242675781</v>
       </c>
       <c r="H1566" t="n">
         <v>3467052</v>
@@ -45870,7 +45870,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1569" t="n">
-        <v>11.590744972229</v>
+        <v>11.5907440185547</v>
       </c>
       <c r="H1569" t="n">
         <v>2348018</v>
@@ -45899,7 +45899,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G1570" t="n">
-        <v>11.3970146179199</v>
+        <v>11.3970155715942</v>
       </c>
       <c r="H1570" t="n">
         <v>1475218</v>
@@ -45957,7 +45957,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.4695911407471</v>
+        <v>10.4695920944214</v>
       </c>
       <c r="H1572" t="n">
         <v>5012765</v>
@@ -46131,7 +46131,7 @@
         <v>13.8950004577637</v>
       </c>
       <c r="G1578" t="n">
-        <v>11.45472240448</v>
+        <v>11.4547214508057</v>
       </c>
       <c r="H1578" t="n">
         <v>1374985</v>
@@ -46363,7 +46363,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1586" t="n">
-        <v>11.4093818664551</v>
+        <v>11.4093809127808</v>
       </c>
       <c r="H1586" t="n">
         <v>2125461</v>
@@ -46479,7 +46479,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G1590" t="n">
-        <v>11.3970146179199</v>
+        <v>11.3970155715942</v>
       </c>
       <c r="H1590" t="n">
         <v>3572823</v>
@@ -46537,7 +46537,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1592" t="n">
-        <v>11.8545436859131</v>
+        <v>11.8545446395874</v>
       </c>
       <c r="H1592" t="n">
         <v>1271450</v>
@@ -46624,7 +46624,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G1595" t="n">
-        <v>11.6773042678833</v>
+        <v>11.677303314209</v>
       </c>
       <c r="H1595" t="n">
         <v>1654206</v>
@@ -46653,7 +46653,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G1596" t="n">
-        <v>11.8627882003784</v>
+        <v>11.8627891540527</v>
       </c>
       <c r="H1596" t="n">
         <v>1215368</v>
@@ -46682,7 +46682,7 @@
         <v>14.2749996185303</v>
       </c>
       <c r="G1597" t="n">
-        <v>11.7679853439331</v>
+        <v>11.7679843902588</v>
       </c>
       <c r="H1597" t="n">
         <v>1267353</v>
@@ -46740,7 +46740,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G1599" t="n">
-        <v>11.4670867919922</v>
+        <v>11.4670877456665</v>
       </c>
       <c r="H1599" t="n">
         <v>1451350</v>
@@ -46769,7 +46769,7 @@
         <v>13.9049997329712</v>
       </c>
       <c r="G1600" t="n">
-        <v>11.462965965271</v>
+        <v>11.4629650115967</v>
       </c>
       <c r="H1600" t="n">
         <v>1448586</v>
@@ -46885,7 +46885,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1604" t="n">
-        <v>11.4258689880371</v>
+        <v>11.4258680343628</v>
       </c>
       <c r="H1604" t="n">
         <v>1692881</v>
@@ -47001,7 +47001,7 @@
         <v>13.1750001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>10.8611707687378</v>
+        <v>10.8611717224121</v>
       </c>
       <c r="H1608" t="n">
         <v>1382613</v>
@@ -47146,7 +47146,7 @@
         <v>12.9549999237061</v>
       </c>
       <c r="G1613" t="n">
-        <v>10.6798076629639</v>
+        <v>10.6798067092896</v>
       </c>
       <c r="H1613" t="n">
         <v>1615033</v>
@@ -47175,7 +47175,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>10.1810598373413</v>
+        <v>10.181058883667</v>
       </c>
       <c r="H1614" t="n">
         <v>3169521</v>
@@ -47204,7 +47204,7 @@
         <v>11.7449998855591</v>
       </c>
       <c r="G1615" t="n">
-        <v>9.68231201171875</v>
+        <v>9.68231105804443</v>
       </c>
       <c r="H1615" t="n">
         <v>1883329</v>
@@ -47233,7 +47233,7 @@
         <v>11.7749996185303</v>
       </c>
       <c r="G1616" t="n">
-        <v>9.7070426940918</v>
+        <v>9.70704174041748</v>
       </c>
       <c r="H1616" t="n">
         <v>2686537</v>
@@ -47262,7 +47262,7 @@
         <v>12.25</v>
       </c>
       <c r="G1617" t="n">
-        <v>10.0986204147339</v>
+        <v>10.0986213684082</v>
       </c>
       <c r="H1617" t="n">
         <v>2016295</v>
@@ -47291,7 +47291,7 @@
         <v>12.0050001144409</v>
       </c>
       <c r="G1618" t="n">
-        <v>9.89664936065674</v>
+        <v>9.89664840698242</v>
       </c>
       <c r="H1618" t="n">
         <v>1774049</v>
@@ -47320,7 +47320,7 @@
         <v>12.375</v>
       </c>
       <c r="G1619" t="n">
-        <v>10.2016687393188</v>
+        <v>10.2016696929932</v>
       </c>
       <c r="H1619" t="n">
         <v>1395068</v>
@@ -47349,7 +47349,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G1620" t="n">
-        <v>10.2181558609009</v>
+        <v>10.2181568145752</v>
       </c>
       <c r="H1620" t="n">
         <v>1077474</v>
@@ -47378,7 +47378,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1621" t="n">
-        <v>10.4283723831177</v>
+        <v>10.4283714294434</v>
       </c>
       <c r="H1621" t="n">
         <v>1833576</v>
@@ -80038,6 +80038,35 @@
         <v>1737728</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>21.0499992370605</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>21.1700000762939</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>20.6299991607666</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>20.6299991607666</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>20.6299991607666</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>1574414</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -456,7 +456,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12352514266968</v>
+        <v>5.12352609634399</v>
       </c>
       <c r="H3" t="n">
         <v>1067026</v>
@@ -485,7 +485,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>4.98062467575073</v>
+        <v>4.98062515258789</v>
       </c>
       <c r="H4" t="n">
         <v>1113419</v>
@@ -572,7 +572,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G7" t="n">
-        <v>4.94228553771973</v>
+        <v>4.94228601455688</v>
       </c>
       <c r="H7" t="n">
         <v>1267080</v>
@@ -630,7 +630,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G9" t="n">
-        <v>5.11655473709106</v>
+        <v>5.11655521392822</v>
       </c>
       <c r="H9" t="n">
         <v>884030</v>
@@ -659,7 +659,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G10" t="n">
-        <v>5.00153779983521</v>
+        <v>5.00153684616089</v>
       </c>
       <c r="H10" t="n">
         <v>950617</v>
@@ -688,7 +688,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G11" t="n">
-        <v>4.85863637924194</v>
+        <v>4.85863590240479</v>
       </c>
       <c r="H11" t="n">
         <v>1145452</v>
@@ -717,7 +717,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G12" t="n">
-        <v>4.74710369110107</v>
+        <v>4.74710321426392</v>
       </c>
       <c r="H12" t="n">
         <v>1179387</v>
@@ -775,7 +775,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G14" t="n">
-        <v>4.48569822311401</v>
+        <v>4.48569869995117</v>
       </c>
       <c r="H14" t="n">
         <v>1521693</v>
@@ -804,7 +804,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>4.64254140853882</v>
+        <v>4.64254188537598</v>
       </c>
       <c r="H15" t="n">
         <v>1328854</v>
@@ -891,7 +891,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>4.86560678482056</v>
+        <v>4.86560773849487</v>
       </c>
       <c r="H18" t="n">
         <v>810566</v>
@@ -920,7 +920,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>5.01896381378174</v>
+        <v>5.0189642906189</v>
       </c>
       <c r="H19" t="n">
         <v>1495887</v>
@@ -1036,7 +1036,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>4.93531465530396</v>
+        <v>4.9353141784668</v>
       </c>
       <c r="H23" t="n">
         <v>890820</v>
@@ -1065,7 +1065,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>4.70876407623291</v>
+        <v>4.70876359939575</v>
       </c>
       <c r="H24" t="n">
         <v>2067827</v>
@@ -1094,7 +1094,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>4.61465835571289</v>
+        <v>4.61465883255005</v>
       </c>
       <c r="H25" t="n">
         <v>1487324</v>
@@ -1152,7 +1152,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>4.39856386184692</v>
+        <v>4.39856433868408</v>
       </c>
       <c r="H27" t="n">
         <v>1769827</v>
@@ -1181,7 +1181,7 @@
         <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>4.18246984481812</v>
+        <v>4.18247032165527</v>
       </c>
       <c r="H28" t="n">
         <v>4309103</v>
@@ -1210,7 +1210,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G29" t="n">
-        <v>4.29051733016968</v>
+        <v>4.29051780700684</v>
       </c>
       <c r="H29" t="n">
         <v>2729696</v>
@@ -1239,7 +1239,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G30" t="n">
-        <v>4.31840085983276</v>
+        <v>4.31839990615845</v>
       </c>
       <c r="H30" t="n">
         <v>1926770</v>
@@ -1297,7 +1297,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G32" t="n">
-        <v>4.60768842697144</v>
+        <v>4.60768747329712</v>
       </c>
       <c r="H32" t="n">
         <v>1203737</v>
@@ -1355,7 +1355,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>4.63557100296021</v>
+        <v>4.63557052612305</v>
       </c>
       <c r="H34" t="n">
         <v>2143900</v>
@@ -1384,7 +1384,7 @@
         <v>6.58500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>4.59026050567627</v>
+        <v>4.59026098251343</v>
       </c>
       <c r="H35" t="n">
         <v>1191515</v>
@@ -1442,7 +1442,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.65299797058105</v>
+        <v>4.65299844741821</v>
       </c>
       <c r="H37" t="n">
         <v>876495</v>
@@ -1529,7 +1529,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>4.82378244400024</v>
+        <v>4.8237829208374</v>
       </c>
       <c r="H40" t="n">
         <v>1384817</v>
@@ -1558,7 +1558,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G41" t="n">
-        <v>4.90394592285156</v>
+        <v>4.90394639968872</v>
       </c>
       <c r="H41" t="n">
         <v>1286913</v>
@@ -1616,7 +1616,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G43" t="n">
-        <v>4.98062467575073</v>
+        <v>4.98062515258789</v>
       </c>
       <c r="H43" t="n">
         <v>820528</v>
@@ -1645,7 +1645,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>4.93531465530396</v>
+        <v>4.9353141784668</v>
       </c>
       <c r="H44" t="n">
         <v>1499459</v>
@@ -1674,7 +1674,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.97713994979858</v>
+        <v>4.97713947296143</v>
       </c>
       <c r="H45" t="n">
         <v>1200447</v>
@@ -1703,7 +1703,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>4.93531465530396</v>
+        <v>4.9353141784668</v>
       </c>
       <c r="H46" t="n">
         <v>964840</v>
@@ -1732,7 +1732,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G47" t="n">
-        <v>4.7715015411377</v>
+        <v>4.77150058746338</v>
       </c>
       <c r="H47" t="n">
         <v>1598235</v>
@@ -1790,7 +1790,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>4.60420227050781</v>
+        <v>4.60420322418213</v>
       </c>
       <c r="H49" t="n">
         <v>1135132</v>
@@ -1819,7 +1819,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G50" t="n">
-        <v>4.7715015411377</v>
+        <v>4.77150058746338</v>
       </c>
       <c r="H50" t="n">
         <v>1777322</v>
@@ -1848,7 +1848,7 @@
         <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>4.8795485496521</v>
+        <v>4.87954807281494</v>
       </c>
       <c r="H51" t="n">
         <v>1102638</v>
@@ -1877,7 +1877,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.90046119689941</v>
+        <v>4.90046072006226</v>
       </c>
       <c r="H52" t="n">
         <v>1406683</v>
@@ -1964,7 +1964,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>4.82029676437378</v>
+        <v>4.82029628753662</v>
       </c>
       <c r="H55" t="n">
         <v>882262</v>
@@ -2022,7 +2022,7 @@
         <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>4.8795485496521</v>
+        <v>4.87954807281494</v>
       </c>
       <c r="H57" t="n">
         <v>1525752</v>
@@ -2051,7 +2051,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>4.93531465530396</v>
+        <v>4.9353141784668</v>
       </c>
       <c r="H58" t="n">
         <v>1306433</v>
@@ -2080,7 +2080,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>4.98062467575073</v>
+        <v>4.98062515258789</v>
       </c>
       <c r="H59" t="n">
         <v>1309079</v>
@@ -2109,7 +2109,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>4.99805116653442</v>
+        <v>4.99805164337158</v>
       </c>
       <c r="H60" t="n">
         <v>1297200</v>
@@ -2167,7 +2167,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>5.15838003158569</v>
+        <v>5.15837907791138</v>
       </c>
       <c r="H62" t="n">
         <v>3573879</v>
@@ -2196,7 +2196,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.15838003158569</v>
+        <v>5.15837907791138</v>
       </c>
       <c r="H63" t="n">
         <v>7332824</v>
@@ -2254,7 +2254,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>4.93880033493042</v>
+        <v>4.93879985809326</v>
       </c>
       <c r="H65" t="n">
         <v>1641462</v>
@@ -2283,7 +2283,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G66" t="n">
-        <v>4.83423852920532</v>
+        <v>4.83423900604248</v>
       </c>
       <c r="H66" t="n">
         <v>2726318</v>
@@ -2312,7 +2312,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G67" t="n">
-        <v>4.79589986801147</v>
+        <v>4.79589939117432</v>
       </c>
       <c r="H67" t="n">
         <v>1700880</v>
@@ -2341,7 +2341,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>4.65299797058105</v>
+        <v>4.65299844741821</v>
       </c>
       <c r="H68" t="n">
         <v>1526742</v>
@@ -2370,7 +2370,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>4.76453113555908</v>
+        <v>4.76453065872192</v>
       </c>
       <c r="H69" t="n">
         <v>1610753</v>
@@ -2399,7 +2399,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.78892755508423</v>
+        <v>4.78892803192139</v>
       </c>
       <c r="H70" t="n">
         <v>1226391</v>
@@ -2457,7 +2457,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>4.83772420883179</v>
+        <v>4.83772373199463</v>
       </c>
       <c r="H72" t="n">
         <v>1303785</v>
@@ -2486,7 +2486,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G73" t="n">
-        <v>4.92485857009888</v>
+        <v>4.92485904693604</v>
       </c>
       <c r="H73" t="n">
         <v>1466819</v>
@@ -2544,7 +2544,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>5.13792514801025</v>
+        <v>5.13792419433594</v>
       </c>
       <c r="H75" t="n">
         <v>2392811</v>
@@ -2573,7 +2573,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G76" t="n">
-        <v>5.0403003692627</v>
+        <v>5.04029989242554</v>
       </c>
       <c r="H76" t="n">
         <v>1288181</v>
@@ -2602,7 +2602,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.08730459213257</v>
+        <v>5.08730411529541</v>
       </c>
       <c r="H77" t="n">
         <v>1355061</v>
@@ -2631,7 +2631,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>5.07645750045776</v>
+        <v>5.07645797729492</v>
       </c>
       <c r="H78" t="n">
         <v>1460707</v>
@@ -2660,7 +2660,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.03668451309204</v>
+        <v>5.0366849899292</v>
       </c>
       <c r="H79" t="n">
         <v>661831</v>
@@ -2718,7 +2718,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>5.13430833816528</v>
+        <v>5.13430881500244</v>
       </c>
       <c r="H81" t="n">
         <v>1260119</v>
@@ -2747,7 +2747,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>5.10538291931152</v>
+        <v>5.10538387298584</v>
       </c>
       <c r="H82" t="n">
         <v>984394</v>
@@ -2805,7 +2805,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>5.06922626495361</v>
+        <v>5.06922674179077</v>
       </c>
       <c r="H84" t="n">
         <v>1187575</v>
@@ -2863,7 +2863,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G86" t="n">
-        <v>4.87036180496216</v>
+        <v>4.87036228179932</v>
       </c>
       <c r="H86" t="n">
         <v>1509534</v>
@@ -2892,7 +2892,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G87" t="n">
-        <v>4.91013479232788</v>
+        <v>4.91013526916504</v>
       </c>
       <c r="H87" t="n">
         <v>881025</v>
@@ -3037,7 +3037,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>4.58833599090576</v>
+        <v>4.58833646774292</v>
       </c>
       <c r="H92" t="n">
         <v>1279308</v>
@@ -3066,7 +3066,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G93" t="n">
-        <v>4.5268702507019</v>
+        <v>4.52686977386475</v>
       </c>
       <c r="H93" t="n">
         <v>1100368</v>
@@ -3124,7 +3124,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G95" t="n">
-        <v>4.77997016906738</v>
+        <v>4.77996921539307</v>
       </c>
       <c r="H95" t="n">
         <v>1736284</v>
@@ -3153,7 +3153,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G96" t="n">
-        <v>4.72211885452271</v>
+        <v>4.72211742401123</v>
       </c>
       <c r="H96" t="n">
         <v>1602098</v>
@@ -3182,7 +3182,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G97" t="n">
-        <v>4.77997016906738</v>
+        <v>4.77996921539307</v>
       </c>
       <c r="H97" t="n">
         <v>1260512</v>
@@ -3211,7 +3211,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G98" t="n">
-        <v>4.72573328018188</v>
+        <v>4.72573375701904</v>
       </c>
       <c r="H98" t="n">
         <v>764494</v>
@@ -3240,7 +3240,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G99" t="n">
-        <v>4.59918403625488</v>
+        <v>4.59918451309204</v>
       </c>
       <c r="H99" t="n">
         <v>2047704</v>
@@ -3269,7 +3269,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>4.56302642822266</v>
+        <v>4.56302690505981</v>
       </c>
       <c r="H100" t="n">
         <v>1433539</v>
@@ -3327,7 +3327,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.73658132553101</v>
+        <v>4.73658084869385</v>
       </c>
       <c r="H102" t="n">
         <v>1604134</v>
@@ -3356,7 +3356,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>4.80166339874268</v>
+        <v>4.80166387557983</v>
       </c>
       <c r="H103" t="n">
         <v>1049093</v>
@@ -3385,7 +3385,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>4.79443168640137</v>
+        <v>4.79443216323853</v>
       </c>
       <c r="H104" t="n">
         <v>741031</v>
@@ -3414,7 +3414,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G105" t="n">
-        <v>4.83058881759644</v>
+        <v>4.83058929443359</v>
       </c>
       <c r="H105" t="n">
         <v>301436</v>
@@ -3443,7 +3443,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>4.74381160736084</v>
+        <v>4.74381256103516</v>
       </c>
       <c r="H106" t="n">
         <v>723429</v>
@@ -3501,7 +3501,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>4.78720092773438</v>
+        <v>4.78720045089722</v>
       </c>
       <c r="H108" t="n">
         <v>846712</v>
@@ -3530,7 +3530,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>4.67511367797852</v>
+        <v>4.67511415481567</v>
       </c>
       <c r="H109" t="n">
         <v>863571</v>
@@ -3559,7 +3559,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>4.74381160736084</v>
+        <v>4.74381256103516</v>
       </c>
       <c r="H110" t="n">
         <v>748078</v>
@@ -3617,7 +3617,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>4.69680738449097</v>
+        <v>4.69680833816528</v>
       </c>
       <c r="H112" t="n">
         <v>755214</v>
@@ -3704,7 +3704,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G115" t="n">
-        <v>4.39308834075928</v>
+        <v>4.39308786392212</v>
       </c>
       <c r="H115" t="n">
         <v>1453904</v>
@@ -3733,7 +3733,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G116" t="n">
-        <v>4.27738571166992</v>
+        <v>4.27738523483276</v>
       </c>
       <c r="H116" t="n">
         <v>1300109</v>
@@ -3791,7 +3791,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>4.29184818267822</v>
+        <v>4.29184865951538</v>
       </c>
       <c r="H118" t="n">
         <v>1213762</v>
@@ -3820,7 +3820,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40032005310059</v>
+        <v>4.40031957626343</v>
       </c>
       <c r="H119" t="n">
         <v>1255915</v>
@@ -3849,7 +3849,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>4.57748937606812</v>
+        <v>4.57748985290527</v>
       </c>
       <c r="H120" t="n">
         <v>1143567</v>
@@ -3907,7 +3907,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>4.6281099319458</v>
+        <v>4.62810945510864</v>
       </c>
       <c r="H122" t="n">
         <v>1201249</v>
@@ -3965,7 +3965,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G124" t="n">
-        <v>4.32439041137695</v>
+        <v>4.32438993453979</v>
       </c>
       <c r="H124" t="n">
         <v>3285007</v>
@@ -3994,7 +3994,7 @@
         <v>5.5</v>
       </c>
       <c r="G125" t="n">
-        <v>3.97728204727173</v>
+        <v>3.97728157043457</v>
       </c>
       <c r="H125" t="n">
         <v>3230849</v>
@@ -4023,7 +4023,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>4.23399782180786</v>
+        <v>4.23399686813354</v>
       </c>
       <c r="H126" t="n">
         <v>1838104</v>
@@ -4139,7 +4139,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02066993713379</v>
       </c>
       <c r="H130" t="n">
         <v>1421546</v>
@@ -4197,7 +4197,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73141264915466</v>
+        <v>3.73141288757324</v>
       </c>
       <c r="H132" t="n">
         <v>3993579</v>
@@ -4284,7 +4284,7 @@
         <v>5.75</v>
       </c>
       <c r="G135" t="n">
-        <v>4.15806722640991</v>
+        <v>4.15806770324707</v>
       </c>
       <c r="H135" t="n">
         <v>1373702</v>
@@ -4400,7 +4400,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G139" t="n">
-        <v>4.04597949981689</v>
+        <v>4.04598045349121</v>
       </c>
       <c r="H139" t="n">
         <v>2836608</v>
@@ -4429,7 +4429,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G140" t="n">
-        <v>4.07852125167847</v>
+        <v>4.07852172851562</v>
       </c>
       <c r="H140" t="n">
         <v>2842855</v>
@@ -4458,7 +4458,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G141" t="n">
-        <v>4.07852125167847</v>
+        <v>4.07852172851562</v>
       </c>
       <c r="H141" t="n">
         <v>2956609</v>
@@ -4487,7 +4487,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>4.15083599090576</v>
+        <v>4.1508355140686</v>
       </c>
       <c r="H142" t="n">
         <v>2137222</v>
@@ -4516,7 +4516,7 @@
         <v>5.75</v>
       </c>
       <c r="G143" t="n">
-        <v>4.15806722640991</v>
+        <v>4.15806770324707</v>
       </c>
       <c r="H143" t="n">
         <v>1184281</v>
@@ -4574,7 +4574,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08936882019043</v>
+        <v>4.08936929702759</v>
       </c>
       <c r="H145" t="n">
         <v>1196054</v>
@@ -4661,7 +4661,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.78564929962158</v>
+        <v>3.78564882278442</v>
       </c>
       <c r="H148" t="n">
         <v>3813192</v>
@@ -4806,7 +4806,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>3.79288053512573</v>
+        <v>3.79288029670715</v>
       </c>
       <c r="H153" t="n">
         <v>2240614</v>
@@ -4835,7 +4835,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>3.82903742790222</v>
+        <v>3.8290376663208</v>
       </c>
       <c r="H154" t="n">
         <v>1283102</v>
@@ -4864,7 +4864,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G155" t="n">
-        <v>3.78926467895508</v>
+        <v>3.78926491737366</v>
       </c>
       <c r="H155" t="n">
         <v>1669619</v>
@@ -4893,7 +4893,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>3.82542181015015</v>
+        <v>3.82542157173157</v>
       </c>
       <c r="H156" t="n">
         <v>1438587</v>
@@ -4951,7 +4951,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G158" t="n">
-        <v>3.8001115322113</v>
+        <v>3.80011248588562</v>
       </c>
       <c r="H158" t="n">
         <v>708270</v>
@@ -5009,7 +5009,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>3.79288053512573</v>
+        <v>3.79288029670715</v>
       </c>
       <c r="H160" t="n">
         <v>1368032</v>
@@ -5038,7 +5038,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>3.68802523612976</v>
+        <v>3.6880247592926</v>
       </c>
       <c r="H161" t="n">
         <v>1424951</v>
@@ -5067,7 +5067,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G162" t="n">
-        <v>3.68440937995911</v>
+        <v>3.68440818786621</v>
       </c>
       <c r="H162" t="n">
         <v>1350688</v>
@@ -5096,7 +5096,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.6337890625</v>
+        <v>3.63378953933716</v>
       </c>
       <c r="H163" t="n">
         <v>2620713</v>
@@ -5125,7 +5125,7 @@
         <v>5</v>
       </c>
       <c r="G164" t="n">
-        <v>3.61571002006531</v>
+        <v>3.61571073532104</v>
       </c>
       <c r="H164" t="n">
         <v>1813564</v>
@@ -5154,7 +5154,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>3.90135169029236</v>
+        <v>3.90135216712952</v>
       </c>
       <c r="H165" t="n">
         <v>4871992</v>
@@ -5183,7 +5183,7 @@
         <v>5.5</v>
       </c>
       <c r="G166" t="n">
-        <v>3.97728204727173</v>
+        <v>3.97728157043457</v>
       </c>
       <c r="H166" t="n">
         <v>3532873</v>
@@ -5212,7 +5212,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>3.91943049430847</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H167" t="n">
         <v>1361661</v>
@@ -5241,7 +5241,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G168" t="n">
-        <v>3.89412021636963</v>
+        <v>3.89412093162537</v>
       </c>
       <c r="H168" t="n">
         <v>1087910</v>
@@ -5328,7 +5328,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G171" t="n">
-        <v>3.94112396240234</v>
+        <v>3.9411244392395</v>
       </c>
       <c r="H171" t="n">
         <v>1334976</v>
@@ -5386,7 +5386,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G173" t="n">
-        <v>3.97005009651184</v>
+        <v>3.97004985809326</v>
       </c>
       <c r="H173" t="n">
         <v>1863318</v>
@@ -5473,7 +5473,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>3.92304611206055</v>
+        <v>3.92304587364197</v>
       </c>
       <c r="H176" t="n">
         <v>1987450</v>
@@ -5502,7 +5502,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H177" t="n">
         <v>2745965</v>
@@ -5531,7 +5531,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H178" t="n">
         <v>1872241</v>
@@ -5560,7 +5560,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>3.76757073402405</v>
+        <v>3.76757121086121</v>
       </c>
       <c r="H179" t="n">
         <v>1730619</v>
@@ -5589,7 +5589,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G180" t="n">
-        <v>3.68079376220703</v>
+        <v>3.68079328536987</v>
       </c>
       <c r="H180" t="n">
         <v>1379650</v>
@@ -5618,7 +5618,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G181" t="n">
-        <v>3.8001115322113</v>
+        <v>3.80011248588562</v>
       </c>
       <c r="H181" t="n">
         <v>1500707</v>
@@ -5647,7 +5647,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G182" t="n">
-        <v>3.78564929962158</v>
+        <v>3.78564882278442</v>
       </c>
       <c r="H182" t="n">
         <v>1349515</v>
@@ -5676,7 +5676,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>3.67356181144714</v>
+        <v>3.6735622882843</v>
       </c>
       <c r="H183" t="n">
         <v>1411142</v>
@@ -5705,7 +5705,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.76033902168274</v>
+        <v>3.76033878326416</v>
       </c>
       <c r="H184" t="n">
         <v>1171746</v>
@@ -5734,7 +5734,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G185" t="n">
-        <v>3.75672340393066</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H185" t="n">
         <v>1626816</v>
@@ -5763,7 +5763,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.76757073402405</v>
+        <v>3.76757121086121</v>
       </c>
       <c r="H186" t="n">
         <v>1095288</v>
@@ -5792,7 +5792,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>3.82542181015015</v>
+        <v>3.82542157173157</v>
       </c>
       <c r="H187" t="n">
         <v>2681246</v>
@@ -5821,7 +5821,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G188" t="n">
-        <v>3.74587607383728</v>
+        <v>3.74587631225586</v>
       </c>
       <c r="H188" t="n">
         <v>1474820</v>
@@ -5879,7 +5879,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>3.74226093292236</v>
+        <v>3.74226069450378</v>
       </c>
       <c r="H190" t="n">
         <v>3263669</v>
@@ -5908,7 +5908,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G191" t="n">
-        <v>3.75310778617859</v>
+        <v>3.75310754776001</v>
       </c>
       <c r="H191" t="n">
         <v>1760882</v>
@@ -5937,7 +5937,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G192" t="n">
-        <v>3.73864507675171</v>
+        <v>3.73864483833313</v>
       </c>
       <c r="H192" t="n">
         <v>1453013</v>
@@ -5966,7 +5966,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72779774665833</v>
+        <v>3.7277979850769</v>
       </c>
       <c r="H193" t="n">
         <v>2119783</v>
@@ -5995,7 +5995,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.70971894264221</v>
+        <v>3.70971870422363</v>
       </c>
       <c r="H194" t="n">
         <v>1549911</v>
@@ -6024,7 +6024,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>3.68079376220703</v>
+        <v>3.68079328536987</v>
       </c>
       <c r="H195" t="n">
         <v>1872030</v>
@@ -6053,7 +6053,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G196" t="n">
-        <v>3.74587607383728</v>
+        <v>3.74587631225586</v>
       </c>
       <c r="H196" t="n">
         <v>1713471</v>
@@ -6082,7 +6082,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>3.73141264915466</v>
+        <v>3.73141288757324</v>
       </c>
       <c r="H197" t="n">
         <v>1836123</v>
@@ -6111,7 +6111,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>3.64825224876404</v>
+        <v>3.6482527256012</v>
       </c>
       <c r="H198" t="n">
         <v>2133006</v>
@@ -6227,7 +6227,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>3.65548324584961</v>
+        <v>3.65548372268677</v>
       </c>
       <c r="H202" t="n">
         <v>30588371</v>
@@ -6256,7 +6256,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>3.73864507675171</v>
+        <v>3.73864483833313</v>
       </c>
       <c r="H203" t="n">
         <v>6162802</v>
@@ -6285,7 +6285,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>3.75672340393066</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H204" t="n">
         <v>5488683</v>
@@ -6314,7 +6314,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G205" t="n">
-        <v>3.74226093292236</v>
+        <v>3.74226069450378</v>
       </c>
       <c r="H205" t="n">
         <v>3684581</v>
@@ -6343,7 +6343,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G206" t="n">
-        <v>3.75672340393066</v>
+        <v>3.75672364234924</v>
       </c>
       <c r="H206" t="n">
         <v>2084886</v>
@@ -6372,7 +6372,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>3.81457543373108</v>
+        <v>3.81457448005676</v>
       </c>
       <c r="H207" t="n">
         <v>4854357</v>
@@ -6430,7 +6430,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>3.87604188919067</v>
+        <v>3.87604141235352</v>
       </c>
       <c r="H209" t="n">
         <v>2199321</v>
@@ -6459,7 +6459,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G210" t="n">
-        <v>3.81819033622742</v>
+        <v>3.81819081306458</v>
       </c>
       <c r="H210" t="n">
         <v>2913261</v>
@@ -6488,7 +6488,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>3.8688108921051</v>
+        <v>3.86881017684937</v>
       </c>
       <c r="H211" t="n">
         <v>2192359</v>
@@ -6546,7 +6546,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>3.99174427986145</v>
+        <v>3.99174499511719</v>
       </c>
       <c r="H213" t="n">
         <v>3510082</v>
@@ -6575,7 +6575,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G214" t="n">
-        <v>3.84711623191833</v>
+        <v>3.84711647033691</v>
       </c>
       <c r="H214" t="n">
         <v>2039874</v>
@@ -6604,7 +6604,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>3.78203344345093</v>
+        <v>3.78203320503235</v>
       </c>
       <c r="H215" t="n">
         <v>1276554</v>
@@ -6633,7 +6633,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68802523612976</v>
+        <v>3.6880247592926</v>
       </c>
       <c r="H216" t="n">
         <v>2131473</v>
@@ -6662,7 +6662,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>3.69164085388184</v>
+        <v>3.69164037704468</v>
       </c>
       <c r="H217" t="n">
         <v>2605202</v>
@@ -6691,7 +6691,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.64463591575623</v>
+        <v>3.6446361541748</v>
       </c>
       <c r="H218" t="n">
         <v>1953060</v>
@@ -6720,7 +6720,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G219" t="n">
-        <v>3.66633033752441</v>
+        <v>3.66633129119873</v>
       </c>
       <c r="H219" t="n">
         <v>1484452</v>
@@ -6749,7 +6749,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>3.64463591575623</v>
+        <v>3.6446361541748</v>
       </c>
       <c r="H220" t="n">
         <v>2407083</v>
@@ -6778,7 +6778,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>3.67356181144714</v>
+        <v>3.6735622882843</v>
       </c>
       <c r="H221" t="n">
         <v>3276707</v>
@@ -6807,7 +6807,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>3.68079376220703</v>
+        <v>3.68079328536987</v>
       </c>
       <c r="H222" t="n">
         <v>3872577</v>
@@ -6836,7 +6836,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G223" t="n">
-        <v>3.65186762809753</v>
+        <v>3.65186715126038</v>
       </c>
       <c r="H223" t="n">
         <v>2767052</v>
@@ -6865,7 +6865,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G224" t="n">
-        <v>3.61281824111938</v>
+        <v>3.61281800270081</v>
       </c>
       <c r="H224" t="n">
         <v>2001893</v>
@@ -6894,7 +6894,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G225" t="n">
-        <v>3.59690856933594</v>
+        <v>3.59690928459167</v>
       </c>
       <c r="H225" t="n">
         <v>2042948</v>
@@ -6952,7 +6952,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>3.47108244895935</v>
+        <v>3.47108268737793</v>
       </c>
       <c r="H227" t="n">
         <v>2432187</v>
@@ -6981,7 +6981,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>3.41323065757751</v>
+        <v>3.41323041915894</v>
       </c>
       <c r="H228" t="n">
         <v>2643530</v>
@@ -7010,7 +7010,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G229" t="n">
-        <v>3.41323065757751</v>
+        <v>3.41323041915894</v>
       </c>
       <c r="H229" t="n">
         <v>2355546</v>
@@ -7039,7 +7039,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G230" t="n">
-        <v>3.40744566917419</v>
+        <v>3.40744543075562</v>
       </c>
       <c r="H230" t="n">
         <v>2323535</v>
@@ -7068,7 +7068,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G231" t="n">
-        <v>3.41033864021301</v>
+        <v>3.4103376865387</v>
       </c>
       <c r="H231" t="n">
         <v>2268934</v>
@@ -7097,7 +7097,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G232" t="n">
-        <v>3.42480111122131</v>
+        <v>3.42480087280273</v>
       </c>
       <c r="H232" t="n">
         <v>1722858</v>
@@ -7155,7 +7155,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G234" t="n">
-        <v>3.34236264228821</v>
+        <v>3.34236335754395</v>
       </c>
       <c r="H234" t="n">
         <v>2323743</v>
@@ -7184,7 +7184,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G235" t="n">
-        <v>3.45517301559448</v>
+        <v>3.4551727771759</v>
       </c>
       <c r="H235" t="n">
         <v>2082364</v>
@@ -7213,7 +7213,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>3.52893400192261</v>
+        <v>3.52893376350403</v>
       </c>
       <c r="H236" t="n">
         <v>6107353</v>
@@ -7242,7 +7242,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51013207435608</v>
+        <v>3.51013231277466</v>
       </c>
       <c r="H237" t="n">
         <v>4013855</v>
@@ -7271,7 +7271,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53327250480652</v>
+        <v>3.53327226638794</v>
       </c>
       <c r="H238" t="n">
         <v>4750178</v>
@@ -7300,7 +7300,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G239" t="n">
-        <v>3.44504904747009</v>
+        <v>3.44504833221436</v>
       </c>
       <c r="H239" t="n">
         <v>4237825</v>
@@ -7358,7 +7358,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.64463591575623</v>
+        <v>3.6446361541748</v>
       </c>
       <c r="H241" t="n">
         <v>4615423</v>
@@ -7387,7 +7387,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>3.76033902168274</v>
+        <v>3.76033878326416</v>
       </c>
       <c r="H242" t="n">
         <v>3062648</v>
@@ -7416,7 +7416,7 @@
         <v>5.125</v>
       </c>
       <c r="G243" t="n">
-        <v>3.70610356330872</v>
+        <v>3.70610380172729</v>
       </c>
       <c r="H243" t="n">
         <v>2409471</v>
@@ -7445,7 +7445,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>3.66633033752441</v>
+        <v>3.66633129119873</v>
       </c>
       <c r="H244" t="n">
         <v>2525526</v>
@@ -7503,7 +7503,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>3.92304611206055</v>
+        <v>3.92304587364197</v>
       </c>
       <c r="H246" t="n">
         <v>2841246</v>
@@ -7532,7 +7532,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G247" t="n">
-        <v>3.9881284236908</v>
+        <v>3.98812890052795</v>
       </c>
       <c r="H247" t="n">
         <v>3264617</v>
@@ -7561,7 +7561,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>3.95197200775146</v>
+        <v>3.95197224617004</v>
       </c>
       <c r="H248" t="n">
         <v>2687315</v>
@@ -7590,7 +7590,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>3.86157917976379</v>
+        <v>3.86157941818237</v>
       </c>
       <c r="H249" t="n">
         <v>1875617</v>
@@ -7619,7 +7619,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G250" t="n">
-        <v>3.89050459861755</v>
+        <v>3.89050436019897</v>
       </c>
       <c r="H250" t="n">
         <v>2805902</v>
@@ -7648,7 +7648,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>3.96281886100769</v>
+        <v>3.96281909942627</v>
       </c>
       <c r="H251" t="n">
         <v>2343541</v>
@@ -7677,7 +7677,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>3.94112396240234</v>
+        <v>3.9411244392395</v>
       </c>
       <c r="H252" t="n">
         <v>3766796</v>
@@ -7735,7 +7735,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G254" t="n">
-        <v>3.97005009651184</v>
+        <v>3.97004985809326</v>
       </c>
       <c r="H254" t="n">
         <v>900511</v>
@@ -7764,7 +7764,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>3.8688108921051</v>
+        <v>3.86881017684937</v>
       </c>
       <c r="H255" t="n">
         <v>1417418</v>
@@ -7793,7 +7793,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>3.88327288627625</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H256" t="n">
         <v>989625</v>
@@ -7822,7 +7822,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>3.85434794425964</v>
+        <v>3.85434675216675</v>
       </c>
       <c r="H257" t="n">
         <v>823107</v>
@@ -7851,7 +7851,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.97005009651184</v>
+        <v>3.97004985809326</v>
       </c>
       <c r="H258" t="n">
         <v>1572602</v>
@@ -7909,7 +7909,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G260" t="n">
-        <v>3.92666172981262</v>
+        <v>3.92666149139404</v>
       </c>
       <c r="H260" t="n">
         <v>2293252</v>
@@ -7938,7 +7938,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>4.01343870162964</v>
+        <v>4.0134391784668</v>
       </c>
       <c r="H261" t="n">
         <v>3965538</v>
@@ -7967,7 +7967,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>3.99897599220276</v>
+        <v>3.99897623062134</v>
       </c>
       <c r="H262" t="n">
         <v>2114774</v>
@@ -7996,7 +7996,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>3.92304611206055</v>
+        <v>3.92304587364197</v>
       </c>
       <c r="H263" t="n">
         <v>1907680</v>
@@ -8025,7 +8025,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.97005009651184</v>
+        <v>3.97004985809326</v>
       </c>
       <c r="H264" t="n">
         <v>1813183</v>
@@ -8054,7 +8054,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>3.99536037445068</v>
+        <v>3.9953601360321</v>
       </c>
       <c r="H265" t="n">
         <v>1848308</v>
@@ -8112,7 +8112,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>3.99174427986145</v>
+        <v>3.99174499511719</v>
       </c>
       <c r="H267" t="n">
         <v>1773147</v>
@@ -8141,7 +8141,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G268" t="n">
-        <v>3.93389320373535</v>
+        <v>3.93389368057251</v>
       </c>
       <c r="H268" t="n">
         <v>1048745</v>
@@ -8170,7 +8170,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G269" t="n">
-        <v>3.92666172981262</v>
+        <v>3.92666149139404</v>
       </c>
       <c r="H269" t="n">
         <v>990913</v>
@@ -8199,7 +8199,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.99174427986145</v>
+        <v>3.99174499511719</v>
       </c>
       <c r="H270" t="n">
         <v>1825982</v>
@@ -8257,7 +8257,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G272" t="n">
-        <v>4.06405925750732</v>
+        <v>4.06405830383301</v>
       </c>
       <c r="H272" t="n">
         <v>3193803</v>
@@ -8286,7 +8286,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G273" t="n">
-        <v>3.97005009651184</v>
+        <v>3.97004985809326</v>
       </c>
       <c r="H273" t="n">
         <v>2818868</v>
@@ -8315,7 +8315,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02066993713379</v>
       </c>
       <c r="H274" t="n">
         <v>2581220</v>
@@ -8344,7 +8344,7 @@
         <v>5.75</v>
       </c>
       <c r="G275" t="n">
-        <v>4.15806722640991</v>
+        <v>4.15806770324707</v>
       </c>
       <c r="H275" t="n">
         <v>3622231</v>
@@ -8373,7 +8373,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>4.08213758468628</v>
+        <v>4.08213710784912</v>
       </c>
       <c r="H276" t="n">
         <v>2705677</v>
@@ -8431,7 +8431,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02066993713379</v>
       </c>
       <c r="H278" t="n">
         <v>2796328</v>
@@ -8460,7 +8460,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G279" t="n">
-        <v>3.97005009651184</v>
+        <v>3.97004985809326</v>
       </c>
       <c r="H279" t="n">
         <v>2453406</v>
@@ -8489,7 +8489,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G280" t="n">
-        <v>4.04597949981689</v>
+        <v>4.04598045349121</v>
       </c>
       <c r="H280" t="n">
         <v>2248107</v>
@@ -8518,7 +8518,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>4.00620698928833</v>
+        <v>4.00620794296265</v>
       </c>
       <c r="H281" t="n">
         <v>2732122</v>
@@ -8547,7 +8547,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G282" t="n">
-        <v>4.04597949981689</v>
+        <v>4.04598045349121</v>
       </c>
       <c r="H282" t="n">
         <v>1468862</v>
@@ -8605,7 +8605,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G284" t="n">
-        <v>3.92666172981262</v>
+        <v>3.92666149139404</v>
       </c>
       <c r="H284" t="n">
         <v>2061382</v>
@@ -8634,7 +8634,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G285" t="n">
-        <v>3.96281886100769</v>
+        <v>3.96281909942627</v>
       </c>
       <c r="H285" t="n">
         <v>1908662</v>
@@ -8663,7 +8663,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.9736659526825</v>
+        <v>3.97366547584534</v>
       </c>
       <c r="H286" t="n">
         <v>1319086</v>
@@ -8692,7 +8692,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G287" t="n">
-        <v>3.91219854354858</v>
+        <v>3.91219902038574</v>
       </c>
       <c r="H287" t="n">
         <v>1173142</v>
@@ -8721,7 +8721,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G288" t="n">
-        <v>3.93389320373535</v>
+        <v>3.93389368057251</v>
       </c>
       <c r="H288" t="n">
         <v>1912685</v>
@@ -8750,7 +8750,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>3.96281886100769</v>
+        <v>3.96281909942627</v>
       </c>
       <c r="H289" t="n">
         <v>2102413</v>
@@ -8779,7 +8779,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G290" t="n">
-        <v>3.94112396240234</v>
+        <v>3.9411244392395</v>
       </c>
       <c r="H290" t="n">
         <v>1967671</v>
@@ -8808,7 +8808,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.92666172981262</v>
+        <v>3.92666149139404</v>
       </c>
       <c r="H291" t="n">
         <v>1485016</v>
@@ -8837,7 +8837,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>3.91943049430847</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H292" t="n">
         <v>2376919</v>
@@ -8866,7 +8866,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G293" t="n">
-        <v>3.94112396240234</v>
+        <v>3.9411244392395</v>
       </c>
       <c r="H293" t="n">
         <v>1002830</v>
@@ -8895,7 +8895,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>3.91943049430847</v>
+        <v>3.91943073272705</v>
       </c>
       <c r="H294" t="n">
         <v>1953366</v>
@@ -8924,7 +8924,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>3.89050459861755</v>
+        <v>3.89050436019897</v>
       </c>
       <c r="H295" t="n">
         <v>2052783</v>
@@ -8982,7 +8982,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.87604188919067</v>
+        <v>3.87604141235352</v>
       </c>
       <c r="H297" t="n">
         <v>2992561</v>
@@ -9011,7 +9011,7 @@
         <v>5.375</v>
       </c>
       <c r="G298" t="n">
-        <v>3.88688898086548</v>
+        <v>3.88688969612122</v>
       </c>
       <c r="H298" t="n">
         <v>6414207</v>
@@ -9069,7 +9069,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G300" t="n">
-        <v>3.98089718818665</v>
+        <v>3.9808976650238</v>
       </c>
       <c r="H300" t="n">
         <v>2265275</v>
@@ -9127,7 +9127,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G302" t="n">
-        <v>4.12914180755615</v>
+        <v>4.12914133071899</v>
       </c>
       <c r="H302" t="n">
         <v>3035336</v>
@@ -9185,7 +9185,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>4.15083599090576</v>
+        <v>4.1508355140686</v>
       </c>
       <c r="H304" t="n">
         <v>1601707</v>
@@ -9214,7 +9214,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G305" t="n">
-        <v>4.17252969741821</v>
+        <v>4.17253017425537</v>
       </c>
       <c r="H305" t="n">
         <v>1549143</v>
@@ -9272,7 +9272,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30269479751587</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H307" t="n">
         <v>2406004</v>
@@ -9301,7 +9301,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>4.30269479751587</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H308" t="n">
         <v>1384487</v>
@@ -9330,7 +9330,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.28100156784058</v>
+        <v>4.28100109100342</v>
       </c>
       <c r="H309" t="n">
         <v>1381742</v>
@@ -9359,7 +9359,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>4.30269479751587</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H310" t="n">
         <v>1166357</v>
@@ -9388,7 +9388,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G311" t="n">
-        <v>4.46540355682373</v>
+        <v>4.46540260314941</v>
       </c>
       <c r="H311" t="n">
         <v>4450530</v>
@@ -9417,7 +9417,7 @@
         <v>6.25</v>
       </c>
       <c r="G312" t="n">
-        <v>4.51963901519775</v>
+        <v>4.51963806152344</v>
       </c>
       <c r="H312" t="n">
         <v>11461676</v>
@@ -9475,7 +9475,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>4.46540355682373</v>
+        <v>4.46540260314941</v>
       </c>
       <c r="H314" t="n">
         <v>3471231</v>
@@ -9504,7 +9504,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.49794340133667</v>
+        <v>4.49794435501099</v>
       </c>
       <c r="H315" t="n">
         <v>1899424</v>
@@ -9591,7 +9591,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.63172578811646</v>
+        <v>4.6317253112793</v>
       </c>
       <c r="H318" t="n">
         <v>1809873</v>
@@ -9794,7 +9794,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.55217981338501</v>
+        <v>4.55217933654785</v>
       </c>
       <c r="H325" t="n">
         <v>2599522</v>
@@ -9823,7 +9823,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G326" t="n">
-        <v>4.55217981338501</v>
+        <v>4.55217933654785</v>
       </c>
       <c r="H326" t="n">
         <v>2329372</v>
@@ -9910,7 +9910,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G329" t="n">
-        <v>4.59918403625488</v>
+        <v>4.59918451309204</v>
       </c>
       <c r="H329" t="n">
         <v>2211159</v>
@@ -9939,7 +9939,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>4.67149829864502</v>
+        <v>4.67149782180786</v>
       </c>
       <c r="H330" t="n">
         <v>2613281</v>
@@ -9997,7 +9997,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>4.64257192611694</v>
+        <v>4.6425724029541</v>
       </c>
       <c r="H332" t="n">
         <v>1809308</v>
@@ -10026,7 +10026,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G333" t="n">
-        <v>4.72211885452271</v>
+        <v>4.72211742401123</v>
       </c>
       <c r="H333" t="n">
         <v>1861825</v>
@@ -10055,7 +10055,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.65703535079956</v>
+        <v>4.65703582763672</v>
       </c>
       <c r="H334" t="n">
         <v>3347408</v>
@@ -10084,7 +10084,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G335" t="n">
-        <v>4.59918403625488</v>
+        <v>4.59918451309204</v>
       </c>
       <c r="H335" t="n">
         <v>3738102</v>
@@ -10113,7 +10113,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G336" t="n">
-        <v>4.8828501701355</v>
+        <v>4.88285064697266</v>
       </c>
       <c r="H336" t="n">
         <v>4467194</v>
@@ -10171,7 +10171,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G338" t="n">
-        <v>4.91310787200928</v>
+        <v>4.91310882568359</v>
       </c>
       <c r="H338" t="n">
         <v>1812525</v>
@@ -10200,7 +10200,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88663244247437</v>
+        <v>4.88663291931152</v>
       </c>
       <c r="H339" t="n">
         <v>1167519</v>
@@ -10229,7 +10229,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>4.93958425521851</v>
+        <v>4.93958377838135</v>
       </c>
       <c r="H340" t="n">
         <v>2188783</v>
@@ -10287,7 +10287,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.91310787200928</v>
+        <v>4.91310882568359</v>
       </c>
       <c r="H342" t="n">
         <v>1543013</v>
@@ -10316,7 +10316,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>5.0417046546936</v>
+        <v>5.04170417785645</v>
       </c>
       <c r="H343" t="n">
         <v>3358984</v>
@@ -10345,7 +10345,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13625955581665</v>
+        <v>5.13626003265381</v>
       </c>
       <c r="H344" t="n">
         <v>2148000</v>
@@ -10374,7 +10374,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.14382457733154</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H345" t="n">
         <v>2913934</v>
@@ -10403,7 +10403,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G346" t="n">
-        <v>5.17786455154419</v>
+        <v>5.17786359786987</v>
       </c>
       <c r="H346" t="n">
         <v>3228661</v>
@@ -10432,7 +10432,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>5.14382457733154</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H347" t="n">
         <v>2197856</v>
@@ -10490,7 +10490,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>5.08709049224854</v>
+        <v>5.08709096908569</v>
       </c>
       <c r="H349" t="n">
         <v>2037566</v>
@@ -10519,7 +10519,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>5.0076642036438</v>
+        <v>5.00766372680664</v>
       </c>
       <c r="H350" t="n">
         <v>2559502</v>
@@ -10606,7 +10606,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.96606063842773</v>
+        <v>4.96606016159058</v>
       </c>
       <c r="H353" t="n">
         <v>2522783</v>
@@ -10635,7 +10635,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G354" t="n">
-        <v>5.09465503692627</v>
+        <v>5.09465551376343</v>
       </c>
       <c r="H354" t="n">
         <v>2760019</v>
@@ -10664,7 +10664,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>5.07196140289307</v>
+        <v>5.07196187973022</v>
       </c>
       <c r="H355" t="n">
         <v>1068280</v>
@@ -10693,7 +10693,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>5.13625955581665</v>
+        <v>5.13626003265381</v>
       </c>
       <c r="H356" t="n">
         <v>1253175</v>
@@ -10722,7 +10722,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>5.1702995300293</v>
+        <v>5.17030000686646</v>
       </c>
       <c r="H357" t="n">
         <v>1872012</v>
@@ -10751,7 +10751,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>5.15138816833496</v>
+        <v>5.15138864517212</v>
       </c>
       <c r="H358" t="n">
         <v>1066471</v>
@@ -10838,7 +10838,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>5.02657556533813</v>
+        <v>5.02657508850098</v>
       </c>
       <c r="H361" t="n">
         <v>1407225</v>
@@ -10867,7 +10867,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G362" t="n">
-        <v>5.06061553955078</v>
+        <v>5.06061506271362</v>
       </c>
       <c r="H362" t="n">
         <v>1677680</v>
@@ -10925,7 +10925,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G364" t="n">
-        <v>5.12869501113892</v>
+        <v>5.12869596481323</v>
       </c>
       <c r="H364" t="n">
         <v>1821816</v>
@@ -10954,7 +10954,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.05683326721191</v>
+        <v>5.05683279037476</v>
       </c>
       <c r="H365" t="n">
         <v>857551</v>
@@ -10983,7 +10983,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17408227920532</v>
+        <v>5.17408180236816</v>
       </c>
       <c r="H366" t="n">
         <v>1623704</v>
@@ -11012,7 +11012,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>5.23838043212891</v>
+        <v>5.23837995529175</v>
       </c>
       <c r="H367" t="n">
         <v>2803808</v>
@@ -11070,7 +11070,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>5.37075805664062</v>
+        <v>5.37075710296631</v>
       </c>
       <c r="H369" t="n">
         <v>2325569</v>
@@ -11099,7 +11099,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G370" t="n">
-        <v>5.33671808242798</v>
+        <v>5.33671712875366</v>
       </c>
       <c r="H370" t="n">
         <v>1720213</v>
@@ -11128,7 +11128,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>5.42370891571045</v>
+        <v>5.42370843887329</v>
       </c>
       <c r="H371" t="n">
         <v>1836918</v>
@@ -11215,7 +11215,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.33293533325195</v>
+        <v>5.33293581008911</v>
       </c>
       <c r="H374" t="n">
         <v>2246270</v>
@@ -11302,7 +11302,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G377" t="n">
-        <v>5.29889440536499</v>
+        <v>5.29889583587646</v>
       </c>
       <c r="H377" t="n">
         <v>1760770</v>
@@ -11331,7 +11331,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G378" t="n">
-        <v>5.21190452575684</v>
+        <v>5.21190357208252</v>
       </c>
       <c r="H378" t="n">
         <v>2634505</v>
@@ -11360,7 +11360,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>5.1702995300293</v>
+        <v>5.17030000686646</v>
       </c>
       <c r="H379" t="n">
         <v>1727362</v>
@@ -11389,7 +11389,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>5.1702995300293</v>
+        <v>5.17030000686646</v>
       </c>
       <c r="H380" t="n">
         <v>1653074</v>
@@ -11418,7 +11418,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.14382457733154</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H381" t="n">
         <v>1459321</v>
@@ -11447,7 +11447,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G382" t="n">
-        <v>5.33671808242798</v>
+        <v>5.33671712875366</v>
       </c>
       <c r="H382" t="n">
         <v>3777893</v>
@@ -11505,7 +11505,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G384" t="n">
-        <v>5.21190452575684</v>
+        <v>5.21190357208252</v>
       </c>
       <c r="H384" t="n">
         <v>2968004</v>
@@ -11650,7 +11650,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>5.49935340881348</v>
+        <v>5.49935293197632</v>
       </c>
       <c r="H389" t="n">
         <v>2989285</v>
@@ -11679,7 +11679,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.52204656600952</v>
+        <v>5.52204561233521</v>
       </c>
       <c r="H390" t="n">
         <v>1962879</v>
@@ -11708,7 +11708,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.43127298355103</v>
+        <v>5.43127346038818</v>
       </c>
       <c r="H391" t="n">
         <v>1825504</v>
@@ -11766,7 +11766,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>5.43127298355103</v>
+        <v>5.43127346038818</v>
       </c>
       <c r="H393" t="n">
         <v>3118560</v>
@@ -11795,7 +11795,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>5.45018482208252</v>
+        <v>5.45018434524536</v>
       </c>
       <c r="H394" t="n">
         <v>1196170</v>
@@ -11824,7 +11824,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.51448202133179</v>
+        <v>5.51448154449463</v>
       </c>
       <c r="H395" t="n">
         <v>1573825</v>
@@ -11853,7 +11853,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G396" t="n">
-        <v>5.47287797927856</v>
+        <v>5.47287750244141</v>
       </c>
       <c r="H396" t="n">
         <v>1629912</v>
@@ -11882,7 +11882,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>5.46153020858765</v>
+        <v>5.4615306854248</v>
       </c>
       <c r="H397" t="n">
         <v>1842267</v>
@@ -11911,7 +11911,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G398" t="n">
-        <v>5.44640159606934</v>
+        <v>5.44640207290649</v>
       </c>
       <c r="H398" t="n">
         <v>1103593</v>
@@ -11969,7 +11969,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49935340881348</v>
+        <v>5.49935293197632</v>
       </c>
       <c r="H400" t="n">
         <v>1347527</v>
@@ -11998,7 +11998,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>5.56365156173706</v>
+        <v>5.5636510848999</v>
       </c>
       <c r="H401" t="n">
         <v>2216564</v>
@@ -12027,7 +12027,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.55986833572388</v>
+        <v>5.55986881256104</v>
       </c>
       <c r="H402" t="n">
         <v>667810</v>
@@ -12085,7 +12085,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>5.62038421630859</v>
+        <v>5.62038373947144</v>
       </c>
       <c r="H404" t="n">
         <v>880276</v>
@@ -12114,7 +12114,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>5.60903787612915</v>
+        <v>5.60903835296631</v>
       </c>
       <c r="H405" t="n">
         <v>1635128</v>
@@ -12143,7 +12143,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G406" t="n">
-        <v>5.62416696548462</v>
+        <v>5.62416648864746</v>
       </c>
       <c r="H406" t="n">
         <v>2126217</v>
@@ -12172,7 +12172,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>5.61282014846802</v>
+        <v>5.61281967163086</v>
       </c>
       <c r="H407" t="n">
         <v>1739803</v>
@@ -12201,7 +12201,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G408" t="n">
-        <v>5.56365156173706</v>
+        <v>5.5636510848999</v>
       </c>
       <c r="H408" t="n">
         <v>1752617</v>
@@ -12317,7 +12317,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>5.68846416473389</v>
+        <v>5.6884651184082</v>
       </c>
       <c r="H412" t="n">
         <v>1193303</v>
@@ -12346,7 +12346,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G413" t="n">
-        <v>5.58256196975708</v>
+        <v>5.58256244659424</v>
       </c>
       <c r="H413" t="n">
         <v>1013975</v>
@@ -12375,7 +12375,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>5.49178838729858</v>
+        <v>5.49178886413574</v>
       </c>
       <c r="H414" t="n">
         <v>1057522</v>
@@ -12404,7 +12404,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G415" t="n">
-        <v>5.57499742507935</v>
+        <v>5.57499694824219</v>
       </c>
       <c r="H415" t="n">
         <v>822935</v>
@@ -12491,7 +12491,7 @@
         <v>7.375</v>
       </c>
       <c r="G418" t="n">
-        <v>5.57878017425537</v>
+        <v>5.57877969741821</v>
       </c>
       <c r="H418" t="n">
         <v>1231791</v>
@@ -12578,7 +12578,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G421" t="n">
-        <v>5.36319351196289</v>
+        <v>5.36319303512573</v>
       </c>
       <c r="H421" t="n">
         <v>1653108</v>
@@ -12607,7 +12607,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.37075805664062</v>
+        <v>5.37075710296631</v>
       </c>
       <c r="H422" t="n">
         <v>1152544</v>
@@ -12636,7 +12636,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G423" t="n">
-        <v>5.37075805664062</v>
+        <v>5.37075710296631</v>
       </c>
       <c r="H423" t="n">
         <v>603194</v>
@@ -12723,7 +12723,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G426" t="n">
-        <v>5.38588666915894</v>
+        <v>5.38588762283325</v>
       </c>
       <c r="H426" t="n">
         <v>990211</v>
@@ -12752,7 +12752,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G427" t="n">
-        <v>5.4577488899231</v>
+        <v>5.45774936676025</v>
       </c>
       <c r="H427" t="n">
         <v>1656906</v>
@@ -12781,7 +12781,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>5.44640159606934</v>
+        <v>5.44640207290649</v>
       </c>
       <c r="H428" t="n">
         <v>954586</v>
@@ -12810,7 +12810,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>5.36319351196289</v>
+        <v>5.36319303512573</v>
       </c>
       <c r="H429" t="n">
         <v>1095025</v>
@@ -12839,7 +12839,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>5.27620124816895</v>
+        <v>5.2762017250061</v>
       </c>
       <c r="H430" t="n">
         <v>1460582</v>
@@ -12897,7 +12897,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G432" t="n">
-        <v>5.19299364089966</v>
+        <v>5.1929931640625</v>
       </c>
       <c r="H432" t="n">
         <v>2898177</v>
@@ -12926,7 +12926,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>5.25729084014893</v>
+        <v>5.25729036331177</v>
       </c>
       <c r="H433" t="n">
         <v>1634980</v>
@@ -12955,7 +12955,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G434" t="n">
-        <v>5.45018482208252</v>
+        <v>5.45018434524536</v>
       </c>
       <c r="H434" t="n">
         <v>2395140</v>
@@ -12984,7 +12984,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G435" t="n">
-        <v>5.53717517852783</v>
+        <v>5.53717565536499</v>
       </c>
       <c r="H435" t="n">
         <v>2361286</v>
@@ -13042,7 +13042,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>5.51826429367065</v>
+        <v>5.51826477050781</v>
       </c>
       <c r="H437" t="n">
         <v>1374556</v>
@@ -13071,7 +13071,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H438" t="n">
         <v>1651810</v>
@@ -13100,7 +13100,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>5.58634471893311</v>
+        <v>5.58634424209595</v>
       </c>
       <c r="H439" t="n">
         <v>1126119</v>
@@ -13129,7 +13129,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G440" t="n">
-        <v>5.59390878677368</v>
+        <v>5.59390926361084</v>
       </c>
       <c r="H440" t="n">
         <v>833534</v>
@@ -13245,7 +13245,7 @@
         <v>7.375</v>
       </c>
       <c r="G444" t="n">
-        <v>5.57878017425537</v>
+        <v>5.57877969741821</v>
       </c>
       <c r="H444" t="n">
         <v>2250625</v>
@@ -13303,7 +13303,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>5.63551330566406</v>
+        <v>5.63551378250122</v>
       </c>
       <c r="H446" t="n">
         <v>1991275</v>
@@ -13332,7 +13332,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>5.62794876098633</v>
+        <v>5.62794780731201</v>
       </c>
       <c r="H447" t="n">
         <v>1310962</v>
@@ -13390,7 +13390,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>5.64307737350464</v>
+        <v>5.6430778503418</v>
       </c>
       <c r="H449" t="n">
         <v>1777272</v>
@@ -13419,7 +13419,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>5.63173151016235</v>
+        <v>5.6317310333252</v>
       </c>
       <c r="H450" t="n">
         <v>1359714</v>
@@ -13448,7 +13448,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>5.51069927215576</v>
+        <v>5.51070022583008</v>
       </c>
       <c r="H451" t="n">
         <v>1897849</v>
@@ -13477,7 +13477,7 @@
         <v>7.25</v>
       </c>
       <c r="G452" t="n">
-        <v>5.48422431945801</v>
+        <v>5.48422479629517</v>
       </c>
       <c r="H452" t="n">
         <v>2645052</v>
@@ -13535,7 +13535,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>5.44640159606934</v>
+        <v>5.44640207290649</v>
       </c>
       <c r="H454" t="n">
         <v>2254350</v>
@@ -13593,7 +13593,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G456" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H456" t="n">
         <v>2136844</v>
@@ -13651,7 +13651,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>5.56365156173706</v>
+        <v>5.5636510848999</v>
       </c>
       <c r="H458" t="n">
         <v>1888765</v>
@@ -13738,7 +13738,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>5.5409574508667</v>
+        <v>5.54095792770386</v>
       </c>
       <c r="H461" t="n">
         <v>653510</v>
@@ -13767,7 +13767,7 @@
         <v>7.25</v>
       </c>
       <c r="G462" t="n">
-        <v>5.48422431945801</v>
+        <v>5.48422479629517</v>
       </c>
       <c r="H462" t="n">
         <v>1324562</v>
@@ -13796,7 +13796,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>5.53717517852783</v>
+        <v>5.53717565536499</v>
       </c>
       <c r="H463" t="n">
         <v>1461630</v>
@@ -13854,7 +13854,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G465" t="n">
-        <v>5.8889217376709</v>
+        <v>5.88892221450806</v>
       </c>
       <c r="H465" t="n">
         <v>6603368</v>
@@ -13883,7 +13883,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>5.85866403579712</v>
+        <v>5.85866451263428</v>
       </c>
       <c r="H466" t="n">
         <v>5913902</v>
@@ -13941,7 +13941,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.01373529434204</v>
+        <v>6.0137357711792</v>
       </c>
       <c r="H468" t="n">
         <v>2796505</v>
@@ -13999,7 +13999,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G470" t="n">
-        <v>6.07425022125244</v>
+        <v>6.07425117492676</v>
       </c>
       <c r="H470" t="n">
         <v>1261592</v>
@@ -14028,7 +14028,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G471" t="n">
-        <v>6.06668663024902</v>
+        <v>6.06668710708618</v>
       </c>
       <c r="H471" t="n">
         <v>1148363</v>
@@ -14057,7 +14057,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>6.05912160873413</v>
+        <v>6.05912208557129</v>
       </c>
       <c r="H472" t="n">
         <v>1518292</v>
@@ -14086,7 +14086,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G473" t="n">
-        <v>6.02508306503296</v>
+        <v>6.02508211135864</v>
       </c>
       <c r="H473" t="n">
         <v>2396168</v>
@@ -14115,7 +14115,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>6.00617170333862</v>
+        <v>6.00617122650146</v>
       </c>
       <c r="H474" t="n">
         <v>1187378</v>
@@ -14144,7 +14144,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>6.02130079269409</v>
+        <v>6.02130031585693</v>
       </c>
       <c r="H475" t="n">
         <v>1937788</v>
@@ -14173,7 +14173,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G476" t="n">
-        <v>6.03264713287354</v>
+        <v>6.03264665603638</v>
       </c>
       <c r="H476" t="n">
         <v>2330028</v>
@@ -14202,7 +14202,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>5.97213172912598</v>
+        <v>5.97213077545166</v>
       </c>
       <c r="H477" t="n">
         <v>1904370</v>
@@ -14260,7 +14260,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>5.8889217376709</v>
+        <v>5.88892221450806</v>
       </c>
       <c r="H479" t="n">
         <v>2778926</v>
@@ -14318,7 +14318,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G481" t="n">
-        <v>5.78680229187012</v>
+        <v>5.78680276870728</v>
       </c>
       <c r="H481" t="n">
         <v>2037192</v>
@@ -14376,7 +14376,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G483" t="n">
-        <v>5.99482536315918</v>
+        <v>5.99482440948486</v>
       </c>
       <c r="H483" t="n">
         <v>2129837</v>
@@ -14405,7 +14405,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>6.04777526855469</v>
+        <v>6.04777574539185</v>
       </c>
       <c r="H484" t="n">
         <v>1409766</v>
@@ -14434,7 +14434,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G485" t="n">
-        <v>6.13476705551147</v>
+        <v>6.13476657867432</v>
       </c>
       <c r="H485" t="n">
         <v>1649104</v>
@@ -14463,7 +14463,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G486" t="n">
-        <v>6.13854932785034</v>
+        <v>6.13854885101318</v>
       </c>
       <c r="H486" t="n">
         <v>1990120</v>
@@ -14492,7 +14492,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>6.0969443321228</v>
+        <v>6.09694480895996</v>
       </c>
       <c r="H487" t="n">
         <v>1240193</v>
@@ -14521,7 +14521,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>6.16124296188354</v>
+        <v>6.16124248504639</v>
       </c>
       <c r="H488" t="n">
         <v>1807013</v>
@@ -14550,7 +14550,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G489" t="n">
-        <v>6.13476705551147</v>
+        <v>6.13476657867432</v>
       </c>
       <c r="H489" t="n">
         <v>1847566</v>
@@ -14579,7 +14579,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G490" t="n">
-        <v>6.21419382095337</v>
+        <v>6.21419286727905</v>
       </c>
       <c r="H490" t="n">
         <v>1822039</v>
@@ -14608,7 +14608,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>6.34278917312622</v>
+        <v>6.34278964996338</v>
       </c>
       <c r="H491" t="n">
         <v>3494738</v>
@@ -14666,7 +14666,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>6.29740238189697</v>
+        <v>6.29740190505981</v>
       </c>
       <c r="H493" t="n">
         <v>3189474</v>
@@ -14724,7 +14724,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>6.39195871353149</v>
+        <v>6.39195728302002</v>
       </c>
       <c r="H495" t="n">
         <v>1802507</v>
@@ -14753,7 +14753,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G496" t="n">
-        <v>6.32009553909302</v>
+        <v>6.32009506225586</v>
       </c>
       <c r="H496" t="n">
         <v>1573542</v>
@@ -14782,7 +14782,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G497" t="n">
-        <v>6.46381950378418</v>
+        <v>6.4638204574585</v>
       </c>
       <c r="H497" t="n">
         <v>1421561</v>
@@ -14840,7 +14840,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G499" t="n">
-        <v>6.44112682342529</v>
+        <v>6.44112730026245</v>
       </c>
       <c r="H499" t="n">
         <v>2396048</v>
@@ -14869,7 +14869,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G500" t="n">
-        <v>6.53946495056152</v>
+        <v>6.53946542739868</v>
       </c>
       <c r="H500" t="n">
         <v>2118776</v>
@@ -14956,7 +14956,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G503" t="n">
-        <v>6.44112682342529</v>
+        <v>6.44112730026245</v>
       </c>
       <c r="H503" t="n">
         <v>1990519</v>
@@ -15014,7 +15014,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>6.50542545318604</v>
+        <v>6.50542497634888</v>
       </c>
       <c r="H505" t="n">
         <v>1051125</v>
@@ -15043,7 +15043,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G506" t="n">
-        <v>6.51298904418945</v>
+        <v>6.51298856735229</v>
       </c>
       <c r="H506" t="n">
         <v>1451098</v>
@@ -15101,7 +15101,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G508" t="n">
-        <v>6.60376167297363</v>
+        <v>6.60376214981079</v>
       </c>
       <c r="H508" t="n">
         <v>1276865</v>
@@ -15159,7 +15159,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.55837535858154</v>
+        <v>6.55837631225586</v>
       </c>
       <c r="H510" t="n">
         <v>1047728</v>
@@ -15188,7 +15188,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G511" t="n">
-        <v>6.45625495910645</v>
+        <v>6.45625591278076</v>
       </c>
       <c r="H511" t="n">
         <v>585989</v>
@@ -15246,7 +15246,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>6.39952278137207</v>
+        <v>6.39952182769775</v>
       </c>
       <c r="H513" t="n">
         <v>2092048</v>
@@ -15275,7 +15275,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G514" t="n">
-        <v>6.65671348571777</v>
+        <v>6.65671300888062</v>
       </c>
       <c r="H514" t="n">
         <v>2595760</v>
@@ -15304,7 +15304,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G515" t="n">
-        <v>6.73992204666138</v>
+        <v>6.73992109298706</v>
       </c>
       <c r="H515" t="n">
         <v>1945979</v>
@@ -15362,7 +15362,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>7.06141138076782</v>
+        <v>7.06141185760498</v>
       </c>
       <c r="H517" t="n">
         <v>3758849</v>
@@ -15391,7 +15391,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G518" t="n">
-        <v>7.12949180603027</v>
+        <v>7.12949085235596</v>
       </c>
       <c r="H518" t="n">
         <v>2703458</v>
@@ -15420,7 +15420,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>7.29969215393066</v>
+        <v>7.29969167709351</v>
       </c>
       <c r="H519" t="n">
         <v>2135357</v>
@@ -15449,7 +15449,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G520" t="n">
-        <v>7.26186990737915</v>
+        <v>7.26187038421631</v>
       </c>
       <c r="H520" t="n">
         <v>2754591</v>
@@ -15478,7 +15478,7 @@
         <v>9.61499977111816</v>
       </c>
       <c r="G521" t="n">
-        <v>7.27321624755859</v>
+        <v>7.27321577072144</v>
       </c>
       <c r="H521" t="n">
         <v>1422538</v>
@@ -15507,7 +15507,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>7.19000720977783</v>
+        <v>7.19000673294067</v>
       </c>
       <c r="H522" t="n">
         <v>2491793</v>
@@ -15536,7 +15536,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>7.22026538848877</v>
+        <v>7.22026443481445</v>
       </c>
       <c r="H523" t="n">
         <v>1774616</v>
@@ -15565,7 +15565,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G524" t="n">
-        <v>7.32238531112671</v>
+        <v>7.32238578796387</v>
       </c>
       <c r="H524" t="n">
         <v>1544485</v>
@@ -15652,7 +15652,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>7.51527881622314</v>
+        <v>7.5152792930603</v>
       </c>
       <c r="H527" t="n">
         <v>3719053</v>
@@ -15681,7 +15681,7 @@
         <v>9.875</v>
       </c>
       <c r="G528" t="n">
-        <v>7.46989154815674</v>
+        <v>7.46989107131958</v>
       </c>
       <c r="H528" t="n">
         <v>1864578</v>
@@ -15739,7 +15739,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>7.64009284973145</v>
+        <v>7.64009094238281</v>
       </c>
       <c r="H530" t="n">
         <v>1886050</v>
@@ -15768,7 +15768,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G531" t="n">
-        <v>7.62496280670166</v>
+        <v>7.6249623298645</v>
       </c>
       <c r="H531" t="n">
         <v>2724662</v>
@@ -15797,7 +15797,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>7.49636745452881</v>
+        <v>7.49636697769165</v>
       </c>
       <c r="H532" t="n">
         <v>2703227</v>
@@ -15826,7 +15826,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>7.57201290130615</v>
+        <v>7.57201194763184</v>
       </c>
       <c r="H533" t="n">
         <v>2351710</v>
@@ -15884,7 +15884,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G535" t="n">
-        <v>7.4540057182312</v>
+        <v>7.45400667190552</v>
       </c>
       <c r="H535" t="n">
         <v>3357817</v>
@@ -15913,7 +15913,7 @@
         <v>9.75</v>
       </c>
       <c r="G536" t="n">
-        <v>7.37533569335938</v>
+        <v>7.37533521652222</v>
       </c>
       <c r="H536" t="n">
         <v>2297778</v>
@@ -15942,7 +15942,7 @@
         <v>9.31799983978271</v>
       </c>
       <c r="G537" t="n">
-        <v>7.04855155944824</v>
+        <v>7.04855251312256</v>
       </c>
       <c r="H537" t="n">
         <v>5044050</v>
@@ -15971,7 +15971,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G538" t="n">
-        <v>7.23009824752808</v>
+        <v>7.23009777069092</v>
       </c>
       <c r="H538" t="n">
         <v>4868264</v>
@@ -16029,7 +16029,7 @@
         <v>9.21399974822998</v>
       </c>
       <c r="G540" t="n">
-        <v>6.96988153457642</v>
+        <v>6.96988201141357</v>
       </c>
       <c r="H540" t="n">
         <v>4499784</v>
@@ -16058,7 +16058,7 @@
         <v>9.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.99711322784424</v>
+        <v>6.99711418151855</v>
       </c>
       <c r="H541" t="n">
         <v>2928469</v>
@@ -16087,7 +16087,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G542" t="n">
-        <v>6.97593402862549</v>
+        <v>6.97593355178833</v>
       </c>
       <c r="H542" t="n">
         <v>1859299</v>
@@ -16116,7 +16116,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G543" t="n">
-        <v>7.03039646148682</v>
+        <v>7.03039693832397</v>
       </c>
       <c r="H543" t="n">
         <v>3747691</v>
@@ -16145,7 +16145,7 @@
         <v>9.53600025177002</v>
       </c>
       <c r="G544" t="n">
-        <v>7.2134575843811</v>
+        <v>7.21345710754395</v>
       </c>
       <c r="H544" t="n">
         <v>2381962</v>
@@ -16290,7 +16290,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G549" t="n">
-        <v>7.51149559020996</v>
+        <v>7.51149702072144</v>
       </c>
       <c r="H549" t="n">
         <v>2091851</v>
@@ -16319,7 +16319,7 @@
         <v>9.90200042724609</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49031639099121</v>
+        <v>7.49031543731689</v>
       </c>
       <c r="H550" t="n">
         <v>2022903</v>
@@ -16348,7 +16348,7 @@
         <v>9.97200012207031</v>
       </c>
       <c r="G551" t="n">
-        <v>7.54326820373535</v>
+        <v>7.54326677322388</v>
       </c>
       <c r="H551" t="n">
         <v>2306092</v>
@@ -16377,7 +16377,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G552" t="n">
-        <v>7.62496280670166</v>
+        <v>7.6249623298645</v>
       </c>
       <c r="H552" t="n">
         <v>1930528</v>
@@ -16406,7 +16406,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G553" t="n">
-        <v>7.65522050857544</v>
+        <v>7.6552209854126</v>
       </c>
       <c r="H553" t="n">
         <v>2284556</v>
@@ -16493,7 +16493,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G556" t="n">
-        <v>7.24220275878906</v>
+        <v>7.2422022819519</v>
       </c>
       <c r="H556" t="n">
         <v>3303724</v>
@@ -16522,7 +16522,7 @@
         <v>9.9680004119873</v>
       </c>
       <c r="G557" t="n">
-        <v>7.54024076461792</v>
+        <v>7.54024267196655</v>
       </c>
       <c r="H557" t="n">
         <v>2648397</v>
@@ -16551,7 +16551,7 @@
         <v>10.1350002288818</v>
       </c>
       <c r="G558" t="n">
-        <v>7.66656732559204</v>
+        <v>7.66656637191772</v>
       </c>
       <c r="H558" t="n">
         <v>1674650</v>
@@ -16609,7 +16609,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G560" t="n">
-        <v>7.78381538391113</v>
+        <v>7.78381633758545</v>
       </c>
       <c r="H560" t="n">
         <v>1473972</v>
@@ -16638,7 +16638,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G561" t="n">
-        <v>7.79138135910034</v>
+        <v>7.79138088226318</v>
       </c>
       <c r="H561" t="n">
         <v>2329031</v>
@@ -16667,7 +16667,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>7.64765644073486</v>
+        <v>7.64765691757202</v>
       </c>
       <c r="H562" t="n">
         <v>1900362</v>
@@ -16696,7 +16696,7 @@
         <v>10.125</v>
       </c>
       <c r="G563" t="n">
-        <v>7.65900373458862</v>
+        <v>7.65900421142578</v>
       </c>
       <c r="H563" t="n">
         <v>1838776</v>
@@ -16725,7 +16725,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G564" t="n">
-        <v>7.74599361419678</v>
+        <v>7.74599313735962</v>
       </c>
       <c r="H564" t="n">
         <v>1632465</v>
@@ -16754,7 +16754,7 @@
         <v>10.3249998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>7.81029224395752</v>
+        <v>7.81029272079468</v>
       </c>
       <c r="H565" t="n">
         <v>3130588</v>
@@ -16783,7 +16783,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>7.64765644073486</v>
+        <v>7.64765691757202</v>
       </c>
       <c r="H566" t="n">
         <v>2427519</v>
@@ -16812,7 +16812,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G567" t="n">
-        <v>7.84433078765869</v>
+        <v>7.84433317184448</v>
       </c>
       <c r="H567" t="n">
         <v>2616314</v>
@@ -16841,7 +16841,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>7.77246952056885</v>
+        <v>7.77246856689453</v>
       </c>
       <c r="H568" t="n">
         <v>1383045</v>
@@ -16870,7 +16870,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G569" t="n">
-        <v>7.57579469680786</v>
+        <v>7.57579278945923</v>
       </c>
       <c r="H569" t="n">
         <v>2012509</v>
@@ -16899,7 +16899,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G570" t="n">
-        <v>7.54931879043579</v>
+        <v>7.54931735992432</v>
       </c>
       <c r="H570" t="n">
         <v>2525070</v>
@@ -16928,7 +16928,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G571" t="n">
-        <v>7.41013193130493</v>
+        <v>7.41013145446777</v>
       </c>
       <c r="H571" t="n">
         <v>2336239</v>
@@ -16957,7 +16957,7 @@
         <v>9.81599998474121</v>
       </c>
       <c r="G572" t="n">
-        <v>7.42526054382324</v>
+        <v>7.4252610206604</v>
       </c>
       <c r="H572" t="n">
         <v>1631785</v>
@@ -16986,7 +16986,7 @@
         <v>9.72799968719482</v>
       </c>
       <c r="G573" t="n">
-        <v>7.35869359970093</v>
+        <v>7.35869407653809</v>
       </c>
       <c r="H573" t="n">
         <v>2223477</v>
@@ -17015,7 +17015,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G574" t="n">
-        <v>7.38895177841187</v>
+        <v>7.38895225524902</v>
       </c>
       <c r="H574" t="n">
         <v>1242505</v>
@@ -17073,7 +17073,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G576" t="n">
-        <v>7.37230968475342</v>
+        <v>7.37231159210205</v>
       </c>
       <c r="H576" t="n">
         <v>2250788</v>
@@ -17131,7 +17131,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G578" t="n">
-        <v>7.31330823898315</v>
+        <v>7.31330728530884</v>
       </c>
       <c r="H578" t="n">
         <v>2180063</v>
@@ -17218,7 +17218,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>7.31482172012329</v>
+        <v>7.31482076644897</v>
       </c>
       <c r="H581" t="n">
         <v>1968934</v>
@@ -17305,7 +17305,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G584" t="n">
-        <v>7.38895177841187</v>
+        <v>7.38895225524902</v>
       </c>
       <c r="H584" t="n">
         <v>1482837</v>
@@ -17334,7 +17334,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>7.46610927581787</v>
+        <v>7.46610975265503</v>
       </c>
       <c r="H585" t="n">
         <v>2347576</v>
@@ -17363,7 +17363,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G586" t="n">
-        <v>7.54175424575806</v>
+        <v>7.54175519943237</v>
       </c>
       <c r="H586" t="n">
         <v>1948968</v>
@@ -17392,7 +17392,7 @@
         <v>9.96399974822998</v>
       </c>
       <c r="G587" t="n">
-        <v>7.53721523284912</v>
+        <v>7.53721475601196</v>
       </c>
       <c r="H587" t="n">
         <v>1703361</v>
@@ -17421,7 +17421,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G588" t="n">
-        <v>7.50695705413818</v>
+        <v>7.5069580078125</v>
       </c>
       <c r="H588" t="n">
         <v>1885121</v>
@@ -17479,7 +17479,7 @@
         <v>10</v>
       </c>
       <c r="G590" t="n">
-        <v>7.78810787200928</v>
+        <v>7.78810834884644</v>
       </c>
       <c r="H590" t="n">
         <v>2393942</v>
@@ -17537,7 +17537,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G592" t="n">
-        <v>7.67440128326416</v>
+        <v>7.67440271377563</v>
       </c>
       <c r="H592" t="n">
         <v>1682061</v>
@@ -17566,7 +17566,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G593" t="n">
-        <v>7.67907381057739</v>
+        <v>7.67907428741455</v>
       </c>
       <c r="H593" t="n">
         <v>956793</v>
@@ -17595,7 +17595,7 @@
         <v>9.9040002822876</v>
       </c>
       <c r="G594" t="n">
-        <v>7.71334314346313</v>
+        <v>7.7133412361145</v>
       </c>
       <c r="H594" t="n">
         <v>1365591</v>
@@ -17624,7 +17624,7 @@
         <v>9.98400020599365</v>
       </c>
       <c r="G595" t="n">
-        <v>7.77564764022827</v>
+        <v>7.7756462097168</v>
       </c>
       <c r="H595" t="n">
         <v>1875685</v>
@@ -17653,7 +17653,7 @@
         <v>9.87399959564209</v>
       </c>
       <c r="G596" t="n">
-        <v>7.68997716903687</v>
+        <v>7.68997764587402</v>
       </c>
       <c r="H596" t="n">
         <v>1637163</v>
@@ -17682,7 +17682,7 @@
         <v>10.0749998092651</v>
       </c>
       <c r="G597" t="n">
-        <v>7.84651803970337</v>
+        <v>7.84651851654053</v>
       </c>
       <c r="H597" t="n">
         <v>1772133</v>
@@ -17711,7 +17711,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G598" t="n">
-        <v>7.91271781921387</v>
+        <v>7.91271734237671</v>
       </c>
       <c r="H598" t="n">
         <v>1339035</v>
@@ -17798,7 +17798,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G601" t="n">
-        <v>7.57004117965698</v>
+        <v>7.57004022598267</v>
       </c>
       <c r="H601" t="n">
         <v>1865136</v>
@@ -17827,7 +17827,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G602" t="n">
-        <v>7.56848335266113</v>
+        <v>7.56848239898682</v>
       </c>
       <c r="H602" t="n">
         <v>2215103</v>
@@ -17856,7 +17856,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58717393875122</v>
+        <v>7.58717441558838</v>
       </c>
       <c r="H603" t="n">
         <v>1708543</v>
@@ -17885,7 +17885,7 @@
         <v>9.72799968719482</v>
       </c>
       <c r="G604" t="n">
-        <v>7.57627105712891</v>
+        <v>7.57627058029175</v>
       </c>
       <c r="H604" t="n">
         <v>1872933</v>
@@ -17914,7 +17914,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G605" t="n">
-        <v>7.16194295883179</v>
+        <v>7.16194486618042</v>
       </c>
       <c r="H605" t="n">
         <v>4253298</v>
@@ -17943,7 +17943,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G606" t="n">
-        <v>7.14481067657471</v>
+        <v>7.14481115341187</v>
       </c>
       <c r="H606" t="n">
         <v>4059527</v>
@@ -18001,7 +18001,7 @@
         <v>8.89799976348877</v>
       </c>
       <c r="G608" t="n">
-        <v>6.92985868453979</v>
+        <v>6.92985820770264</v>
       </c>
       <c r="H608" t="n">
         <v>2087544</v>
@@ -18059,7 +18059,7 @@
         <v>9.1560001373291</v>
       </c>
       <c r="G610" t="n">
-        <v>7.13079166412354</v>
+        <v>7.13079261779785</v>
       </c>
       <c r="H610" t="n">
         <v>2396179</v>
@@ -18088,7 +18088,7 @@
         <v>9.18200016021729</v>
       </c>
       <c r="G611" t="n">
-        <v>7.15104150772095</v>
+        <v>7.15104007720947</v>
       </c>
       <c r="H611" t="n">
         <v>2695423</v>
@@ -18117,7 +18117,7 @@
         <v>8.78600025177002</v>
       </c>
       <c r="G612" t="n">
-        <v>6.84263229370117</v>
+        <v>6.84263134002686</v>
       </c>
       <c r="H612" t="n">
         <v>4006077</v>
@@ -18175,7 +18175,7 @@
         <v>7.95599985122681</v>
       </c>
       <c r="G614" t="n">
-        <v>6.19621849060059</v>
+        <v>6.19621896743774</v>
       </c>
       <c r="H614" t="n">
         <v>6227171</v>
@@ -18204,7 +18204,7 @@
         <v>8.4680004119873</v>
       </c>
       <c r="G615" t="n">
-        <v>6.59496974945068</v>
+        <v>6.59497022628784</v>
       </c>
       <c r="H615" t="n">
         <v>6446132</v>
@@ -18233,7 +18233,7 @@
         <v>8.55399990081787</v>
       </c>
       <c r="G616" t="n">
-        <v>6.66194772720337</v>
+        <v>6.66194820404053</v>
       </c>
       <c r="H616" t="n">
         <v>5399976</v>
@@ -18262,7 +18262,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G617" t="n">
-        <v>6.84418916702271</v>
+        <v>6.84418964385986</v>
       </c>
       <c r="H617" t="n">
         <v>4418459</v>
@@ -18320,7 +18320,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G619" t="n">
-        <v>6.56537532806396</v>
+        <v>6.56537580490112</v>
       </c>
       <c r="H619" t="n">
         <v>3748575</v>
@@ -18349,7 +18349,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G620" t="n">
-        <v>6.9547815322876</v>
+        <v>6.95478105545044</v>
       </c>
       <c r="H620" t="n">
         <v>4511558</v>
@@ -18378,7 +18378,7 @@
         <v>8.9040002822876</v>
       </c>
       <c r="G621" t="n">
-        <v>6.93453121185303</v>
+        <v>6.93453168869019</v>
       </c>
       <c r="H621" t="n">
         <v>3217269</v>
@@ -18407,7 +18407,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G622" t="n">
-        <v>6.88313055038452</v>
+        <v>6.88313007354736</v>
       </c>
       <c r="H622" t="n">
         <v>2212311</v>
@@ -18436,7 +18436,7 @@
         <v>8.98200035095215</v>
       </c>
       <c r="G623" t="n">
-        <v>6.99527978897095</v>
+        <v>6.99527835845947</v>
       </c>
       <c r="H623" t="n">
         <v>2980931</v>
@@ -18494,7 +18494,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>7.3052453994751</v>
+        <v>7.30524492263794</v>
       </c>
       <c r="H625" t="n">
         <v>2854136</v>
@@ -18523,7 +18523,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G626" t="n">
-        <v>7.41895198822021</v>
+        <v>7.41895246505737</v>
       </c>
       <c r="H626" t="n">
         <v>3415478</v>
@@ -18581,7 +18581,7 @@
         <v>9.44400024414062</v>
       </c>
       <c r="G628" t="n">
-        <v>7.35508918762207</v>
+        <v>7.35509014129639</v>
       </c>
       <c r="H628" t="n">
         <v>2791658</v>
@@ -18610,7 +18610,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G629" t="n">
-        <v>7.41895198822021</v>
+        <v>7.41895246505737</v>
       </c>
       <c r="H629" t="n">
         <v>2609330</v>
@@ -18639,7 +18639,7 @@
         <v>9.62199974060059</v>
       </c>
       <c r="G630" t="n">
-        <v>7.49371814727783</v>
+        <v>7.49371671676636</v>
       </c>
       <c r="H630" t="n">
         <v>1981592</v>
@@ -18668,7 +18668,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.42206716537476</v>
+        <v>7.4220666885376</v>
       </c>
       <c r="H631" t="n">
         <v>1832919</v>
@@ -18697,7 +18697,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G632" t="n">
-        <v>7.51396656036377</v>
+        <v>7.51396608352661</v>
       </c>
       <c r="H632" t="n">
         <v>2002552</v>
@@ -18726,7 +18726,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34730052947998</v>
+        <v>7.34730100631714</v>
       </c>
       <c r="H633" t="n">
         <v>1418464</v>
@@ -18755,7 +18755,7 @@
         <v>9.51399993896484</v>
       </c>
       <c r="G634" t="n">
-        <v>7.40960693359375</v>
+        <v>7.40960550308228</v>
       </c>
       <c r="H634" t="n">
         <v>1335688</v>
@@ -18784,7 +18784,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G635" t="n">
-        <v>7.37533950805664</v>
+        <v>7.37533807754517</v>
       </c>
       <c r="H635" t="n">
         <v>2226807</v>
@@ -18842,7 +18842,7 @@
         <v>9.67199993133545</v>
       </c>
       <c r="G637" t="n">
-        <v>7.53265810012817</v>
+        <v>7.53265857696533</v>
       </c>
       <c r="H637" t="n">
         <v>1755750</v>
@@ -18871,7 +18871,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G638" t="n">
-        <v>7.54044628143311</v>
+        <v>7.54044675827026</v>
       </c>
       <c r="H638" t="n">
         <v>1450594</v>
@@ -18900,7 +18900,7 @@
         <v>9.83199977874756</v>
       </c>
       <c r="G639" t="n">
-        <v>7.65726757049561</v>
+        <v>7.65726804733276</v>
       </c>
       <c r="H639" t="n">
         <v>2310754</v>
@@ -18929,7 +18929,7 @@
         <v>9.95800018310547</v>
       </c>
       <c r="G640" t="n">
-        <v>7.7553973197937</v>
+        <v>7.75539827346802</v>
       </c>
       <c r="H640" t="n">
         <v>1366476</v>
@@ -18958,7 +18958,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G641" t="n">
-        <v>7.73359060287476</v>
+        <v>7.73359155654907</v>
       </c>
       <c r="H641" t="n">
         <v>2425450</v>
@@ -18987,7 +18987,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>7.65571069717407</v>
+        <v>7.65570974349976</v>
       </c>
       <c r="H642" t="n">
         <v>2366673</v>
@@ -19016,7 +19016,7 @@
         <v>9.95800018310547</v>
       </c>
       <c r="G643" t="n">
-        <v>7.7553973197937</v>
+        <v>7.75539827346802</v>
       </c>
       <c r="H643" t="n">
         <v>1094692</v>
@@ -19045,7 +19045,7 @@
         <v>9.98200035095215</v>
       </c>
       <c r="G644" t="n">
-        <v>7.77408933639526</v>
+        <v>7.77408981323242</v>
       </c>
       <c r="H644" t="n">
         <v>1259309</v>
@@ -19074,7 +19074,7 @@
         <v>9.97599983215332</v>
       </c>
       <c r="G645" t="n">
-        <v>7.76941633224487</v>
+        <v>7.76941585540771</v>
       </c>
       <c r="H645" t="n">
         <v>1764860</v>
@@ -19103,7 +19103,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G646" t="n">
-        <v>7.88935422897339</v>
+        <v>7.88935327529907</v>
       </c>
       <c r="H646" t="n">
         <v>1558159</v>
@@ -19161,7 +19161,7 @@
         <v>10.25</v>
       </c>
       <c r="G648" t="n">
-        <v>7.98281049728394</v>
+        <v>7.98281097412109</v>
       </c>
       <c r="H648" t="n">
         <v>1690670</v>
@@ -19190,7 +19190,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G649" t="n">
-        <v>7.99059867858887</v>
+        <v>7.99059915542603</v>
       </c>
       <c r="H649" t="n">
         <v>1803691</v>
@@ -19248,7 +19248,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G651" t="n">
-        <v>7.97112798690796</v>
+        <v>7.9711275100708</v>
       </c>
       <c r="H651" t="n">
         <v>1564940</v>
@@ -19277,7 +19277,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G652" t="n">
-        <v>7.88156509399414</v>
+        <v>7.8815655708313</v>
       </c>
       <c r="H652" t="n">
         <v>2800521</v>
@@ -19306,7 +19306,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G653" t="n">
-        <v>7.92829465866089</v>
+        <v>7.92829322814941</v>
       </c>
       <c r="H653" t="n">
         <v>1215020</v>
@@ -19451,7 +19451,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>7.94387054443359</v>
+        <v>7.94386959075928</v>
       </c>
       <c r="H658" t="n">
         <v>1136695</v>
@@ -19480,7 +19480,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G659" t="n">
-        <v>7.82704925537109</v>
+        <v>7.82704830169678</v>
       </c>
       <c r="H659" t="n">
         <v>2131963</v>
@@ -19509,7 +19509,7 @@
         <v>10.1949996948242</v>
       </c>
       <c r="G660" t="n">
-        <v>7.93997526168823</v>
+        <v>7.93997669219971</v>
       </c>
       <c r="H660" t="n">
         <v>3005063</v>
@@ -19538,7 +19538,7 @@
         <v>10.0749998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>7.84651803970337</v>
+        <v>7.84651851654053</v>
       </c>
       <c r="H661" t="n">
         <v>2018865</v>
@@ -19596,7 +19596,7 @@
         <v>9.97399997711182</v>
       </c>
       <c r="G663" t="n">
-        <v>7.76785802841187</v>
+        <v>7.76785945892334</v>
       </c>
       <c r="H663" t="n">
         <v>1716459</v>
@@ -19625,7 +19625,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G664" t="n">
-        <v>7.87377738952637</v>
+        <v>7.87377691268921</v>
       </c>
       <c r="H664" t="n">
         <v>1635276</v>
@@ -19654,7 +19654,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G665" t="n">
-        <v>7.78032064437866</v>
+        <v>7.78031969070435</v>
       </c>
       <c r="H665" t="n">
         <v>1671254</v>
@@ -19683,7 +19683,7 @@
         <v>10.0649995803833</v>
       </c>
       <c r="G666" t="n">
-        <v>7.83873081207275</v>
+        <v>7.83872985839844</v>
       </c>
       <c r="H666" t="n">
         <v>1430460</v>
@@ -19712,7 +19712,7 @@
         <v>9.9980001449585</v>
       </c>
       <c r="G667" t="n">
-        <v>7.78655099868774</v>
+        <v>7.78655004501343</v>
       </c>
       <c r="H667" t="n">
         <v>2346193</v>
@@ -19741,7 +19741,7 @@
         <v>10.0450000762939</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82315492630005</v>
+        <v>7.82315540313721</v>
       </c>
       <c r="H668" t="n">
         <v>1487833</v>
@@ -19770,7 +19770,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>7.90493011474609</v>
+        <v>7.90492868423462</v>
       </c>
       <c r="H669" t="n">
         <v>1683531</v>
@@ -19886,7 +19886,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>8.00228023529053</v>
+        <v>8.00227928161621</v>
       </c>
       <c r="H673" t="n">
         <v>1399727</v>
@@ -19973,7 +19973,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G676" t="n">
-        <v>7.92829465866089</v>
+        <v>7.92829322814941</v>
       </c>
       <c r="H676" t="n">
         <v>710530</v>
@@ -20002,7 +20002,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>7.90493011474609</v>
+        <v>7.90492868423462</v>
       </c>
       <c r="H677" t="n">
         <v>485302</v>
@@ -20031,7 +20031,7 @@
         <v>10.125</v>
       </c>
       <c r="G678" t="n">
-        <v>7.8854603767395</v>
+        <v>7.88545942306519</v>
       </c>
       <c r="H678" t="n">
         <v>979518</v>
@@ -20089,7 +20089,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>7.99059867858887</v>
+        <v>7.99059915542603</v>
       </c>
       <c r="H680" t="n">
         <v>2347882</v>
@@ -20205,7 +20205,7 @@
         <v>10.8549995422363</v>
       </c>
       <c r="G684" t="n">
-        <v>8.4539909362793</v>
+        <v>8.45399188995361</v>
       </c>
       <c r="H684" t="n">
         <v>2386527</v>
@@ -20234,7 +20234,7 @@
         <v>10.8549995422363</v>
       </c>
       <c r="G685" t="n">
-        <v>8.4539909362793</v>
+        <v>8.45399188995361</v>
       </c>
       <c r="H685" t="n">
         <v>2264319</v>
@@ -20263,7 +20263,7 @@
         <v>10.8450002670288</v>
       </c>
       <c r="G686" t="n">
-        <v>8.44620323181152</v>
+        <v>8.44620418548584</v>
       </c>
       <c r="H686" t="n">
         <v>1462185</v>
@@ -20292,7 +20292,7 @@
         <v>11</v>
       </c>
       <c r="G687" t="n">
-        <v>8.56691837310791</v>
+        <v>8.56691932678223</v>
       </c>
       <c r="H687" t="n">
         <v>1662128</v>
@@ -20321,7 +20321,7 @@
         <v>11.0749998092651</v>
       </c>
       <c r="G688" t="n">
-        <v>8.62532997131348</v>
+        <v>8.62532901763916</v>
       </c>
       <c r="H688" t="n">
         <v>1214004</v>
@@ -20350,7 +20350,7 @@
         <v>11.1750001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>8.70321178436279</v>
+        <v>8.70321083068848</v>
       </c>
       <c r="H689" t="n">
         <v>1354647</v>
@@ -20379,7 +20379,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G690" t="n">
-        <v>8.70710563659668</v>
+        <v>8.70710468292236</v>
       </c>
       <c r="H690" t="n">
         <v>1937510</v>
@@ -20408,7 +20408,7 @@
         <v>11.2749996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>8.78109264373779</v>
+        <v>8.78109073638916</v>
       </c>
       <c r="H691" t="n">
         <v>1764544</v>
@@ -20437,7 +20437,7 @@
         <v>11.4049997329712</v>
       </c>
       <c r="G692" t="n">
-        <v>8.88233757019043</v>
+        <v>8.88233661651611</v>
       </c>
       <c r="H692" t="n">
         <v>1927177</v>
@@ -20495,7 +20495,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97579383850098</v>
+        <v>8.97579479217529</v>
       </c>
       <c r="H694" t="n">
         <v>2464064</v>
@@ -20524,7 +20524,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G695" t="n">
-        <v>8.88623142242432</v>
+        <v>8.88623046875</v>
       </c>
       <c r="H695" t="n">
         <v>2081330</v>
@@ -20553,7 +20553,7 @@
         <v>11.6450004577637</v>
       </c>
       <c r="G696" t="n">
-        <v>9.06925201416016</v>
+        <v>9.06925296783447</v>
       </c>
       <c r="H696" t="n">
         <v>3391477</v>
@@ -20611,7 +20611,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G698" t="n">
-        <v>9.26006031036377</v>
+        <v>9.26006126403809</v>
       </c>
       <c r="H698" t="n">
         <v>2932183</v>
@@ -20640,7 +20640,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G699" t="n">
-        <v>9.26006031036377</v>
+        <v>9.26006126403809</v>
       </c>
       <c r="H699" t="n">
         <v>2455162</v>
@@ -20698,7 +20698,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G701" t="n">
-        <v>8.9680061340332</v>
+        <v>8.96800804138184</v>
       </c>
       <c r="H701" t="n">
         <v>3242374</v>
@@ -20756,7 +20756,7 @@
         <v>11.5</v>
       </c>
       <c r="G703" t="n">
-        <v>8.95632362365723</v>
+        <v>8.95632457733154</v>
       </c>
       <c r="H703" t="n">
         <v>1952895</v>
@@ -20843,7 +20843,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G706" t="n">
-        <v>8.77719879150391</v>
+        <v>8.77719783782959</v>
       </c>
       <c r="H706" t="n">
         <v>2022064</v>
@@ -20872,7 +20872,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G707" t="n">
-        <v>8.35663986206055</v>
+        <v>8.35663795471191</v>
       </c>
       <c r="H707" t="n">
         <v>2950337</v>
@@ -20901,7 +20901,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>8.33327674865723</v>
+        <v>8.33327579498291</v>
       </c>
       <c r="H708" t="n">
         <v>3183760</v>
@@ -21017,7 +21017,7 @@
         <v>9.75</v>
       </c>
       <c r="G712" t="n">
-        <v>7.59340524673462</v>
+        <v>7.59340476989746</v>
       </c>
       <c r="H712" t="n">
         <v>1222884</v>
@@ -21046,7 +21046,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G713" t="n">
-        <v>7.819260597229</v>
+        <v>7.81926155090332</v>
       </c>
       <c r="H713" t="n">
         <v>2218488</v>
@@ -21075,7 +21075,7 @@
         <v>9.68599987030029</v>
       </c>
       <c r="G714" t="n">
-        <v>7.5435619354248</v>
+        <v>7.54356241226196</v>
       </c>
       <c r="H714" t="n">
         <v>1628235</v>
@@ -21104,7 +21104,7 @@
         <v>9.23400020599365</v>
       </c>
       <c r="G715" t="n">
-        <v>7.19153928756714</v>
+        <v>7.19153833389282</v>
       </c>
       <c r="H715" t="n">
         <v>2554878</v>
@@ -21133,7 +21133,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G716" t="n">
-        <v>6.984375</v>
+        <v>6.98437595367432</v>
       </c>
       <c r="H716" t="n">
         <v>4261848</v>
@@ -21220,7 +21220,7 @@
         <v>8.72599983215332</v>
       </c>
       <c r="G719" t="n">
-        <v>6.79590368270874</v>
+        <v>6.79590272903442</v>
       </c>
       <c r="H719" t="n">
         <v>1904345</v>
@@ -21249,7 +21249,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G720" t="n">
-        <v>7.04979562759399</v>
+        <v>7.04979467391968</v>
       </c>
       <c r="H720" t="n">
         <v>3077402</v>
@@ -21278,7 +21278,7 @@
         <v>8.77400016784668</v>
       </c>
       <c r="G721" t="n">
-        <v>6.83328533172607</v>
+        <v>6.83328580856323</v>
       </c>
       <c r="H721" t="n">
         <v>2229912</v>
@@ -21307,7 +21307,7 @@
         <v>9.04599952697754</v>
       </c>
       <c r="G722" t="n">
-        <v>7.0451226234436</v>
+        <v>7.04512214660645</v>
       </c>
       <c r="H722" t="n">
         <v>2486851</v>
@@ -21336,7 +21336,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G723" t="n">
-        <v>7.06692934036255</v>
+        <v>7.06692886352539</v>
       </c>
       <c r="H723" t="n">
         <v>1554170</v>
@@ -21365,7 +21365,7 @@
         <v>9.24600028991699</v>
       </c>
       <c r="G724" t="n">
-        <v>7.2008843421936</v>
+        <v>7.20088529586792</v>
       </c>
       <c r="H724" t="n">
         <v>2577826</v>
@@ -21394,7 +21394,7 @@
         <v>9.38599967956543</v>
       </c>
       <c r="G725" t="n">
-        <v>7.30991792678833</v>
+        <v>7.30991840362549</v>
       </c>
       <c r="H725" t="n">
         <v>2225319</v>
@@ -21423,7 +21423,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G726" t="n">
-        <v>7.62922954559326</v>
+        <v>7.62923002243042</v>
       </c>
       <c r="H726" t="n">
         <v>3121627</v>
@@ -21452,7 +21452,7 @@
         <v>9.58399963378906</v>
       </c>
       <c r="G727" t="n">
-        <v>7.4641227722168</v>
+        <v>7.46412324905396</v>
       </c>
       <c r="H727" t="n">
         <v>2256475</v>
@@ -21481,7 +21481,7 @@
         <v>9.60200023651123</v>
       </c>
       <c r="G728" t="n">
-        <v>7.47814226150513</v>
+        <v>7.47814130783081</v>
       </c>
       <c r="H728" t="n">
         <v>2181089</v>
@@ -21510,7 +21510,7 @@
         <v>9.62600040435791</v>
       </c>
       <c r="G729" t="n">
-        <v>7.49683332443237</v>
+        <v>7.49683284759521</v>
       </c>
       <c r="H729" t="n">
         <v>2191642</v>
@@ -21539,7 +21539,7 @@
         <v>9.87600040435791</v>
       </c>
       <c r="G730" t="n">
-        <v>7.69153499603271</v>
+        <v>7.69153547286987</v>
       </c>
       <c r="H730" t="n">
         <v>2117523</v>
@@ -21626,7 +21626,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G733" t="n">
-        <v>7.67128658294678</v>
+        <v>7.67128705978394</v>
       </c>
       <c r="H733" t="n">
         <v>1695599</v>
@@ -21655,7 +21655,7 @@
         <v>9.7480001449585</v>
       </c>
       <c r="G734" t="n">
-        <v>7.59184694290161</v>
+        <v>7.59184837341309</v>
       </c>
       <c r="H734" t="n">
         <v>1440632</v>
@@ -21684,7 +21684,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>7.49216032028198</v>
+        <v>7.49215984344482</v>
       </c>
       <c r="H735" t="n">
         <v>1346144</v>
@@ -21713,7 +21713,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G736" t="n">
-        <v>7.50150537490845</v>
+        <v>7.50150585174561</v>
       </c>
       <c r="H736" t="n">
         <v>1763545</v>
@@ -21742,7 +21742,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G737" t="n">
-        <v>7.54044628143311</v>
+        <v>7.54044675827026</v>
       </c>
       <c r="H737" t="n">
         <v>1242108</v>
@@ -21771,7 +21771,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G738" t="n">
-        <v>7.47502470016479</v>
+        <v>7.47502517700195</v>
       </c>
       <c r="H738" t="n">
         <v>1502534</v>
@@ -21800,7 +21800,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G739" t="n">
-        <v>7.50150537490845</v>
+        <v>7.50150585174561</v>
       </c>
       <c r="H739" t="n">
         <v>1314109</v>
@@ -21829,7 +21829,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G740" t="n">
-        <v>7.45633554458618</v>
+        <v>7.45633459091187</v>
       </c>
       <c r="H740" t="n">
         <v>1338612</v>
@@ -21887,7 +21887,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G742" t="n">
-        <v>7.62922954559326</v>
+        <v>7.62923002243042</v>
       </c>
       <c r="H742" t="n">
         <v>1900863</v>
@@ -21916,7 +21916,7 @@
         <v>9.86800003051758</v>
       </c>
       <c r="G743" t="n">
-        <v>7.68530416488647</v>
+        <v>7.68530607223511</v>
       </c>
       <c r="H743" t="n">
         <v>1171865</v>
@@ -21945,7 +21945,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G744" t="n">
-        <v>7.61832666397095</v>
+        <v>7.61832714080811</v>
       </c>
       <c r="H744" t="n">
         <v>867162</v>
@@ -22003,7 +22003,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G746" t="n">
-        <v>7.37533950805664</v>
+        <v>7.37533807754517</v>
       </c>
       <c r="H746" t="n">
         <v>2300576</v>
@@ -22032,7 +22032,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G747" t="n">
-        <v>7.5606951713562</v>
+        <v>7.56069612503052</v>
       </c>
       <c r="H747" t="n">
         <v>1765087</v>
@@ -22061,7 +22061,7 @@
         <v>9.58199977874756</v>
       </c>
       <c r="G748" t="n">
-        <v>7.46256589889526</v>
+        <v>7.46256494522095</v>
       </c>
       <c r="H748" t="n">
         <v>1190558</v>
@@ -22090,7 +22090,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G749" t="n">
-        <v>7.57004117965698</v>
+        <v>7.57004022598267</v>
       </c>
       <c r="H749" t="n">
         <v>948540</v>
@@ -22148,7 +22148,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G751" t="n">
-        <v>7.11677312850952</v>
+        <v>7.11677265167236</v>
       </c>
       <c r="H751" t="n">
         <v>1246812</v>
@@ -22177,7 +22177,7 @@
         <v>8.93400001525879</v>
       </c>
       <c r="G752" t="n">
-        <v>6.95789575576782</v>
+        <v>6.95789527893066</v>
       </c>
       <c r="H752" t="n">
         <v>1417279</v>
@@ -22206,7 +22206,7 @@
         <v>8.96399974822998</v>
       </c>
       <c r="G753" t="n">
-        <v>6.98126029968262</v>
+        <v>6.98125982284546</v>
       </c>
       <c r="H753" t="n">
         <v>1257283</v>
@@ -22235,7 +22235,7 @@
         <v>9.20199966430664</v>
       </c>
       <c r="G754" t="n">
-        <v>7.16661643981934</v>
+        <v>7.16661691665649</v>
       </c>
       <c r="H754" t="n">
         <v>1386476</v>
@@ -22264,7 +22264,7 @@
         <v>9.26599979400635</v>
       </c>
       <c r="G755" t="n">
-        <v>7.21646022796631</v>
+        <v>7.21646070480347</v>
       </c>
       <c r="H755" t="n">
         <v>1453615</v>
@@ -22293,7 +22293,7 @@
         <v>9.14400005340576</v>
       </c>
       <c r="G756" t="n">
-        <v>7.12144613265991</v>
+        <v>7.12144708633423</v>
       </c>
       <c r="H756" t="n">
         <v>1431356</v>
@@ -22409,7 +22409,7 @@
         <v>8.67800045013428</v>
       </c>
       <c r="G760" t="n">
-        <v>6.75852108001709</v>
+        <v>6.75852012634277</v>
       </c>
       <c r="H760" t="n">
         <v>1544396</v>
@@ -22438,7 +22438,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G761" t="n">
-        <v>6.79123067855835</v>
+        <v>6.79122972488403</v>
       </c>
       <c r="H761" t="n">
         <v>3192777</v>
@@ -22467,7 +22467,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G762" t="n">
-        <v>6.67440843582153</v>
+        <v>6.67440795898438</v>
       </c>
       <c r="H762" t="n">
         <v>1360582</v>
@@ -22525,7 +22525,7 @@
         <v>8.75399971008301</v>
       </c>
       <c r="G764" t="n">
-        <v>6.81770944595337</v>
+        <v>6.81770992279053</v>
       </c>
       <c r="H764" t="n">
         <v>599172</v>
@@ -22554,7 +22554,7 @@
         <v>8.64599990844727</v>
       </c>
       <c r="G765" t="n">
-        <v>6.73359727859497</v>
+        <v>6.73359823226929</v>
       </c>
       <c r="H765" t="n">
         <v>673720</v>
@@ -22583,7 +22583,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>6.97035646438599</v>
+        <v>6.97035598754883</v>
       </c>
       <c r="H766" t="n">
         <v>1340515</v>
@@ -22641,7 +22641,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G768" t="n">
-        <v>7.30368804931641</v>
+        <v>7.30368852615356</v>
       </c>
       <c r="H768" t="n">
         <v>2435460</v>
@@ -22699,7 +22699,7 @@
         <v>9.35799980163574</v>
       </c>
       <c r="G770" t="n">
-        <v>7.28811025619507</v>
+        <v>7.28811168670654</v>
       </c>
       <c r="H770" t="n">
         <v>1569621</v>
@@ -22728,7 +22728,7 @@
         <v>9.34200000762939</v>
       </c>
       <c r="G771" t="n">
-        <v>7.27565145492554</v>
+        <v>7.27565050125122</v>
       </c>
       <c r="H771" t="n">
         <v>745472</v>
@@ -22757,7 +22757,7 @@
         <v>9.32400035858154</v>
       </c>
       <c r="G772" t="n">
-        <v>7.26163101196289</v>
+        <v>7.26163196563721</v>
       </c>
       <c r="H772" t="n">
         <v>1127917</v>
@@ -22786,7 +22786,7 @@
         <v>9.45199966430664</v>
       </c>
       <c r="G773" t="n">
-        <v>7.36131954193115</v>
+        <v>7.36131858825684</v>
       </c>
       <c r="H773" t="n">
         <v>1035601</v>
@@ -22815,7 +22815,7 @@
         <v>9.98400020599365</v>
       </c>
       <c r="G774" t="n">
-        <v>7.77564764022827</v>
+        <v>7.7756462097168</v>
       </c>
       <c r="H774" t="n">
         <v>2817294</v>
@@ -22844,7 +22844,7 @@
         <v>9.81400012969971</v>
       </c>
       <c r="G775" t="n">
-        <v>7.64324951171875</v>
+        <v>7.64324855804443</v>
       </c>
       <c r="H775" t="n">
         <v>1788822</v>
@@ -22902,7 +22902,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G777" t="n">
-        <v>7.67128658294678</v>
+        <v>7.67128705978394</v>
       </c>
       <c r="H777" t="n">
         <v>636119</v>
@@ -22931,7 +22931,7 @@
         <v>9.75</v>
       </c>
       <c r="G778" t="n">
-        <v>7.59340524673462</v>
+        <v>7.59340476989746</v>
       </c>
       <c r="H778" t="n">
         <v>2227314</v>
@@ -22960,7 +22960,7 @@
         <v>9.77600002288818</v>
       </c>
       <c r="G779" t="n">
-        <v>7.61365365982056</v>
+        <v>7.61365413665771</v>
       </c>
       <c r="H779" t="n">
         <v>1141108</v>
@@ -22989,7 +22989,7 @@
         <v>9.80399990081787</v>
       </c>
       <c r="G780" t="n">
-        <v>7.63546085357666</v>
+        <v>7.63546133041382</v>
       </c>
       <c r="H780" t="n">
         <v>1718367</v>
@@ -23018,7 +23018,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G781" t="n">
-        <v>7.67128658294678</v>
+        <v>7.67128705978394</v>
       </c>
       <c r="H781" t="n">
         <v>1045527</v>
@@ -23047,7 +23047,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>7.49994897842407</v>
+        <v>7.49994707107544</v>
       </c>
       <c r="H782" t="n">
         <v>2133329</v>
@@ -23105,7 +23105,7 @@
         <v>9.71599960327148</v>
       </c>
       <c r="G784" t="n">
-        <v>7.56692552566528</v>
+        <v>7.56692600250244</v>
       </c>
       <c r="H784" t="n">
         <v>1186119</v>
@@ -23134,7 +23134,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G785" t="n">
-        <v>7.38935661315918</v>
+        <v>7.3893575668335</v>
       </c>
       <c r="H785" t="n">
         <v>1747399</v>
@@ -23163,7 +23163,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G786" t="n">
-        <v>7.29122734069824</v>
+        <v>7.2912278175354</v>
       </c>
       <c r="H786" t="n">
         <v>1771629</v>
@@ -23192,7 +23192,7 @@
         <v>9.68400001525879</v>
       </c>
       <c r="G787" t="n">
-        <v>7.54200458526611</v>
+        <v>7.5420036315918</v>
       </c>
       <c r="H787" t="n">
         <v>2237986</v>
@@ -23221,7 +23221,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>7.63234615325928</v>
+        <v>7.63234519958496</v>
       </c>
       <c r="H788" t="n">
         <v>1925351</v>
@@ -23250,7 +23250,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G789" t="n">
-        <v>7.72112846374512</v>
+        <v>7.72112989425659</v>
       </c>
       <c r="H789" t="n">
         <v>2853647</v>
@@ -23279,7 +23279,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G790" t="n">
-        <v>7.51864004135132</v>
+        <v>7.518639087677</v>
       </c>
       <c r="H790" t="n">
         <v>1606565</v>
@@ -23308,7 +23308,7 @@
         <v>9.67199993133545</v>
       </c>
       <c r="G791" t="n">
-        <v>7.53265810012817</v>
+        <v>7.53265857696533</v>
       </c>
       <c r="H791" t="n">
         <v>1450610</v>
@@ -23337,7 +23337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>7.63234615325928</v>
+        <v>7.63234519958496</v>
       </c>
       <c r="H792" t="n">
         <v>1134194</v>
@@ -23366,7 +23366,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G793" t="n">
-        <v>7.70711183547974</v>
+        <v>7.70711040496826</v>
       </c>
       <c r="H793" t="n">
         <v>1362044</v>
@@ -23395,7 +23395,7 @@
         <v>10.3850002288818</v>
       </c>
       <c r="G794" t="n">
-        <v>8.08794975280762</v>
+        <v>8.08795070648193</v>
       </c>
       <c r="H794" t="n">
         <v>2774829</v>
@@ -23424,7 +23424,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G795" t="n">
-        <v>7.93218851089478</v>
+        <v>7.93218898773193</v>
       </c>
       <c r="H795" t="n">
         <v>1716361</v>
@@ -23453,7 +23453,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G796" t="n">
-        <v>8.13857173919678</v>
+        <v>8.13857078552246</v>
       </c>
       <c r="H796" t="n">
         <v>2076813</v>
@@ -23482,7 +23482,7 @@
         <v>10.6049995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>8.2592887878418</v>
+        <v>8.25928783416748</v>
       </c>
       <c r="H797" t="n">
         <v>1945920</v>
@@ -23511,7 +23511,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G798" t="n">
-        <v>8.07626724243164</v>
+        <v>8.07626914978027</v>
       </c>
       <c r="H798" t="n">
         <v>1758371</v>
@@ -23540,7 +23540,7 @@
         <v>10.2250003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>7.96334028244019</v>
+        <v>7.96333885192871</v>
       </c>
       <c r="H799" t="n">
         <v>1346337</v>
@@ -23569,7 +23569,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G800" t="n">
-        <v>7.78032064437866</v>
+        <v>7.78031969070435</v>
       </c>
       <c r="H800" t="n">
         <v>1528819</v>
@@ -23627,7 +23627,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G802" t="n">
-        <v>7.97112798690796</v>
+        <v>7.9711275100708</v>
       </c>
       <c r="H802" t="n">
         <v>895345</v>
@@ -23714,7 +23714,7 @@
         <v>10.9250001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>8.50850772857666</v>
+        <v>8.50850677490234</v>
       </c>
       <c r="H805" t="n">
         <v>3610798</v>
@@ -23772,7 +23772,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G807" t="n">
-        <v>8.74604606628418</v>
+        <v>8.74604415893555</v>
       </c>
       <c r="H807" t="n">
         <v>2305395</v>
@@ -23801,7 +23801,7 @@
         <v>11.3249998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>8.82003307342529</v>
+        <v>8.82003211975098</v>
       </c>
       <c r="H808" t="n">
         <v>2716995</v>
@@ -23830,7 +23830,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G809" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84729099273682</v>
       </c>
       <c r="H809" t="n">
         <v>1817140</v>
@@ -23859,7 +23859,7 @@
         <v>11.1549997329712</v>
       </c>
       <c r="G810" t="n">
-        <v>8.68763446807861</v>
+        <v>8.68763542175293</v>
       </c>
       <c r="H810" t="n">
         <v>2692692</v>
@@ -23888,7 +23888,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G811" t="n">
-        <v>8.73825740814209</v>
+        <v>8.73825836181641</v>
       </c>
       <c r="H811" t="n">
         <v>1562978</v>
@@ -23917,7 +23917,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G812" t="n">
-        <v>8.94074726104736</v>
+        <v>8.94074630737305</v>
       </c>
       <c r="H812" t="n">
         <v>1506561</v>
@@ -23946,7 +23946,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G813" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84729099273682</v>
       </c>
       <c r="H813" t="n">
         <v>1579810</v>
@@ -24062,7 +24062,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>9.03420639038086</v>
+        <v>9.03420543670654</v>
       </c>
       <c r="H817" t="n">
         <v>1302193</v>
@@ -24091,7 +24091,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>8.97579383850098</v>
+        <v>8.97579479217529</v>
       </c>
       <c r="H818" t="n">
         <v>1515731</v>
@@ -24120,7 +24120,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G819" t="n">
-        <v>8.9796895980835</v>
+        <v>8.97968769073486</v>
       </c>
       <c r="H819" t="n">
         <v>1509775</v>
@@ -24149,7 +24149,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>9.03420639038086</v>
+        <v>9.03420543670654</v>
       </c>
       <c r="H820" t="n">
         <v>1173045</v>
@@ -24178,7 +24178,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G821" t="n">
-        <v>8.9796895980835</v>
+        <v>8.97968769073486</v>
       </c>
       <c r="H821" t="n">
         <v>1872525</v>
@@ -24236,7 +24236,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>8.88623142242432</v>
+        <v>8.88623046875</v>
       </c>
       <c r="H823" t="n">
         <v>928821</v>
@@ -24294,7 +24294,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G825" t="n">
-        <v>9.01862812042236</v>
+        <v>9.01862907409668</v>
       </c>
       <c r="H825" t="n">
         <v>1208089</v>
@@ -24381,7 +24381,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G828" t="n">
-        <v>9.0575704574585</v>
+        <v>9.05756950378418</v>
       </c>
       <c r="H828" t="n">
         <v>1567568</v>
@@ -24410,7 +24410,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G829" t="n">
-        <v>9.26006031036377</v>
+        <v>9.26006126403809</v>
       </c>
       <c r="H829" t="n">
         <v>1825749</v>
@@ -24526,7 +24526,7 @@
         <v>11.6949996948242</v>
       </c>
       <c r="G833" t="n">
-        <v>9.10819149017334</v>
+        <v>9.10819244384766</v>
       </c>
       <c r="H833" t="n">
         <v>2046449</v>
@@ -24729,7 +24729,7 @@
         <v>12.1549997329712</v>
       </c>
       <c r="G840" t="n">
-        <v>9.46644496917725</v>
+        <v>9.46644592285156</v>
       </c>
       <c r="H840" t="n">
         <v>3396186</v>
@@ -24787,7 +24787,7 @@
         <v>11.875</v>
       </c>
       <c r="G842" t="n">
-        <v>9.48481559753418</v>
+        <v>9.4848165512085</v>
       </c>
       <c r="H842" t="n">
         <v>2291062</v>
@@ -24816,7 +24816,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G843" t="n">
-        <v>9.43290138244629</v>
+        <v>9.43290042877197</v>
       </c>
       <c r="H843" t="n">
         <v>1259655</v>
@@ -24845,7 +24845,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G844" t="n">
-        <v>9.61660575866699</v>
+        <v>9.61660480499268</v>
       </c>
       <c r="H844" t="n">
         <v>1827623</v>
@@ -24932,7 +24932,7 @@
         <v>11.4250001907349</v>
       </c>
       <c r="G847" t="n">
-        <v>9.12539100646973</v>
+        <v>9.12539196014404</v>
       </c>
       <c r="H847" t="n">
         <v>3542588</v>
@@ -24961,7 +24961,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G848" t="n">
-        <v>9.05749893188477</v>
+        <v>9.05749988555908</v>
       </c>
       <c r="H848" t="n">
         <v>3489736</v>
@@ -24990,7 +24990,7 @@
         <v>11.0749998092651</v>
       </c>
       <c r="G849" t="n">
-        <v>8.84583854675293</v>
+        <v>8.84583950042725</v>
       </c>
       <c r="H849" t="n">
         <v>2243947</v>
@@ -25019,7 +25019,7 @@
         <v>10.25</v>
       </c>
       <c r="G850" t="n">
-        <v>8.18689346313477</v>
+        <v>8.18689441680908</v>
       </c>
       <c r="H850" t="n">
         <v>9379536</v>
@@ -25106,7 +25106,7 @@
         <v>9.85200023651123</v>
       </c>
       <c r="G853" t="n">
-        <v>7.8690037727356</v>
+        <v>7.86900234222412</v>
       </c>
       <c r="H853" t="n">
         <v>8322960</v>
@@ -25164,7 +25164,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G855" t="n">
-        <v>7.82427310943604</v>
+        <v>7.82427406311035</v>
       </c>
       <c r="H855" t="n">
         <v>4768720</v>
@@ -25280,7 +25280,7 @@
         <v>9.78800010681152</v>
       </c>
       <c r="G859" t="n">
-        <v>7.81788492202759</v>
+        <v>7.8178858757019</v>
       </c>
       <c r="H859" t="n">
         <v>2935413</v>
@@ -25309,7 +25309,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G860" t="n">
-        <v>7.90734148025513</v>
+        <v>7.90733957290649</v>
       </c>
       <c r="H860" t="n">
         <v>3084500</v>
@@ -25338,7 +25338,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G861" t="n">
-        <v>7.79552030563354</v>
+        <v>7.7955207824707</v>
       </c>
       <c r="H861" t="n">
         <v>3096684</v>
@@ -25367,7 +25367,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G862" t="n">
-        <v>7.71085596084595</v>
+        <v>7.71085548400879</v>
       </c>
       <c r="H862" t="n">
         <v>4209402</v>
@@ -25396,7 +25396,7 @@
         <v>9.75</v>
       </c>
       <c r="G863" t="n">
-        <v>7.78753328323364</v>
+        <v>7.7875337600708</v>
       </c>
       <c r="H863" t="n">
         <v>2936234</v>
@@ -25425,7 +25425,7 @@
         <v>9.69200038909912</v>
       </c>
       <c r="G864" t="n">
-        <v>7.74120759963989</v>
+        <v>7.74120855331421</v>
       </c>
       <c r="H864" t="n">
         <v>2306537</v>
@@ -25454,7 +25454,7 @@
         <v>9.5</v>
       </c>
       <c r="G865" t="n">
-        <v>7.58785343170166</v>
+        <v>7.58785390853882</v>
       </c>
       <c r="H865" t="n">
         <v>41491512</v>
@@ -25483,7 +25483,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G866" t="n">
-        <v>7.3897705078125</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H866" t="n">
         <v>3383104</v>
@@ -25512,7 +25512,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G867" t="n">
-        <v>7.3897705078125</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H867" t="n">
         <v>2186192</v>
@@ -25541,7 +25541,7 @@
         <v>9.27600002288818</v>
       </c>
       <c r="G868" t="n">
-        <v>7.40893888473511</v>
+        <v>7.40893936157227</v>
       </c>
       <c r="H868" t="n">
         <v>3447972</v>
@@ -25599,7 +25599,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G870" t="n">
-        <v>7.48881196975708</v>
+        <v>7.48881149291992</v>
       </c>
       <c r="H870" t="n">
         <v>3609501</v>
@@ -25628,7 +25628,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G871" t="n">
-        <v>7.48401880264282</v>
+        <v>7.48401927947998</v>
       </c>
       <c r="H871" t="n">
         <v>3039397</v>
@@ -25657,7 +25657,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G872" t="n">
-        <v>7.42331600189209</v>
+        <v>7.42331552505493</v>
       </c>
       <c r="H872" t="n">
         <v>2716855</v>
@@ -25686,7 +25686,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>7.42810821533203</v>
+        <v>7.42810916900635</v>
       </c>
       <c r="H873" t="n">
         <v>2226876</v>
@@ -25715,7 +25715,7 @@
         <v>9.28400039672852</v>
       </c>
       <c r="G874" t="n">
-        <v>7.41532945632935</v>
+        <v>7.41532897949219</v>
       </c>
       <c r="H874" t="n">
         <v>1970639</v>
@@ -25744,7 +25744,7 @@
         <v>9.32400035858154</v>
       </c>
       <c r="G875" t="n">
-        <v>7.44727802276611</v>
+        <v>7.44727754592896</v>
       </c>
       <c r="H875" t="n">
         <v>2366989</v>
@@ -25773,7 +25773,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G876" t="n">
-        <v>7.30829954147339</v>
+        <v>7.30830001831055</v>
       </c>
       <c r="H876" t="n">
         <v>2609119</v>
@@ -25889,7 +25889,7 @@
         <v>9.31799983978271</v>
       </c>
       <c r="G880" t="n">
-        <v>7.44248628616333</v>
+        <v>7.44248533248901</v>
       </c>
       <c r="H880" t="n">
         <v>3120201</v>
@@ -25918,7 +25918,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G881" t="n">
-        <v>7.53993034362793</v>
+        <v>7.53992938995361</v>
       </c>
       <c r="H881" t="n">
         <v>2730493</v>
@@ -25947,7 +25947,7 @@
         <v>9.54800033569336</v>
       </c>
       <c r="G882" t="n">
-        <v>7.62619256973267</v>
+        <v>7.62619209289551</v>
       </c>
       <c r="H882" t="n">
         <v>4544189</v>
@@ -25976,7 +25976,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G883" t="n">
-        <v>7.82267618179321</v>
+        <v>7.82267713546753</v>
       </c>
       <c r="H883" t="n">
         <v>9587699</v>
@@ -26034,7 +26034,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G885" t="n">
-        <v>7.784339427948</v>
+        <v>7.78433847427368</v>
       </c>
       <c r="H885" t="n">
         <v>2051706</v>
@@ -26092,7 +26092,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G887" t="n">
-        <v>7.66772603988647</v>
+        <v>7.66772508621216</v>
       </c>
       <c r="H887" t="n">
         <v>1395178</v>
@@ -26121,7 +26121,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G888" t="n">
-        <v>7.83545780181885</v>
+        <v>7.83545589447021</v>
       </c>
       <c r="H888" t="n">
         <v>2776001</v>
@@ -26150,7 +26150,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G889" t="n">
-        <v>7.87539291381836</v>
+        <v>7.8753924369812</v>
       </c>
       <c r="H889" t="n">
         <v>1816841</v>
@@ -26208,7 +26208,7 @@
         <v>10.375</v>
       </c>
       <c r="G891" t="n">
-        <v>8.28673458099365</v>
+        <v>8.28673362731934</v>
       </c>
       <c r="H891" t="n">
         <v>3795422</v>
@@ -26237,7 +26237,7 @@
         <v>10.7049999237061</v>
       </c>
       <c r="G892" t="n">
-        <v>8.55031108856201</v>
+        <v>8.55031204223633</v>
       </c>
       <c r="H892" t="n">
         <v>4017984</v>
@@ -26266,7 +26266,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G893" t="n">
-        <v>8.53833198547363</v>
+        <v>8.538330078125</v>
       </c>
       <c r="H893" t="n">
         <v>2655809</v>
@@ -26411,7 +26411,7 @@
         <v>10.1949996948242</v>
       </c>
       <c r="G898" t="n">
-        <v>8.14296436309814</v>
+        <v>8.14296340942383</v>
       </c>
       <c r="H898" t="n">
         <v>4494724</v>
@@ -26440,7 +26440,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G899" t="n">
-        <v>7.99919509887695</v>
+        <v>7.99919414520264</v>
       </c>
       <c r="H899" t="n">
         <v>4054784</v>
@@ -26498,7 +26498,7 @@
         <v>9.99600028991699</v>
       </c>
       <c r="G901" t="n">
-        <v>7.98401927947998</v>
+        <v>7.98401784896851</v>
       </c>
       <c r="H901" t="n">
         <v>5063833</v>
@@ -26527,7 +26527,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G902" t="n">
-        <v>8.01517009735107</v>
+        <v>8.01516914367676</v>
       </c>
       <c r="H902" t="n">
         <v>4327579</v>
@@ -26585,7 +26585,7 @@
         <v>9.72599983215332</v>
       </c>
       <c r="G904" t="n">
-        <v>7.76836252212524</v>
+        <v>7.76836442947388</v>
       </c>
       <c r="H904" t="n">
         <v>2332272</v>
@@ -26643,7 +26643,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G906" t="n">
-        <v>7.99919509887695</v>
+        <v>7.99919414520264</v>
       </c>
       <c r="H906" t="n">
         <v>3450602</v>
@@ -26672,7 +26672,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G907" t="n">
-        <v>7.78114318847656</v>
+        <v>7.7811427116394</v>
       </c>
       <c r="H907" t="n">
         <v>4500422</v>
@@ -26701,7 +26701,7 @@
         <v>9.48200035095215</v>
       </c>
       <c r="G908" t="n">
-        <v>7.57347583770752</v>
+        <v>7.57347679138184</v>
       </c>
       <c r="H908" t="n">
         <v>3994996</v>
@@ -26730,7 +26730,7 @@
         <v>9.32400035858154</v>
       </c>
       <c r="G909" t="n">
-        <v>7.44727802276611</v>
+        <v>7.44727754592896</v>
       </c>
       <c r="H909" t="n">
         <v>2346327</v>
@@ -26759,7 +26759,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G910" t="n">
-        <v>7.09264612197876</v>
+        <v>7.0926456451416</v>
       </c>
       <c r="H910" t="n">
         <v>6988119</v>
@@ -26788,7 +26788,7 @@
         <v>8.99199962615967</v>
       </c>
       <c r="G911" t="n">
-        <v>7.18210172653198</v>
+        <v>7.1821026802063</v>
       </c>
       <c r="H911" t="n">
         <v>5318727</v>
@@ -26817,7 +26817,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>7.29232549667358</v>
+        <v>7.29232597351074</v>
       </c>
       <c r="H912" t="n">
         <v>3452685</v>
@@ -26846,7 +26846,7 @@
         <v>8.91199970245361</v>
       </c>
       <c r="G913" t="n">
-        <v>7.11820507049561</v>
+        <v>7.11820363998413</v>
       </c>
       <c r="H913" t="n">
         <v>3482642</v>
@@ -26875,7 +26875,7 @@
         <v>8.70600032806396</v>
       </c>
       <c r="G914" t="n">
-        <v>6.95366811752319</v>
+        <v>6.95366764068604</v>
       </c>
       <c r="H914" t="n">
         <v>3818373</v>
@@ -26933,7 +26933,7 @@
         <v>8.90799999237061</v>
       </c>
       <c r="G916" t="n">
-        <v>7.11500930786133</v>
+        <v>7.11501026153564</v>
       </c>
       <c r="H916" t="n">
         <v>3000799</v>
@@ -26991,7 +26991,7 @@
         <v>8.94400024414062</v>
       </c>
       <c r="G918" t="n">
-        <v>7.14376544952393</v>
+        <v>7.14376401901245</v>
       </c>
       <c r="H918" t="n">
         <v>3640894</v>
@@ -27049,7 +27049,7 @@
         <v>8.95199966430664</v>
       </c>
       <c r="G920" t="n">
-        <v>7.15015363693237</v>
+        <v>7.15015411376953</v>
       </c>
       <c r="H920" t="n">
         <v>4222607</v>
@@ -27107,7 +27107,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G922" t="n">
-        <v>6.91373205184937</v>
+        <v>6.91373252868652</v>
       </c>
       <c r="H922" t="n">
         <v>8269820</v>
@@ -27165,7 +27165,7 @@
         <v>8.7519998550415</v>
       </c>
       <c r="G924" t="n">
-        <v>6.99040842056274</v>
+        <v>6.9904088973999</v>
       </c>
       <c r="H924" t="n">
         <v>1609495</v>
@@ -27194,7 +27194,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G925" t="n">
-        <v>7.28433799743652</v>
+        <v>7.28433895111084</v>
       </c>
       <c r="H925" t="n">
         <v>3106887</v>
@@ -27223,7 +27223,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G926" t="n">
-        <v>7.3897705078125</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H926" t="n">
         <v>3676274</v>
@@ -27252,7 +27252,7 @@
         <v>8.97599983215332</v>
       </c>
       <c r="G927" t="n">
-        <v>7.16932249069214</v>
+        <v>7.16932344436646</v>
       </c>
       <c r="H927" t="n">
         <v>2682189</v>
@@ -27281,7 +27281,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>7.30829954147339</v>
+        <v>7.30830001831055</v>
       </c>
       <c r="H928" t="n">
         <v>1790407</v>
@@ -27310,7 +27310,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G929" t="n">
-        <v>7.47763013839722</v>
+        <v>7.47763061523438</v>
       </c>
       <c r="H929" t="n">
         <v>2993658</v>
@@ -27339,7 +27339,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G930" t="n">
-        <v>7.4520697593689</v>
+        <v>7.45207023620605</v>
       </c>
       <c r="H930" t="n">
         <v>3565618</v>
@@ -27397,7 +27397,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G932" t="n">
-        <v>7.49040937423706</v>
+        <v>7.4904088973999</v>
       </c>
       <c r="H932" t="n">
         <v>2552791</v>
@@ -27455,7 +27455,7 @@
         <v>9.30799961090088</v>
       </c>
       <c r="G934" t="n">
-        <v>7.43449831008911</v>
+        <v>7.43449878692627</v>
       </c>
       <c r="H934" t="n">
         <v>2299813</v>
@@ -27484,7 +27484,7 @@
         <v>9.57600021362305</v>
       </c>
       <c r="G935" t="n">
-        <v>7.64855480194092</v>
+        <v>7.64855527877808</v>
       </c>
       <c r="H935" t="n">
         <v>2783823</v>
@@ -27542,7 +27542,7 @@
         <v>9.75</v>
       </c>
       <c r="G937" t="n">
-        <v>7.78753328323364</v>
+        <v>7.7875337600708</v>
       </c>
       <c r="H937" t="n">
         <v>3105529</v>
@@ -27571,7 +27571,7 @@
         <v>9.87399959564209</v>
       </c>
       <c r="G938" t="n">
-        <v>7.88657569885254</v>
+        <v>7.88657331466675</v>
       </c>
       <c r="H938" t="n">
         <v>2632372</v>
@@ -27600,7 +27600,7 @@
         <v>9.51399993896484</v>
       </c>
       <c r="G939" t="n">
-        <v>7.59903526306152</v>
+        <v>7.59903430938721</v>
       </c>
       <c r="H939" t="n">
         <v>5535766</v>
@@ -27629,7 +27629,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G940" t="n">
-        <v>7.42810821533203</v>
+        <v>7.42810916900635</v>
       </c>
       <c r="H940" t="n">
         <v>5627338</v>
@@ -27658,7 +27658,7 @@
         <v>9.42399978637695</v>
       </c>
       <c r="G941" t="n">
-        <v>7.52714967727661</v>
+        <v>7.52715015411377</v>
       </c>
       <c r="H941" t="n">
         <v>4089597</v>
@@ -27716,7 +27716,7 @@
         <v>9.76399993896484</v>
       </c>
       <c r="G943" t="n">
-        <v>7.79871416091919</v>
+        <v>7.79871463775635</v>
       </c>
       <c r="H943" t="n">
         <v>2951390</v>
@@ -27745,7 +27745,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G944" t="n">
-        <v>7.4760308265686</v>
+        <v>7.47603130340576</v>
       </c>
       <c r="H944" t="n">
         <v>3957734</v>
@@ -27803,7 +27803,7 @@
         <v>9.68400001525879</v>
       </c>
       <c r="G946" t="n">
-        <v>7.73481702804565</v>
+        <v>7.7348165512085</v>
       </c>
       <c r="H946" t="n">
         <v>3294725</v>
@@ -27890,7 +27890,7 @@
         <v>9.46399974822998</v>
       </c>
       <c r="G949" t="n">
-        <v>7.55909776687622</v>
+        <v>7.55909872055054</v>
       </c>
       <c r="H949" t="n">
         <v>2542049</v>
@@ -27919,7 +27919,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G950" t="n">
-        <v>7.4760308265686</v>
+        <v>7.47603130340576</v>
       </c>
       <c r="H950" t="n">
         <v>2511171</v>
@@ -27977,7 +27977,7 @@
         <v>9.61800003051758</v>
       </c>
       <c r="G952" t="n">
-        <v>7.68210220336914</v>
+        <v>7.68210124969482</v>
       </c>
       <c r="H952" t="n">
         <v>2277483</v>
@@ -28035,7 +28035,7 @@
         <v>9.60400009155273</v>
       </c>
       <c r="G954" t="n">
-        <v>7.67091941833496</v>
+        <v>7.67091989517212</v>
       </c>
       <c r="H954" t="n">
         <v>3812669</v>
@@ -28093,7 +28093,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G956" t="n">
-        <v>7.61181449890137</v>
+        <v>7.61181497573853</v>
       </c>
       <c r="H956" t="n">
         <v>3325856</v>
@@ -28122,7 +28122,7 @@
         <v>9.64599990844727</v>
       </c>
       <c r="G957" t="n">
-        <v>7.70446538925171</v>
+        <v>7.70446634292603</v>
       </c>
       <c r="H957" t="n">
         <v>2491109</v>
@@ -28151,7 +28151,7 @@
         <v>9.67800045013428</v>
       </c>
       <c r="G958" t="n">
-        <v>7.73002624511719</v>
+        <v>7.73002529144287</v>
       </c>
       <c r="H958" t="n">
         <v>1695957</v>
@@ -28180,7 +28180,7 @@
         <v>9.22799968719482</v>
       </c>
       <c r="G959" t="n">
-        <v>7.37060070037842</v>
+        <v>7.37060022354126</v>
       </c>
       <c r="H959" t="n">
         <v>5305999</v>
@@ -28238,7 +28238,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G961" t="n">
-        <v>7.60382843017578</v>
+        <v>7.60382747650146</v>
       </c>
       <c r="H961" t="n">
         <v>2228905</v>
@@ -28267,7 +28267,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G962" t="n">
-        <v>7.82587289810181</v>
+        <v>7.82587194442749</v>
       </c>
       <c r="H962" t="n">
         <v>3624613</v>
@@ -28325,7 +28325,7 @@
         <v>9.85599994659424</v>
       </c>
       <c r="G964" t="n">
-        <v>7.8721981048584</v>
+        <v>7.87219715118408</v>
       </c>
       <c r="H964" t="n">
         <v>3827704</v>
@@ -28441,7 +28441,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G968" t="n">
-        <v>8.24280261993408</v>
+        <v>8.24280452728271</v>
       </c>
       <c r="H968" t="n">
         <v>3726083</v>
@@ -28499,7 +28499,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>8.14695835113525</v>
+        <v>8.14695739746094</v>
       </c>
       <c r="H970" t="n">
         <v>2753561</v>
@@ -28528,7 +28528,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G971" t="n">
-        <v>8.13497829437256</v>
+        <v>8.13497638702393</v>
       </c>
       <c r="H971" t="n">
         <v>2606880</v>
@@ -28615,7 +28615,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>8.30670166015625</v>
+        <v>8.30670261383057</v>
       </c>
       <c r="H974" t="n">
         <v>2791666</v>
@@ -28673,7 +28673,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>8.06708526611328</v>
+        <v>8.0670862197876</v>
       </c>
       <c r="H976" t="n">
         <v>3863982</v>
@@ -28702,7 +28702,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G977" t="n">
-        <v>8.29072761535645</v>
+        <v>8.29072666168213</v>
       </c>
       <c r="H977" t="n">
         <v>2778678</v>
@@ -28731,7 +28731,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>8.52635097503662</v>
+        <v>8.5263500213623</v>
       </c>
       <c r="H978" t="n">
         <v>4481429</v>
@@ -28760,7 +28760,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>8.62619209289551</v>
+        <v>8.62619018554688</v>
       </c>
       <c r="H979" t="n">
         <v>4920323</v>
@@ -28789,7 +28789,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G980" t="n">
-        <v>8.66612720489502</v>
+        <v>8.66612815856934</v>
       </c>
       <c r="H980" t="n">
         <v>5778319</v>
@@ -28818,7 +28818,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>8.82587146759033</v>
+        <v>8.82587051391602</v>
       </c>
       <c r="H981" t="n">
         <v>4117319</v>
@@ -28847,7 +28847,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G982" t="n">
-        <v>8.79392242431641</v>
+        <v>8.79392147064209</v>
       </c>
       <c r="H982" t="n">
         <v>3106214</v>
@@ -28905,7 +28905,7 @@
         <v>11.4350004196167</v>
       </c>
       <c r="G984" t="n">
-        <v>9.13337993621826</v>
+        <v>9.13338088989258</v>
       </c>
       <c r="H984" t="n">
         <v>4526531</v>
@@ -28934,7 +28934,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G985" t="n">
-        <v>9.18929004669189</v>
+        <v>9.18928909301758</v>
       </c>
       <c r="H985" t="n">
         <v>4781545</v>
@@ -28963,7 +28963,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G986" t="n">
-        <v>9.17331409454346</v>
+        <v>9.17331504821777</v>
       </c>
       <c r="H986" t="n">
         <v>2658902</v>
@@ -28992,7 +28992,7 @@
         <v>11.4650001525879</v>
       </c>
       <c r="G987" t="n">
-        <v>9.15734100341797</v>
+        <v>9.15734195709229</v>
       </c>
       <c r="H987" t="n">
         <v>4652682</v>
@@ -29021,7 +29021,7 @@
         <v>11.3649997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>9.077467918396</v>
+        <v>9.07746696472168</v>
       </c>
       <c r="H988" t="n">
         <v>3944843</v>
@@ -29050,7 +29050,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G989" t="n">
-        <v>8.96963977813721</v>
+        <v>8.96964073181152</v>
       </c>
       <c r="H989" t="n">
         <v>3925640</v>
@@ -29137,7 +29137,7 @@
         <v>11.4750003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>9.16532897949219</v>
+        <v>9.16532802581787</v>
       </c>
       <c r="H992" t="n">
         <v>5004718</v>
@@ -29195,7 +29195,7 @@
         <v>11.6949996948242</v>
       </c>
       <c r="G994" t="n">
-        <v>9.34104633331299</v>
+        <v>9.34104537963867</v>
       </c>
       <c r="H994" t="n">
         <v>3609909</v>
@@ -29224,7 +29224,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G995" t="n">
-        <v>9.21724510192871</v>
+        <v>9.21724414825439</v>
       </c>
       <c r="H995" t="n">
         <v>1999084</v>
@@ -29253,7 +29253,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G996" t="n">
-        <v>9.18929004669189</v>
+        <v>9.18928909301758</v>
       </c>
       <c r="H996" t="n">
         <v>2523570</v>
@@ -29311,7 +29311,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G998" t="n">
-        <v>8.88976860046387</v>
+        <v>8.88976764678955</v>
       </c>
       <c r="H998" t="n">
         <v>3788755</v>
@@ -29340,7 +29340,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>8.9456787109375</v>
+        <v>8.94568061828613</v>
       </c>
       <c r="H999" t="n">
         <v>3174901</v>
@@ -29398,7 +29398,7 @@
         <v>11.2749996185303</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.00558376312256</v>
+        <v>9.00558280944824</v>
       </c>
       <c r="H1001" t="n">
         <v>2053937</v>
@@ -29427,7 +29427,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.04152584075928</v>
+        <v>9.04152488708496</v>
       </c>
       <c r="H1002" t="n">
         <v>1640835</v>
@@ -29456,7 +29456,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1003" t="n">
-        <v>8.85782051086426</v>
+        <v>8.85781955718994</v>
       </c>
       <c r="H1003" t="n">
         <v>2487483</v>
@@ -29514,7 +29514,7 @@
         <v>11.1049995422363</v>
       </c>
       <c r="G1005" t="n">
-        <v>8.86979961395264</v>
+        <v>8.86980056762695</v>
       </c>
       <c r="H1005" t="n">
         <v>1275169</v>
@@ -29572,7 +29572,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.7779483795166</v>
+        <v>8.77794647216797</v>
       </c>
       <c r="H1007" t="n">
         <v>3734976</v>
@@ -29601,7 +29601,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>8.9456787109375</v>
+        <v>8.94568061828613</v>
       </c>
       <c r="H1008" t="n">
         <v>1694693</v>
@@ -29717,7 +29717,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G1012" t="n">
-        <v>8.68210220336914</v>
+        <v>8.68210124969482</v>
       </c>
       <c r="H1012" t="n">
         <v>7489165</v>
@@ -29746,7 +29746,7 @@
         <v>10.914999961853</v>
       </c>
       <c r="G1013" t="n">
-        <v>8.71804332733154</v>
+        <v>8.71804428100586</v>
       </c>
       <c r="H1013" t="n">
         <v>1113622</v>
@@ -29775,7 +29775,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1014" t="n">
-        <v>8.60222911834717</v>
+        <v>8.60222816467285</v>
       </c>
       <c r="H1014" t="n">
         <v>1398596</v>
@@ -29804,7 +29804,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G1015" t="n">
-        <v>8.53833198547363</v>
+        <v>8.538330078125</v>
       </c>
       <c r="H1015" t="n">
         <v>1093478</v>
@@ -29833,7 +29833,7 @@
         <v>11.0050001144409</v>
       </c>
       <c r="G1016" t="n">
-        <v>8.78992748260498</v>
+        <v>8.7899284362793</v>
       </c>
       <c r="H1016" t="n">
         <v>2455109</v>
@@ -29862,7 +29862,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1017" t="n">
-        <v>8.55430507659912</v>
+        <v>8.55430603027344</v>
       </c>
       <c r="H1017" t="n">
         <v>2299389</v>
@@ -29891,7 +29891,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.49839687347412</v>
+        <v>8.4983959197998</v>
       </c>
       <c r="H1018" t="n">
         <v>2208761</v>
@@ -29978,7 +29978,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1021" t="n">
-        <v>9.2332181930542</v>
+        <v>9.23321914672852</v>
       </c>
       <c r="H1021" t="n">
         <v>5413395</v>
@@ -30007,7 +30007,7 @@
         <v>11.2049999237061</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.94967460632324</v>
+        <v>8.94967174530029</v>
       </c>
       <c r="H1022" t="n">
         <v>2994173</v>
@@ -30065,7 +30065,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.91372871398926</v>
+        <v>8.91373062133789</v>
       </c>
       <c r="H1024" t="n">
         <v>2042666</v>
@@ -30123,7 +30123,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.96963977813721</v>
+        <v>8.96964073181152</v>
       </c>
       <c r="H1026" t="n">
         <v>2056874</v>
@@ -30152,7 +30152,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.87379360198975</v>
+        <v>8.87379455566406</v>
       </c>
       <c r="H1027" t="n">
         <v>3061847</v>
@@ -30239,7 +30239,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.87379360198975</v>
+        <v>8.87379455566406</v>
       </c>
       <c r="H1030" t="n">
         <v>2515719</v>
@@ -30268,7 +30268,7 @@
         <v>10.9650001525879</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.75797843933105</v>
+        <v>8.75797939300537</v>
       </c>
       <c r="H1031" t="n">
         <v>2744367</v>
@@ -30297,7 +30297,7 @@
         <v>10.9849996566772</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.77395439147949</v>
+        <v>8.77395343780518</v>
       </c>
       <c r="H1032" t="n">
         <v>1962560</v>
@@ -30326,7 +30326,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1033" t="n">
-        <v>8.45047283172607</v>
+        <v>8.45047187805176</v>
       </c>
       <c r="H1033" t="n">
         <v>3787301</v>
@@ -30355,7 +30355,7 @@
         <v>10.9849996566772</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.77395439147949</v>
+        <v>8.77395343780518</v>
       </c>
       <c r="H1034" t="n">
         <v>3705420</v>
@@ -30384,7 +30384,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1035" t="n">
-        <v>8.9297046661377</v>
+        <v>8.92970561981201</v>
       </c>
       <c r="H1035" t="n">
         <v>3264579</v>
@@ -30413,7 +30413,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.7699613571167</v>
+        <v>8.76996040344238</v>
       </c>
       <c r="H1036" t="n">
         <v>3530447</v>
@@ -30442,7 +30442,7 @@
         <v>10.5749998092651</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.44647884368896</v>
+        <v>8.44647693634033</v>
       </c>
       <c r="H1037" t="n">
         <v>3746846</v>
@@ -30471,7 +30471,7 @@
         <v>10.8149995803833</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.63817119598389</v>
+        <v>8.63817024230957</v>
       </c>
       <c r="H1038" t="n">
         <v>1938612</v>
@@ -30500,7 +30500,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.85782051086426</v>
+        <v>8.85781955718994</v>
       </c>
       <c r="H1039" t="n">
         <v>3040168</v>
@@ -30558,7 +30558,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1041" t="n">
-        <v>9.04152584075928</v>
+        <v>9.04152488708496</v>
       </c>
       <c r="H1041" t="n">
         <v>3018932</v>
@@ -30616,7 +30616,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1043" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1043" t="n">
         <v>3510236</v>
@@ -30645,7 +30645,7 @@
         <v>11.0249996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.80590343475342</v>
+        <v>8.8059024810791</v>
       </c>
       <c r="H1044" t="n">
         <v>13058672</v>
@@ -30674,7 +30674,7 @@
         <v>10.9549999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.74999141693115</v>
+        <v>8.74999332427979</v>
       </c>
       <c r="H1045" t="n">
         <v>7473511</v>
@@ -30732,7 +30732,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.72203636169434</v>
+        <v>8.72203731536865</v>
       </c>
       <c r="H1047" t="n">
         <v>2991609</v>
@@ -30761,7 +30761,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.82587146759033</v>
+        <v>8.82587051391602</v>
       </c>
       <c r="H1048" t="n">
         <v>3631770</v>
@@ -30848,7 +30848,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.85782051086426</v>
+        <v>8.85781955718994</v>
       </c>
       <c r="H1051" t="n">
         <v>4474988</v>
@@ -30935,7 +30935,7 @@
         <v>9.79399967193604</v>
       </c>
       <c r="G1054" t="n">
-        <v>7.82267618179321</v>
+        <v>7.82267713546753</v>
       </c>
       <c r="H1054" t="n">
         <v>4733298</v>
@@ -30964,7 +30964,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1055" t="n">
-        <v>7.94727754592896</v>
+        <v>7.94727659225464</v>
       </c>
       <c r="H1055" t="n">
         <v>5340136</v>
@@ -31022,7 +31022,7 @@
         <v>9.49400043487549</v>
       </c>
       <c r="G1057" t="n">
-        <v>7.58305978775024</v>
+        <v>7.58306074142456</v>
       </c>
       <c r="H1057" t="n">
         <v>6625541</v>
@@ -31051,7 +31051,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.29232549667358</v>
+        <v>7.29232597351074</v>
       </c>
       <c r="H1058" t="n">
         <v>5987425</v>
@@ -31080,7 +31080,7 @@
         <v>9.33399963378906</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.45526552200317</v>
+        <v>7.45526456832886</v>
       </c>
       <c r="H1059" t="n">
         <v>6715202</v>
@@ -31109,7 +31109,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.06868362426758</v>
+        <v>7.06868410110474</v>
       </c>
       <c r="H1060" t="n">
         <v>7522341</v>
@@ -31138,7 +31138,7 @@
         <v>8.87199974060059</v>
       </c>
       <c r="G1061" t="n">
-        <v>7.08625555038452</v>
+        <v>7.08625507354736</v>
       </c>
       <c r="H1061" t="n">
         <v>6565588</v>
@@ -31167,7 +31167,7 @@
         <v>8.97399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.16772556304932</v>
+        <v>7.16772508621216</v>
       </c>
       <c r="H1062" t="n">
         <v>6835049</v>
@@ -31196,7 +31196,7 @@
         <v>8.11800003051758</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.48401975631714</v>
+        <v>6.4840202331543</v>
       </c>
       <c r="H1063" t="n">
         <v>9088534</v>
@@ -31254,7 +31254,7 @@
         <v>7.87599992752075</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.29072904586792</v>
+        <v>6.29072952270508</v>
       </c>
       <c r="H1065" t="n">
         <v>8515424</v>
@@ -31312,7 +31312,7 @@
         <v>7.7039999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.15334939956665</v>
+        <v>6.15334892272949</v>
       </c>
       <c r="H1067" t="n">
         <v>8728518</v>
@@ -31399,7 +31399,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.00958013534546</v>
+        <v>6.00957918167114</v>
       </c>
       <c r="H1070" t="n">
         <v>4306496</v>
@@ -31428,7 +31428,7 @@
         <v>7.47800016403198</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.97283792495728</v>
+        <v>5.97283840179443</v>
       </c>
       <c r="H1071" t="n">
         <v>5432734</v>
@@ -31457,7 +31457,7 @@
         <v>7.46400022506714</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.96165609359741</v>
+        <v>5.96165657043457</v>
       </c>
       <c r="H1072" t="n">
         <v>8966093</v>
@@ -31486,7 +31486,7 @@
         <v>7.47800016403198</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.97283792495728</v>
+        <v>5.97283840179443</v>
       </c>
       <c r="H1073" t="n">
         <v>6801824</v>
@@ -31544,7 +31544,7 @@
         <v>8.0959997177124</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.46644735336304</v>
+        <v>6.46644830703735</v>
       </c>
       <c r="H1075" t="n">
         <v>6663653</v>
@@ -31631,7 +31631,7 @@
         <v>8.42199993133545</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.72683095932007</v>
+        <v>6.72683048248291</v>
       </c>
       <c r="H1078" t="n">
         <v>4833258</v>
@@ -31689,7 +31689,7 @@
         <v>8.28400039672852</v>
       </c>
       <c r="G1080" t="n">
-        <v>6.61660814285278</v>
+        <v>6.61660718917847</v>
       </c>
       <c r="H1080" t="n">
         <v>3960886</v>
@@ -31718,7 +31718,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.82906675338745</v>
+        <v>6.82906818389893</v>
       </c>
       <c r="H1081" t="n">
         <v>2997795</v>
@@ -31747,7 +31747,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.14855623245239</v>
+        <v>7.14855527877808</v>
       </c>
       <c r="H1082" t="n">
         <v>4108088</v>
@@ -31776,7 +31776,7 @@
         <v>9.1540002822876</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.31149578094482</v>
+        <v>7.31149435043335</v>
       </c>
       <c r="H1083" t="n">
         <v>3944078</v>
@@ -31834,7 +31834,7 @@
         <v>9.44400024414062</v>
       </c>
       <c r="G1085" t="n">
-        <v>7.54312515258789</v>
+        <v>7.54312419891357</v>
       </c>
       <c r="H1085" t="n">
         <v>2782876</v>
@@ -31863,7 +31863,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.54152679443359</v>
+        <v>7.54152727127075</v>
       </c>
       <c r="H1086" t="n">
         <v>3112691</v>
@@ -31892,7 +31892,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.63577747344971</v>
+        <v>7.63577651977539</v>
       </c>
       <c r="H1087" t="n">
         <v>3037142</v>
@@ -31921,7 +31921,7 @@
         <v>8.83399963378906</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.05590438842773</v>
+        <v>7.05590486526489</v>
       </c>
       <c r="H1088" t="n">
         <v>3989061</v>
@@ -31979,7 +31979,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.94887542724609</v>
+        <v>6.94887590408325</v>
       </c>
       <c r="H1090" t="n">
         <v>2959801</v>
@@ -32037,7 +32037,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.51916313171387</v>
+        <v>6.51916360855103</v>
       </c>
       <c r="H1092" t="n">
         <v>3812138</v>
@@ -32095,7 +32095,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.37858724594116</v>
+        <v>7.37858819961548</v>
       </c>
       <c r="H1094" t="n">
         <v>3739189</v>
@@ -32153,7 +32153,7 @@
         <v>9.50399971008301</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.59104681015015</v>
+        <v>7.59104776382446</v>
       </c>
       <c r="H1096" t="n">
         <v>2859434</v>
@@ -32182,7 +32182,7 @@
         <v>9.73400020599365</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.77475357055664</v>
+        <v>7.77475452423096</v>
       </c>
       <c r="H1097" t="n">
         <v>4503742</v>
@@ -32269,7 +32269,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.75398731231689</v>
+        <v>7.75398635864258</v>
       </c>
       <c r="H1100" t="n">
         <v>3245092</v>
@@ -32298,7 +32298,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.87539291381836</v>
+        <v>7.8753924369812</v>
       </c>
       <c r="H1101" t="n">
         <v>3644756</v>
@@ -32327,7 +32327,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.48401880264282</v>
+        <v>7.48401927947998</v>
       </c>
       <c r="H1102" t="n">
         <v>2760070</v>
@@ -32385,7 +32385,7 @@
         <v>9.67800045013428</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.73002624511719</v>
+        <v>7.73002529144287</v>
       </c>
       <c r="H1104" t="n">
         <v>2049636</v>
@@ -32443,7 +32443,7 @@
         <v>10.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>8.38657379150391</v>
+        <v>8.38657283782959</v>
       </c>
       <c r="H1106" t="n">
         <v>4240249</v>
@@ -32472,7 +32472,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.04312324523926</v>
+        <v>8.04312419891357</v>
       </c>
       <c r="H1107" t="n">
         <v>3890832</v>
@@ -32501,7 +32501,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G1108" t="n">
-        <v>7.92491388320923</v>
+        <v>7.92491245269775</v>
       </c>
       <c r="H1108" t="n">
         <v>3412501</v>
@@ -32588,7 +32588,7 @@
         <v>9.85599994659424</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.8721981048584</v>
+        <v>7.87219715118408</v>
       </c>
       <c r="H1111" t="n">
         <v>4793223</v>
@@ -32617,7 +32617,7 @@
         <v>10</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.98721361160278</v>
+        <v>7.98721313476562</v>
       </c>
       <c r="H1112" t="n">
         <v>2919582</v>
@@ -32646,7 +32646,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.90414667129517</v>
+        <v>7.90414619445801</v>
       </c>
       <c r="H1113" t="n">
         <v>2881408</v>
@@ -32675,7 +32675,7 @@
         <v>10.164999961853</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.11900329589844</v>
+        <v>8.11900234222412</v>
       </c>
       <c r="H1114" t="n">
         <v>2882778</v>
@@ -32733,7 +32733,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.15893936157227</v>
+        <v>8.15893840789795</v>
       </c>
       <c r="H1116" t="n">
         <v>3531557</v>
@@ -32762,7 +32762,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G1117" t="n">
-        <v>7.99919509887695</v>
+        <v>7.99919414520264</v>
       </c>
       <c r="H1117" t="n">
         <v>5418734</v>
@@ -32791,7 +32791,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.46245288848877</v>
+        <v>8.46245384216309</v>
       </c>
       <c r="H1118" t="n">
         <v>5851958</v>
@@ -32820,7 +32820,7 @@
         <v>10.5050001144409</v>
       </c>
       <c r="G1119" t="n">
-        <v>8.3905668258667</v>
+        <v>8.39056777954102</v>
       </c>
       <c r="H1119" t="n">
         <v>3689423</v>
@@ -32849,7 +32849,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.43449687957764</v>
+        <v>8.43449783325195</v>
       </c>
       <c r="H1120" t="n">
         <v>1695218</v>
@@ -32878,7 +32878,7 @@
         <v>10.7449998855591</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.58226013183594</v>
+        <v>8.58226108551025</v>
       </c>
       <c r="H1121" t="n">
         <v>3426447</v>
@@ -32907,7 +32907,7 @@
         <v>10.8549995422363</v>
       </c>
       <c r="G1122" t="n">
-        <v>8.6701192855835</v>
+        <v>8.67012023925781</v>
       </c>
       <c r="H1122" t="n">
         <v>4731648</v>
@@ -32936,7 +32936,7 @@
         <v>11.0249996185303</v>
       </c>
       <c r="G1123" t="n">
-        <v>8.80590343475342</v>
+        <v>8.8059024810791</v>
       </c>
       <c r="H1123" t="n">
         <v>6087208</v>
@@ -32965,7 +32965,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G1124" t="n">
-        <v>9.00158977508545</v>
+        <v>9.00159072875977</v>
       </c>
       <c r="H1124" t="n">
         <v>5968047</v>
@@ -33023,7 +33023,7 @@
         <v>11.2849998474121</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.01357078552246</v>
+        <v>9.01356983184814</v>
       </c>
       <c r="H1126" t="n">
         <v>4644758</v>
@@ -33052,7 +33052,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1127" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1127" t="n">
         <v>6001479</v>
@@ -33139,7 +33139,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1130" t="n">
         <v>3791918</v>
@@ -33168,7 +33168,7 @@
         <v>12.1049995422363</v>
       </c>
       <c r="G1131" t="n">
-        <v>9.66852188110352</v>
+        <v>9.6685209274292</v>
       </c>
       <c r="H1131" t="n">
         <v>5466379</v>
@@ -33226,7 +33226,7 @@
         <v>11.9949998855591</v>
       </c>
       <c r="G1133" t="n">
-        <v>9.58066177368164</v>
+        <v>9.58066272735596</v>
       </c>
       <c r="H1133" t="n">
         <v>4887510</v>
@@ -33255,7 +33255,7 @@
         <v>12.1049995422363</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.66852188110352</v>
+        <v>9.6685209274292</v>
       </c>
       <c r="H1134" t="n">
         <v>6321064</v>
@@ -33284,7 +33284,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G1135" t="n">
-        <v>9.67251682281494</v>
+        <v>9.67251586914062</v>
       </c>
       <c r="H1135" t="n">
         <v>2316152</v>
@@ -33313,7 +33313,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>9.90414333343506</v>
+        <v>9.90414428710938</v>
       </c>
       <c r="H1136" t="n">
         <v>2729665</v>
@@ -33342,7 +33342,7 @@
         <v>11.9049997329712</v>
       </c>
       <c r="G1137" t="n">
-        <v>9.50877666473389</v>
+        <v>9.5087776184082</v>
       </c>
       <c r="H1137" t="n">
         <v>2750768</v>
@@ -33429,7 +33429,7 @@
         <v>12.1350002288818</v>
       </c>
       <c r="G1140" t="n">
-        <v>9.69248294830322</v>
+        <v>9.69248390197754</v>
       </c>
       <c r="H1140" t="n">
         <v>2532076</v>
@@ -33487,7 +33487,7 @@
         <v>12</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.58465671539307</v>
+        <v>9.58465576171875</v>
       </c>
       <c r="H1142" t="n">
         <v>2680965</v>
@@ -33545,7 +33545,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1144" t="n">
-        <v>9.96804237365723</v>
+        <v>9.96804141998291</v>
       </c>
       <c r="H1144" t="n">
         <v>2298824</v>
@@ -33574,7 +33574,7 @@
         <v>12.9350004196167</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.3314619064331</v>
+        <v>10.3314609527588</v>
       </c>
       <c r="H1145" t="n">
         <v>3020159</v>
@@ -33603,7 +33603,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.303505897522</v>
+        <v>10.3035049438477</v>
       </c>
       <c r="H1146" t="n">
         <v>2254164</v>
@@ -33632,7 +33632,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1147" t="n">
-        <v>10.2795438766479</v>
+        <v>10.2795429229736</v>
       </c>
       <c r="H1147" t="n">
         <v>2278939</v>
@@ -33661,7 +33661,7 @@
         <v>12.4650001525879</v>
       </c>
       <c r="G1148" t="n">
-        <v>9.95606231689453</v>
+        <v>9.9560604095459</v>
       </c>
       <c r="H1148" t="n">
         <v>2497031</v>
@@ -33690,7 +33690,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.0239524841309</v>
+        <v>10.0239534378052</v>
       </c>
       <c r="H1149" t="n">
         <v>1941841</v>
@@ -33719,7 +33719,7 @@
         <v>12.6149997711182</v>
       </c>
       <c r="G1150" t="n">
-        <v>10.0758695602417</v>
+        <v>10.075870513916</v>
       </c>
       <c r="H1150" t="n">
         <v>2190781</v>
@@ -33748,7 +33748,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.0159645080566</v>
+        <v>10.015965461731</v>
       </c>
       <c r="H1151" t="n">
         <v>2046846</v>
@@ -33777,7 +33777,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1152" t="n">
-        <v>10.2555828094482</v>
+        <v>10.2555818557739</v>
       </c>
       <c r="H1152" t="n">
         <v>2833459</v>
@@ -33806,7 +33806,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1153" t="n">
-        <v>10.2475957870483</v>
+        <v>10.247594833374</v>
       </c>
       <c r="H1153" t="n">
         <v>1709681</v>
@@ -33835,7 +33835,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1154" t="n">
-        <v>10.2555828094482</v>
+        <v>10.2555818557739</v>
       </c>
       <c r="H1154" t="n">
         <v>2139138</v>
@@ -33864,7 +33864,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1155" t="n">
-        <v>10.4313020706177</v>
+        <v>10.4313011169434</v>
       </c>
       <c r="H1155" t="n">
         <v>1707918</v>
@@ -33951,7 +33951,7 @@
         <v>12.9949998855591</v>
       </c>
       <c r="G1158" t="n">
-        <v>10.3793830871582</v>
+        <v>10.3793840408325</v>
       </c>
       <c r="H1158" t="n">
         <v>2100816</v>
@@ -34038,7 +34038,7 @@
         <v>12.5749998092651</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.0439205169678</v>
+        <v>10.0439214706421</v>
       </c>
       <c r="H1161" t="n">
         <v>1632196</v>
@@ -34067,7 +34067,7 @@
         <v>12.6949996948242</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.1397676467896</v>
+        <v>10.1397686004639</v>
       </c>
       <c r="H1162" t="n">
         <v>1596490</v>
@@ -34096,7 +34096,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1163" t="n">
-        <v>9.72842693328857</v>
+        <v>9.72842597961426</v>
       </c>
       <c r="H1163" t="n">
         <v>3582329</v>
@@ -34183,7 +34183,7 @@
         <v>12.4549999237061</v>
       </c>
       <c r="G1166" t="n">
-        <v>9.94807434082031</v>
+        <v>9.94807529449463</v>
       </c>
       <c r="H1166" t="n">
         <v>2576220</v>
@@ -34270,7 +34270,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.0319414138794</v>
+        <v>10.0319404602051</v>
       </c>
       <c r="H1169" t="n">
         <v>1855713</v>
@@ -34299,7 +34299,7 @@
         <v>12.5749998092651</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.0439205169678</v>
+        <v>10.0439214706421</v>
       </c>
       <c r="H1170" t="n">
         <v>1593190</v>
@@ -34328,7 +34328,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1171" t="n">
-        <v>10.6549434661865</v>
+        <v>10.6549425125122</v>
       </c>
       <c r="H1171" t="n">
         <v>4757283</v>
@@ -34357,7 +34357,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>10.4632511138916</v>
+        <v>10.4632501602173</v>
       </c>
       <c r="H1172" t="n">
         <v>2403879</v>
@@ -34618,7 +34618,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.4313020706177</v>
+        <v>10.4313011169434</v>
       </c>
       <c r="H1181" t="n">
         <v>1659077</v>
@@ -34647,7 +34647,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1182" t="n">
-        <v>10.395357131958</v>
+        <v>10.3953590393066</v>
       </c>
       <c r="H1182" t="n">
         <v>1255095</v>
@@ -34676,7 +34676,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.2715578079224</v>
+        <v>10.2715559005737</v>
       </c>
       <c r="H1183" t="n">
         <v>1496652</v>
@@ -34705,7 +34705,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1184" t="n">
-        <v>10.2475957870483</v>
+        <v>10.247594833374</v>
       </c>
       <c r="H1184" t="n">
         <v>1713707</v>
@@ -34792,7 +34792,7 @@
         <v>12.75</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.1836977005005</v>
+        <v>10.1836967468262</v>
       </c>
       <c r="H1187" t="n">
         <v>1805856</v>
@@ -34821,7 +34821,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1188" t="n">
-        <v>9.70047092437744</v>
+        <v>9.70047187805176</v>
       </c>
       <c r="H1188" t="n">
         <v>3544011</v>
@@ -34850,7 +34850,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1189" t="n">
-        <v>9.70047092437744</v>
+        <v>9.70047187805176</v>
       </c>
       <c r="H1189" t="n">
         <v>3489054</v>
@@ -34879,7 +34879,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1190" t="n">
-        <v>10.0479135513306</v>
+        <v>10.0479145050049</v>
       </c>
       <c r="H1190" t="n">
         <v>1971503</v>
@@ -34908,7 +34908,7 @@
         <v>12.3450002670288</v>
       </c>
       <c r="G1191" t="n">
-        <v>9.86021518707275</v>
+        <v>9.86021614074707</v>
       </c>
       <c r="H1191" t="n">
         <v>3073555</v>
@@ -34995,7 +34995,7 @@
         <v>12.2849998474121</v>
       </c>
       <c r="G1194" t="n">
-        <v>9.81229209899902</v>
+        <v>9.81229114532471</v>
       </c>
       <c r="H1194" t="n">
         <v>2522094</v>
@@ -35082,7 +35082,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1197" t="n">
-        <v>9.6605339050293</v>
+        <v>9.66053581237793</v>
       </c>
       <c r="H1197" t="n">
         <v>4051901</v>
@@ -35111,7 +35111,7 @@
         <v>11.835000038147</v>
       </c>
       <c r="G1198" t="n">
-        <v>9.45286750793457</v>
+        <v>9.45286655426025</v>
       </c>
       <c r="H1198" t="n">
         <v>3900033</v>
@@ -35140,7 +35140,7 @@
         <v>11.8549995422363</v>
       </c>
       <c r="G1199" t="n">
-        <v>9.46884059906006</v>
+        <v>9.46884155273438</v>
       </c>
       <c r="H1199" t="n">
         <v>5347852</v>
@@ -35198,7 +35198,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1201" t="n">
-        <v>9.21724510192871</v>
+        <v>9.21724414825439</v>
       </c>
       <c r="H1201" t="n">
         <v>2205040</v>
@@ -35285,7 +35285,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>9.20526313781738</v>
+        <v>9.2052640914917</v>
       </c>
       <c r="H1204" t="n">
         <v>1942516</v>
@@ -35372,7 +35372,7 @@
         <v>11.7550001144409</v>
       </c>
       <c r="G1207" t="n">
-        <v>9.3889684677124</v>
+        <v>9.38896942138672</v>
       </c>
       <c r="H1207" t="n">
         <v>1808298</v>
@@ -35430,7 +35430,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>9.43290138244629</v>
+        <v>9.43290042877197</v>
       </c>
       <c r="H1209" t="n">
         <v>1470610</v>
@@ -35488,7 +35488,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1211" t="n">
-        <v>9.73641204833984</v>
+        <v>9.73641300201416</v>
       </c>
       <c r="H1211" t="n">
         <v>2580855</v>
@@ -35517,7 +35517,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1212" t="n">
-        <v>9.5367317199707</v>
+        <v>9.53673267364502</v>
       </c>
       <c r="H1212" t="n">
         <v>1845468</v>
@@ -35633,7 +35633,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>9.70446395874023</v>
+        <v>9.70446300506592</v>
       </c>
       <c r="H1216" t="n">
         <v>1283011</v>
@@ -35691,7 +35691,7 @@
         <v>12.0450000762939</v>
       </c>
       <c r="G1218" t="n">
-        <v>9.62059879302979</v>
+        <v>9.6205997467041</v>
       </c>
       <c r="H1218" t="n">
         <v>2131053</v>
@@ -35720,7 +35720,7 @@
         <v>12.1850004196167</v>
       </c>
       <c r="G1219" t="n">
-        <v>9.73241996765137</v>
+        <v>9.73242092132568</v>
       </c>
       <c r="H1219" t="n">
         <v>1691327</v>
@@ -35749,7 +35749,7 @@
         <v>12.1850004196167</v>
       </c>
       <c r="G1220" t="n">
-        <v>9.73241996765137</v>
+        <v>9.73242092132568</v>
       </c>
       <c r="H1220" t="n">
         <v>1258661</v>
@@ -35865,7 +35865,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>9.2332181930542</v>
+        <v>9.23321914672852</v>
       </c>
       <c r="H1224" t="n">
         <v>1611869</v>
@@ -35923,7 +35923,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G1226" t="n">
-        <v>9.18130111694336</v>
+        <v>9.18130207061768</v>
       </c>
       <c r="H1226" t="n">
         <v>2440165</v>
@@ -35952,7 +35952,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1227" t="n">
-        <v>9.05749893188477</v>
+        <v>9.05749988555908</v>
       </c>
       <c r="H1227" t="n">
         <v>3989513</v>
@@ -35981,7 +35981,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1228" t="n">
-        <v>9.31309223175049</v>
+        <v>9.31309127807617</v>
       </c>
       <c r="H1228" t="n">
         <v>3480652</v>
@@ -36010,7 +36010,7 @@
         <v>11.75</v>
       </c>
       <c r="G1229" t="n">
-        <v>9.38497638702393</v>
+        <v>9.38497734069824</v>
       </c>
       <c r="H1229" t="n">
         <v>2210167</v>
@@ -36039,7 +36039,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1230" t="n">
-        <v>9.60063171386719</v>
+        <v>9.6006326675415</v>
       </c>
       <c r="H1230" t="n">
         <v>2561401</v>
@@ -36097,7 +36097,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1232" t="n">
-        <v>9.99999237060547</v>
+        <v>9.99999141693115</v>
       </c>
       <c r="H1232" t="n">
         <v>2555508</v>
@@ -36184,7 +36184,7 @@
         <v>12.1850004196167</v>
       </c>
       <c r="G1235" t="n">
-        <v>9.73241996765137</v>
+        <v>9.73242092132568</v>
       </c>
       <c r="H1235" t="n">
         <v>10965888</v>
@@ -36213,7 +36213,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1236" t="n">
-        <v>9.61660575866699</v>
+        <v>9.61660480499268</v>
       </c>
       <c r="H1236" t="n">
         <v>10407305</v>
@@ -36242,7 +36242,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1237" t="n">
-        <v>9.70047092437744</v>
+        <v>9.70047187805176</v>
       </c>
       <c r="H1237" t="n">
         <v>4914667</v>
@@ -36271,7 +36271,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G1238" t="n">
-        <v>9.57666873931885</v>
+        <v>9.57666969299316</v>
       </c>
       <c r="H1238" t="n">
         <v>4203286</v>
@@ -36358,7 +36358,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1241" t="n">
-        <v>9.88817024230957</v>
+        <v>9.8881721496582</v>
       </c>
       <c r="H1241" t="n">
         <v>2451860</v>
@@ -36387,7 +36387,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.119800567627</v>
+        <v>10.1197996139526</v>
       </c>
       <c r="H1242" t="n">
         <v>4296989</v>
@@ -36445,7 +36445,7 @@
         <v>12.5550003051758</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.027946472168</v>
+        <v>10.0279455184937</v>
       </c>
       <c r="H1244" t="n">
         <v>1426258</v>
@@ -36503,7 +36503,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.2555828094482</v>
+        <v>10.2555818557739</v>
       </c>
       <c r="H1246" t="n">
         <v>2608186</v>
@@ -36532,7 +36532,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1247" t="n">
-        <v>10.4073400497437</v>
+        <v>10.4073390960693</v>
       </c>
       <c r="H1247" t="n">
         <v>3387027</v>
@@ -36619,7 +36619,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G1250" t="n">
-        <v>10.4912042617798</v>
+        <v>10.4912052154541</v>
       </c>
       <c r="H1250" t="n">
         <v>3814049</v>
@@ -36764,7 +36764,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1255" t="n">
-        <v>10.4951982498169</v>
+        <v>10.4951972961426</v>
       </c>
       <c r="H1255" t="n">
         <v>2070881</v>
@@ -36967,7 +36967,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.395357131958</v>
+        <v>10.3953590393066</v>
       </c>
       <c r="H1262" t="n">
         <v>2331252</v>
@@ -37141,7 +37141,7 @@
         <v>13.4250001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.7228345870972</v>
+        <v>10.7228326797485</v>
       </c>
       <c r="H1268" t="n">
         <v>1985023</v>
@@ -37170,7 +37170,7 @@
         <v>13.3850002288818</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.6908864974976</v>
+        <v>10.6908855438232</v>
       </c>
       <c r="H1269" t="n">
         <v>1267820</v>
@@ -37257,7 +37257,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>10.7348146438599</v>
+        <v>10.7348136901855</v>
       </c>
       <c r="H1272" t="n">
         <v>2318767</v>
@@ -37286,7 +37286,7 @@
         <v>13.4549999237061</v>
       </c>
       <c r="G1273" t="n">
-        <v>10.7467966079712</v>
+        <v>10.7467947006226</v>
       </c>
       <c r="H1273" t="n">
         <v>2628093</v>
@@ -37431,7 +37431,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1278" t="n">
-        <v>11.0942401885986</v>
+        <v>11.0942392349243</v>
       </c>
       <c r="H1278" t="n">
         <v>1878203</v>
@@ -37460,7 +37460,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>11.0543031692505</v>
+        <v>11.0543041229248</v>
       </c>
       <c r="H1279" t="n">
         <v>2276701</v>
@@ -37489,7 +37489,7 @@
         <v>13.6850004196167</v>
       </c>
       <c r="G1280" t="n">
-        <v>10.9305028915405</v>
+        <v>10.9305019378662</v>
       </c>
       <c r="H1280" t="n">
         <v>2944954</v>
@@ -37518,7 +37518,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1281" t="n">
-        <v>11.0543031692505</v>
+        <v>11.0543041229248</v>
       </c>
       <c r="H1281" t="n">
         <v>1350537</v>
@@ -37576,7 +37576,7 @@
         <v>13.4650001525879</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.7547836303711</v>
+        <v>10.7547826766968</v>
       </c>
       <c r="H1283" t="n">
         <v>1402695</v>
@@ -37634,7 +37634,7 @@
         <v>13.3050003051758</v>
       </c>
       <c r="G1285" t="n">
-        <v>10.6269884109497</v>
+        <v>10.6269874572754</v>
       </c>
       <c r="H1285" t="n">
         <v>1995436</v>
@@ -37692,7 +37692,7 @@
         <v>13.1949996948242</v>
       </c>
       <c r="G1287" t="n">
-        <v>10.5391273498535</v>
+        <v>10.5391292572021</v>
       </c>
       <c r="H1287" t="n">
         <v>1130799</v>
@@ -37721,7 +37721,7 @@
         <v>12.9549999237061</v>
       </c>
       <c r="G1288" t="n">
-        <v>10.3474340438843</v>
+        <v>10.3474359512329</v>
       </c>
       <c r="H1288" t="n">
         <v>2182575</v>
@@ -37750,7 +37750,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G1289" t="n">
-        <v>10.4912042617798</v>
+        <v>10.4912052154541</v>
       </c>
       <c r="H1289" t="n">
         <v>1661895</v>
@@ -37837,7 +37837,7 @@
         <v>13.3850002288818</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.6908864974976</v>
+        <v>10.6908855438232</v>
       </c>
       <c r="H1292" t="n">
         <v>2057784</v>
@@ -37866,7 +37866,7 @@
         <v>13.6149997711182</v>
       </c>
       <c r="G1293" t="n">
-        <v>10.8745908737183</v>
+        <v>10.8745918273926</v>
       </c>
       <c r="H1293" t="n">
         <v>3418460</v>
@@ -37895,7 +37895,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1294" t="n">
-        <v>11.5495100021362</v>
+        <v>11.5495109558105</v>
       </c>
       <c r="H1294" t="n">
         <v>4480665</v>
@@ -37924,7 +37924,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1295" t="n">
-        <v>11.6613321304321</v>
+        <v>11.6613311767578</v>
       </c>
       <c r="H1295" t="n">
         <v>2883119</v>
@@ -37953,7 +37953,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.9408845901489</v>
+        <v>11.9408836364746</v>
       </c>
       <c r="H1296" t="n">
         <v>2938775</v>
@@ -37982,7 +37982,7 @@
         <v>14.625</v>
       </c>
       <c r="G1297" t="n">
-        <v>11.6812992095947</v>
+        <v>11.681300163269</v>
       </c>
       <c r="H1297" t="n">
         <v>5786878</v>
@@ -38040,7 +38040,7 @@
         <v>14.7849998474121</v>
       </c>
       <c r="G1299" t="n">
-        <v>11.8090944290161</v>
+        <v>11.8090953826904</v>
       </c>
       <c r="H1299" t="n">
         <v>2016808</v>
@@ -38069,7 +38069,7 @@
         <v>15.0649995803833</v>
       </c>
       <c r="G1300" t="n">
-        <v>12.0327367782593</v>
+        <v>12.0327377319336</v>
       </c>
       <c r="H1300" t="n">
         <v>2233779</v>
@@ -38127,7 +38127,7 @@
         <v>15.0550003051758</v>
       </c>
       <c r="G1302" t="n">
-        <v>12.0247497558594</v>
+        <v>12.0247507095337</v>
       </c>
       <c r="H1302" t="n">
         <v>1763614</v>
@@ -38156,7 +38156,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>11.9009485244751</v>
+        <v>11.9009466171265</v>
       </c>
       <c r="H1303" t="n">
         <v>2058910</v>
@@ -38185,7 +38185,7 @@
         <v>14.6750001907349</v>
       </c>
       <c r="G1304" t="n">
-        <v>11.7212362289429</v>
+        <v>11.7212371826172</v>
       </c>
       <c r="H1304" t="n">
         <v>2049234</v>
@@ -38214,7 +38214,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>11.8610105514526</v>
+        <v>11.861011505127</v>
       </c>
       <c r="H1305" t="n">
         <v>1878355</v>
@@ -38243,7 +38243,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>11.7332172393799</v>
+        <v>11.7332162857056</v>
       </c>
       <c r="H1306" t="n">
         <v>1508288</v>
@@ -38301,7 +38301,7 @@
         <v>14.875</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.8809804916382</v>
+        <v>11.8809795379639</v>
       </c>
       <c r="H1308" t="n">
         <v>1942114</v>
@@ -38330,7 +38330,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412052154541</v>
       </c>
       <c r="H1309" t="n">
         <v>1874170</v>
@@ -38359,7 +38359,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.6373701095581</v>
+        <v>11.6373691558838</v>
       </c>
       <c r="H1310" t="n">
         <v>2259876</v>
@@ -38417,7 +38417,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.6174020767212</v>
+        <v>11.6174030303955</v>
       </c>
       <c r="H1312" t="n">
         <v>1617916</v>
@@ -38446,7 +38446,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.5894479751587</v>
+        <v>11.5894470214844</v>
       </c>
       <c r="H1313" t="n">
         <v>1721144</v>
@@ -38475,7 +38475,7 @@
         <v>14.375</v>
       </c>
       <c r="G1314" t="n">
-        <v>11.4816188812256</v>
+        <v>11.4816198348999</v>
       </c>
       <c r="H1314" t="n">
         <v>2664252</v>
@@ -38504,7 +38504,7 @@
         <v>14.4449996948242</v>
       </c>
       <c r="G1315" t="n">
-        <v>11.5375299453735</v>
+        <v>11.5375289916992</v>
       </c>
       <c r="H1315" t="n">
         <v>3249636</v>
@@ -38533,7 +38533,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1316" t="n">
-        <v>11.8210754394531</v>
+        <v>11.8210763931274</v>
       </c>
       <c r="H1316" t="n">
         <v>3169148</v>
@@ -38562,7 +38562,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G1317" t="n">
-        <v>11.7132482528687</v>
+        <v>11.713249206543</v>
       </c>
       <c r="H1317" t="n">
         <v>2266381</v>
@@ -38678,7 +38678,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G1321" t="n">
-        <v>11.5295429229736</v>
+        <v>11.5295438766479</v>
       </c>
       <c r="H1321" t="n">
         <v>2559551</v>
@@ -38707,7 +38707,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1322" t="n">
-        <v>11.5335359573364</v>
+        <v>11.5335369110107</v>
       </c>
       <c r="H1322" t="n">
         <v>2971886</v>
@@ -38736,7 +38736,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1323" t="n">
-        <v>11.5495100021362</v>
+        <v>11.5495109558105</v>
       </c>
       <c r="H1323" t="n">
         <v>2040470</v>
@@ -38765,7 +38765,7 @@
         <v>14.625</v>
       </c>
       <c r="G1324" t="n">
-        <v>11.6812992095947</v>
+        <v>11.681300163269</v>
       </c>
       <c r="H1324" t="n">
         <v>2036602</v>
@@ -38794,7 +38794,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>11.5015869140625</v>
+        <v>11.5015878677368</v>
       </c>
       <c r="H1325" t="n">
         <v>3849807</v>
@@ -38852,7 +38852,7 @@
         <v>14.2049999237061</v>
       </c>
       <c r="G1327" t="n">
-        <v>11.3458366394043</v>
+        <v>11.34583568573</v>
       </c>
       <c r="H1327" t="n">
         <v>3020417</v>
@@ -38968,7 +38968,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1331" t="n">
-        <v>11.0383281707764</v>
+        <v>11.0383291244507</v>
       </c>
       <c r="H1331" t="n">
         <v>1424152</v>
@@ -39084,7 +39084,7 @@
         <v>13.8450002670288</v>
       </c>
       <c r="G1335" t="n">
-        <v>11.0582971572876</v>
+        <v>11.0582981109619</v>
       </c>
       <c r="H1335" t="n">
         <v>1961062</v>
@@ -39113,7 +39113,7 @@
         <v>13.9750003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>11.162130355835</v>
+        <v>11.1621313095093</v>
       </c>
       <c r="H1336" t="n">
         <v>2194077</v>
@@ -39171,7 +39171,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G1338" t="n">
-        <v>11.1581382751465</v>
+        <v>11.1581363677979</v>
       </c>
       <c r="H1338" t="n">
         <v>2070120</v>
@@ -39200,7 +39200,7 @@
         <v>14.085000038147</v>
       </c>
       <c r="G1339" t="n">
-        <v>11.2499904632568</v>
+        <v>11.2499895095825</v>
       </c>
       <c r="H1339" t="n">
         <v>1667008</v>
@@ -39229,7 +39229,7 @@
         <v>14.1549997329712</v>
       </c>
       <c r="G1340" t="n">
-        <v>11.3058996200562</v>
+        <v>11.3059015274048</v>
       </c>
       <c r="H1340" t="n">
         <v>1950768</v>
@@ -39316,7 +39316,7 @@
         <v>14.3450002670288</v>
       </c>
       <c r="G1343" t="n">
-        <v>11.4576578140259</v>
+        <v>11.4576568603516</v>
       </c>
       <c r="H1343" t="n">
         <v>1718139</v>
@@ -39432,7 +39432,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1347" t="n">
-        <v>11.0303411483765</v>
+        <v>11.0303430557251</v>
       </c>
       <c r="H1347" t="n">
         <v>1361313</v>
@@ -39461,7 +39461,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.0503091812134</v>
+        <v>11.0503101348877</v>
       </c>
       <c r="H1348" t="n">
         <v>1776773</v>
@@ -39606,7 +39606,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1353" t="n">
-        <v>11.437689781189</v>
+        <v>11.4376888275146</v>
       </c>
       <c r="H1353" t="n">
         <v>2427988</v>
@@ -39722,7 +39722,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1357" t="n">
-        <v>11.2300233840942</v>
+        <v>11.2300214767456</v>
       </c>
       <c r="H1357" t="n">
         <v>2197571</v>
@@ -39751,7 +39751,7 @@
         <v>14.1450004577637</v>
       </c>
       <c r="G1358" t="n">
-        <v>11.2979135513306</v>
+        <v>11.2979145050049</v>
       </c>
       <c r="H1358" t="n">
         <v>2141691</v>
@@ -39838,7 +39838,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1361" t="n">
-        <v>11.22203540802</v>
+        <v>11.2220344543457</v>
       </c>
       <c r="H1361" t="n">
         <v>2710046</v>
@@ -39896,7 +39896,7 @@
         <v>14.1850004196167</v>
       </c>
       <c r="G1363" t="n">
-        <v>11.3298616409302</v>
+        <v>11.3298635482788</v>
       </c>
       <c r="H1363" t="n">
         <v>2085712</v>
@@ -39925,7 +39925,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1364" t="n">
-        <v>11.1501502990723</v>
+        <v>11.1501493453979</v>
       </c>
       <c r="H1364" t="n">
         <v>2556785</v>
@@ -39954,7 +39954,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1365" t="n">
-        <v>11.0503091812134</v>
+        <v>11.0503101348877</v>
       </c>
       <c r="H1365" t="n">
         <v>5330028</v>
@@ -39983,7 +39983,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.7507905960083</v>
+        <v>10.7507886886597</v>
       </c>
       <c r="H1366" t="n">
         <v>3014854</v>
@@ -40012,7 +40012,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G1367" t="n">
-        <v>10.7907257080078</v>
+        <v>10.7907266616821</v>
       </c>
       <c r="H1367" t="n">
         <v>2156987</v>
@@ -40128,7 +40128,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1371" t="n">
-        <v>10.9105339050293</v>
+        <v>10.910532951355</v>
       </c>
       <c r="H1371" t="n">
         <v>1884972</v>
@@ -40157,7 +40157,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1372" t="n">
-        <v>10.9424829483032</v>
+        <v>10.9424819946289</v>
       </c>
       <c r="H1372" t="n">
         <v>3312012</v>
@@ -40186,7 +40186,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G1373" t="n">
-        <v>10.9185209274292</v>
+        <v>10.9185199737549</v>
       </c>
       <c r="H1373" t="n">
         <v>1919959</v>
@@ -40244,7 +40244,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.9664440155029</v>
+        <v>10.9664430618286</v>
       </c>
       <c r="H1375" t="n">
         <v>2050342</v>
@@ -40273,7 +40273,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.9504690170288</v>
+        <v>10.9504699707031</v>
       </c>
       <c r="H1376" t="n">
         <v>1450757</v>
@@ -40389,7 +40389,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1380" t="n">
-        <v>11.2140474319458</v>
+        <v>11.2140483856201</v>
       </c>
       <c r="H1380" t="n">
         <v>1937096</v>
@@ -40418,7 +40418,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1381" t="n">
-        <v>11.1341762542725</v>
+        <v>11.1341743469238</v>
       </c>
       <c r="H1381" t="n">
         <v>1518297</v>
@@ -40447,7 +40447,7 @@
         <v>13.8950004577637</v>
       </c>
       <c r="G1382" t="n">
-        <v>11.0982341766357</v>
+        <v>11.0982322692871</v>
       </c>
       <c r="H1382" t="n">
         <v>1378576</v>
@@ -40563,7 +40563,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1386" t="n">
-        <v>11.4896068572998</v>
+        <v>11.4896078109741</v>
       </c>
       <c r="H1386" t="n">
         <v>4000594</v>
@@ -40592,7 +40592,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1387" t="n">
-        <v>11.4217166900635</v>
+        <v>11.4217147827148</v>
       </c>
       <c r="H1387" t="n">
         <v>2321321</v>
@@ -40650,7 +40650,7 @@
         <v>14.2349996566772</v>
       </c>
       <c r="G1389" t="n">
-        <v>11.369797706604</v>
+        <v>11.3697986602783</v>
       </c>
       <c r="H1389" t="n">
         <v>2308326</v>
@@ -40708,7 +40708,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.6533441543579</v>
+        <v>11.6533451080322</v>
       </c>
       <c r="H1391" t="n">
         <v>2668942</v>
@@ -40766,7 +40766,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1393" t="n">
-        <v>11.8210754394531</v>
+        <v>11.8210763931274</v>
       </c>
       <c r="H1393" t="n">
         <v>1553039</v>
@@ -40795,7 +40795,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1394" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412052154541</v>
       </c>
       <c r="H1394" t="n">
         <v>1395345</v>
@@ -40824,7 +40824,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1395" t="n">
-        <v>11.7891273498535</v>
+        <v>11.7891263961792</v>
       </c>
       <c r="H1395" t="n">
         <v>1136188</v>
@@ -40853,7 +40853,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1396" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412052154541</v>
       </c>
       <c r="H1396" t="n">
         <v>2499043</v>
@@ -40882,7 +40882,7 @@
         <v>14.7049999237061</v>
       </c>
       <c r="G1397" t="n">
-        <v>11.7451982498169</v>
+        <v>11.7451972961426</v>
       </c>
       <c r="H1397" t="n">
         <v>2503933</v>
@@ -40911,7 +40911,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1398" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412052154541</v>
       </c>
       <c r="H1398" t="n">
         <v>1445021</v>
@@ -40969,7 +40969,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412052154541</v>
       </c>
       <c r="H1400" t="n">
         <v>2955995</v>
@@ -40998,7 +40998,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1401" t="n">
-        <v>11.7891273498535</v>
+        <v>11.7891263961792</v>
       </c>
       <c r="H1401" t="n">
         <v>2541193</v>
@@ -41056,7 +41056,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>11.9408845901489</v>
+        <v>11.9408836364746</v>
       </c>
       <c r="H1403" t="n">
         <v>2597551</v>
@@ -41114,7 +41114,7 @@
         <v>14.7049999237061</v>
       </c>
       <c r="G1405" t="n">
-        <v>11.7451982498169</v>
+        <v>11.7451972961426</v>
       </c>
       <c r="H1405" t="n">
         <v>3201643</v>
@@ -41230,7 +41230,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1409" t="n">
-        <v>11.0503091812134</v>
+        <v>11.0503101348877</v>
       </c>
       <c r="H1409" t="n">
         <v>2133933</v>
@@ -41259,7 +41259,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0543031692505</v>
+        <v>11.0543041229248</v>
       </c>
       <c r="H1410" t="n">
         <v>1386695</v>
@@ -41288,7 +41288,7 @@
         <v>14.1549997329712</v>
       </c>
       <c r="G1411" t="n">
-        <v>11.3058996200562</v>
+        <v>11.3059015274048</v>
       </c>
       <c r="H1411" t="n">
         <v>1527090</v>
@@ -41317,7 +41317,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1412" t="n">
-        <v>11.3418426513672</v>
+        <v>11.3418436050415</v>
       </c>
       <c r="H1412" t="n">
         <v>1413536</v>
@@ -41375,7 +41375,7 @@
         <v>14.6149997711182</v>
       </c>
       <c r="G1414" t="n">
-        <v>11.6733121871948</v>
+        <v>11.6733112335205</v>
       </c>
       <c r="H1414" t="n">
         <v>1166228</v>
@@ -41404,7 +41404,7 @@
         <v>14.7349996566772</v>
       </c>
       <c r="G1415" t="n">
-        <v>11.7691593170166</v>
+        <v>11.7691583633423</v>
       </c>
       <c r="H1415" t="n">
         <v>1465703</v>
@@ -41491,7 +41491,7 @@
         <v>15.1149997711182</v>
       </c>
       <c r="G1418" t="n">
-        <v>12.0726728439331</v>
+        <v>12.0726737976074</v>
       </c>
       <c r="H1418" t="n">
         <v>2580461</v>
@@ -41520,7 +41520,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1419" t="n">
-        <v>11.8210754394531</v>
+        <v>11.8210763931274</v>
       </c>
       <c r="H1419" t="n">
         <v>2280337</v>
@@ -41549,7 +41549,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1420" t="n">
-        <v>11.9129295349121</v>
+        <v>11.9129276275635</v>
       </c>
       <c r="H1420" t="n">
         <v>2494707</v>
@@ -41636,7 +41636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.7396059036255</v>
+        <v>12.7396049499512</v>
       </c>
       <c r="H1423" t="n">
         <v>2715997</v>
@@ -41694,7 +41694,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1425" t="n">
-        <v>12.9552602767944</v>
+        <v>12.9552593231201</v>
       </c>
       <c r="H1425" t="n">
         <v>1568736</v>
@@ -41752,7 +41752,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1427" t="n">
-        <v>12.9712343215942</v>
+        <v>12.9712352752686</v>
       </c>
       <c r="H1427" t="n">
         <v>1658401</v>
@@ -41839,7 +41839,7 @@
         <v>15.9449996948242</v>
       </c>
       <c r="G1430" t="n">
-        <v>12.7356128692627</v>
+        <v>12.7356119155884</v>
       </c>
       <c r="H1430" t="n">
         <v>1600785</v>
@@ -41897,7 +41897,7 @@
         <v>15.9350004196167</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.7276248931885</v>
+        <v>12.7276258468628</v>
       </c>
       <c r="H1432" t="n">
         <v>2077557</v>
@@ -41926,7 +41926,7 @@
         <v>15.7349996566772</v>
       </c>
       <c r="G1433" t="n">
-        <v>12.5678815841675</v>
+        <v>12.5678796768188</v>
       </c>
       <c r="H1433" t="n">
         <v>1618942</v>
@@ -41955,7 +41955,7 @@
         <v>15.8649997711182</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.6717138290405</v>
+        <v>12.6717147827148</v>
       </c>
       <c r="H1434" t="n">
         <v>919515</v>
@@ -41984,7 +41984,7 @@
         <v>15.8950004577637</v>
       </c>
       <c r="G1435" t="n">
-        <v>12.6956758499146</v>
+        <v>12.6956777572632</v>
       </c>
       <c r="H1435" t="n">
         <v>1183165</v>
@@ -42042,7 +42042,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.6757068634033</v>
+        <v>12.6757078170776</v>
       </c>
       <c r="H1437" t="n">
         <v>1032977</v>
@@ -42158,7 +42158,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G1441" t="n">
-        <v>12.3881683349609</v>
+        <v>12.3881673812866</v>
       </c>
       <c r="H1441" t="n">
         <v>2136237</v>
@@ -42187,7 +42187,7 @@
         <v>15.5150003433228</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.3921632766724</v>
+        <v>12.3921604156494</v>
       </c>
       <c r="H1442" t="n">
         <v>1547130</v>
@@ -42216,7 +42216,7 @@
         <v>15.3850002288818</v>
       </c>
       <c r="G1443" t="n">
-        <v>12.2883272171021</v>
+        <v>12.2883281707764</v>
       </c>
       <c r="H1443" t="n">
         <v>1281238</v>
@@ -42245,7 +42245,7 @@
         <v>15.4250001907349</v>
       </c>
       <c r="G1444" t="n">
-        <v>12.320276260376</v>
+        <v>12.3202772140503</v>
       </c>
       <c r="H1444" t="n">
         <v>1175282</v>
@@ -42274,7 +42274,7 @@
         <v>15.5950002670288</v>
       </c>
       <c r="G1445" t="n">
-        <v>12.4560604095459</v>
+        <v>12.4560613632202</v>
       </c>
       <c r="H1445" t="n">
         <v>1585753</v>
@@ -42303,7 +42303,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1446" t="n">
-        <v>12.3562202453613</v>
+        <v>12.356219291687</v>
       </c>
       <c r="H1446" t="n">
         <v>1126431</v>
@@ -42390,7 +42390,7 @@
         <v>15.2650003433228</v>
       </c>
       <c r="G1449" t="n">
-        <v>12.1924800872803</v>
+        <v>12.1924819946289</v>
       </c>
       <c r="H1449" t="n">
         <v>1028998</v>
@@ -42477,7 +42477,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1452" t="n">
-        <v>12.7475929260254</v>
+        <v>12.7475938796997</v>
       </c>
       <c r="H1452" t="n">
         <v>2430932</v>
@@ -42593,7 +42593,7 @@
         <v>15.6850004196167</v>
       </c>
       <c r="G1456" t="n">
-        <v>12.5279445648193</v>
+        <v>12.5279455184937</v>
       </c>
       <c r="H1456" t="n">
         <v>1260691</v>
@@ -42622,7 +42622,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G1457" t="n">
-        <v>12.7515869140625</v>
+        <v>12.7515859603882</v>
       </c>
       <c r="H1457" t="n">
         <v>1567852</v>
@@ -42651,7 +42651,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1458" t="n">
-        <v>12.7396059036255</v>
+        <v>12.7396049499512</v>
       </c>
       <c r="H1458" t="n">
         <v>1335880</v>
@@ -42709,7 +42709,7 @@
         <v>15.6049995422363</v>
       </c>
       <c r="G1460" t="n">
-        <v>12.4640464782715</v>
+        <v>12.4640455245972</v>
       </c>
       <c r="H1460" t="n">
         <v>2177254</v>
@@ -42854,7 +42854,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1465" t="n">
-        <v>12.4920015335083</v>
+        <v>12.4920024871826</v>
       </c>
       <c r="H1465" t="n">
         <v>1777738</v>
@@ -42883,7 +42883,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1466" t="n">
-        <v>12.5079755783081</v>
+        <v>12.5079774856567</v>
       </c>
       <c r="H1466" t="n">
         <v>1754636</v>
@@ -42912,7 +42912,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1467" t="n">
-        <v>12.5479125976562</v>
+        <v>12.5479116439819</v>
       </c>
       <c r="H1467" t="n">
         <v>1599052</v>
@@ -42970,7 +42970,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G1469" t="n">
-        <v>12.5119705200195</v>
+        <v>12.5119695663452</v>
       </c>
       <c r="H1469" t="n">
         <v>998564</v>
@@ -42999,7 +42999,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1470" t="n">
-        <v>12.7156448364258</v>
+        <v>12.7156438827515</v>
       </c>
       <c r="H1470" t="n">
         <v>1136614</v>
@@ -43028,7 +43028,7 @@
         <v>15.8149995803833</v>
       </c>
       <c r="G1471" t="n">
-        <v>12.6317777633667</v>
+        <v>12.631778717041</v>
       </c>
       <c r="H1471" t="n">
         <v>1311446</v>
@@ -43057,7 +43057,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1472" t="n">
-        <v>13.0990304946899</v>
+        <v>13.0990295410156</v>
       </c>
       <c r="H1472" t="n">
         <v>3176373</v>
@@ -43086,7 +43086,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1473" t="n">
-        <v>13.2747488021851</v>
+        <v>13.2747497558594</v>
       </c>
       <c r="H1473" t="n">
         <v>2062427</v>
@@ -43173,7 +43173,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1476" t="n">
-        <v>13.2907228469849</v>
+        <v>13.2907209396362</v>
       </c>
       <c r="H1476" t="n">
         <v>1193898</v>
@@ -43202,7 +43202,7 @@
         <v>16.6049995422363</v>
       </c>
       <c r="G1477" t="n">
-        <v>13.2627687454224</v>
+        <v>13.262767791748</v>
       </c>
       <c r="H1477" t="n">
         <v>1049924</v>
@@ -43231,7 +43231,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G1478" t="n">
-        <v>13.2867298126221</v>
+        <v>13.2867307662964</v>
       </c>
       <c r="H1478" t="n">
         <v>1057708</v>
@@ -43260,7 +43260,7 @@
         <v>16.7849998474121</v>
       </c>
       <c r="G1479" t="n">
-        <v>13.4065389633179</v>
+        <v>13.4065370559692</v>
       </c>
       <c r="H1479" t="n">
         <v>1867478</v>
@@ -43347,7 +43347,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>13.2188377380371</v>
+        <v>13.2188367843628</v>
       </c>
       <c r="H1482" t="n">
         <v>1516881</v>
@@ -43376,7 +43376,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1483" t="n">
-        <v>13.1908826828003</v>
+        <v>13.1908836364746</v>
       </c>
       <c r="H1483" t="n">
         <v>2049036</v>
@@ -43405,7 +43405,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1484" t="n">
-        <v>13.4864101409912</v>
+        <v>13.4864110946655</v>
       </c>
       <c r="H1484" t="n">
         <v>1652168</v>
@@ -43434,7 +43434,7 @@
         <v>16.5949993133545</v>
       </c>
       <c r="G1485" t="n">
-        <v>13.2547807693481</v>
+        <v>13.2547798156738</v>
       </c>
       <c r="H1485" t="n">
         <v>2137623</v>
@@ -43550,7 +43550,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1489" t="n">
-        <v>13.8019046783447</v>
+        <v>13.801905632019</v>
       </c>
       <c r="H1489" t="n">
         <v>1634220</v>
@@ -43579,7 +43579,7 @@
         <v>16.9650001525879</v>
       </c>
       <c r="G1490" t="n">
-        <v>13.5503091812134</v>
+        <v>13.5503082275391</v>
       </c>
       <c r="H1490" t="n">
         <v>2551876</v>
@@ -43608,7 +43608,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1491" t="n">
-        <v>13.6341724395752</v>
+        <v>13.6341733932495</v>
       </c>
       <c r="H1491" t="n">
         <v>2128741</v>
@@ -43637,7 +43637,7 @@
         <v>17.2350006103516</v>
       </c>
       <c r="G1492" t="n">
-        <v>13.7659616470337</v>
+        <v>13.765962600708</v>
       </c>
       <c r="H1492" t="n">
         <v>1101791</v>
@@ -43695,7 +43695,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1494" t="n">
-        <v>13.8019046783447</v>
+        <v>13.801905632019</v>
       </c>
       <c r="H1494" t="n">
         <v>1276201</v>
@@ -43724,7 +43724,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G1495" t="n">
-        <v>13.7340135574341</v>
+        <v>13.7340126037598</v>
       </c>
       <c r="H1495" t="n">
         <v>1671596</v>
@@ -43782,7 +43782,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1497" t="n">
-        <v>13.6900835037231</v>
+        <v>13.6900844573975</v>
       </c>
       <c r="H1497" t="n">
         <v>1392449</v>
@@ -43811,7 +43811,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1498" t="n">
-        <v>13.6022233963013</v>
+        <v>13.6022243499756</v>
       </c>
       <c r="H1498" t="n">
         <v>2170985</v>
@@ -43927,7 +43927,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>13.1488170623779</v>
+        <v>13.1488161087036</v>
       </c>
       <c r="H1502" t="n">
         <v>1269802</v>
@@ -44014,7 +44014,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>12.7696027755737</v>
+        <v>12.769603729248</v>
       </c>
       <c r="H1505" t="n">
         <v>3379076</v>
@@ -44420,7 +44420,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1519" t="n">
-        <v>12.2914657592773</v>
+        <v>12.291464805603</v>
       </c>
       <c r="H1519" t="n">
         <v>1618355</v>
@@ -44449,7 +44449,7 @@
         <v>15.1450004577637</v>
       </c>
       <c r="G1520" t="n">
-        <v>12.4851951599121</v>
+        <v>12.4851942062378</v>
       </c>
       <c r="H1520" t="n">
         <v>1000909</v>
@@ -44478,7 +44478,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G1521" t="n">
-        <v>12.472827911377</v>
+        <v>12.4728288650513</v>
       </c>
       <c r="H1521" t="n">
         <v>1033382</v>
@@ -44507,7 +44507,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1522" t="n">
-        <v>12.4316091537476</v>
+        <v>12.4316082000732</v>
       </c>
       <c r="H1522" t="n">
         <v>884943</v>
@@ -44565,7 +44565,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1524" t="n">
-        <v>12.753116607666</v>
+        <v>12.7531156539917</v>
       </c>
       <c r="H1524" t="n">
         <v>717626</v>
@@ -44652,7 +44652,7 @@
         <v>15.7150001525879</v>
       </c>
       <c r="G1527" t="n">
-        <v>12.9550886154175</v>
+        <v>12.9550895690918</v>
       </c>
       <c r="H1527" t="n">
         <v>1349901</v>
@@ -44681,7 +44681,7 @@
         <v>15.7550001144409</v>
       </c>
       <c r="G1528" t="n">
-        <v>12.9880638122559</v>
+        <v>12.9880628585815</v>
       </c>
       <c r="H1528" t="n">
         <v>1478008</v>
@@ -44739,7 +44739,7 @@
         <v>15.4849996566772</v>
       </c>
       <c r="G1530" t="n">
-        <v>12.7654819488525</v>
+        <v>12.7654809951782</v>
       </c>
       <c r="H1530" t="n">
         <v>2272621</v>
@@ -44971,7 +44971,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1538" t="n">
-        <v>12.7943353652954</v>
+        <v>12.7943363189697</v>
       </c>
       <c r="H1538" t="n">
         <v>1559958</v>
@@ -45000,7 +45000,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1539" t="n">
-        <v>12.5470218658447</v>
+        <v>12.547022819519</v>
       </c>
       <c r="H1539" t="n">
         <v>2294685</v>
@@ -45029,7 +45029,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1540" t="n">
-        <v>12.7036533355713</v>
+        <v>12.703652381897</v>
       </c>
       <c r="H1540" t="n">
         <v>1654184</v>
@@ -45087,7 +45087,7 @@
         <v>14.9049997329712</v>
       </c>
       <c r="G1542" t="n">
-        <v>12.2873420715332</v>
+        <v>12.2873430252075</v>
       </c>
       <c r="H1542" t="n">
         <v>2442254</v>
@@ -45145,7 +45145,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1544" t="n">
-        <v>12.0853700637817</v>
+        <v>12.0853691101074</v>
       </c>
       <c r="H1544" t="n">
         <v>1509739</v>
@@ -45174,7 +45174,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1545" t="n">
-        <v>12.0276651382446</v>
+        <v>12.0276641845703</v>
       </c>
       <c r="H1545" t="n">
         <v>2375692</v>
@@ -45232,7 +45232,7 @@
         <v>14.8050003051758</v>
       </c>
       <c r="G1547" t="n">
-        <v>12.204906463623</v>
+        <v>12.2049055099487</v>
       </c>
       <c r="H1547" t="n">
         <v>1674780</v>
@@ -45348,7 +45348,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1551" t="n">
-        <v>12.2955865859985</v>
+        <v>12.2955856323242</v>
       </c>
       <c r="H1551" t="n">
         <v>2768969</v>
@@ -45464,7 +45464,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1555" t="n">
-        <v>13.1240863800049</v>
+        <v>13.1240854263306</v>
       </c>
       <c r="H1555" t="n">
         <v>2679109</v>
@@ -45522,7 +45522,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G1557" t="n">
-        <v>12.7696027755737</v>
+        <v>12.769603729248</v>
       </c>
       <c r="H1557" t="n">
         <v>2118294</v>
@@ -45580,7 +45580,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1559" t="n">
-        <v>13.173547744751</v>
+        <v>13.1735486984253</v>
       </c>
       <c r="H1559" t="n">
         <v>1914655</v>
@@ -45667,7 +45667,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G1562" t="n">
-        <v>12.9138698577881</v>
+        <v>12.9138689041138</v>
       </c>
       <c r="H1562" t="n">
         <v>1531379</v>
@@ -45783,7 +45783,7 @@
         <v>14.8549995422363</v>
       </c>
       <c r="G1566" t="n">
-        <v>12.2461242675781</v>
+        <v>12.2461233139038</v>
       </c>
       <c r="H1566" t="n">
         <v>3467052</v>
@@ -45870,7 +45870,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1569" t="n">
-        <v>11.590744972229</v>
+        <v>11.5907440185547</v>
       </c>
       <c r="H1569" t="n">
         <v>2348018</v>
@@ -45957,7 +45957,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.4695901870728</v>
+        <v>10.4695911407471</v>
       </c>
       <c r="H1572" t="n">
         <v>5012765</v>
@@ -45986,7 +45986,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G1573" t="n">
-        <v>10.1439619064331</v>
+        <v>10.1439638137817</v>
       </c>
       <c r="H1573" t="n">
         <v>3131711</v>
@@ -46044,7 +46044,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1575" t="n">
-        <v>10.8982667922974</v>
+        <v>10.8982677459717</v>
       </c>
       <c r="H1575" t="n">
         <v>3582696</v>
@@ -46102,7 +46102,7 @@
         <v>13.8149995803833</v>
       </c>
       <c r="G1577" t="n">
-        <v>11.3887710571289</v>
+        <v>11.3887701034546</v>
       </c>
       <c r="H1577" t="n">
         <v>2021098</v>
@@ -46189,7 +46189,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G1580" t="n">
-        <v>11.5454034805298</v>
+        <v>11.5454025268555</v>
       </c>
       <c r="H1580" t="n">
         <v>2851617</v>
@@ -46247,7 +46247,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G1582" t="n">
-        <v>11.5454034805298</v>
+        <v>11.5454025268555</v>
       </c>
       <c r="H1582" t="n">
         <v>1865620</v>
@@ -46421,7 +46421,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1588" t="n">
-        <v>11.8586664199829</v>
+        <v>11.8586673736572</v>
       </c>
       <c r="H1588" t="n">
         <v>3015569</v>
@@ -46450,7 +46450,7 @@
         <v>14.25</v>
       </c>
       <c r="G1589" t="n">
-        <v>11.7473764419556</v>
+        <v>11.7473754882812</v>
       </c>
       <c r="H1589" t="n">
         <v>1722196</v>
@@ -46508,7 +46508,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G1591" t="n">
-        <v>11.7803506851196</v>
+        <v>11.7803516387939</v>
       </c>
       <c r="H1591" t="n">
         <v>1833250</v>
@@ -46537,7 +46537,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1592" t="n">
-        <v>11.8545446395874</v>
+        <v>11.8545455932617</v>
       </c>
       <c r="H1592" t="n">
         <v>1271450</v>
@@ -46595,7 +46595,7 @@
         <v>13.9650001525879</v>
       </c>
       <c r="G1594" t="n">
-        <v>11.5124282836914</v>
+        <v>11.5124292373657</v>
       </c>
       <c r="H1594" t="n">
         <v>2213985</v>
@@ -46624,7 +46624,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G1595" t="n">
-        <v>11.677303314209</v>
+        <v>11.6773023605347</v>
       </c>
       <c r="H1595" t="n">
         <v>1654206</v>
@@ -46653,7 +46653,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G1596" t="n">
-        <v>11.8627901077271</v>
+        <v>11.8627891540527</v>
       </c>
       <c r="H1596" t="n">
         <v>1215368</v>
@@ -46711,7 +46711,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G1598" t="n">
-        <v>11.5041837692261</v>
+        <v>11.5041847229004</v>
       </c>
       <c r="H1598" t="n">
         <v>2058742</v>
@@ -46740,7 +46740,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G1599" t="n">
-        <v>11.4670886993408</v>
+        <v>11.4670867919922</v>
       </c>
       <c r="H1599" t="n">
         <v>1451350</v>
@@ -46972,7 +46972,7 @@
         <v>13.1450004577637</v>
       </c>
       <c r="G1607" t="n">
-        <v>10.8364400863647</v>
+        <v>10.8364391326904</v>
       </c>
       <c r="H1607" t="n">
         <v>1533202</v>
@@ -47001,7 +47001,7 @@
         <v>13.1750001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>10.8611717224121</v>
+        <v>10.8611707687378</v>
       </c>
       <c r="H1608" t="n">
         <v>1382613</v>
@@ -47030,7 +47030,7 @@
         <v>13.3249998092651</v>
       </c>
       <c r="G1609" t="n">
-        <v>10.9848279953003</v>
+        <v>10.984827041626</v>
       </c>
       <c r="H1609" t="n">
         <v>1315335</v>
@@ -47146,7 +47146,7 @@
         <v>12.9549999237061</v>
       </c>
       <c r="G1613" t="n">
-        <v>10.6798067092896</v>
+        <v>10.6798076629639</v>
       </c>
       <c r="H1613" t="n">
         <v>1615033</v>
@@ -47262,7 +47262,7 @@
         <v>12.25</v>
       </c>
       <c r="G1617" t="n">
-        <v>10.0986223220825</v>
+        <v>10.0986213684082</v>
       </c>
       <c r="H1617" t="n">
         <v>2016295</v>
@@ -47349,7 +47349,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G1620" t="n">
-        <v>10.2181558609009</v>
+        <v>10.2181568145752</v>
       </c>
       <c r="H1620" t="n">
         <v>1077474</v>
@@ -47378,7 +47378,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1621" t="n">
-        <v>10.4283714294434</v>
+        <v>10.4283723831177</v>
       </c>
       <c r="H1621" t="n">
         <v>1833576</v>
@@ -47465,7 +47465,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1624" t="n">
-        <v>10.3706665039062</v>
+        <v>10.3706655502319</v>
       </c>
       <c r="H1624" t="n">
         <v>2233114</v>
@@ -80154,6 +80154,35 @@
         <v>1360726</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>21.3299999237061</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>20.9699993133545</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>21.1499996185303</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>1673341</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FBK.MI.xlsx
+++ b/data/FBK.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>5.15489482879639</v>
+        <v>5.15489387512207</v>
       </c>
       <c r="H2" t="n">
         <v>1120023</v>
@@ -456,7 +456,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>5.12352514266968</v>
+        <v>5.12352561950684</v>
       </c>
       <c r="H3" t="n">
         <v>1067026</v>
@@ -514,7 +514,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9492564201355</v>
+        <v>4.94925737380981</v>
       </c>
       <c r="H5" t="n">
         <v>1633938</v>
@@ -543,7 +543,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>5.06775951385498</v>
+        <v>5.06775903701782</v>
       </c>
       <c r="H6" t="n">
         <v>1754689</v>
@@ -601,7 +601,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>5.07124471664429</v>
+        <v>5.07124519348145</v>
       </c>
       <c r="H8" t="n">
         <v>1072008</v>
@@ -630,7 +630,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G9" t="n">
-        <v>5.11655473709106</v>
+        <v>5.11655569076538</v>
       </c>
       <c r="H9" t="n">
         <v>884030</v>
@@ -659,7 +659,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G10" t="n">
-        <v>5.00153732299805</v>
+        <v>5.00153684616089</v>
       </c>
       <c r="H10" t="n">
         <v>950617</v>
@@ -688,7 +688,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G11" t="n">
-        <v>4.85863590240479</v>
+        <v>4.85863542556763</v>
       </c>
       <c r="H11" t="n">
         <v>1145452</v>
@@ -775,7 +775,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G14" t="n">
-        <v>4.48569917678833</v>
+        <v>4.48569869995117</v>
       </c>
       <c r="H14" t="n">
         <v>1521693</v>
@@ -833,7 +833,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.78195714950562</v>
+        <v>4.78195762634277</v>
       </c>
       <c r="H16" t="n">
         <v>1223809</v>
@@ -862,7 +862,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G17" t="n">
-        <v>4.78195714950562</v>
+        <v>4.78195762634277</v>
       </c>
       <c r="H17" t="n">
         <v>801131</v>
@@ -891,7 +891,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G18" t="n">
-        <v>4.86560678482056</v>
+        <v>4.86560726165771</v>
       </c>
       <c r="H18" t="n">
         <v>810566</v>
@@ -949,7 +949,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>4.86212110519409</v>
+        <v>4.86212158203125</v>
       </c>
       <c r="H20" t="n">
         <v>774619</v>
@@ -1036,7 +1036,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G23" t="n">
-        <v>4.93531513214111</v>
+        <v>4.93531465530396</v>
       </c>
       <c r="H23" t="n">
         <v>890820</v>
@@ -1065,7 +1065,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G24" t="n">
-        <v>4.70876455307007</v>
+        <v>4.70876359939575</v>
       </c>
       <c r="H24" t="n">
         <v>2067827</v>
@@ -1094,7 +1094,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>4.61465835571289</v>
+        <v>4.61465883255005</v>
       </c>
       <c r="H25" t="n">
         <v>1487324</v>
@@ -1123,7 +1123,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>4.56586360931396</v>
+        <v>4.56586408615112</v>
       </c>
       <c r="H26" t="n">
         <v>807599</v>
@@ -1152,7 +1152,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>4.39856433868408</v>
+        <v>4.39856481552124</v>
       </c>
       <c r="H27" t="n">
         <v>1769827</v>
@@ -1181,7 +1181,7 @@
         <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>4.18246984481812</v>
+        <v>4.18247032165527</v>
       </c>
       <c r="H28" t="n">
         <v>4309103</v>
@@ -1210,7 +1210,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G29" t="n">
-        <v>4.29051780700684</v>
+        <v>4.29051733016968</v>
       </c>
       <c r="H29" t="n">
         <v>2729696</v>
@@ -1355,7 +1355,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>4.63557195663452</v>
+        <v>4.63557052612305</v>
       </c>
       <c r="H34" t="n">
         <v>2143900</v>
@@ -1413,7 +1413,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G36" t="n">
-        <v>4.53798007965088</v>
+        <v>4.53797960281372</v>
       </c>
       <c r="H36" t="n">
         <v>826666</v>
@@ -1442,7 +1442,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>4.65299844741821</v>
+        <v>4.6529974937439</v>
       </c>
       <c r="H37" t="n">
         <v>876495</v>
@@ -1500,7 +1500,7 @@
         <v>6.75</v>
       </c>
       <c r="G39" t="n">
-        <v>4.7052788734436</v>
+        <v>4.70527839660645</v>
       </c>
       <c r="H39" t="n">
         <v>1611257</v>
@@ -1587,7 +1587,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G42" t="n">
-        <v>4.9144024848938</v>
+        <v>4.91440296173096</v>
       </c>
       <c r="H42" t="n">
         <v>1229361</v>
@@ -1645,7 +1645,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>4.93531513214111</v>
+        <v>4.93531465530396</v>
       </c>
       <c r="H44" t="n">
         <v>1499459</v>
@@ -1674,7 +1674,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.97713947296143</v>
+        <v>4.97713899612427</v>
       </c>
       <c r="H45" t="n">
         <v>1200447</v>
@@ -1703,7 +1703,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>4.93531513214111</v>
+        <v>4.93531465530396</v>
       </c>
       <c r="H46" t="n">
         <v>964840</v>
@@ -1732,7 +1732,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G47" t="n">
-        <v>4.7715015411377</v>
+        <v>4.77150106430054</v>
       </c>
       <c r="H47" t="n">
         <v>1598235</v>
@@ -1761,7 +1761,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>4.66345453262329</v>
+        <v>4.66345357894897</v>
       </c>
       <c r="H48" t="n">
         <v>1329087</v>
@@ -1819,7 +1819,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G50" t="n">
-        <v>4.7715015411377</v>
+        <v>4.77150106430054</v>
       </c>
       <c r="H50" t="n">
         <v>1777322</v>
@@ -1848,7 +1848,7 @@
         <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>4.87954807281494</v>
+        <v>4.8795485496521</v>
       </c>
       <c r="H51" t="n">
         <v>1102638</v>
@@ -1877,7 +1877,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>4.90046119689941</v>
+        <v>4.90046167373657</v>
       </c>
       <c r="H52" t="n">
         <v>1406683</v>
@@ -1906,7 +1906,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>4.9144024848938</v>
+        <v>4.91440296173096</v>
       </c>
       <c r="H53" t="n">
         <v>813066</v>
@@ -1935,7 +1935,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>4.86212110519409</v>
+        <v>4.86212158203125</v>
       </c>
       <c r="H54" t="n">
         <v>720606</v>
@@ -1964,7 +1964,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>4.82029676437378</v>
+        <v>4.82029628753662</v>
       </c>
       <c r="H55" t="n">
         <v>882262</v>
@@ -1993,7 +1993,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>4.80635547637939</v>
+        <v>4.80635499954224</v>
       </c>
       <c r="H56" t="n">
         <v>2597623</v>
@@ -2022,7 +2022,7 @@
         <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>4.87954807281494</v>
+        <v>4.8795485496521</v>
       </c>
       <c r="H57" t="n">
         <v>1525752</v>
@@ -2051,7 +2051,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>4.93531513214111</v>
+        <v>4.93531465530396</v>
       </c>
       <c r="H58" t="n">
         <v>1306433</v>
@@ -2109,7 +2109,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>4.99805212020874</v>
+        <v>4.9980525970459</v>
       </c>
       <c r="H60" t="n">
         <v>1297200</v>
@@ -2138,7 +2138,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.03987693786621</v>
+        <v>5.03987646102905</v>
       </c>
       <c r="H61" t="n">
         <v>1384814</v>
@@ -2167,7 +2167,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>5.15838003158569</v>
+        <v>5.15837955474854</v>
       </c>
       <c r="H62" t="n">
         <v>3573879</v>
@@ -2196,7 +2196,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.15838003158569</v>
+        <v>5.15837955474854</v>
       </c>
       <c r="H63" t="n">
         <v>7332824</v>
@@ -2225,7 +2225,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>5.03987693786621</v>
+        <v>5.03987646102905</v>
       </c>
       <c r="H64" t="n">
         <v>2320617</v>
@@ -2283,7 +2283,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G66" t="n">
-        <v>4.83423852920532</v>
+        <v>4.83423900604248</v>
       </c>
       <c r="H66" t="n">
         <v>2726318</v>
@@ -2341,7 +2341,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>4.65299844741821</v>
+        <v>4.6529974937439</v>
       </c>
       <c r="H68" t="n">
         <v>1526742</v>
@@ -2370,7 +2370,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>4.76453065872192</v>
+        <v>4.76453113555908</v>
       </c>
       <c r="H69" t="n">
         <v>1610753</v>
@@ -2399,7 +2399,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>4.78892803192139</v>
+        <v>4.78892850875854</v>
       </c>
       <c r="H70" t="n">
         <v>1226391</v>
@@ -2457,7 +2457,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G72" t="n">
-        <v>4.83772373199463</v>
+        <v>4.83772325515747</v>
       </c>
       <c r="H72" t="n">
         <v>1303785</v>
@@ -2486,7 +2486,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G73" t="n">
-        <v>4.92485857009888</v>
+        <v>4.92485904693604</v>
       </c>
       <c r="H73" t="n">
         <v>1466819</v>
@@ -2544,7 +2544,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>5.1379246711731</v>
+        <v>5.13792419433594</v>
       </c>
       <c r="H75" t="n">
         <v>2392811</v>
@@ -2573,7 +2573,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G76" t="n">
-        <v>5.0403003692627</v>
+        <v>5.04029989242554</v>
       </c>
       <c r="H76" t="n">
         <v>1288181</v>
@@ -2602,7 +2602,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.08730459213257</v>
+        <v>5.08730411529541</v>
       </c>
       <c r="H77" t="n">
         <v>1355061</v>
@@ -2660,7 +2660,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.0366849899292</v>
+        <v>5.03668451309204</v>
       </c>
       <c r="H79" t="n">
         <v>661831</v>
@@ -2689,7 +2689,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G80" t="n">
-        <v>4.97521781921387</v>
+        <v>4.97521829605103</v>
       </c>
       <c r="H80" t="n">
         <v>902966</v>
@@ -2718,7 +2718,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G81" t="n">
-        <v>5.13430833816528</v>
+        <v>5.13430976867676</v>
       </c>
       <c r="H81" t="n">
         <v>1260119</v>
@@ -2892,7 +2892,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G87" t="n">
-        <v>4.91013526916504</v>
+        <v>4.91013479232788</v>
       </c>
       <c r="H87" t="n">
         <v>881025</v>
@@ -2921,7 +2921,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G88" t="n">
-        <v>4.78358507156372</v>
+        <v>4.7835841178894</v>
       </c>
       <c r="H88" t="n">
         <v>1186632</v>
@@ -3008,7 +3008,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G91" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H91" t="n">
         <v>1099290</v>
@@ -3037,7 +3037,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>4.58833646774292</v>
+        <v>4.58833599090576</v>
       </c>
       <c r="H92" t="n">
         <v>1279308</v>
@@ -3095,7 +3095,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G94" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H94" t="n">
         <v>860712</v>
@@ -3153,7 +3153,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G96" t="n">
-        <v>4.72211885452271</v>
+        <v>4.72211790084839</v>
       </c>
       <c r="H96" t="n">
         <v>1602098</v>
@@ -3269,7 +3269,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>4.56302738189697</v>
+        <v>4.56302690505981</v>
       </c>
       <c r="H100" t="n">
         <v>1433539</v>
@@ -3298,7 +3298,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>4.66426706314087</v>
+        <v>4.66426610946655</v>
       </c>
       <c r="H101" t="n">
         <v>1319208</v>
@@ -3327,7 +3327,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.73658084869385</v>
+        <v>4.73658180236816</v>
       </c>
       <c r="H102" t="n">
         <v>1604134</v>
@@ -3356,7 +3356,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>4.80166387557983</v>
+        <v>4.80166339874268</v>
       </c>
       <c r="H103" t="n">
         <v>1049093</v>
@@ -3385,7 +3385,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G104" t="n">
-        <v>4.79443216323853</v>
+        <v>4.79443264007568</v>
       </c>
       <c r="H104" t="n">
         <v>741031</v>
@@ -3414,7 +3414,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G105" t="n">
-        <v>4.83058834075928</v>
+        <v>4.83058929443359</v>
       </c>
       <c r="H105" t="n">
         <v>301436</v>
@@ -3443,7 +3443,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>4.74381256103516</v>
+        <v>4.743812084198</v>
       </c>
       <c r="H106" t="n">
         <v>723429</v>
@@ -3472,7 +3472,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G107" t="n">
-        <v>4.76912117004395</v>
+        <v>4.76912260055542</v>
       </c>
       <c r="H107" t="n">
         <v>591876</v>
@@ -3501,7 +3501,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>4.78720045089722</v>
+        <v>4.78720092773438</v>
       </c>
       <c r="H108" t="n">
         <v>846712</v>
@@ -3530,7 +3530,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>4.67511367797852</v>
+        <v>4.67511415481567</v>
       </c>
       <c r="H109" t="n">
         <v>863571</v>
@@ -3559,7 +3559,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>4.74381256103516</v>
+        <v>4.743812084198</v>
       </c>
       <c r="H110" t="n">
         <v>748078</v>
@@ -3588,7 +3588,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G111" t="n">
-        <v>4.78358507156372</v>
+        <v>4.7835841178894</v>
       </c>
       <c r="H111" t="n">
         <v>765813</v>
@@ -3675,7 +3675,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G114" t="n">
-        <v>4.45094013214111</v>
+        <v>4.45093965530396</v>
       </c>
       <c r="H114" t="n">
         <v>1314856</v>
@@ -3820,7 +3820,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G119" t="n">
-        <v>4.40031957626343</v>
+        <v>4.40032005310059</v>
       </c>
       <c r="H119" t="n">
         <v>1255915</v>
@@ -3849,7 +3849,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>4.57748937606812</v>
+        <v>4.57748985290527</v>
       </c>
       <c r="H120" t="n">
         <v>1143567</v>
@@ -3878,7 +3878,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.55579471588135</v>
+        <v>4.55579566955566</v>
       </c>
       <c r="H121" t="n">
         <v>919785</v>
@@ -3936,7 +3936,7 @@
         <v>6.625</v>
       </c>
       <c r="G123" t="n">
-        <v>4.79081678390503</v>
+        <v>4.79081630706787</v>
       </c>
       <c r="H123" t="n">
         <v>2174412</v>
@@ -3965,7 +3965,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G124" t="n">
-        <v>4.32438945770264</v>
+        <v>4.32438993453979</v>
       </c>
       <c r="H124" t="n">
         <v>3285007</v>
@@ -3994,7 +3994,7 @@
         <v>5.5</v>
       </c>
       <c r="G125" t="n">
-        <v>3.97728157043457</v>
+        <v>3.97728204727173</v>
       </c>
       <c r="H125" t="n">
         <v>3230849</v>
@@ -4023,7 +4023,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>4.23399686813354</v>
+        <v>4.23399639129639</v>
       </c>
       <c r="H126" t="n">
         <v>1838104</v>
@@ -4081,7 +4081,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G128" t="n">
-        <v>4.23038053512573</v>
+        <v>4.23038148880005</v>
       </c>
       <c r="H128" t="n">
         <v>1666098</v>
@@ -4139,7 +4139,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02066993713379</v>
       </c>
       <c r="H130" t="n">
         <v>1421546</v>
@@ -4168,7 +4168,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G131" t="n">
-        <v>3.94835567474365</v>
+        <v>3.94835615158081</v>
       </c>
       <c r="H131" t="n">
         <v>845896</v>
@@ -4197,7 +4197,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73141312599182</v>
+        <v>3.73141360282898</v>
       </c>
       <c r="H132" t="n">
         <v>3993579</v>
@@ -4255,7 +4255,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G134" t="n">
-        <v>4.10744762420654</v>
+        <v>4.10744714736938</v>
       </c>
       <c r="H134" t="n">
         <v>2661785</v>
@@ -4284,7 +4284,7 @@
         <v>5.75</v>
       </c>
       <c r="G135" t="n">
-        <v>4.15806674957275</v>
+        <v>4.15806722640991</v>
       </c>
       <c r="H135" t="n">
         <v>1373702</v>
@@ -4313,7 +4313,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G136" t="n">
-        <v>4.10744762420654</v>
+        <v>4.10744714736938</v>
       </c>
       <c r="H136" t="n">
         <v>35821264</v>
@@ -4342,7 +4342,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>4.03513288497925</v>
+        <v>4.03513336181641</v>
       </c>
       <c r="H137" t="n">
         <v>3708802</v>
@@ -4371,7 +4371,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G138" t="n">
-        <v>4.10744762420654</v>
+        <v>4.10744714736938</v>
       </c>
       <c r="H138" t="n">
         <v>5373931</v>
@@ -4429,7 +4429,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G140" t="n">
-        <v>4.07852172851562</v>
+        <v>4.07852125167847</v>
       </c>
       <c r="H140" t="n">
         <v>2842855</v>
@@ -4458,7 +4458,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G141" t="n">
-        <v>4.07852172851562</v>
+        <v>4.07852125167847</v>
       </c>
       <c r="H141" t="n">
         <v>2956609</v>
@@ -4487,7 +4487,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>4.1508355140686</v>
+        <v>4.15083599090576</v>
       </c>
       <c r="H142" t="n">
         <v>2137222</v>
@@ -4516,7 +4516,7 @@
         <v>5.75</v>
       </c>
       <c r="G143" t="n">
-        <v>4.15806674957275</v>
+        <v>4.15806722640991</v>
       </c>
       <c r="H143" t="n">
         <v>1184281</v>
@@ -4545,7 +4545,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G144" t="n">
-        <v>4.09298419952393</v>
+        <v>4.09298372268677</v>
       </c>
       <c r="H144" t="n">
         <v>1612665</v>
@@ -4574,7 +4574,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G145" t="n">
-        <v>4.08936977386475</v>
+        <v>4.08936929702759</v>
       </c>
       <c r="H145" t="n">
         <v>1196054</v>
@@ -4661,7 +4661,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.78564834594727</v>
+        <v>3.78564977645874</v>
       </c>
       <c r="H148" t="n">
         <v>3813192</v>
@@ -4748,7 +4748,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G151" t="n">
-        <v>3.69525647163391</v>
+        <v>3.69525623321533</v>
       </c>
       <c r="H151" t="n">
         <v>2847800</v>
@@ -4777,7 +4777,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G152" t="n">
-        <v>3.69525647163391</v>
+        <v>3.69525623321533</v>
       </c>
       <c r="H152" t="n">
         <v>2463690</v>
@@ -4806,7 +4806,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>3.79288053512573</v>
+        <v>3.79288029670715</v>
       </c>
       <c r="H153" t="n">
         <v>2240614</v>
@@ -4835,7 +4835,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>3.82903742790222</v>
+        <v>3.82903718948364</v>
       </c>
       <c r="H154" t="n">
         <v>1283102</v>
@@ -4864,7 +4864,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G155" t="n">
-        <v>3.7892644405365</v>
+        <v>3.78926396369934</v>
       </c>
       <c r="H155" t="n">
         <v>1669619</v>
@@ -4922,7 +4922,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G157" t="n">
-        <v>3.81095886230469</v>
+        <v>3.81095957756042</v>
       </c>
       <c r="H157" t="n">
         <v>1021306</v>
@@ -4951,7 +4951,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G158" t="n">
-        <v>3.80011296272278</v>
+        <v>3.8001115322113</v>
       </c>
       <c r="H158" t="n">
         <v>708270</v>
@@ -5009,7 +5009,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>3.79288053512573</v>
+        <v>3.79288029670715</v>
       </c>
       <c r="H160" t="n">
         <v>1368032</v>
@@ -5067,7 +5067,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G162" t="n">
-        <v>3.68440890312195</v>
+        <v>3.68440914154053</v>
       </c>
       <c r="H162" t="n">
         <v>1350688</v>
@@ -5096,7 +5096,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.63378930091858</v>
+        <v>3.63378882408142</v>
       </c>
       <c r="H163" t="n">
         <v>2620713</v>
@@ -5125,7 +5125,7 @@
         <v>5</v>
       </c>
       <c r="G164" t="n">
-        <v>3.61571073532104</v>
+        <v>3.61571025848389</v>
       </c>
       <c r="H164" t="n">
         <v>1813564</v>
@@ -5183,7 +5183,7 @@
         <v>5.5</v>
       </c>
       <c r="G166" t="n">
-        <v>3.97728157043457</v>
+        <v>3.97728204727173</v>
       </c>
       <c r="H166" t="n">
         <v>3532873</v>
@@ -5212,7 +5212,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>3.91942977905273</v>
+        <v>3.91943025588989</v>
       </c>
       <c r="H167" t="n">
         <v>1361661</v>
@@ -5386,7 +5386,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G173" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H173" t="n">
         <v>1863318</v>
@@ -5415,7 +5415,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>3.94835567474365</v>
+        <v>3.94835615158081</v>
       </c>
       <c r="H174" t="n">
         <v>1218944</v>
@@ -5444,7 +5444,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>3.90496778488159</v>
+        <v>3.90496730804443</v>
       </c>
       <c r="H175" t="n">
         <v>796583</v>
@@ -5473,7 +5473,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>3.92304635047913</v>
+        <v>3.92304587364197</v>
       </c>
       <c r="H176" t="n">
         <v>1987450</v>
@@ -5502,7 +5502,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.88327264785767</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H177" t="n">
         <v>2745965</v>
@@ -5531,7 +5531,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88327264785767</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H178" t="n">
         <v>1872241</v>
@@ -5560,7 +5560,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>3.76757049560547</v>
+        <v>3.76757073402405</v>
       </c>
       <c r="H179" t="n">
         <v>1730619</v>
@@ -5618,7 +5618,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G181" t="n">
-        <v>3.80011296272278</v>
+        <v>3.8001115322113</v>
       </c>
       <c r="H181" t="n">
         <v>1500707</v>
@@ -5647,7 +5647,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G182" t="n">
-        <v>3.78564834594727</v>
+        <v>3.78564977645874</v>
       </c>
       <c r="H182" t="n">
         <v>1349515</v>
@@ -5676,7 +5676,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>3.67356204986572</v>
+        <v>3.67356181144714</v>
       </c>
       <c r="H183" t="n">
         <v>1411142</v>
@@ -5705,7 +5705,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.76033902168274</v>
+        <v>3.76033926010132</v>
       </c>
       <c r="H184" t="n">
         <v>1171746</v>
@@ -5734,7 +5734,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G185" t="n">
-        <v>3.75672292709351</v>
+        <v>3.75672316551208</v>
       </c>
       <c r="H185" t="n">
         <v>1626816</v>
@@ -5763,7 +5763,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.76757049560547</v>
+        <v>3.76757073402405</v>
       </c>
       <c r="H186" t="n">
         <v>1095288</v>
@@ -5821,7 +5821,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G188" t="n">
-        <v>3.7458758354187</v>
+        <v>3.74587655067444</v>
       </c>
       <c r="H188" t="n">
         <v>1474820</v>
@@ -5850,7 +5850,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66994643211365</v>
+        <v>3.66994619369507</v>
       </c>
       <c r="H189" t="n">
         <v>2099802</v>
@@ -5908,7 +5908,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G191" t="n">
-        <v>3.75310730934143</v>
+        <v>3.75310707092285</v>
       </c>
       <c r="H191" t="n">
         <v>1760882</v>
@@ -5937,7 +5937,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G192" t="n">
-        <v>3.73864507675171</v>
+        <v>3.73864459991455</v>
       </c>
       <c r="H192" t="n">
         <v>1453013</v>
@@ -5966,7 +5966,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G193" t="n">
-        <v>3.7277979850769</v>
+        <v>3.72779774665833</v>
       </c>
       <c r="H193" t="n">
         <v>2119783</v>
@@ -5995,7 +5995,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.70971870422363</v>
+        <v>3.70971918106079</v>
       </c>
       <c r="H194" t="n">
         <v>1549911</v>
@@ -6053,7 +6053,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G196" t="n">
-        <v>3.7458758354187</v>
+        <v>3.74587655067444</v>
       </c>
       <c r="H196" t="n">
         <v>1713471</v>
@@ -6082,7 +6082,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G197" t="n">
-        <v>3.73141312599182</v>
+        <v>3.73141360282898</v>
       </c>
       <c r="H197" t="n">
         <v>1836123</v>
@@ -6111,7 +6111,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>3.64825201034546</v>
+        <v>3.64825248718262</v>
       </c>
       <c r="H198" t="n">
         <v>2133006</v>
@@ -6140,7 +6140,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.6229419708252</v>
+        <v>3.62294220924377</v>
       </c>
       <c r="H199" t="n">
         <v>2626540</v>
@@ -6198,7 +6198,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G201" t="n">
-        <v>3.46240448951721</v>
+        <v>3.46240496635437</v>
       </c>
       <c r="H201" t="n">
         <v>2854684</v>
@@ -6227,7 +6227,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G202" t="n">
-        <v>3.65548300743103</v>
+        <v>3.65548372268677</v>
       </c>
       <c r="H202" t="n">
         <v>30588371</v>
@@ -6256,7 +6256,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>3.73864507675171</v>
+        <v>3.73864459991455</v>
       </c>
       <c r="H203" t="n">
         <v>6162802</v>
@@ -6285,7 +6285,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>3.75672292709351</v>
+        <v>3.75672316551208</v>
       </c>
       <c r="H204" t="n">
         <v>5488683</v>
@@ -6343,7 +6343,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G206" t="n">
-        <v>3.75672292709351</v>
+        <v>3.75672316551208</v>
       </c>
       <c r="H206" t="n">
         <v>2084886</v>
@@ -6372,7 +6372,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>3.81457424163818</v>
+        <v>3.81457448005676</v>
       </c>
       <c r="H207" t="n">
         <v>4854357</v>
@@ -6401,7 +6401,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G208" t="n">
-        <v>3.83265352249146</v>
+        <v>3.8326530456543</v>
       </c>
       <c r="H208" t="n">
         <v>3501461</v>
@@ -6430,7 +6430,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>3.87604236602783</v>
+        <v>3.87604188919067</v>
       </c>
       <c r="H209" t="n">
         <v>2199321</v>
@@ -6459,7 +6459,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G210" t="n">
-        <v>3.81819081306458</v>
+        <v>3.818190574646</v>
       </c>
       <c r="H210" t="n">
         <v>2913261</v>
@@ -6488,7 +6488,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>3.86881065368652</v>
+        <v>3.86881017684937</v>
       </c>
       <c r="H211" t="n">
         <v>2192359</v>
@@ -6517,7 +6517,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.93750929832458</v>
+        <v>3.93750977516174</v>
       </c>
       <c r="H212" t="n">
         <v>2143095</v>
@@ -6604,7 +6604,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>3.78203320503235</v>
+        <v>3.78203344345093</v>
       </c>
       <c r="H215" t="n">
         <v>1276554</v>
@@ -6662,7 +6662,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G217" t="n">
-        <v>3.69164037704468</v>
+        <v>3.69164061546326</v>
       </c>
       <c r="H217" t="n">
         <v>2605202</v>
@@ -6691,7 +6691,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.64463686943054</v>
+        <v>3.6446361541748</v>
       </c>
       <c r="H218" t="n">
         <v>1953060</v>
@@ -6720,7 +6720,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G219" t="n">
-        <v>3.66633081436157</v>
+        <v>3.66633057594299</v>
       </c>
       <c r="H219" t="n">
         <v>1484452</v>
@@ -6749,7 +6749,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>3.64463686943054</v>
+        <v>3.6446361541748</v>
       </c>
       <c r="H220" t="n">
         <v>2407083</v>
@@ -6778,7 +6778,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>3.67356204986572</v>
+        <v>3.67356181144714</v>
       </c>
       <c r="H221" t="n">
         <v>3276707</v>
@@ -6836,7 +6836,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G223" t="n">
-        <v>3.65186786651611</v>
+        <v>3.65186762809753</v>
       </c>
       <c r="H223" t="n">
         <v>2767052</v>
@@ -6865,7 +6865,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G224" t="n">
-        <v>3.61281800270081</v>
+        <v>3.61281752586365</v>
       </c>
       <c r="H224" t="n">
         <v>2001893</v>
@@ -6894,7 +6894,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G225" t="n">
-        <v>3.5969090461731</v>
+        <v>3.59690880775452</v>
       </c>
       <c r="H225" t="n">
         <v>2042948</v>
@@ -6923,7 +6923,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G226" t="n">
-        <v>3.50579333305359</v>
+        <v>3.50579309463501</v>
       </c>
       <c r="H226" t="n">
         <v>2943006</v>
@@ -6952,7 +6952,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>3.47108244895935</v>
+        <v>3.47108221054077</v>
       </c>
       <c r="H227" t="n">
         <v>2432187</v>
@@ -7039,7 +7039,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G230" t="n">
-        <v>3.40744566917419</v>
+        <v>3.40744590759277</v>
       </c>
       <c r="H230" t="n">
         <v>2323535</v>
@@ -7097,7 +7097,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G232" t="n">
-        <v>3.42480134963989</v>
+        <v>3.42480111122131</v>
       </c>
       <c r="H232" t="n">
         <v>1722858</v>
@@ -7155,7 +7155,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G234" t="n">
-        <v>3.34236288070679</v>
+        <v>3.34236311912537</v>
       </c>
       <c r="H234" t="n">
         <v>2323743</v>
@@ -7184,7 +7184,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G235" t="n">
-        <v>3.45517325401306</v>
+        <v>3.45517301559448</v>
       </c>
       <c r="H235" t="n">
         <v>2082364</v>
@@ -7213,7 +7213,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G236" t="n">
-        <v>3.52893352508545</v>
+        <v>3.52893400192261</v>
       </c>
       <c r="H236" t="n">
         <v>6107353</v>
@@ -7271,7 +7271,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53327250480652</v>
+        <v>3.53327202796936</v>
       </c>
       <c r="H238" t="n">
         <v>4750178</v>
@@ -7358,7 +7358,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.64463686943054</v>
+        <v>3.6446361541748</v>
       </c>
       <c r="H241" t="n">
         <v>4615423</v>
@@ -7387,7 +7387,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>3.76033902168274</v>
+        <v>3.76033926010132</v>
       </c>
       <c r="H242" t="n">
         <v>3062648</v>
@@ -7416,7 +7416,7 @@
         <v>5.125</v>
       </c>
       <c r="G243" t="n">
-        <v>3.70610404014587</v>
+        <v>3.70610356330872</v>
       </c>
       <c r="H243" t="n">
         <v>2409471</v>
@@ -7445,7 +7445,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G244" t="n">
-        <v>3.66633081436157</v>
+        <v>3.66633057594299</v>
       </c>
       <c r="H244" t="n">
         <v>2525526</v>
@@ -7474,7 +7474,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.94835567474365</v>
+        <v>3.94835615158081</v>
       </c>
       <c r="H245" t="n">
         <v>6476581</v>
@@ -7503,7 +7503,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>3.92304635047913</v>
+        <v>3.92304587364197</v>
       </c>
       <c r="H246" t="n">
         <v>2841246</v>
@@ -7532,7 +7532,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G247" t="n">
-        <v>3.9881284236908</v>
+        <v>3.98812890052795</v>
       </c>
       <c r="H247" t="n">
         <v>3264617</v>
@@ -7561,7 +7561,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>3.95197176933289</v>
+        <v>3.95197129249573</v>
       </c>
       <c r="H248" t="n">
         <v>2687315</v>
@@ -7590,7 +7590,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>3.86157894134521</v>
+        <v>3.86157941818237</v>
       </c>
       <c r="H249" t="n">
         <v>1875617</v>
@@ -7735,7 +7735,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G254" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H254" t="n">
         <v>900511</v>
@@ -7764,7 +7764,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>3.86881065368652</v>
+        <v>3.86881017684937</v>
       </c>
       <c r="H255" t="n">
         <v>1417418</v>
@@ -7793,7 +7793,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>3.88327264785767</v>
+        <v>3.88327312469482</v>
       </c>
       <c r="H256" t="n">
         <v>989625</v>
@@ -7851,7 +7851,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H258" t="n">
         <v>1572602</v>
@@ -7880,7 +7880,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>3.93750929832458</v>
+        <v>3.93750977516174</v>
       </c>
       <c r="H259" t="n">
         <v>2238448</v>
@@ -7909,7 +7909,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9266619682312</v>
+        <v>3.92666101455688</v>
       </c>
       <c r="H260" t="n">
         <v>2293252</v>
@@ -7938,7 +7938,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>4.01343870162964</v>
+        <v>4.0134391784668</v>
       </c>
       <c r="H261" t="n">
         <v>3965538</v>
@@ -7967,7 +7967,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>3.99897575378418</v>
+        <v>3.99897623062134</v>
       </c>
       <c r="H262" t="n">
         <v>2114774</v>
@@ -7996,7 +7996,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>3.92304635047913</v>
+        <v>3.92304587364197</v>
       </c>
       <c r="H263" t="n">
         <v>1907680</v>
@@ -8025,7 +8025,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H264" t="n">
         <v>1813183</v>
@@ -8083,7 +8083,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>3.90496778488159</v>
+        <v>3.90496730804443</v>
       </c>
       <c r="H266" t="n">
         <v>1253458</v>
@@ -8170,7 +8170,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G269" t="n">
-        <v>3.9266619682312</v>
+        <v>3.92666101455688</v>
       </c>
       <c r="H269" t="n">
         <v>990913</v>
@@ -8228,7 +8228,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G271" t="n">
-        <v>4.02790212631226</v>
+        <v>4.0279016494751</v>
       </c>
       <c r="H271" t="n">
         <v>2977261</v>
@@ -8286,7 +8286,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G273" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H273" t="n">
         <v>2818868</v>
@@ -8315,7 +8315,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02066993713379</v>
       </c>
       <c r="H274" t="n">
         <v>2581220</v>
@@ -8344,7 +8344,7 @@
         <v>5.75</v>
       </c>
       <c r="G275" t="n">
-        <v>4.15806674957275</v>
+        <v>4.15806722640991</v>
       </c>
       <c r="H275" t="n">
         <v>3622231</v>
@@ -8373,7 +8373,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>4.08213663101196</v>
+        <v>4.0821361541748</v>
       </c>
       <c r="H276" t="n">
         <v>2705677</v>
@@ -8431,7 +8431,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>4.02067041397095</v>
+        <v>4.02066993713379</v>
       </c>
       <c r="H278" t="n">
         <v>2796328</v>
@@ -8460,7 +8460,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G279" t="n">
-        <v>3.97004985809326</v>
+        <v>3.97005033493042</v>
       </c>
       <c r="H279" t="n">
         <v>2453406</v>
@@ -8518,7 +8518,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G281" t="n">
-        <v>4.00620746612549</v>
+        <v>4.00620698928833</v>
       </c>
       <c r="H281" t="n">
         <v>2732122</v>
@@ -8605,7 +8605,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G284" t="n">
-        <v>3.9266619682312</v>
+        <v>3.92666101455688</v>
       </c>
       <c r="H284" t="n">
         <v>2061382</v>
@@ -8663,7 +8663,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>3.9736659526825</v>
+        <v>3.97366642951965</v>
       </c>
       <c r="H286" t="n">
         <v>1319086</v>
@@ -8692,7 +8692,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G287" t="n">
-        <v>3.91219806671143</v>
+        <v>3.91219902038574</v>
       </c>
       <c r="H287" t="n">
         <v>1173142</v>
@@ -8808,7 +8808,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G291" t="n">
-        <v>3.9266619682312</v>
+        <v>3.92666101455688</v>
       </c>
       <c r="H291" t="n">
         <v>1485016</v>
@@ -8837,7 +8837,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G292" t="n">
-        <v>3.91942977905273</v>
+        <v>3.91943025588989</v>
       </c>
       <c r="H292" t="n">
         <v>2376919</v>
@@ -8895,7 +8895,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G294" t="n">
-        <v>3.91942977905273</v>
+        <v>3.91943025588989</v>
       </c>
       <c r="H294" t="n">
         <v>1953366</v>
@@ -8953,7 +8953,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.90496778488159</v>
+        <v>3.90496730804443</v>
       </c>
       <c r="H296" t="n">
         <v>2215104</v>
@@ -8982,7 +8982,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G297" t="n">
-        <v>3.87604236602783</v>
+        <v>3.87604188919067</v>
       </c>
       <c r="H297" t="n">
         <v>2992561</v>
@@ -9011,7 +9011,7 @@
         <v>5.375</v>
       </c>
       <c r="G298" t="n">
-        <v>3.88688826560974</v>
+        <v>3.8868887424469</v>
       </c>
       <c r="H298" t="n">
         <v>6414207</v>
@@ -9040,7 +9040,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>3.90496778488159</v>
+        <v>3.90496730804443</v>
       </c>
       <c r="H299" t="n">
         <v>2120956</v>
@@ -9069,7 +9069,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G300" t="n">
-        <v>3.98089718818665</v>
+        <v>3.9808976650238</v>
       </c>
       <c r="H300" t="n">
         <v>2265275</v>
@@ -9098,7 +9098,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>4.03513288497925</v>
+        <v>4.03513336181641</v>
       </c>
       <c r="H301" t="n">
         <v>3496797</v>
@@ -9156,7 +9156,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>4.14360523223877</v>
+        <v>4.14360380172729</v>
       </c>
       <c r="H303" t="n">
         <v>2285686</v>
@@ -9185,7 +9185,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G304" t="n">
-        <v>4.1508355140686</v>
+        <v>4.15083599090576</v>
       </c>
       <c r="H304" t="n">
         <v>1601707</v>
@@ -9243,7 +9243,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>4.23038053512573</v>
+        <v>4.23038148880005</v>
       </c>
       <c r="H306" t="n">
         <v>2069014</v>
@@ -9272,7 +9272,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30269622802734</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H307" t="n">
         <v>2406004</v>
@@ -9301,7 +9301,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G308" t="n">
-        <v>4.30269622802734</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H308" t="n">
         <v>1384487</v>
@@ -9330,7 +9330,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>4.28100156784058</v>
+        <v>4.28100109100342</v>
       </c>
       <c r="H309" t="n">
         <v>1381742</v>
@@ -9359,7 +9359,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>4.30269622802734</v>
+        <v>4.30269575119019</v>
       </c>
       <c r="H310" t="n">
         <v>1166357</v>
@@ -9417,7 +9417,7 @@
         <v>6.25</v>
       </c>
       <c r="G312" t="n">
-        <v>4.51963758468628</v>
+        <v>4.51963806152344</v>
       </c>
       <c r="H312" t="n">
         <v>11461676</v>
@@ -9504,7 +9504,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.49794340133667</v>
+        <v>4.49794387817383</v>
       </c>
       <c r="H315" t="n">
         <v>1899424</v>
@@ -9533,7 +9533,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G316" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H316" t="n">
         <v>2691680</v>
@@ -9562,7 +9562,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G317" t="n">
-        <v>4.66426706314087</v>
+        <v>4.66426610946655</v>
       </c>
       <c r="H317" t="n">
         <v>2928708</v>
@@ -9591,7 +9591,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.6317253112793</v>
+        <v>4.63172483444214</v>
       </c>
       <c r="H318" t="n">
         <v>1809873</v>
@@ -9649,7 +9649,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G320" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H320" t="n">
         <v>2065719</v>
@@ -9678,7 +9678,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G321" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H321" t="n">
         <v>1808708</v>
@@ -9707,7 +9707,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H322" t="n">
         <v>1061389</v>
@@ -9765,7 +9765,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G324" t="n">
-        <v>4.62087821960449</v>
+        <v>4.62087774276733</v>
       </c>
       <c r="H324" t="n">
         <v>2138251</v>
@@ -9794,7 +9794,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.55217981338501</v>
+        <v>4.55217885971069</v>
       </c>
       <c r="H325" t="n">
         <v>2599522</v>
@@ -9823,7 +9823,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G326" t="n">
-        <v>4.55217981338501</v>
+        <v>4.55217885971069</v>
       </c>
       <c r="H326" t="n">
         <v>2329372</v>
@@ -9852,7 +9852,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>4.55579471588135</v>
+        <v>4.55579566955566</v>
       </c>
       <c r="H327" t="n">
         <v>2299424</v>
@@ -9881,7 +9881,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G328" t="n">
-        <v>4.61364650726318</v>
+        <v>4.61364698410034</v>
       </c>
       <c r="H328" t="n">
         <v>2087223</v>
@@ -10026,7 +10026,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G333" t="n">
-        <v>4.72211885452271</v>
+        <v>4.72211790084839</v>
       </c>
       <c r="H333" t="n">
         <v>1861825</v>
@@ -10055,7 +10055,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G334" t="n">
-        <v>4.6570348739624</v>
+        <v>4.65703582763672</v>
       </c>
       <c r="H334" t="n">
         <v>3347408</v>
@@ -10113,7 +10113,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G336" t="n">
-        <v>4.88285064697266</v>
+        <v>4.88285112380981</v>
       </c>
       <c r="H336" t="n">
         <v>4467194</v>
@@ -10142,7 +10142,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>4.94714879989624</v>
+        <v>4.94714784622192</v>
       </c>
       <c r="H337" t="n">
         <v>2939903</v>
@@ -10171,7 +10171,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G338" t="n">
-        <v>4.91310787200928</v>
+        <v>4.91310882568359</v>
       </c>
       <c r="H338" t="n">
         <v>1812525</v>
@@ -10200,7 +10200,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88663291931152</v>
+        <v>4.88663339614868</v>
       </c>
       <c r="H339" t="n">
         <v>1167519</v>
@@ -10258,7 +10258,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G341" t="n">
-        <v>4.97740650177002</v>
+        <v>4.97740602493286</v>
       </c>
       <c r="H341" t="n">
         <v>1985770</v>
@@ -10287,7 +10287,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>4.91310787200928</v>
+        <v>4.91310882568359</v>
       </c>
       <c r="H342" t="n">
         <v>1543013</v>
@@ -10316,7 +10316,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>5.04170417785645</v>
+        <v>5.0417046546936</v>
       </c>
       <c r="H343" t="n">
         <v>3358984</v>
@@ -10345,7 +10345,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13626050949097</v>
+        <v>5.13626003265381</v>
       </c>
       <c r="H344" t="n">
         <v>2148000</v>
@@ -10374,7 +10374,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.14382410049438</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H345" t="n">
         <v>2913934</v>
@@ -10432,7 +10432,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>5.14382410049438</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H347" t="n">
         <v>2197856</v>
@@ -10461,7 +10461,7 @@
         <v>6.625</v>
       </c>
       <c r="G348" t="n">
-        <v>5.01144599914551</v>
+        <v>5.01144695281982</v>
       </c>
       <c r="H348" t="n">
         <v>2180864</v>
@@ -10490,7 +10490,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>5.08709049224854</v>
+        <v>5.08709096908569</v>
       </c>
       <c r="H349" t="n">
         <v>2037566</v>
@@ -10519,7 +10519,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G350" t="n">
-        <v>5.00766372680664</v>
+        <v>5.0076642036438</v>
       </c>
       <c r="H350" t="n">
         <v>2559502</v>
@@ -10548,7 +10548,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>5.03035736083984</v>
+        <v>5.030357837677</v>
       </c>
       <c r="H351" t="n">
         <v>2299129</v>
@@ -10606,7 +10606,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>4.96606016159058</v>
+        <v>4.96605968475342</v>
       </c>
       <c r="H353" t="n">
         <v>2522783</v>
@@ -10664,7 +10664,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>5.07196187973022</v>
+        <v>5.07196092605591</v>
       </c>
       <c r="H355" t="n">
         <v>1068280</v>
@@ -10693,7 +10693,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>5.13626050949097</v>
+        <v>5.13626003265381</v>
       </c>
       <c r="H356" t="n">
         <v>1253175</v>
@@ -10722,7 +10722,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17030000686646</v>
+        <v>5.1702995300293</v>
       </c>
       <c r="H357" t="n">
         <v>1872012</v>
@@ -10751,7 +10751,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>5.15138864517212</v>
+        <v>5.15138912200928</v>
       </c>
       <c r="H358" t="n">
         <v>1066471</v>
@@ -10780,7 +10780,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G359" t="n">
-        <v>5.18542814254761</v>
+        <v>5.18542861938477</v>
       </c>
       <c r="H359" t="n">
         <v>1621300</v>
@@ -10954,7 +10954,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.0568323135376</v>
+        <v>5.05683326721191</v>
       </c>
       <c r="H365" t="n">
         <v>857551</v>
@@ -10983,7 +10983,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17408132553101</v>
+        <v>5.17408180236816</v>
       </c>
       <c r="H366" t="n">
         <v>1623704</v>
@@ -11012,7 +11012,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>5.23837995529175</v>
+        <v>5.23838090896606</v>
       </c>
       <c r="H367" t="n">
         <v>2803808</v>
@@ -11041,7 +11041,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>5.40857934951782</v>
+        <v>5.40858030319214</v>
       </c>
       <c r="H368" t="n">
         <v>3520150</v>
@@ -11099,7 +11099,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G370" t="n">
-        <v>5.33671808242798</v>
+        <v>5.33671760559082</v>
       </c>
       <c r="H370" t="n">
         <v>1720213</v>
@@ -11128,7 +11128,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>5.42370891571045</v>
+        <v>5.42370796203613</v>
       </c>
       <c r="H371" t="n">
         <v>1836918</v>
@@ -11157,7 +11157,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G372" t="n">
-        <v>5.41614389419556</v>
+        <v>5.41614437103271</v>
       </c>
       <c r="H372" t="n">
         <v>2245553</v>
@@ -11215,7 +11215,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.33293533325195</v>
+        <v>5.33293581008911</v>
       </c>
       <c r="H374" t="n">
         <v>2246270</v>
@@ -11244,7 +11244,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G375" t="n">
-        <v>5.41236209869385</v>
+        <v>5.41236257553101</v>
       </c>
       <c r="H375" t="n">
         <v>1237025</v>
@@ -11273,7 +11273,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.34806394577026</v>
+        <v>5.34806442260742</v>
       </c>
       <c r="H376" t="n">
         <v>1253710</v>
@@ -11302,7 +11302,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G377" t="n">
-        <v>5.29889535903931</v>
+        <v>5.29889488220215</v>
       </c>
       <c r="H377" t="n">
         <v>1760770</v>
@@ -11331,7 +11331,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G378" t="n">
-        <v>5.21190404891968</v>
+        <v>5.21190357208252</v>
       </c>
       <c r="H378" t="n">
         <v>2634505</v>
@@ -11360,7 +11360,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17030000686646</v>
+        <v>5.1702995300293</v>
       </c>
       <c r="H379" t="n">
         <v>1727362</v>
@@ -11389,7 +11389,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17030000686646</v>
+        <v>5.1702995300293</v>
       </c>
       <c r="H380" t="n">
         <v>1653074</v>
@@ -11418,7 +11418,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.14382410049438</v>
+        <v>5.1438250541687</v>
       </c>
       <c r="H381" t="n">
         <v>1459321</v>
@@ -11447,7 +11447,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G382" t="n">
-        <v>5.33671808242798</v>
+        <v>5.33671760559082</v>
       </c>
       <c r="H382" t="n">
         <v>3777893</v>
@@ -11476,7 +11476,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G383" t="n">
-        <v>5.31780624389648</v>
+        <v>5.31780576705933</v>
       </c>
       <c r="H383" t="n">
         <v>3176819</v>
@@ -11505,7 +11505,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G384" t="n">
-        <v>5.21190404891968</v>
+        <v>5.21190357208252</v>
       </c>
       <c r="H384" t="n">
         <v>2968004</v>
@@ -11534,7 +11534,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G385" t="n">
-        <v>5.40479755401611</v>
+        <v>5.40479803085327</v>
       </c>
       <c r="H385" t="n">
         <v>2375031</v>
@@ -11563,7 +11563,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G386" t="n">
-        <v>5.48044204711914</v>
+        <v>5.48044157028198</v>
       </c>
       <c r="H386" t="n">
         <v>2718690</v>
@@ -11592,7 +11592,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>5.54474020004272</v>
+        <v>5.54473972320557</v>
       </c>
       <c r="H387" t="n">
         <v>3228470</v>
@@ -11621,7 +11621,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>5.65820598602295</v>
+        <v>5.65820693969727</v>
       </c>
       <c r="H388" t="n">
         <v>2690430</v>
@@ -11650,7 +11650,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G389" t="n">
-        <v>5.49935340881348</v>
+        <v>5.49935293197632</v>
       </c>
       <c r="H389" t="n">
         <v>2989285</v>
@@ -11679,7 +11679,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.52204656600952</v>
+        <v>5.52204704284668</v>
       </c>
       <c r="H390" t="n">
         <v>1962879</v>
@@ -11737,7 +11737,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>5.54474020004272</v>
+        <v>5.54473972320557</v>
       </c>
       <c r="H392" t="n">
         <v>1316398</v>
@@ -11824,7 +11824,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>5.51448154449463</v>
+        <v>5.51448202133179</v>
       </c>
       <c r="H395" t="n">
         <v>1573825</v>
@@ -11853,7 +11853,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G396" t="n">
-        <v>5.47287797927856</v>
+        <v>5.47287750244141</v>
       </c>
       <c r="H396" t="n">
         <v>1629912</v>
@@ -11911,7 +11911,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G398" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640254974365</v>
       </c>
       <c r="H398" t="n">
         <v>1103593</v>
@@ -11940,7 +11940,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G399" t="n">
-        <v>5.40479755401611</v>
+        <v>5.40479803085327</v>
       </c>
       <c r="H399" t="n">
         <v>1176652</v>
@@ -11969,7 +11969,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49935340881348</v>
+        <v>5.49935293197632</v>
       </c>
       <c r="H400" t="n">
         <v>1347527</v>
@@ -12085,7 +12085,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>5.62038373947144</v>
+        <v>5.62038421630859</v>
       </c>
       <c r="H404" t="n">
         <v>880276</v>
@@ -12143,7 +12143,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G406" t="n">
-        <v>5.62416648864746</v>
+        <v>5.6241660118103</v>
       </c>
       <c r="H406" t="n">
         <v>2126217</v>
@@ -12230,7 +12230,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.65442514419556</v>
+        <v>5.6544246673584</v>
       </c>
       <c r="H409" t="n">
         <v>1900336</v>
@@ -12259,7 +12259,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G410" t="n">
-        <v>5.71494007110596</v>
+        <v>5.7149395942688</v>
       </c>
       <c r="H410" t="n">
         <v>1739188</v>
@@ -12317,7 +12317,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>5.68846416473389</v>
+        <v>5.68846368789673</v>
       </c>
       <c r="H412" t="n">
         <v>1193303</v>
@@ -12375,7 +12375,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G414" t="n">
-        <v>5.4917893409729</v>
+        <v>5.49178886413574</v>
       </c>
       <c r="H414" t="n">
         <v>1057522</v>
@@ -12462,7 +12462,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G417" t="n">
-        <v>5.57121562957764</v>
+        <v>5.57121467590332</v>
       </c>
       <c r="H417" t="n">
         <v>874805</v>
@@ -12520,7 +12520,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G419" t="n">
-        <v>5.49557065963745</v>
+        <v>5.49557113647461</v>
       </c>
       <c r="H419" t="n">
         <v>902775</v>
@@ -12665,7 +12665,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.34806394577026</v>
+        <v>5.34806442260742</v>
       </c>
       <c r="H424" t="n">
         <v>423239</v>
@@ -12723,7 +12723,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G426" t="n">
-        <v>5.38588714599609</v>
+        <v>5.38588666915894</v>
       </c>
       <c r="H426" t="n">
         <v>990211</v>
@@ -12781,7 +12781,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640254974365</v>
       </c>
       <c r="H428" t="n">
         <v>954586</v>
@@ -12839,7 +12839,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G430" t="n">
-        <v>5.2762017250061</v>
+        <v>5.27620220184326</v>
       </c>
       <c r="H430" t="n">
         <v>1460582</v>
@@ -12868,7 +12868,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G431" t="n">
-        <v>5.21568632125854</v>
+        <v>5.21568584442139</v>
       </c>
       <c r="H431" t="n">
         <v>1685536</v>
@@ -13042,7 +13042,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>5.51826429367065</v>
+        <v>5.51826477050781</v>
       </c>
       <c r="H437" t="n">
         <v>1374556</v>
@@ -13100,7 +13100,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>5.58634424209595</v>
+        <v>5.58634471893311</v>
       </c>
       <c r="H439" t="n">
         <v>1126119</v>
@@ -13129,7 +13129,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G440" t="n">
-        <v>5.59390926361084</v>
+        <v>5.59390878677368</v>
       </c>
       <c r="H440" t="n">
         <v>833534</v>
@@ -13158,7 +13158,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>5.65442514419556</v>
+        <v>5.6544246673584</v>
       </c>
       <c r="H441" t="n">
         <v>2098893</v>
@@ -13303,7 +13303,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>5.63551330566406</v>
+        <v>5.63551378250122</v>
       </c>
       <c r="H446" t="n">
         <v>1991275</v>
@@ -13332,7 +13332,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>5.62794876098633</v>
+        <v>5.62794923782349</v>
       </c>
       <c r="H447" t="n">
         <v>1310962</v>
@@ -13390,7 +13390,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>5.64307737350464</v>
+        <v>5.6430778503418</v>
       </c>
       <c r="H449" t="n">
         <v>1777272</v>
@@ -13477,7 +13477,7 @@
         <v>7.25</v>
       </c>
       <c r="G452" t="n">
-        <v>5.48422479629517</v>
+        <v>5.48422431945801</v>
       </c>
       <c r="H452" t="n">
         <v>2645052</v>
@@ -13506,7 +13506,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>5.45396709442139</v>
+        <v>5.45396661758423</v>
       </c>
       <c r="H453" t="n">
         <v>2269990</v>
@@ -13535,7 +13535,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>5.44640207290649</v>
+        <v>5.44640254974365</v>
       </c>
       <c r="H454" t="n">
         <v>2254350</v>
@@ -13767,7 +13767,7 @@
         <v>7.25</v>
       </c>
       <c r="G462" t="n">
-        <v>5.48422479629517</v>
+        <v>5.48422431945801</v>
       </c>
       <c r="H462" t="n">
         <v>1324562</v>
@@ -13854,7 +13854,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G465" t="n">
-        <v>5.88892221450806</v>
+        <v>5.88892269134521</v>
       </c>
       <c r="H465" t="n">
         <v>6603368</v>
@@ -13883,7 +13883,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>5.85866498947144</v>
+        <v>5.85866451263428</v>
       </c>
       <c r="H466" t="n">
         <v>5913902</v>
@@ -13912,7 +13912,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G467" t="n">
-        <v>6.02886438369751</v>
+        <v>6.02886486053467</v>
       </c>
       <c r="H467" t="n">
         <v>5565313</v>
@@ -13999,7 +13999,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G470" t="n">
-        <v>6.07425117492676</v>
+        <v>6.0742506980896</v>
       </c>
       <c r="H470" t="n">
         <v>1261592</v>
@@ -14028,7 +14028,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G471" t="n">
-        <v>6.06668710708618</v>
+        <v>6.06668663024902</v>
       </c>
       <c r="H471" t="n">
         <v>1148363</v>
@@ -14260,7 +14260,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>5.88892221450806</v>
+        <v>5.88892269134521</v>
       </c>
       <c r="H479" t="n">
         <v>2778926</v>
@@ -14289,7 +14289,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G480" t="n">
-        <v>5.83597183227539</v>
+        <v>5.83597135543823</v>
       </c>
       <c r="H480" t="n">
         <v>1764454</v>
@@ -14405,7 +14405,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>6.04777526855469</v>
+        <v>6.04777574539185</v>
       </c>
       <c r="H484" t="n">
         <v>1409766</v>
@@ -14434,7 +14434,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G485" t="n">
-        <v>6.13476610183716</v>
+        <v>6.13476705551147</v>
       </c>
       <c r="H485" t="n">
         <v>1649104</v>
@@ -14521,7 +14521,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G488" t="n">
-        <v>6.16124248504639</v>
+        <v>6.16124296188354</v>
       </c>
       <c r="H488" t="n">
         <v>1807013</v>
@@ -14550,7 +14550,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G489" t="n">
-        <v>6.13476610183716</v>
+        <v>6.13476705551147</v>
       </c>
       <c r="H489" t="n">
         <v>1847566</v>
@@ -14608,7 +14608,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>6.34278917312622</v>
+        <v>6.34278964996338</v>
       </c>
       <c r="H491" t="n">
         <v>3494738</v>
@@ -14666,7 +14666,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>6.29740190505981</v>
+        <v>6.29740238189697</v>
       </c>
       <c r="H493" t="n">
         <v>3189474</v>
@@ -14695,7 +14695,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G494" t="n">
-        <v>6.3617000579834</v>
+        <v>6.36170053482056</v>
       </c>
       <c r="H494" t="n">
         <v>2642211</v>
@@ -14724,7 +14724,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>6.39195823669434</v>
+        <v>6.39195775985718</v>
       </c>
       <c r="H495" t="n">
         <v>1802507</v>
@@ -14753,7 +14753,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G496" t="n">
-        <v>6.32009553909302</v>
+        <v>6.32009506225586</v>
       </c>
       <c r="H496" t="n">
         <v>1573542</v>
@@ -14869,7 +14869,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G500" t="n">
-        <v>6.53946590423584</v>
+        <v>6.53946495056152</v>
       </c>
       <c r="H500" t="n">
         <v>2118776</v>
@@ -14985,7 +14985,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G504" t="n">
-        <v>6.52811813354492</v>
+        <v>6.52811861038208</v>
       </c>
       <c r="H504" t="n">
         <v>1354361</v>
@@ -15014,7 +15014,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>6.50542449951172</v>
+        <v>6.50542593002319</v>
       </c>
       <c r="H505" t="n">
         <v>1051125</v>
@@ -15130,7 +15130,7 @@
         <v>8.73499965667725</v>
       </c>
       <c r="G509" t="n">
-        <v>6.60754442214966</v>
+        <v>6.6075439453125</v>
       </c>
       <c r="H509" t="n">
         <v>1787823</v>
@@ -15159,7 +15159,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.5583758354187</v>
+        <v>6.55837535858154</v>
       </c>
       <c r="H510" t="n">
         <v>1047728</v>
@@ -15188,7 +15188,7 @@
         <v>8.53499984741211</v>
       </c>
       <c r="G511" t="n">
-        <v>6.4562554359436</v>
+        <v>6.45625591278076</v>
       </c>
       <c r="H511" t="n">
         <v>585989</v>
@@ -15246,7 +15246,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>6.39952230453491</v>
+        <v>6.39952278137207</v>
       </c>
       <c r="H513" t="n">
         <v>2092048</v>
@@ -15275,7 +15275,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G514" t="n">
-        <v>6.65671443939209</v>
+        <v>6.65671396255493</v>
       </c>
       <c r="H514" t="n">
         <v>2595760</v>
@@ -15362,7 +15362,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>7.06141233444214</v>
+        <v>7.06141138076782</v>
       </c>
       <c r="H517" t="n">
         <v>3758849</v>
@@ -15391,7 +15391,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G518" t="n">
-        <v>7.12949228286743</v>
+        <v>7.12949132919312</v>
       </c>
       <c r="H518" t="n">
         <v>2703458</v>
@@ -15420,7 +15420,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>7.29969120025635</v>
+        <v>7.29969167709351</v>
       </c>
       <c r="H519" t="n">
         <v>2135357</v>
@@ -15449,7 +15449,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G520" t="n">
-        <v>7.26187038421631</v>
+        <v>7.26186990737915</v>
       </c>
       <c r="H520" t="n">
         <v>2754591</v>
@@ -15507,7 +15507,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>7.19000720977783</v>
+        <v>7.19000816345215</v>
       </c>
       <c r="H522" t="n">
         <v>2491793</v>
@@ -15536,7 +15536,7 @@
         <v>9.54500007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>7.22026538848877</v>
+        <v>7.22026395797729</v>
       </c>
       <c r="H523" t="n">
         <v>1774616</v>
@@ -15565,7 +15565,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G524" t="n">
-        <v>7.32238578796387</v>
+        <v>7.32238531112671</v>
       </c>
       <c r="H524" t="n">
         <v>1544485</v>
@@ -15594,7 +15594,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>7.3412971496582</v>
+        <v>7.34129571914673</v>
       </c>
       <c r="H525" t="n">
         <v>2716719</v>
@@ -15623,7 +15623,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>7.38290023803711</v>
+        <v>7.38290071487427</v>
       </c>
       <c r="H526" t="n">
         <v>2937349</v>
@@ -15652,7 +15652,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>7.51528024673462</v>
+        <v>7.5152792930603</v>
       </c>
       <c r="H527" t="n">
         <v>3719053</v>
@@ -15739,7 +15739,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>7.64009284973145</v>
+        <v>7.64009094238281</v>
       </c>
       <c r="H530" t="n">
         <v>1886050</v>
@@ -15768,7 +15768,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G531" t="n">
-        <v>7.62496328353882</v>
+        <v>7.6249623298645</v>
       </c>
       <c r="H531" t="n">
         <v>2724662</v>
@@ -15797,7 +15797,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>7.49636888504028</v>
+        <v>7.49636840820312</v>
       </c>
       <c r="H532" t="n">
         <v>2703227</v>
@@ -15826,7 +15826,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>7.57201099395752</v>
+        <v>7.57201194763184</v>
       </c>
       <c r="H533" t="n">
         <v>2351710</v>
@@ -15855,7 +15855,7 @@
         <v>10.0249996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>7.58335781097412</v>
+        <v>7.58335733413696</v>
       </c>
       <c r="H534" t="n">
         <v>2726639</v>
@@ -15884,7 +15884,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G535" t="n">
-        <v>7.45400619506836</v>
+        <v>7.45400762557983</v>
       </c>
       <c r="H535" t="n">
         <v>3357817</v>
@@ -15913,7 +15913,7 @@
         <v>9.75</v>
       </c>
       <c r="G536" t="n">
-        <v>7.37533664703369</v>
+        <v>7.37533521652222</v>
       </c>
       <c r="H536" t="n">
         <v>2297778</v>
@@ -15942,7 +15942,7 @@
         <v>9.31799983978271</v>
       </c>
       <c r="G537" t="n">
-        <v>7.04855108261108</v>
+        <v>7.0485520362854</v>
       </c>
       <c r="H537" t="n">
         <v>5044050</v>
@@ -16000,7 +16000,7 @@
         <v>9.58800029754639</v>
       </c>
       <c r="G539" t="n">
-        <v>7.25279235839844</v>
+        <v>7.25279331207275</v>
       </c>
       <c r="H539" t="n">
         <v>3063469</v>
@@ -16058,7 +16058,7 @@
         <v>9.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.99711418151855</v>
+        <v>6.99711322784424</v>
       </c>
       <c r="H541" t="n">
         <v>2928469</v>
@@ -16087,7 +16087,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G542" t="n">
-        <v>6.97593450546265</v>
+        <v>6.97593355178833</v>
       </c>
       <c r="H542" t="n">
         <v>1859299</v>
@@ -16116,7 +16116,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G543" t="n">
-        <v>7.03039741516113</v>
+        <v>7.03039693832397</v>
       </c>
       <c r="H543" t="n">
         <v>3747691</v>
@@ -16174,7 +16174,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G545" t="n">
-        <v>7.31028127670288</v>
+        <v>7.31028175354004</v>
       </c>
       <c r="H545" t="n">
         <v>1876859</v>
@@ -16203,7 +16203,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G546" t="n">
-        <v>7.31028127670288</v>
+        <v>7.31028175354004</v>
       </c>
       <c r="H546" t="n">
         <v>1280155</v>
@@ -16232,7 +16232,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G547" t="n">
-        <v>7.41164541244507</v>
+        <v>7.41164445877075</v>
       </c>
       <c r="H547" t="n">
         <v>1795777</v>
@@ -16261,7 +16261,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G548" t="n">
-        <v>7.48577642440796</v>
+        <v>7.48577690124512</v>
       </c>
       <c r="H548" t="n">
         <v>1631990</v>
@@ -16290,7 +16290,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G549" t="n">
-        <v>7.51149606704712</v>
+        <v>7.51149702072144</v>
       </c>
       <c r="H549" t="n">
         <v>2091851</v>
@@ -16377,7 +16377,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G552" t="n">
-        <v>7.62496328353882</v>
+        <v>7.6249623298645</v>
       </c>
       <c r="H552" t="n">
         <v>1930528</v>
@@ -16406,7 +16406,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G553" t="n">
-        <v>7.65522050857544</v>
+        <v>7.65522003173828</v>
       </c>
       <c r="H553" t="n">
         <v>2284556</v>
@@ -16435,7 +16435,7 @@
         <v>10.1450004577637</v>
       </c>
       <c r="G554" t="n">
-        <v>7.67413091659546</v>
+        <v>7.67413187026978</v>
       </c>
       <c r="H554" t="n">
         <v>2059806</v>
@@ -16464,7 +16464,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G555" t="n">
-        <v>7.41164541244507</v>
+        <v>7.41164445877075</v>
       </c>
       <c r="H555" t="n">
         <v>3047161</v>
@@ -16493,7 +16493,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G556" t="n">
-        <v>7.24220275878906</v>
+        <v>7.2422022819519</v>
       </c>
       <c r="H556" t="n">
         <v>3303724</v>
@@ -16522,7 +16522,7 @@
         <v>9.9680004119873</v>
       </c>
       <c r="G557" t="n">
-        <v>7.54024219512939</v>
+        <v>7.54024124145508</v>
       </c>
       <c r="H557" t="n">
         <v>2648397</v>
@@ -16551,7 +16551,7 @@
         <v>10.1350002288818</v>
       </c>
       <c r="G558" t="n">
-        <v>7.66656732559204</v>
+        <v>7.6665678024292</v>
       </c>
       <c r="H558" t="n">
         <v>1674650</v>
@@ -16580,7 +16580,7 @@
         <v>10.1450004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>7.67413091659546</v>
+        <v>7.67413187026978</v>
       </c>
       <c r="H559" t="n">
         <v>1864379</v>
@@ -16638,7 +16638,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G561" t="n">
-        <v>7.7913818359375</v>
+        <v>7.79138088226318</v>
       </c>
       <c r="H561" t="n">
         <v>2329031</v>
@@ -16667,7 +16667,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>7.64765548706055</v>
+        <v>7.64765501022339</v>
       </c>
       <c r="H562" t="n">
         <v>1900362</v>
@@ -16696,7 +16696,7 @@
         <v>10.125</v>
       </c>
       <c r="G563" t="n">
-        <v>7.65900230407715</v>
+        <v>7.65900278091431</v>
       </c>
       <c r="H563" t="n">
         <v>1838776</v>
@@ -16783,7 +16783,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G566" t="n">
-        <v>7.64765548706055</v>
+        <v>7.64765501022339</v>
       </c>
       <c r="H566" t="n">
         <v>2427519</v>
@@ -16812,7 +16812,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G567" t="n">
-        <v>7.84433221817017</v>
+        <v>7.84433317184448</v>
       </c>
       <c r="H567" t="n">
         <v>2616314</v>
@@ -16841,7 +16841,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G568" t="n">
-        <v>7.77246761322021</v>
+        <v>7.77246856689453</v>
       </c>
       <c r="H568" t="n">
         <v>1383045</v>
@@ -16870,7 +16870,7 @@
         <v>10.0150003433228</v>
       </c>
       <c r="G569" t="n">
-        <v>7.57579469680786</v>
+        <v>7.57579374313354</v>
       </c>
       <c r="H569" t="n">
         <v>2012509</v>
@@ -16899,7 +16899,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G570" t="n">
-        <v>7.54931735992432</v>
+        <v>7.54931783676147</v>
       </c>
       <c r="H570" t="n">
         <v>2525070</v>
@@ -16957,7 +16957,7 @@
         <v>9.81599998474121</v>
       </c>
       <c r="G572" t="n">
-        <v>7.42526149749756</v>
+        <v>7.42526006698608</v>
       </c>
       <c r="H572" t="n">
         <v>1631785</v>
@@ -16986,7 +16986,7 @@
         <v>9.72799968719482</v>
       </c>
       <c r="G573" t="n">
-        <v>7.35869312286377</v>
+        <v>7.35869359970093</v>
       </c>
       <c r="H573" t="n">
         <v>2223477</v>
@@ -17015,7 +17015,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G574" t="n">
-        <v>7.38895177841187</v>
+        <v>7.38895225524902</v>
       </c>
       <c r="H574" t="n">
         <v>1242505</v>
@@ -17044,7 +17044,7 @@
         <v>9.69400024414062</v>
       </c>
       <c r="G575" t="n">
-        <v>7.33297538757324</v>
+        <v>7.33297491073608</v>
       </c>
       <c r="H575" t="n">
         <v>1849914</v>
@@ -17073,7 +17073,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G576" t="n">
-        <v>7.37231063842773</v>
+        <v>7.37231159210205</v>
       </c>
       <c r="H576" t="n">
         <v>2250788</v>
@@ -17102,7 +17102,7 @@
         <v>10</v>
       </c>
       <c r="G577" t="n">
-        <v>7.56444787979126</v>
+        <v>7.56444692611694</v>
       </c>
       <c r="H577" t="n">
         <v>2437053</v>
@@ -17131,7 +17131,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G578" t="n">
-        <v>7.31330823898315</v>
+        <v>7.31330728530884</v>
       </c>
       <c r="H578" t="n">
         <v>2180063</v>
@@ -17160,7 +17160,7 @@
         <v>9.74400043487549</v>
       </c>
       <c r="G579" t="n">
-        <v>7.37079763412476</v>
+        <v>7.3707971572876</v>
       </c>
       <c r="H579" t="n">
         <v>2335571</v>
@@ -17189,7 +17189,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G580" t="n">
-        <v>7.41164541244507</v>
+        <v>7.41164445877075</v>
       </c>
       <c r="H580" t="n">
         <v>1565533</v>
@@ -17218,7 +17218,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>7.31481981277466</v>
+        <v>7.31482076644897</v>
       </c>
       <c r="H581" t="n">
         <v>1968934</v>
@@ -17276,7 +17276,7 @@
         <v>9.66399955749512</v>
       </c>
       <c r="G583" t="n">
-        <v>7.31028127670288</v>
+        <v>7.31028175354004</v>
       </c>
       <c r="H583" t="n">
         <v>1594651</v>
@@ -17305,7 +17305,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G584" t="n">
-        <v>7.38895177841187</v>
+        <v>7.38895225524902</v>
       </c>
       <c r="H584" t="n">
         <v>1482837</v>
@@ -17334,7 +17334,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>7.46610975265503</v>
+        <v>7.46610832214355</v>
       </c>
       <c r="H585" t="n">
         <v>2347576</v>
@@ -17363,7 +17363,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G586" t="n">
-        <v>7.54175424575806</v>
+        <v>7.54175472259521</v>
       </c>
       <c r="H586" t="n">
         <v>1948968</v>
@@ -17392,7 +17392,7 @@
         <v>9.96399974822998</v>
       </c>
       <c r="G587" t="n">
-        <v>7.53721475601196</v>
+        <v>7.53721523284912</v>
       </c>
       <c r="H587" t="n">
         <v>1703361</v>
@@ -17421,7 +17421,7 @@
         <v>9.92399978637695</v>
       </c>
       <c r="G588" t="n">
-        <v>7.50695657730103</v>
+        <v>7.5069580078125</v>
       </c>
       <c r="H588" t="n">
         <v>1885121</v>
@@ -17450,7 +17450,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G589" t="n">
-        <v>7.74138021469116</v>
+        <v>7.74137926101685</v>
       </c>
       <c r="H589" t="n">
         <v>2999699</v>
@@ -17479,7 +17479,7 @@
         <v>10</v>
       </c>
       <c r="G590" t="n">
-        <v>7.78810834884644</v>
+        <v>7.78810787200928</v>
       </c>
       <c r="H590" t="n">
         <v>2393942</v>
@@ -17508,7 +17508,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G591" t="n">
-        <v>7.71957349777222</v>
+        <v>7.7195725440979</v>
       </c>
       <c r="H591" t="n">
         <v>1307523</v>
@@ -17537,7 +17537,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G592" t="n">
-        <v>7.67440176010132</v>
+        <v>7.67440271377563</v>
       </c>
       <c r="H592" t="n">
         <v>1682061</v>
@@ -17595,7 +17595,7 @@
         <v>9.9040002822876</v>
       </c>
       <c r="G594" t="n">
-        <v>7.7133412361145</v>
+        <v>7.71334218978882</v>
       </c>
       <c r="H594" t="n">
         <v>1365591</v>
@@ -17624,7 +17624,7 @@
         <v>9.98400020599365</v>
       </c>
       <c r="G595" t="n">
-        <v>7.77564811706543</v>
+        <v>7.77564716339111</v>
       </c>
       <c r="H595" t="n">
         <v>1875685</v>
@@ -17740,7 +17740,7 @@
         <v>9.80799961090088</v>
       </c>
       <c r="G599" t="n">
-        <v>7.6385760307312</v>
+        <v>7.63857650756836</v>
       </c>
       <c r="H599" t="n">
         <v>2981084</v>
@@ -17769,7 +17769,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G600" t="n">
-        <v>7.71957349777222</v>
+        <v>7.7195725440979</v>
       </c>
       <c r="H600" t="n">
         <v>2179245</v>
@@ -17798,7 +17798,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G601" t="n">
-        <v>7.57004070281982</v>
+        <v>7.57004022598267</v>
       </c>
       <c r="H601" t="n">
         <v>1865136</v>
@@ -17856,7 +17856,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G603" t="n">
-        <v>7.58717489242554</v>
+        <v>7.58717441558838</v>
       </c>
       <c r="H603" t="n">
         <v>1708543</v>
@@ -18001,7 +18001,7 @@
         <v>8.89799976348877</v>
       </c>
       <c r="G608" t="n">
-        <v>6.92985820770264</v>
+        <v>6.92985868453979</v>
       </c>
       <c r="H608" t="n">
         <v>2087544</v>
@@ -18030,7 +18030,7 @@
         <v>9.1879997253418</v>
       </c>
       <c r="G609" t="n">
-        <v>7.15571212768555</v>
+        <v>7.15571355819702</v>
       </c>
       <c r="H609" t="n">
         <v>2450008</v>
@@ -18059,7 +18059,7 @@
         <v>9.1560001373291</v>
       </c>
       <c r="G610" t="n">
-        <v>7.13079261779785</v>
+        <v>7.13079214096069</v>
       </c>
       <c r="H610" t="n">
         <v>2396179</v>
@@ -18088,7 +18088,7 @@
         <v>9.18200016021729</v>
       </c>
       <c r="G611" t="n">
-        <v>7.15104007720947</v>
+        <v>7.15104103088379</v>
       </c>
       <c r="H611" t="n">
         <v>2695423</v>
@@ -18175,7 +18175,7 @@
         <v>7.95599985122681</v>
       </c>
       <c r="G614" t="n">
-        <v>6.19621849060059</v>
+        <v>6.19621801376343</v>
       </c>
       <c r="H614" t="n">
         <v>6227171</v>
@@ -18204,7 +18204,7 @@
         <v>8.4680004119873</v>
       </c>
       <c r="G615" t="n">
-        <v>6.59497022628784</v>
+        <v>6.594970703125</v>
       </c>
       <c r="H615" t="n">
         <v>6446132</v>
@@ -18233,7 +18233,7 @@
         <v>8.55399990081787</v>
       </c>
       <c r="G616" t="n">
-        <v>6.66194772720337</v>
+        <v>6.66194868087769</v>
       </c>
       <c r="H616" t="n">
         <v>5399976</v>
@@ -18291,7 +18291,7 @@
         <v>8.56400012969971</v>
       </c>
       <c r="G618" t="n">
-        <v>6.66973543167114</v>
+        <v>6.66973638534546</v>
       </c>
       <c r="H618" t="n">
         <v>2483270</v>
@@ -18320,7 +18320,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G619" t="n">
-        <v>6.56537628173828</v>
+        <v>6.56537532806396</v>
       </c>
       <c r="H619" t="n">
         <v>3748575</v>
@@ -18378,7 +18378,7 @@
         <v>8.9040002822876</v>
       </c>
       <c r="G621" t="n">
-        <v>6.93453168869019</v>
+        <v>6.93453216552734</v>
       </c>
       <c r="H621" t="n">
         <v>3217269</v>
@@ -18407,7 +18407,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G622" t="n">
-        <v>6.88312959671021</v>
+        <v>6.88313007354736</v>
       </c>
       <c r="H622" t="n">
         <v>2212311</v>
@@ -18523,7 +18523,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G626" t="n">
-        <v>7.41895151138306</v>
+        <v>7.41895198822021</v>
       </c>
       <c r="H626" t="n">
         <v>3415478</v>
@@ -18552,7 +18552,7 @@
         <v>9.48200035095215</v>
       </c>
       <c r="G627" t="n">
-        <v>7.38468456268311</v>
+        <v>7.38468360900879</v>
       </c>
       <c r="H627" t="n">
         <v>4653579</v>
@@ -18581,7 +18581,7 @@
         <v>9.44400024414062</v>
       </c>
       <c r="G628" t="n">
-        <v>7.35509061813354</v>
+        <v>7.35508918762207</v>
       </c>
       <c r="H628" t="n">
         <v>2791658</v>
@@ -18610,7 +18610,7 @@
         <v>9.52600002288818</v>
       </c>
       <c r="G629" t="n">
-        <v>7.41895151138306</v>
+        <v>7.41895198822021</v>
       </c>
       <c r="H629" t="n">
         <v>2609330</v>
@@ -18639,7 +18639,7 @@
         <v>9.62199974060059</v>
       </c>
       <c r="G630" t="n">
-        <v>7.4937162399292</v>
+        <v>7.49371671676636</v>
       </c>
       <c r="H630" t="n">
         <v>1981592</v>
@@ -18668,7 +18668,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G631" t="n">
-        <v>7.4220666885376</v>
+        <v>7.42206573486328</v>
       </c>
       <c r="H631" t="n">
         <v>1832919</v>
@@ -18697,7 +18697,7 @@
         <v>9.64799976348877</v>
       </c>
       <c r="G632" t="n">
-        <v>7.51396703720093</v>
+        <v>7.51396512985229</v>
       </c>
       <c r="H632" t="n">
         <v>2002552</v>
@@ -18784,7 +18784,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G635" t="n">
-        <v>7.37533712387085</v>
+        <v>7.37533855438232</v>
       </c>
       <c r="H635" t="n">
         <v>2226807</v>
@@ -18813,7 +18813,7 @@
         <v>9.51799964904785</v>
       </c>
       <c r="G636" t="n">
-        <v>7.41272115707397</v>
+        <v>7.41272068023682</v>
       </c>
       <c r="H636" t="n">
         <v>1572602</v>
@@ -18871,7 +18871,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G638" t="n">
-        <v>7.54044580459595</v>
+        <v>7.54044675827026</v>
       </c>
       <c r="H638" t="n">
         <v>1450594</v>
@@ -18900,7 +18900,7 @@
         <v>9.83199977874756</v>
       </c>
       <c r="G639" t="n">
-        <v>7.65726757049561</v>
+        <v>7.65726804733276</v>
       </c>
       <c r="H639" t="n">
         <v>2310754</v>
@@ -18958,7 +18958,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G641" t="n">
-        <v>7.73359155654907</v>
+        <v>7.73359251022339</v>
       </c>
       <c r="H641" t="n">
         <v>2425450</v>
@@ -19045,7 +19045,7 @@
         <v>9.98200035095215</v>
       </c>
       <c r="G644" t="n">
-        <v>7.77408981323242</v>
+        <v>7.77408885955811</v>
       </c>
       <c r="H644" t="n">
         <v>1259309</v>
@@ -19103,7 +19103,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G646" t="n">
-        <v>7.88935422897339</v>
+        <v>7.88935232162476</v>
       </c>
       <c r="H646" t="n">
         <v>1558159</v>
@@ -19161,7 +19161,7 @@
         <v>10.25</v>
       </c>
       <c r="G648" t="n">
-        <v>7.98281097412109</v>
+        <v>7.98280954360962</v>
       </c>
       <c r="H648" t="n">
         <v>1690670</v>
@@ -19190,7 +19190,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G649" t="n">
-        <v>7.99059915542603</v>
+        <v>7.99060010910034</v>
       </c>
       <c r="H649" t="n">
         <v>1803691</v>
@@ -19248,7 +19248,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G651" t="n">
-        <v>7.97112846374512</v>
+        <v>7.9711275100708</v>
       </c>
       <c r="H651" t="n">
         <v>1564940</v>
@@ -19393,7 +19393,7 @@
         <v>10.2449998855591</v>
       </c>
       <c r="G656" t="n">
-        <v>7.97891712188721</v>
+        <v>7.97891616821289</v>
       </c>
       <c r="H656" t="n">
         <v>1210034</v>
@@ -19451,7 +19451,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>7.94387054443359</v>
+        <v>7.94386959075928</v>
       </c>
       <c r="H658" t="n">
         <v>1136695</v>
@@ -19480,7 +19480,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G659" t="n">
-        <v>7.82704925537109</v>
+        <v>7.82704830169678</v>
       </c>
       <c r="H659" t="n">
         <v>2131963</v>
@@ -19596,7 +19596,7 @@
         <v>9.97399997711182</v>
       </c>
       <c r="G663" t="n">
-        <v>7.76785850524902</v>
+        <v>7.76785945892334</v>
       </c>
       <c r="H663" t="n">
         <v>1716459</v>
@@ -19625,7 +19625,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G664" t="n">
-        <v>7.87377691268921</v>
+        <v>7.87377595901489</v>
       </c>
       <c r="H664" t="n">
         <v>1635276</v>
@@ -19654,7 +19654,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G665" t="n">
-        <v>7.78031969070435</v>
+        <v>7.78031873703003</v>
       </c>
       <c r="H665" t="n">
         <v>1671254</v>
@@ -19683,7 +19683,7 @@
         <v>10.0649995803833</v>
       </c>
       <c r="G666" t="n">
-        <v>7.83873081207275</v>
+        <v>7.83872985839844</v>
       </c>
       <c r="H666" t="n">
         <v>1430460</v>
@@ -19712,7 +19712,7 @@
         <v>9.9980001449585</v>
       </c>
       <c r="G667" t="n">
-        <v>7.78654909133911</v>
+        <v>7.78655099868774</v>
       </c>
       <c r="H667" t="n">
         <v>2346193</v>
@@ -19741,7 +19741,7 @@
         <v>10.0450000762939</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82315349578857</v>
+        <v>7.82315444946289</v>
       </c>
       <c r="H668" t="n">
         <v>1487833</v>
@@ -19799,7 +19799,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G670" t="n">
-        <v>7.92050552368164</v>
+        <v>7.9205060005188</v>
       </c>
       <c r="H670" t="n">
         <v>1766590</v>
@@ -19857,7 +19857,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G672" t="n">
-        <v>7.92050552368164</v>
+        <v>7.9205060005188</v>
       </c>
       <c r="H672" t="n">
         <v>1017100</v>
@@ -20031,7 +20031,7 @@
         <v>10.125</v>
       </c>
       <c r="G678" t="n">
-        <v>7.88545846939087</v>
+        <v>7.88545942306519</v>
       </c>
       <c r="H678" t="n">
         <v>979518</v>
@@ -20060,7 +20060,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>8.0256462097168</v>
+        <v>8.02564525604248</v>
       </c>
       <c r="H679" t="n">
         <v>1440548</v>
@@ -20089,7 +20089,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>7.99059915542603</v>
+        <v>7.99060010910034</v>
       </c>
       <c r="H680" t="n">
         <v>2347882</v>
@@ -20205,7 +20205,7 @@
         <v>10.8549995422363</v>
       </c>
       <c r="G684" t="n">
-        <v>8.45399188995361</v>
+        <v>8.4539909362793</v>
       </c>
       <c r="H684" t="n">
         <v>2386527</v>
@@ -20234,7 +20234,7 @@
         <v>10.8549995422363</v>
       </c>
       <c r="G685" t="n">
-        <v>8.45399188995361</v>
+        <v>8.4539909362793</v>
       </c>
       <c r="H685" t="n">
         <v>2264319</v>
@@ -20263,7 +20263,7 @@
         <v>10.8450002670288</v>
       </c>
       <c r="G686" t="n">
-        <v>8.44620323181152</v>
+        <v>8.44620418548584</v>
       </c>
       <c r="H686" t="n">
         <v>1462185</v>
@@ -20379,7 +20379,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G690" t="n">
-        <v>8.70710563659668</v>
+        <v>8.70710468292236</v>
       </c>
       <c r="H690" t="n">
         <v>1937510</v>
@@ -20437,7 +20437,7 @@
         <v>11.4049997329712</v>
       </c>
       <c r="G692" t="n">
-        <v>8.88233757019043</v>
+        <v>8.88233661651611</v>
       </c>
       <c r="H692" t="n">
         <v>1927177</v>
@@ -20495,7 +20495,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97579383850098</v>
+        <v>8.97579479217529</v>
       </c>
       <c r="H694" t="n">
         <v>2464064</v>
@@ -20553,7 +20553,7 @@
         <v>11.6450004577637</v>
       </c>
       <c r="G696" t="n">
-        <v>9.06925201416016</v>
+        <v>9.06925296783447</v>
       </c>
       <c r="H696" t="n">
         <v>3391477</v>
@@ -20582,7 +20582,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G697" t="n">
-        <v>9.09650993347168</v>
+        <v>9.096510887146</v>
       </c>
       <c r="H697" t="n">
         <v>2058581</v>
@@ -20611,7 +20611,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G698" t="n">
-        <v>9.26006031036377</v>
+        <v>9.26006126403809</v>
       </c>
       <c r="H698" t="n">
         <v>2932183</v>
@@ -20640,7 +20640,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G699" t="n">
-        <v>9.26006031036377</v>
+        <v>9.26006126403809</v>
       </c>
       <c r="H699" t="n">
         <v>2455162</v>
@@ -20669,7 +20669,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>9.13155746459961</v>
+        <v>9.13155651092529</v>
       </c>
       <c r="H700" t="n">
         <v>2810250</v>
@@ -20698,7 +20698,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G701" t="n">
-        <v>8.9680061340332</v>
+        <v>8.96800804138184</v>
       </c>
       <c r="H701" t="n">
         <v>3242374</v>
@@ -20814,7 +20814,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G705" t="n">
-        <v>8.85507965087891</v>
+        <v>8.85507869720459</v>
       </c>
       <c r="H705" t="n">
         <v>1870685</v>
@@ -20843,7 +20843,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G706" t="n">
-        <v>8.77719879150391</v>
+        <v>8.77719783782959</v>
       </c>
       <c r="H706" t="n">
         <v>2022064</v>
@@ -20901,7 +20901,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G708" t="n">
-        <v>8.33327579498291</v>
+        <v>8.33327484130859</v>
       </c>
       <c r="H708" t="n">
         <v>3183760</v>
@@ -20959,7 +20959,7 @@
         <v>9.95600032806396</v>
       </c>
       <c r="G710" t="n">
-        <v>7.75384044647217</v>
+        <v>7.75384140014648</v>
       </c>
       <c r="H710" t="n">
         <v>4164604</v>
@@ -20988,7 +20988,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G711" t="n">
-        <v>7.60742330551147</v>
+        <v>7.60742378234863</v>
       </c>
       <c r="H711" t="n">
         <v>3737657</v>
@@ -21017,7 +21017,7 @@
         <v>9.75</v>
       </c>
       <c r="G712" t="n">
-        <v>7.59340572357178</v>
+        <v>7.59340476989746</v>
       </c>
       <c r="H712" t="n">
         <v>1222884</v>
@@ -21075,7 +21075,7 @@
         <v>9.68599987030029</v>
       </c>
       <c r="G714" t="n">
-        <v>7.5435619354248</v>
+        <v>7.54356145858765</v>
       </c>
       <c r="H714" t="n">
         <v>1628235</v>
@@ -21104,7 +21104,7 @@
         <v>9.23400020599365</v>
       </c>
       <c r="G715" t="n">
-        <v>7.19153881072998</v>
+        <v>7.19153928756714</v>
       </c>
       <c r="H715" t="n">
         <v>2554878</v>
@@ -21133,7 +21133,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G716" t="n">
-        <v>6.98437595367432</v>
+        <v>6.98437547683716</v>
       </c>
       <c r="H716" t="n">
         <v>4261848</v>
@@ -21162,7 +21162,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G717" t="n">
-        <v>6.97347211837769</v>
+        <v>6.97347259521484</v>
       </c>
       <c r="H717" t="n">
         <v>2245507</v>
@@ -21191,7 +21191,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G718" t="n">
-        <v>6.89559078216553</v>
+        <v>6.89559125900269</v>
       </c>
       <c r="H718" t="n">
         <v>3317195</v>
@@ -21249,7 +21249,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G720" t="n">
-        <v>7.04979515075684</v>
+        <v>7.04979562759399</v>
       </c>
       <c r="H720" t="n">
         <v>3077402</v>
@@ -21278,7 +21278,7 @@
         <v>8.77400016784668</v>
       </c>
       <c r="G721" t="n">
-        <v>6.83328628540039</v>
+        <v>6.83328533172607</v>
       </c>
       <c r="H721" t="n">
         <v>2229912</v>
@@ -21336,7 +21336,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G723" t="n">
-        <v>7.06692934036255</v>
+        <v>7.06692886352539</v>
       </c>
       <c r="H723" t="n">
         <v>1554170</v>
@@ -21365,7 +21365,7 @@
         <v>9.24600028991699</v>
       </c>
       <c r="G724" t="n">
-        <v>7.20088481903076</v>
+        <v>7.20088529586792</v>
       </c>
       <c r="H724" t="n">
         <v>2577826</v>
@@ -21394,7 +21394,7 @@
         <v>9.38599967956543</v>
       </c>
       <c r="G725" t="n">
-        <v>7.30991697311401</v>
+        <v>7.30991744995117</v>
       </c>
       <c r="H725" t="n">
         <v>2225319</v>
@@ -21423,7 +21423,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G726" t="n">
-        <v>7.62922954559326</v>
+        <v>7.62923002243042</v>
       </c>
       <c r="H726" t="n">
         <v>3121627</v>
@@ -21452,7 +21452,7 @@
         <v>9.58399963378906</v>
       </c>
       <c r="G727" t="n">
-        <v>7.46412229537964</v>
+        <v>7.4641227722168</v>
       </c>
       <c r="H727" t="n">
         <v>2256475</v>
@@ -21481,7 +21481,7 @@
         <v>9.60200023651123</v>
       </c>
       <c r="G728" t="n">
-        <v>7.47814226150513</v>
+        <v>7.47814035415649</v>
       </c>
       <c r="H728" t="n">
         <v>2181089</v>
@@ -21539,7 +21539,7 @@
         <v>9.87600040435791</v>
       </c>
       <c r="G730" t="n">
-        <v>7.69153499603271</v>
+        <v>7.69153642654419</v>
       </c>
       <c r="H730" t="n">
         <v>2117523</v>
@@ -21597,7 +21597,7 @@
         <v>9.82400035858154</v>
       </c>
       <c r="G732" t="n">
-        <v>7.65103816986084</v>
+        <v>7.65103673934937</v>
       </c>
       <c r="H732" t="n">
         <v>1608151</v>
@@ -21626,7 +21626,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G733" t="n">
-        <v>7.67128610610962</v>
+        <v>7.67128705978394</v>
       </c>
       <c r="H733" t="n">
         <v>1695599</v>
@@ -21655,7 +21655,7 @@
         <v>9.7480001449585</v>
       </c>
       <c r="G734" t="n">
-        <v>7.59184837341309</v>
+        <v>7.59184741973877</v>
       </c>
       <c r="H734" t="n">
         <v>1440632</v>
@@ -21684,7 +21684,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>7.49215936660767</v>
+        <v>7.49215984344482</v>
       </c>
       <c r="H735" t="n">
         <v>1346144</v>
@@ -21713,7 +21713,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G736" t="n">
-        <v>7.50150537490845</v>
+        <v>7.50150489807129</v>
       </c>
       <c r="H736" t="n">
         <v>1763545</v>
@@ -21742,7 +21742,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G737" t="n">
-        <v>7.54044580459595</v>
+        <v>7.54044675827026</v>
       </c>
       <c r="H737" t="n">
         <v>1242108</v>
@@ -21771,7 +21771,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G738" t="n">
-        <v>7.47502565383911</v>
+        <v>7.47502517700195</v>
       </c>
       <c r="H738" t="n">
         <v>1502534</v>
@@ -21800,7 +21800,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G739" t="n">
-        <v>7.50150537490845</v>
+        <v>7.50150489807129</v>
       </c>
       <c r="H739" t="n">
         <v>1314109</v>
@@ -21829,7 +21829,7 @@
         <v>9.57400035858154</v>
       </c>
       <c r="G740" t="n">
-        <v>7.45633506774902</v>
+        <v>7.45633459091187</v>
       </c>
       <c r="H740" t="n">
         <v>1338612</v>
@@ -21858,7 +21858,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G741" t="n">
-        <v>7.55135011672974</v>
+        <v>7.55134963989258</v>
       </c>
       <c r="H741" t="n">
         <v>915115</v>
@@ -21887,7 +21887,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G742" t="n">
-        <v>7.62922954559326</v>
+        <v>7.62923002243042</v>
       </c>
       <c r="H742" t="n">
         <v>1900863</v>
@@ -21945,7 +21945,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G744" t="n">
-        <v>7.61832571029663</v>
+        <v>7.61832714080811</v>
       </c>
       <c r="H744" t="n">
         <v>867162</v>
@@ -21974,7 +21974,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>7.40025997161865</v>
+        <v>7.40025949478149</v>
       </c>
       <c r="H745" t="n">
         <v>1424402</v>
@@ -22003,7 +22003,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G746" t="n">
-        <v>7.37533712387085</v>
+        <v>7.37533855438232</v>
       </c>
       <c r="H746" t="n">
         <v>2300576</v>
@@ -22032,7 +22032,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G747" t="n">
-        <v>7.56069469451904</v>
+        <v>7.56069612503052</v>
       </c>
       <c r="H747" t="n">
         <v>1765087</v>
@@ -22061,7 +22061,7 @@
         <v>9.58199977874756</v>
       </c>
       <c r="G748" t="n">
-        <v>7.46256542205811</v>
+        <v>7.46256446838379</v>
       </c>
       <c r="H748" t="n">
         <v>1190558</v>
@@ -22090,7 +22090,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G749" t="n">
-        <v>7.57004070281982</v>
+        <v>7.57004022598267</v>
       </c>
       <c r="H749" t="n">
         <v>948540</v>
@@ -22119,7 +22119,7 @@
         <v>9.0620002746582</v>
       </c>
       <c r="G750" t="n">
-        <v>7.05758428573608</v>
+        <v>7.05758476257324</v>
       </c>
       <c r="H750" t="n">
         <v>2355774</v>
@@ -22148,7 +22148,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G751" t="n">
-        <v>7.11677265167236</v>
+        <v>7.11677360534668</v>
       </c>
       <c r="H751" t="n">
         <v>1246812</v>
@@ -22177,7 +22177,7 @@
         <v>8.93400001525879</v>
       </c>
       <c r="G752" t="n">
-        <v>6.95789623260498</v>
+        <v>6.95789575576782</v>
       </c>
       <c r="H752" t="n">
         <v>1417279</v>
@@ -22206,7 +22206,7 @@
         <v>8.96399974822998</v>
       </c>
       <c r="G753" t="n">
-        <v>6.98126029968262</v>
+        <v>6.98125982284546</v>
       </c>
       <c r="H753" t="n">
         <v>1257283</v>
@@ -22235,7 +22235,7 @@
         <v>9.20199966430664</v>
       </c>
       <c r="G754" t="n">
-        <v>7.16661643981934</v>
+        <v>7.16661596298218</v>
       </c>
       <c r="H754" t="n">
         <v>1386476</v>
@@ -22293,7 +22293,7 @@
         <v>9.14400005340576</v>
       </c>
       <c r="G756" t="n">
-        <v>7.12144660949707</v>
+        <v>7.12144613265991</v>
       </c>
       <c r="H756" t="n">
         <v>1431356</v>
@@ -22322,7 +22322,7 @@
         <v>8.98400020599365</v>
       </c>
       <c r="G757" t="n">
-        <v>6.99683666229248</v>
+        <v>6.99683618545532</v>
       </c>
       <c r="H757" t="n">
         <v>1069839</v>
@@ -22351,7 +22351,7 @@
         <v>8.92599964141846</v>
       </c>
       <c r="G758" t="n">
-        <v>6.95166492462158</v>
+        <v>6.95166540145874</v>
       </c>
       <c r="H758" t="n">
         <v>1205149</v>
@@ -22409,7 +22409,7 @@
         <v>8.67800045013428</v>
       </c>
       <c r="G760" t="n">
-        <v>6.75852060317993</v>
+        <v>6.75852012634277</v>
       </c>
       <c r="H760" t="n">
         <v>1544396</v>
@@ -22438,7 +22438,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G761" t="n">
-        <v>6.79122972488403</v>
+        <v>6.79123067855835</v>
       </c>
       <c r="H761" t="n">
         <v>3192777</v>
@@ -22467,7 +22467,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G762" t="n">
-        <v>6.67440748214722</v>
+        <v>6.67440795898438</v>
       </c>
       <c r="H762" t="n">
         <v>1360582</v>
@@ -22554,7 +22554,7 @@
         <v>8.64599990844727</v>
       </c>
       <c r="G765" t="n">
-        <v>6.73359823226929</v>
+        <v>6.73359870910645</v>
       </c>
       <c r="H765" t="n">
         <v>673720</v>
@@ -22583,7 +22583,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>6.97035789489746</v>
+        <v>6.9703574180603</v>
       </c>
       <c r="H766" t="n">
         <v>1340515</v>
@@ -22612,7 +22612,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="n">
-        <v>7.0092978477478</v>
+        <v>7.00929737091064</v>
       </c>
       <c r="H767" t="n">
         <v>975227</v>
@@ -22641,7 +22641,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G768" t="n">
-        <v>7.30368852615356</v>
+        <v>7.30368757247925</v>
       </c>
       <c r="H768" t="n">
         <v>2435460</v>
@@ -22670,7 +22670,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G769" t="n">
-        <v>7.34106969833374</v>
+        <v>7.34107065200806</v>
       </c>
       <c r="H769" t="n">
         <v>2297944</v>
@@ -22699,7 +22699,7 @@
         <v>9.35799980163574</v>
       </c>
       <c r="G770" t="n">
-        <v>7.28811120986938</v>
+        <v>7.28811073303223</v>
       </c>
       <c r="H770" t="n">
         <v>1569621</v>
@@ -22786,7 +22786,7 @@
         <v>9.45199966430664</v>
       </c>
       <c r="G773" t="n">
-        <v>7.36132001876831</v>
+        <v>7.36131858825684</v>
       </c>
       <c r="H773" t="n">
         <v>1035601</v>
@@ -22815,7 +22815,7 @@
         <v>9.98400020599365</v>
       </c>
       <c r="G774" t="n">
-        <v>7.77564811706543</v>
+        <v>7.77564716339111</v>
       </c>
       <c r="H774" t="n">
         <v>2817294</v>
@@ -22844,7 +22844,7 @@
         <v>9.81400012969971</v>
       </c>
       <c r="G775" t="n">
-        <v>7.64324855804443</v>
+        <v>7.64324951171875</v>
       </c>
       <c r="H775" t="n">
         <v>1788822</v>
@@ -22902,7 +22902,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G777" t="n">
-        <v>7.67128610610962</v>
+        <v>7.67128705978394</v>
       </c>
       <c r="H777" t="n">
         <v>636119</v>
@@ -22931,7 +22931,7 @@
         <v>9.75</v>
       </c>
       <c r="G778" t="n">
-        <v>7.59340572357178</v>
+        <v>7.59340476989746</v>
       </c>
       <c r="H778" t="n">
         <v>2227314</v>
@@ -22960,7 +22960,7 @@
         <v>9.77600002288818</v>
       </c>
       <c r="G779" t="n">
-        <v>7.61365365982056</v>
+        <v>7.61365413665771</v>
       </c>
       <c r="H779" t="n">
         <v>1141108</v>
@@ -22989,7 +22989,7 @@
         <v>9.80399990081787</v>
       </c>
       <c r="G780" t="n">
-        <v>7.6354603767395</v>
+        <v>7.63546133041382</v>
       </c>
       <c r="H780" t="n">
         <v>1718367</v>
@@ -23018,7 +23018,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G781" t="n">
-        <v>7.67128610610962</v>
+        <v>7.67128705978394</v>
       </c>
       <c r="H781" t="n">
         <v>1045527</v>
@@ -23076,7 +23076,7 @@
         <v>9.74400043487549</v>
       </c>
       <c r="G783" t="n">
-        <v>7.58873271942139</v>
+        <v>7.58873224258423</v>
       </c>
       <c r="H783" t="n">
         <v>1303463</v>
@@ -23105,7 +23105,7 @@
         <v>9.71599960327148</v>
       </c>
       <c r="G784" t="n">
-        <v>7.56692504882812</v>
+        <v>7.56692600250244</v>
       </c>
       <c r="H784" t="n">
         <v>1186119</v>
@@ -23134,7 +23134,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G785" t="n">
-        <v>7.38935661315918</v>
+        <v>7.3893575668335</v>
       </c>
       <c r="H785" t="n">
         <v>1747399</v>
@@ -23192,7 +23192,7 @@
         <v>9.68400001525879</v>
       </c>
       <c r="G787" t="n">
-        <v>7.54200458526611</v>
+        <v>7.54200410842896</v>
       </c>
       <c r="H787" t="n">
         <v>2237986</v>
@@ -23221,7 +23221,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>7.63234567642212</v>
+        <v>7.63234615325928</v>
       </c>
       <c r="H788" t="n">
         <v>1925351</v>
@@ -23279,7 +23279,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G790" t="n">
-        <v>7.51863956451416</v>
+        <v>7.518639087677</v>
       </c>
       <c r="H790" t="n">
         <v>1606565</v>
@@ -23337,7 +23337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>7.63234567642212</v>
+        <v>7.63234615325928</v>
       </c>
       <c r="H792" t="n">
         <v>1134194</v>
@@ -23395,7 +23395,7 @@
         <v>10.3850002288818</v>
       </c>
       <c r="G794" t="n">
-        <v>8.08795070648193</v>
+        <v>8.08794975280762</v>
       </c>
       <c r="H794" t="n">
         <v>2774829</v>
@@ -23453,7 +23453,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G796" t="n">
-        <v>8.13857269287109</v>
+        <v>8.13857173919678</v>
       </c>
       <c r="H796" t="n">
         <v>2076813</v>
@@ -23482,7 +23482,7 @@
         <v>10.6049995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>8.2592887878418</v>
+        <v>8.25928783416748</v>
       </c>
       <c r="H797" t="n">
         <v>1945920</v>
@@ -23511,7 +23511,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G798" t="n">
-        <v>8.07626819610596</v>
+        <v>8.07626914978027</v>
       </c>
       <c r="H798" t="n">
         <v>1758371</v>
@@ -23569,7 +23569,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G800" t="n">
-        <v>7.78031969070435</v>
+        <v>7.78031873703003</v>
       </c>
       <c r="H800" t="n">
         <v>1528819</v>
@@ -23598,7 +23598,7 @@
         <v>10.1149997711182</v>
       </c>
       <c r="G801" t="n">
-        <v>7.87766981124878</v>
+        <v>7.8776707649231</v>
       </c>
       <c r="H801" t="n">
         <v>969648</v>
@@ -23627,7 +23627,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G802" t="n">
-        <v>7.97112846374512</v>
+        <v>7.9711275100708</v>
       </c>
       <c r="H802" t="n">
         <v>895345</v>
@@ -23801,7 +23801,7 @@
         <v>11.3249998092651</v>
       </c>
       <c r="G808" t="n">
-        <v>8.82003307342529</v>
+        <v>8.82003211975098</v>
       </c>
       <c r="H808" t="n">
         <v>2716995</v>
@@ -23917,7 +23917,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G812" t="n">
-        <v>8.94074726104736</v>
+        <v>8.94074821472168</v>
       </c>
       <c r="H812" t="n">
         <v>1506561</v>
@@ -23975,7 +23975,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>8.83950233459473</v>
+        <v>8.83950328826904</v>
       </c>
       <c r="H814" t="n">
         <v>1299960</v>
@@ -24004,7 +24004,7 @@
         <v>11.414999961853</v>
       </c>
       <c r="G815" t="n">
-        <v>8.89012432098389</v>
+        <v>8.8901252746582</v>
       </c>
       <c r="H815" t="n">
         <v>1150336</v>
@@ -24062,7 +24062,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>9.03420639038086</v>
+        <v>9.03420543670654</v>
       </c>
       <c r="H817" t="n">
         <v>1302193</v>
@@ -24091,7 +24091,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>8.97579383850098</v>
+        <v>8.97579479217529</v>
       </c>
       <c r="H818" t="n">
         <v>1515731</v>
@@ -24149,7 +24149,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>9.03420639038086</v>
+        <v>9.03420543670654</v>
       </c>
       <c r="H820" t="n">
         <v>1173045</v>
@@ -24207,7 +24207,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G822" t="n">
-        <v>8.83950233459473</v>
+        <v>8.83950328826904</v>
       </c>
       <c r="H822" t="n">
         <v>1630799</v>
@@ -24294,7 +24294,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G825" t="n">
-        <v>9.01862812042236</v>
+        <v>9.01862907409668</v>
       </c>
       <c r="H825" t="n">
         <v>1208089</v>
@@ -24323,7 +24323,7 @@
         <v>11.7250003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>9.13155746459961</v>
+        <v>9.13155651092529</v>
       </c>
       <c r="H826" t="n">
         <v>1938732</v>
@@ -24352,7 +24352,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G827" t="n">
-        <v>9.23669528961182</v>
+        <v>9.23669624328613</v>
       </c>
       <c r="H827" t="n">
         <v>2343980</v>
@@ -24410,7 +24410,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G829" t="n">
-        <v>9.26006031036377</v>
+        <v>9.26006126403809</v>
       </c>
       <c r="H829" t="n">
         <v>1825749</v>
@@ -24439,7 +24439,7 @@
         <v>11.8649997711182</v>
       </c>
       <c r="G830" t="n">
-        <v>9.24059104919434</v>
+        <v>9.24059009552002</v>
       </c>
       <c r="H830" t="n">
         <v>1520646</v>
@@ -24555,7 +24555,7 @@
         <v>11.7049999237061</v>
       </c>
       <c r="G834" t="n">
-        <v>9.11598110198975</v>
+        <v>9.11598014831543</v>
       </c>
       <c r="H834" t="n">
         <v>1851448</v>
@@ -24787,7 +24787,7 @@
         <v>11.875</v>
       </c>
       <c r="G842" t="n">
-        <v>9.48481559753418</v>
+        <v>9.4848165512085</v>
       </c>
       <c r="H842" t="n">
         <v>2291062</v>
@@ -24816,7 +24816,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G843" t="n">
-        <v>9.43289947509766</v>
+        <v>9.43290042877197</v>
       </c>
       <c r="H843" t="n">
         <v>1259655</v>
@@ -24845,7 +24845,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G844" t="n">
-        <v>9.61660480499268</v>
+        <v>9.61660575866699</v>
       </c>
       <c r="H844" t="n">
         <v>1827623</v>
@@ -24903,7 +24903,7 @@
         <v>11.7349996566772</v>
       </c>
       <c r="G846" t="n">
-        <v>9.37299537658691</v>
+        <v>9.37299633026123</v>
       </c>
       <c r="H846" t="n">
         <v>2397719</v>
@@ -24932,7 +24932,7 @@
         <v>11.4250001907349</v>
       </c>
       <c r="G847" t="n">
-        <v>9.12539100646973</v>
+        <v>9.12539196014404</v>
       </c>
       <c r="H847" t="n">
         <v>3542588</v>
@@ -24961,7 +24961,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G848" t="n">
-        <v>9.05749988555908</v>
+        <v>9.0575008392334</v>
       </c>
       <c r="H848" t="n">
         <v>3489736</v>
@@ -25019,7 +25019,7 @@
         <v>10.25</v>
       </c>
       <c r="G850" t="n">
-        <v>8.18689441680908</v>
+        <v>8.18689346313477</v>
       </c>
       <c r="H850" t="n">
         <v>9379536</v>
@@ -25077,7 +25077,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G852" t="n">
-        <v>7.97123956680298</v>
+        <v>7.97123861312866</v>
       </c>
       <c r="H852" t="n">
         <v>5435251</v>
@@ -25164,7 +25164,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G855" t="n">
-        <v>7.82427501678467</v>
+        <v>7.82427310943604</v>
       </c>
       <c r="H855" t="n">
         <v>4768720</v>
@@ -25193,7 +25193,7 @@
         <v>9.68200016021729</v>
       </c>
       <c r="G856" t="n">
-        <v>7.73321962356567</v>
+        <v>7.73322057723999</v>
       </c>
       <c r="H856" t="n">
         <v>4453381</v>
@@ -25222,7 +25222,7 @@
         <v>9.91800022125244</v>
       </c>
       <c r="G857" t="n">
-        <v>7.92171859741211</v>
+        <v>7.92171764373779</v>
       </c>
       <c r="H857" t="n">
         <v>3773414</v>
@@ -25338,7 +25338,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G861" t="n">
-        <v>7.79552173614502</v>
+        <v>7.7955207824707</v>
       </c>
       <c r="H861" t="n">
         <v>3096684</v>
@@ -25367,7 +25367,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G862" t="n">
-        <v>7.71085643768311</v>
+        <v>7.71085548400879</v>
       </c>
       <c r="H862" t="n">
         <v>4209402</v>
@@ -25483,7 +25483,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G866" t="n">
-        <v>7.38976955413818</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H866" t="n">
         <v>3383104</v>
@@ -25512,7 +25512,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G867" t="n">
-        <v>7.38976955413818</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H867" t="n">
         <v>2186192</v>
@@ -25541,7 +25541,7 @@
         <v>9.27600002288818</v>
       </c>
       <c r="G868" t="n">
-        <v>7.40893936157227</v>
+        <v>7.40894031524658</v>
       </c>
       <c r="H868" t="n">
         <v>3447972</v>
@@ -25570,7 +25570,7 @@
         <v>9.15200042724609</v>
       </c>
       <c r="G869" t="n">
-        <v>7.30989789962769</v>
+        <v>7.30989742279053</v>
       </c>
       <c r="H869" t="n">
         <v>2728437</v>
@@ -25599,7 +25599,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G870" t="n">
-        <v>7.48881149291992</v>
+        <v>7.48881244659424</v>
       </c>
       <c r="H870" t="n">
         <v>3609501</v>
@@ -25628,7 +25628,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G871" t="n">
-        <v>7.48401880264282</v>
+        <v>7.48401832580566</v>
       </c>
       <c r="H871" t="n">
         <v>3039397</v>
@@ -25657,7 +25657,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G872" t="n">
-        <v>7.42331504821777</v>
+        <v>7.42331552505493</v>
       </c>
       <c r="H872" t="n">
         <v>2716855</v>
@@ -25744,7 +25744,7 @@
         <v>9.32400035858154</v>
       </c>
       <c r="G875" t="n">
-        <v>7.44727802276611</v>
+        <v>7.44727849960327</v>
       </c>
       <c r="H875" t="n">
         <v>2366989</v>
@@ -25773,7 +25773,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G876" t="n">
-        <v>7.30830049514771</v>
+        <v>7.30830001831055</v>
       </c>
       <c r="H876" t="n">
         <v>2609119</v>
@@ -25831,7 +25831,7 @@
         <v>9.04599952697754</v>
       </c>
       <c r="G878" t="n">
-        <v>7.22523355484009</v>
+        <v>7.22523307800293</v>
       </c>
       <c r="H878" t="n">
         <v>2560254</v>
@@ -25860,7 +25860,7 @@
         <v>9.10400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>7.27155876159668</v>
+        <v>7.27155923843384</v>
       </c>
       <c r="H879" t="n">
         <v>1514267</v>
@@ -25889,7 +25889,7 @@
         <v>9.31799983978271</v>
       </c>
       <c r="G880" t="n">
-        <v>7.44248676300049</v>
+        <v>7.44248533248901</v>
       </c>
       <c r="H880" t="n">
         <v>3120201</v>
@@ -25947,7 +25947,7 @@
         <v>9.54800033569336</v>
       </c>
       <c r="G882" t="n">
-        <v>7.62619066238403</v>
+        <v>7.62619113922119</v>
       </c>
       <c r="H882" t="n">
         <v>4544189</v>
@@ -26121,7 +26121,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G888" t="n">
-        <v>7.83545589447021</v>
+        <v>7.83545684814453</v>
       </c>
       <c r="H888" t="n">
         <v>2776001</v>
@@ -26150,7 +26150,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G889" t="n">
-        <v>7.8753924369812</v>
+        <v>7.87539339065552</v>
       </c>
       <c r="H889" t="n">
         <v>1816841</v>
@@ -26179,7 +26179,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>7.91532850265503</v>
+        <v>7.91532945632935</v>
       </c>
       <c r="H890" t="n">
         <v>2445491</v>
@@ -26208,7 +26208,7 @@
         <v>10.375</v>
       </c>
       <c r="G891" t="n">
-        <v>8.28673267364502</v>
+        <v>8.28673362731934</v>
       </c>
       <c r="H891" t="n">
         <v>3795422</v>
@@ -26295,7 +26295,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G894" t="n">
-        <v>8.23082447052002</v>
+        <v>8.2308235168457</v>
       </c>
       <c r="H894" t="n">
         <v>3674591</v>
@@ -26324,7 +26324,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G895" t="n">
-        <v>8.07507228851318</v>
+        <v>8.07507133483887</v>
       </c>
       <c r="H895" t="n">
         <v>20394805</v>
@@ -26672,7 +26672,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G907" t="n">
-        <v>7.78114175796509</v>
+        <v>7.7811427116394</v>
       </c>
       <c r="H907" t="n">
         <v>4500422</v>
@@ -26701,7 +26701,7 @@
         <v>9.48200035095215</v>
       </c>
       <c r="G908" t="n">
-        <v>7.57347631454468</v>
+        <v>7.57347583770752</v>
       </c>
       <c r="H908" t="n">
         <v>3994996</v>
@@ -26730,7 +26730,7 @@
         <v>9.32400035858154</v>
       </c>
       <c r="G909" t="n">
-        <v>7.44727802276611</v>
+        <v>7.44727849960327</v>
       </c>
       <c r="H909" t="n">
         <v>2346327</v>
@@ -26788,7 +26788,7 @@
         <v>8.99199962615967</v>
       </c>
       <c r="G911" t="n">
-        <v>7.18210172653198</v>
+        <v>7.1821026802063</v>
       </c>
       <c r="H911" t="n">
         <v>5318727</v>
@@ -26817,7 +26817,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>7.2923264503479</v>
+        <v>7.29232597351074</v>
       </c>
       <c r="H912" t="n">
         <v>3452685</v>
@@ -26875,7 +26875,7 @@
         <v>8.70600032806396</v>
       </c>
       <c r="G914" t="n">
-        <v>6.95366716384888</v>
+        <v>6.95366764068604</v>
       </c>
       <c r="H914" t="n">
         <v>3818373</v>
@@ -26904,7 +26904,7 @@
         <v>8.90200042724609</v>
       </c>
       <c r="G915" t="n">
-        <v>7.11021757125854</v>
+        <v>7.11021709442139</v>
       </c>
       <c r="H915" t="n">
         <v>3135920</v>
@@ -26962,7 +26962,7 @@
         <v>9.32199954986572</v>
       </c>
       <c r="G917" t="n">
-        <v>7.44567966461182</v>
+        <v>7.44568014144897</v>
       </c>
       <c r="H917" t="n">
         <v>4116961</v>
@@ -26991,7 +26991,7 @@
         <v>8.94400024414062</v>
       </c>
       <c r="G918" t="n">
-        <v>7.14376449584961</v>
+        <v>7.14376401901245</v>
       </c>
       <c r="H918" t="n">
         <v>3640894</v>
@@ -27049,7 +27049,7 @@
         <v>8.95199966430664</v>
       </c>
       <c r="G920" t="n">
-        <v>7.15015411376953</v>
+        <v>7.15015363693237</v>
       </c>
       <c r="H920" t="n">
         <v>4222607</v>
@@ -27136,7 +27136,7 @@
         <v>8.81799983978271</v>
       </c>
       <c r="G923" t="n">
-        <v>7.04312419891357</v>
+        <v>7.04312372207642</v>
       </c>
       <c r="H923" t="n">
         <v>2812033</v>
@@ -27165,7 +27165,7 @@
         <v>8.7519998550415</v>
       </c>
       <c r="G924" t="n">
-        <v>6.9904088973999</v>
+        <v>6.99040842056274</v>
       </c>
       <c r="H924" t="n">
         <v>1609495</v>
@@ -27223,7 +27223,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G926" t="n">
-        <v>7.38976955413818</v>
+        <v>7.38977003097534</v>
       </c>
       <c r="H926" t="n">
         <v>3676274</v>
@@ -27252,7 +27252,7 @@
         <v>8.97599983215332</v>
       </c>
       <c r="G927" t="n">
-        <v>7.16932153701782</v>
+        <v>7.1693229675293</v>
       </c>
       <c r="H927" t="n">
         <v>2682189</v>
@@ -27281,7 +27281,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>7.30830049514771</v>
+        <v>7.30830001831055</v>
       </c>
       <c r="H928" t="n">
         <v>1790407</v>
@@ -27310,7 +27310,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G929" t="n">
-        <v>7.4776291847229</v>
+        <v>7.47762966156006</v>
       </c>
       <c r="H929" t="n">
         <v>2993658</v>
@@ -27339,7 +27339,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G930" t="n">
-        <v>7.45207023620605</v>
+        <v>7.45207118988037</v>
       </c>
       <c r="H930" t="n">
         <v>3565618</v>
@@ -27368,7 +27368,7 @@
         <v>9.55799961090088</v>
       </c>
       <c r="G931" t="n">
-        <v>7.63417863845825</v>
+        <v>7.63417720794678</v>
       </c>
       <c r="H931" t="n">
         <v>3624408</v>
@@ -27426,7 +27426,7 @@
         <v>9.43599987030029</v>
       </c>
       <c r="G933" t="n">
-        <v>7.53673505783081</v>
+        <v>7.53673362731934</v>
       </c>
       <c r="H933" t="n">
         <v>1759671</v>
@@ -27455,7 +27455,7 @@
         <v>9.30799961090088</v>
       </c>
       <c r="G934" t="n">
-        <v>7.43449878692627</v>
+        <v>7.43449831008911</v>
       </c>
       <c r="H934" t="n">
         <v>2299813</v>
@@ -27600,7 +27600,7 @@
         <v>9.51399993896484</v>
       </c>
       <c r="G939" t="n">
-        <v>7.59903478622437</v>
+        <v>7.59903526306152</v>
       </c>
       <c r="H939" t="n">
         <v>5535766</v>
@@ -27658,7 +27658,7 @@
         <v>9.42399978637695</v>
       </c>
       <c r="G941" t="n">
-        <v>7.52714967727661</v>
+        <v>7.52715015411377</v>
       </c>
       <c r="H941" t="n">
         <v>4089597</v>
@@ -27687,7 +27687,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G942" t="n">
-        <v>7.8674054145813</v>
+        <v>7.86740589141846</v>
       </c>
       <c r="H942" t="n">
         <v>4696889</v>
@@ -27716,7 +27716,7 @@
         <v>9.76399993896484</v>
       </c>
       <c r="G943" t="n">
-        <v>7.79871463775635</v>
+        <v>7.79871559143066</v>
       </c>
       <c r="H943" t="n">
         <v>2951390</v>
@@ -27745,7 +27745,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G944" t="n">
-        <v>7.47603225708008</v>
+        <v>7.47603130340576</v>
       </c>
       <c r="H944" t="n">
         <v>3957734</v>
@@ -27774,7 +27774,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G945" t="n">
-        <v>7.50798082351685</v>
+        <v>7.50798034667969</v>
       </c>
       <c r="H945" t="n">
         <v>2575989</v>
@@ -27803,7 +27803,7 @@
         <v>9.68400001525879</v>
       </c>
       <c r="G946" t="n">
-        <v>7.73481845855713</v>
+        <v>7.73481750488281</v>
       </c>
       <c r="H946" t="n">
         <v>3294725</v>
@@ -27832,7 +27832,7 @@
         <v>9.91800022125244</v>
       </c>
       <c r="G947" t="n">
-        <v>7.92171859741211</v>
+        <v>7.92171764373779</v>
       </c>
       <c r="H947" t="n">
         <v>8266753</v>
@@ -27861,7 +27861,7 @@
         <v>9.63199996948242</v>
       </c>
       <c r="G948" t="n">
-        <v>7.69328355789185</v>
+        <v>7.69328308105469</v>
       </c>
       <c r="H948" t="n">
         <v>3325238</v>
@@ -27919,7 +27919,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G950" t="n">
-        <v>7.47603225708008</v>
+        <v>7.47603130340576</v>
       </c>
       <c r="H950" t="n">
         <v>2511171</v>
@@ -27977,7 +27977,7 @@
         <v>9.61800003051758</v>
       </c>
       <c r="G952" t="n">
-        <v>7.6821026802063</v>
+        <v>7.68210220336914</v>
       </c>
       <c r="H952" t="n">
         <v>2277483</v>
@@ -28035,7 +28035,7 @@
         <v>9.60400009155273</v>
       </c>
       <c r="G954" t="n">
-        <v>7.67091989517212</v>
+        <v>7.67091941833496</v>
       </c>
       <c r="H954" t="n">
         <v>3812669</v>
@@ -28064,7 +28064,7 @@
         <v>9.36600017547607</v>
       </c>
       <c r="G955" t="n">
-        <v>7.48082447052002</v>
+        <v>7.48082399368286</v>
       </c>
       <c r="H955" t="n">
         <v>5487603</v>
@@ -28151,7 +28151,7 @@
         <v>9.67800045013428</v>
       </c>
       <c r="G958" t="n">
-        <v>7.73002624511719</v>
+        <v>7.73002433776855</v>
       </c>
       <c r="H958" t="n">
         <v>1695957</v>
@@ -28180,7 +28180,7 @@
         <v>9.22799968719482</v>
       </c>
       <c r="G959" t="n">
-        <v>7.37060022354126</v>
+        <v>7.37060117721558</v>
       </c>
       <c r="H959" t="n">
         <v>5305999</v>
@@ -28209,7 +28209,7 @@
         <v>9.3120002746582</v>
       </c>
       <c r="G960" t="n">
-        <v>7.43769264221191</v>
+        <v>7.43769359588623</v>
       </c>
       <c r="H960" t="n">
         <v>4104628</v>
@@ -28238,7 +28238,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G961" t="n">
-        <v>7.60382795333862</v>
+        <v>7.60382747650146</v>
       </c>
       <c r="H961" t="n">
         <v>2228905</v>
@@ -28296,7 +28296,7 @@
         <v>9.5959997177124</v>
       </c>
       <c r="G963" t="n">
-        <v>7.66452980041504</v>
+        <v>7.6645302772522</v>
       </c>
       <c r="H963" t="n">
         <v>2791419</v>
@@ -28383,7 +28383,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G966" t="n">
-        <v>8.03513622283936</v>
+        <v>8.03513717651367</v>
       </c>
       <c r="H966" t="n">
         <v>4312250</v>
@@ -28441,7 +28441,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G968" t="n">
-        <v>8.24280452728271</v>
+        <v>8.2428035736084</v>
       </c>
       <c r="H968" t="n">
         <v>3726083</v>
@@ -28499,7 +28499,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G970" t="n">
-        <v>8.14695739746094</v>
+        <v>8.14695644378662</v>
       </c>
       <c r="H970" t="n">
         <v>2753561</v>
@@ -28528,7 +28528,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G971" t="n">
-        <v>8.13497734069824</v>
+        <v>8.13497638702393</v>
       </c>
       <c r="H971" t="n">
         <v>2606880</v>
@@ -28586,7 +28586,7 @@
         <v>10.4049997329712</v>
       </c>
       <c r="G973" t="n">
-        <v>8.31069564819336</v>
+        <v>8.31069469451904</v>
       </c>
       <c r="H973" t="n">
         <v>2851886</v>
@@ -28615,7 +28615,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>8.30670166015625</v>
+        <v>8.30670261383057</v>
       </c>
       <c r="H974" t="n">
         <v>2791666</v>
@@ -28702,7 +28702,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G977" t="n">
-        <v>8.29072761535645</v>
+        <v>8.29072856903076</v>
       </c>
       <c r="H977" t="n">
         <v>2778678</v>
@@ -28731,7 +28731,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>8.52635097503662</v>
+        <v>8.5263500213623</v>
       </c>
       <c r="H978" t="n">
         <v>4481429</v>
@@ -28789,7 +28789,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G980" t="n">
-        <v>8.66612720489502</v>
+        <v>8.66612815856934</v>
       </c>
       <c r="H980" t="n">
         <v>5778319</v>
@@ -28847,7 +28847,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G982" t="n">
-        <v>8.79392147064209</v>
+        <v>8.79392242431641</v>
       </c>
       <c r="H982" t="n">
         <v>3106214</v>
@@ -28876,7 +28876,7 @@
         <v>11.1350002288818</v>
       </c>
       <c r="G983" t="n">
-        <v>8.89376258850098</v>
+        <v>8.89376354217529</v>
       </c>
       <c r="H983" t="n">
         <v>2887920</v>
@@ -28905,7 +28905,7 @@
         <v>11.4350004196167</v>
       </c>
       <c r="G984" t="n">
-        <v>9.13337898254395</v>
+        <v>9.13337993621826</v>
       </c>
       <c r="H984" t="n">
         <v>4526531</v>
@@ -28934,7 +28934,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G985" t="n">
-        <v>9.18929004669189</v>
+        <v>9.18928909301758</v>
       </c>
       <c r="H985" t="n">
         <v>4781545</v>
@@ -29050,7 +29050,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G989" t="n">
-        <v>8.96963977813721</v>
+        <v>8.96964073181152</v>
       </c>
       <c r="H989" t="n">
         <v>3925640</v>
@@ -29108,7 +29108,7 @@
         <v>11.3149995803833</v>
       </c>
       <c r="G991" t="n">
-        <v>9.03753089904785</v>
+        <v>9.03753185272217</v>
       </c>
       <c r="H991" t="n">
         <v>2809996</v>
@@ -29137,7 +29137,7 @@
         <v>11.4750003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>9.16532802581787</v>
+        <v>9.16532707214355</v>
       </c>
       <c r="H992" t="n">
         <v>5004718</v>
@@ -29253,7 +29253,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G996" t="n">
-        <v>9.18929004669189</v>
+        <v>9.18928909301758</v>
       </c>
       <c r="H996" t="n">
         <v>2523570</v>
@@ -29311,7 +29311,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G998" t="n">
-        <v>8.88976955413818</v>
+        <v>8.88976860046387</v>
       </c>
       <c r="H998" t="n">
         <v>3788755</v>
@@ -29340,7 +29340,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>8.9456787109375</v>
+        <v>8.94567966461182</v>
       </c>
       <c r="H999" t="n">
         <v>3174901</v>
@@ -29398,7 +29398,7 @@
         <v>11.2749996185303</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.00558185577393</v>
+        <v>9.00558376312256</v>
       </c>
       <c r="H1001" t="n">
         <v>2053937</v>
@@ -29485,7 +29485,7 @@
         <v>11.2250003814697</v>
       </c>
       <c r="G1004" t="n">
-        <v>8.96564769744873</v>
+        <v>8.96564674377441</v>
       </c>
       <c r="H1004" t="n">
         <v>2474084</v>
@@ -29543,7 +29543,7 @@
         <v>11.1750001907349</v>
       </c>
       <c r="G1006" t="n">
-        <v>8.9257116317749</v>
+        <v>8.92571067810059</v>
       </c>
       <c r="H1006" t="n">
         <v>2853173</v>
@@ -29601,7 +29601,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>8.9456787109375</v>
+        <v>8.94567966461182</v>
       </c>
       <c r="H1008" t="n">
         <v>1694693</v>
@@ -29630,7 +29630,7 @@
         <v>11</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.78593444824219</v>
+        <v>8.7859354019165</v>
       </c>
       <c r="H1009" t="n">
         <v>2151620</v>
@@ -29659,7 +29659,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.70606327056885</v>
+        <v>8.70606231689453</v>
       </c>
       <c r="H1010" t="n">
         <v>2991662</v>
@@ -29746,7 +29746,7 @@
         <v>10.914999961853</v>
       </c>
       <c r="G1013" t="n">
-        <v>8.71804332733154</v>
+        <v>8.71804428100586</v>
       </c>
       <c r="H1013" t="n">
         <v>1113622</v>
@@ -29775,7 +29775,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1014" t="n">
-        <v>8.60222911834717</v>
+        <v>8.60222816467285</v>
       </c>
       <c r="H1014" t="n">
         <v>1398596</v>
@@ -29891,7 +29891,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.49839496612549</v>
+        <v>8.4983959197998</v>
       </c>
       <c r="H1018" t="n">
         <v>2208761</v>
@@ -29920,7 +29920,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G1019" t="n">
-        <v>8.7619743347168</v>
+        <v>8.76197338104248</v>
       </c>
       <c r="H1019" t="n">
         <v>2603454</v>
@@ -29949,7 +29949,7 @@
         <v>11.1450004577637</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.9017505645752</v>
+        <v>8.90174961090088</v>
       </c>
       <c r="H1020" t="n">
         <v>2810469</v>
@@ -29978,7 +29978,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1021" t="n">
-        <v>9.23321914672852</v>
+        <v>9.23322010040283</v>
       </c>
       <c r="H1021" t="n">
         <v>5413395</v>
@@ -30007,7 +30007,7 @@
         <v>11.2049999237061</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.94967365264893</v>
+        <v>8.94967269897461</v>
       </c>
       <c r="H1022" t="n">
         <v>2994173</v>
@@ -30036,7 +30036,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.813889503479</v>
+        <v>8.81389045715332</v>
       </c>
       <c r="H1023" t="n">
         <v>1921010</v>
@@ -30123,7 +30123,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.96963977813721</v>
+        <v>8.96964073181152</v>
       </c>
       <c r="H1026" t="n">
         <v>2056874</v>
@@ -30181,7 +30181,7 @@
         <v>10.9949998855591</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.78194236755371</v>
+        <v>8.78194046020508</v>
       </c>
       <c r="H1028" t="n">
         <v>2076115</v>
@@ -30268,7 +30268,7 @@
         <v>10.9650001525879</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.75797939300537</v>
+        <v>8.75798034667969</v>
       </c>
       <c r="H1031" t="n">
         <v>2744367</v>
@@ -30297,7 +30297,7 @@
         <v>10.9849996566772</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.77395439147949</v>
+        <v>8.77395343780518</v>
       </c>
       <c r="H1032" t="n">
         <v>1962560</v>
@@ -30355,7 +30355,7 @@
         <v>10.9849996566772</v>
       </c>
       <c r="G1034" t="n">
-        <v>8.77395439147949</v>
+        <v>8.77395343780518</v>
       </c>
       <c r="H1034" t="n">
         <v>3705420</v>
@@ -30413,7 +30413,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.76995944976807</v>
+        <v>8.76996040344238</v>
       </c>
       <c r="H1036" t="n">
         <v>3530447</v>
@@ -30471,7 +30471,7 @@
         <v>10.8149995803833</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.6381721496582</v>
+        <v>8.63817119598389</v>
       </c>
       <c r="H1038" t="n">
         <v>1938612</v>
@@ -30529,7 +30529,7 @@
         <v>11.1850004196167</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.9336986541748</v>
+        <v>8.93369960784912</v>
       </c>
       <c r="H1040" t="n">
         <v>3365961</v>
@@ -30616,7 +30616,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1043" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1043" t="n">
         <v>3510236</v>
@@ -30674,7 +30674,7 @@
         <v>10.9549999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.74999141693115</v>
+        <v>8.74999237060547</v>
       </c>
       <c r="H1045" t="n">
         <v>7473511</v>
@@ -30732,7 +30732,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.72203731536865</v>
+        <v>8.72203636169434</v>
       </c>
       <c r="H1047" t="n">
         <v>2991609</v>
@@ -30906,7 +30906,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1053" t="n">
-        <v>8.03513622283936</v>
+        <v>8.03513717651367</v>
       </c>
       <c r="H1053" t="n">
         <v>7262508</v>
@@ -31051,7 +31051,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1058" t="n">
-        <v>7.2923264503479</v>
+        <v>7.29232597351074</v>
       </c>
       <c r="H1058" t="n">
         <v>5987425</v>
@@ -31080,7 +31080,7 @@
         <v>9.33399963378906</v>
       </c>
       <c r="G1059" t="n">
-        <v>7.45526552200317</v>
+        <v>7.45526456832886</v>
       </c>
       <c r="H1059" t="n">
         <v>6715202</v>
@@ -31109,7 +31109,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1060" t="n">
-        <v>7.06868410110474</v>
+        <v>7.06868457794189</v>
       </c>
       <c r="H1060" t="n">
         <v>7522341</v>
@@ -31167,7 +31167,7 @@
         <v>8.97399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.16772556304932</v>
+        <v>7.16772508621216</v>
       </c>
       <c r="H1062" t="n">
         <v>6835049</v>
@@ -31196,7 +31196,7 @@
         <v>8.11800003051758</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.48402070999146</v>
+        <v>6.4840202331543</v>
       </c>
       <c r="H1063" t="n">
         <v>9088534</v>
@@ -31254,7 +31254,7 @@
         <v>7.87599992752075</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.29072904586792</v>
+        <v>6.29072952270508</v>
       </c>
       <c r="H1065" t="n">
         <v>8515424</v>
@@ -31283,7 +31283,7 @@
         <v>6.91800022125244</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.52555418014526</v>
+        <v>5.52555465698242</v>
       </c>
       <c r="H1066" t="n">
         <v>11037017</v>
@@ -31312,7 +31312,7 @@
         <v>7.7039999961853</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.15334892272949</v>
+        <v>6.15334939956665</v>
       </c>
       <c r="H1067" t="n">
         <v>8728518</v>
@@ -31341,7 +31341,7 @@
         <v>7.60599994659424</v>
       </c>
       <c r="G1068" t="n">
-        <v>6.07507419586182</v>
+        <v>6.07507467269897</v>
       </c>
       <c r="H1068" t="n">
         <v>9491413</v>
@@ -31399,7 +31399,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.0095796585083</v>
+        <v>6.00958013534546</v>
       </c>
       <c r="H1070" t="n">
         <v>4306496</v>
@@ -31428,7 +31428,7 @@
         <v>7.47800016403198</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.97283792495728</v>
+        <v>5.97283887863159</v>
       </c>
       <c r="H1071" t="n">
         <v>5432734</v>
@@ -31486,7 +31486,7 @@
         <v>7.47800016403198</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.97283792495728</v>
+        <v>5.97283887863159</v>
       </c>
       <c r="H1073" t="n">
         <v>6801824</v>
@@ -31544,7 +31544,7 @@
         <v>8.0959997177124</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.4664478302002</v>
+        <v>6.46644830703735</v>
       </c>
       <c r="H1075" t="n">
         <v>6663653</v>
@@ -31573,7 +31573,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G1076" t="n">
-        <v>7.05909967422485</v>
+        <v>7.0590991973877</v>
       </c>
       <c r="H1076" t="n">
         <v>4904120</v>
@@ -31602,7 +31602,7 @@
         <v>8.26799964904785</v>
       </c>
       <c r="G1077" t="n">
-        <v>6.60382843017578</v>
+        <v>6.60382795333862</v>
       </c>
       <c r="H1077" t="n">
         <v>5413314</v>
@@ -31631,7 +31631,7 @@
         <v>8.42199993133545</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.72683048248291</v>
+        <v>6.72683095932007</v>
       </c>
       <c r="H1078" t="n">
         <v>4833258</v>
@@ -31660,7 +31660,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1079" t="n">
-        <v>6.62140035629272</v>
+        <v>6.62139987945557</v>
       </c>
       <c r="H1079" t="n">
         <v>6100687</v>
@@ -31689,7 +31689,7 @@
         <v>8.28400039672852</v>
       </c>
       <c r="G1080" t="n">
-        <v>6.61660814285278</v>
+        <v>6.61660766601562</v>
       </c>
       <c r="H1080" t="n">
         <v>3960886</v>
@@ -31718,7 +31718,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.82906770706177</v>
+        <v>6.82906723022461</v>
       </c>
       <c r="H1081" t="n">
         <v>2997795</v>
@@ -31747,7 +31747,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.14855527877808</v>
+        <v>7.14855623245239</v>
       </c>
       <c r="H1082" t="n">
         <v>4108088</v>
@@ -31776,7 +31776,7 @@
         <v>9.1540002822876</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.31149625778198</v>
+        <v>7.31149530410767</v>
       </c>
       <c r="H1083" t="n">
         <v>3944078</v>
@@ -31805,7 +31805,7 @@
         <v>9.3120002746582</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.43769264221191</v>
+        <v>7.43769359588623</v>
       </c>
       <c r="H1084" t="n">
         <v>4073943</v>
@@ -31834,7 +31834,7 @@
         <v>9.44400024414062</v>
       </c>
       <c r="G1085" t="n">
-        <v>7.54312467575073</v>
+        <v>7.54312419891357</v>
       </c>
       <c r="H1085" t="n">
         <v>2782876</v>
@@ -31863,7 +31863,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.54152774810791</v>
+        <v>7.54152727127075</v>
       </c>
       <c r="H1086" t="n">
         <v>3112691</v>
@@ -31921,7 +31921,7 @@
         <v>8.83399963378906</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.05590391159058</v>
+        <v>7.05590438842773</v>
       </c>
       <c r="H1088" t="n">
         <v>3989061</v>
@@ -32008,7 +32008,7 @@
         <v>8.73200035095215</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.9744348526001</v>
+        <v>6.97443532943726</v>
       </c>
       <c r="H1091" t="n">
         <v>1843759</v>
@@ -32037,7 +32037,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.51916313171387</v>
+        <v>6.51916360855103</v>
       </c>
       <c r="H1092" t="n">
         <v>3812138</v>
@@ -32066,7 +32066,7 @@
         <v>8.75800037384033</v>
       </c>
       <c r="G1093" t="n">
-        <v>6.99520111083984</v>
+        <v>6.99520254135132</v>
       </c>
       <c r="H1093" t="n">
         <v>4516225</v>
@@ -32095,7 +32095,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.378586769104</v>
+        <v>7.37858819961548</v>
       </c>
       <c r="H1094" t="n">
         <v>3739189</v>
@@ -32124,7 +32124,7 @@
         <v>9.21199989318848</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.35782051086426</v>
+        <v>7.35782146453857</v>
       </c>
       <c r="H1095" t="n">
         <v>3046006</v>
@@ -32153,7 +32153,7 @@
         <v>9.50399971008301</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.5910472869873</v>
+        <v>7.59104776382446</v>
       </c>
       <c r="H1096" t="n">
         <v>2859434</v>
@@ -32182,7 +32182,7 @@
         <v>9.73400020599365</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.77475357055664</v>
+        <v>7.77475452423096</v>
       </c>
       <c r="H1097" t="n">
         <v>4503742</v>
@@ -32211,7 +32211,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.15494441986084</v>
+        <v>8.15494537353516</v>
       </c>
       <c r="H1098" t="n">
         <v>3932915</v>
@@ -32240,7 +32240,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>8.09903526306152</v>
+        <v>8.09903430938721</v>
       </c>
       <c r="H1099" t="n">
         <v>4848283</v>
@@ -32269,7 +32269,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.75398635864258</v>
+        <v>7.75398731231689</v>
       </c>
       <c r="H1100" t="n">
         <v>3245092</v>
@@ -32298,7 +32298,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.8753924369812</v>
+        <v>7.87539339065552</v>
       </c>
       <c r="H1101" t="n">
         <v>3644756</v>
@@ -32327,7 +32327,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.48401880264282</v>
+        <v>7.48401832580566</v>
       </c>
       <c r="H1102" t="n">
         <v>2760070</v>
@@ -32356,7 +32356,7 @@
         <v>9.43599987030029</v>
       </c>
       <c r="G1103" t="n">
-        <v>7.53673505783081</v>
+        <v>7.53673362731934</v>
       </c>
       <c r="H1103" t="n">
         <v>2286557</v>
@@ -32385,7 +32385,7 @@
         <v>9.67800045013428</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.73002624511719</v>
+        <v>7.73002433776855</v>
       </c>
       <c r="H1104" t="n">
         <v>2049636</v>
@@ -32414,7 +32414,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.97922563552856</v>
+        <v>7.97922515869141</v>
       </c>
       <c r="H1105" t="n">
         <v>2838825</v>
@@ -32443,7 +32443,7 @@
         <v>10.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>8.38657474517822</v>
+        <v>8.38657379150391</v>
       </c>
       <c r="H1106" t="n">
         <v>4240249</v>
@@ -32501,7 +32501,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G1108" t="n">
-        <v>7.92491245269775</v>
+        <v>7.92491340637207</v>
       </c>
       <c r="H1108" t="n">
         <v>3412501</v>
@@ -32530,7 +32530,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.03513622283936</v>
+        <v>8.03513717651367</v>
       </c>
       <c r="H1109" t="n">
         <v>2307002</v>
@@ -32559,7 +32559,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.17091941833496</v>
+        <v>8.17091846466064</v>
       </c>
       <c r="H1110" t="n">
         <v>2199846</v>
@@ -32820,7 +32820,7 @@
         <v>10.5050001144409</v>
       </c>
       <c r="G1119" t="n">
-        <v>8.3905668258667</v>
+        <v>8.39056777954102</v>
       </c>
       <c r="H1119" t="n">
         <v>3689423</v>
@@ -33052,7 +33052,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1127" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1127" t="n">
         <v>6001479</v>
@@ -33081,7 +33081,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.24919414520264</v>
+        <v>9.24919319152832</v>
       </c>
       <c r="H1128" t="n">
         <v>6303518</v>
@@ -33110,7 +33110,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1129" t="n">
-        <v>9.24919414520264</v>
+        <v>9.24919319152832</v>
       </c>
       <c r="H1129" t="n">
         <v>6742191</v>
@@ -33139,7 +33139,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.32906627655029</v>
+        <v>9.32906532287598</v>
       </c>
       <c r="H1130" t="n">
         <v>3791918</v>
@@ -33168,7 +33168,7 @@
         <v>12.1049995422363</v>
       </c>
       <c r="G1131" t="n">
-        <v>9.66852188110352</v>
+        <v>9.6685209274292</v>
       </c>
       <c r="H1131" t="n">
         <v>5466379</v>
@@ -33255,7 +33255,7 @@
         <v>12.1049995422363</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.66852188110352</v>
+        <v>9.6685209274292</v>
       </c>
       <c r="H1134" t="n">
         <v>6321064</v>
@@ -33313,7 +33313,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>9.90414428710938</v>
+        <v>9.90414524078369</v>
       </c>
       <c r="H1136" t="n">
         <v>2729665</v>
@@ -33342,7 +33342,7 @@
         <v>11.9049997329712</v>
       </c>
       <c r="G1137" t="n">
-        <v>9.50877666473389</v>
+        <v>9.5087776184082</v>
       </c>
       <c r="H1137" t="n">
         <v>2750768</v>
@@ -33429,7 +33429,7 @@
         <v>12.1350002288818</v>
       </c>
       <c r="G1140" t="n">
-        <v>9.69248390197754</v>
+        <v>9.69248294830322</v>
       </c>
       <c r="H1140" t="n">
         <v>2532076</v>
@@ -33487,7 +33487,7 @@
         <v>12</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.58465671539307</v>
+        <v>9.58465576171875</v>
       </c>
       <c r="H1142" t="n">
         <v>2680965</v>
@@ -33545,7 +33545,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1144" t="n">
-        <v>9.96804141998291</v>
+        <v>9.96804046630859</v>
       </c>
       <c r="H1144" t="n">
         <v>2298824</v>
@@ -33632,7 +33632,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1147" t="n">
-        <v>10.2795429229736</v>
+        <v>10.2795438766479</v>
       </c>
       <c r="H1147" t="n">
         <v>2278939</v>
@@ -33661,7 +33661,7 @@
         <v>12.4650001525879</v>
       </c>
       <c r="G1148" t="n">
-        <v>9.95606231689453</v>
+        <v>9.95606136322021</v>
       </c>
       <c r="H1148" t="n">
         <v>2497031</v>
@@ -33690,7 +33690,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.0239524841309</v>
+        <v>10.0239534378052</v>
       </c>
       <c r="H1149" t="n">
         <v>1941841</v>
@@ -33777,7 +33777,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1152" t="n">
-        <v>10.2555818557739</v>
+        <v>10.2555809020996</v>
       </c>
       <c r="H1152" t="n">
         <v>2833459</v>
@@ -33835,7 +33835,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1154" t="n">
-        <v>10.2555818557739</v>
+        <v>10.2555809020996</v>
       </c>
       <c r="H1154" t="n">
         <v>2139138</v>
@@ -33980,7 +33980,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1159" t="n">
-        <v>10.2396068572998</v>
+        <v>10.2396078109741</v>
       </c>
       <c r="H1159" t="n">
         <v>2000207</v>
@@ -34038,7 +34038,7 @@
         <v>12.5749998092651</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.0439205169678</v>
+        <v>10.0439214706421</v>
       </c>
       <c r="H1161" t="n">
         <v>1632196</v>
@@ -34067,7 +34067,7 @@
         <v>12.6949996948242</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.1397666931152</v>
+        <v>10.1397686004639</v>
       </c>
       <c r="H1162" t="n">
         <v>1596490</v>
@@ -34183,7 +34183,7 @@
         <v>12.4549999237061</v>
       </c>
       <c r="G1166" t="n">
-        <v>9.94807434082031</v>
+        <v>9.94807529449463</v>
       </c>
       <c r="H1166" t="n">
         <v>2576220</v>
@@ -34212,7 +34212,7 @@
         <v>12.4849996566772</v>
       </c>
       <c r="G1167" t="n">
-        <v>9.9720344543457</v>
+        <v>9.97203636169434</v>
       </c>
       <c r="H1167" t="n">
         <v>1574489</v>
@@ -34241,7 +34241,7 @@
         <v>12.335000038147</v>
       </c>
       <c r="G1168" t="n">
-        <v>9.85222816467285</v>
+        <v>9.85222911834717</v>
       </c>
       <c r="H1168" t="n">
         <v>1577674</v>
@@ -34299,7 +34299,7 @@
         <v>12.5749998092651</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.0439205169678</v>
+        <v>10.0439214706421</v>
       </c>
       <c r="H1170" t="n">
         <v>1593190</v>
@@ -34328,7 +34328,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1171" t="n">
-        <v>10.6549434661865</v>
+        <v>10.6549425125122</v>
       </c>
       <c r="H1171" t="n">
         <v>4757283</v>
@@ -34357,7 +34357,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>10.4632511138916</v>
+        <v>10.4632501602173</v>
       </c>
       <c r="H1172" t="n">
         <v>2403879</v>
@@ -34444,7 +34444,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1175" t="n">
-        <v>10.2076587677002</v>
+        <v>10.2076578140259</v>
       </c>
       <c r="H1175" t="n">
         <v>1086646</v>
@@ -34647,7 +34647,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1182" t="n">
-        <v>10.3953590393066</v>
+        <v>10.3953580856323</v>
       </c>
       <c r="H1182" t="n">
         <v>1255095</v>
@@ -34792,7 +34792,7 @@
         <v>12.75</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.1836967468262</v>
+        <v>10.1836977005005</v>
       </c>
       <c r="H1187" t="n">
         <v>1805856</v>
@@ -34821,7 +34821,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1188" t="n">
-        <v>9.70046997070312</v>
+        <v>9.70047187805176</v>
       </c>
       <c r="H1188" t="n">
         <v>3544011</v>
@@ -34850,7 +34850,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1189" t="n">
-        <v>9.70046997070312</v>
+        <v>9.70047187805176</v>
       </c>
       <c r="H1189" t="n">
         <v>3489054</v>
@@ -34908,7 +34908,7 @@
         <v>12.3450002670288</v>
       </c>
       <c r="G1191" t="n">
-        <v>9.86021518707275</v>
+        <v>9.86021614074707</v>
       </c>
       <c r="H1191" t="n">
         <v>3073555</v>
@@ -34937,7 +34937,7 @@
         <v>12.4849996566772</v>
       </c>
       <c r="G1192" t="n">
-        <v>9.9720344543457</v>
+        <v>9.97203636169434</v>
       </c>
       <c r="H1192" t="n">
         <v>1653099</v>
@@ -34966,7 +34966,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1193" t="n">
-        <v>9.93609237670898</v>
+        <v>9.93609428405762</v>
       </c>
       <c r="H1193" t="n">
         <v>1746011</v>
@@ -35024,7 +35024,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1195" t="n">
-        <v>9.81628608703613</v>
+        <v>9.81628513336182</v>
       </c>
       <c r="H1195" t="n">
         <v>1898118</v>
@@ -35053,7 +35053,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1196" t="n">
-        <v>9.81628608703613</v>
+        <v>9.81628513336182</v>
       </c>
       <c r="H1196" t="n">
         <v>1881642</v>
@@ -35082,7 +35082,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1197" t="n">
-        <v>9.66053581237793</v>
+        <v>9.66053676605225</v>
       </c>
       <c r="H1197" t="n">
         <v>4051901</v>
@@ -35111,7 +35111,7 @@
         <v>11.835000038147</v>
       </c>
       <c r="G1198" t="n">
-        <v>9.45286750793457</v>
+        <v>9.45286655426025</v>
       </c>
       <c r="H1198" t="n">
         <v>3900033</v>
@@ -35140,7 +35140,7 @@
         <v>11.8549995422363</v>
       </c>
       <c r="G1199" t="n">
-        <v>9.46884059906006</v>
+        <v>9.46884155273438</v>
       </c>
       <c r="H1199" t="n">
         <v>5347852</v>
@@ -35227,7 +35227,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1202" t="n">
-        <v>9.09743595123291</v>
+        <v>9.09743690490723</v>
       </c>
       <c r="H1202" t="n">
         <v>2583908</v>
@@ -35256,7 +35256,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1203" t="n">
-        <v>9.36101531982422</v>
+        <v>9.36101627349854</v>
       </c>
       <c r="H1203" t="n">
         <v>2853738</v>
@@ -35285,7 +35285,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>9.20526313781738</v>
+        <v>9.2052640914917</v>
       </c>
       <c r="H1204" t="n">
         <v>1942516</v>
@@ -35314,7 +35314,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1205" t="n">
-        <v>9.35302829742432</v>
+        <v>9.35302734375</v>
       </c>
       <c r="H1205" t="n">
         <v>1929201</v>
@@ -35372,7 +35372,7 @@
         <v>11.7550001144409</v>
       </c>
       <c r="G1207" t="n">
-        <v>9.38896942138672</v>
+        <v>9.38897037506104</v>
       </c>
       <c r="H1207" t="n">
         <v>1808298</v>
@@ -35401,7 +35401,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1208" t="n">
-        <v>9.45686149597168</v>
+        <v>9.456862449646</v>
       </c>
       <c r="H1208" t="n">
         <v>1980347</v>
@@ -35430,7 +35430,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>9.43289947509766</v>
+        <v>9.43290042877197</v>
       </c>
       <c r="H1209" t="n">
         <v>1470610</v>
@@ -35459,7 +35459,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1210" t="n">
-        <v>9.65654182434082</v>
+        <v>9.6565408706665</v>
       </c>
       <c r="H1210" t="n">
         <v>2338885</v>
@@ -35488,7 +35488,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1211" t="n">
-        <v>9.73641204833984</v>
+        <v>9.73641300201416</v>
       </c>
       <c r="H1211" t="n">
         <v>2580855</v>
@@ -35575,7 +35575,7 @@
         <v>12.2650003433228</v>
       </c>
       <c r="G1214" t="n">
-        <v>9.7963171005249</v>
+        <v>9.79631805419922</v>
       </c>
       <c r="H1214" t="n">
         <v>1386265</v>
@@ -35604,7 +35604,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1215" t="n">
-        <v>9.83226108551025</v>
+        <v>9.83226013183594</v>
       </c>
       <c r="H1215" t="n">
         <v>1215225</v>
@@ -35720,7 +35720,7 @@
         <v>12.1850004196167</v>
       </c>
       <c r="G1219" t="n">
-        <v>9.73242092132568</v>
+        <v>9.73241996765137</v>
       </c>
       <c r="H1219" t="n">
         <v>1691327</v>
@@ -35749,7 +35749,7 @@
         <v>12.1850004196167</v>
       </c>
       <c r="G1220" t="n">
-        <v>9.73242092132568</v>
+        <v>9.73241996765137</v>
       </c>
       <c r="H1220" t="n">
         <v>1258661</v>
@@ -35865,7 +35865,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>9.23321914672852</v>
+        <v>9.23322010040283</v>
       </c>
       <c r="H1224" t="n">
         <v>1611869</v>
@@ -35923,7 +35923,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G1226" t="n">
-        <v>9.18130111694336</v>
+        <v>9.18130302429199</v>
       </c>
       <c r="H1226" t="n">
         <v>2440165</v>
@@ -35952,7 +35952,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1227" t="n">
-        <v>9.05749988555908</v>
+        <v>9.0575008392334</v>
       </c>
       <c r="H1227" t="n">
         <v>3989513</v>
@@ -36126,7 +36126,7 @@
         <v>12.4750003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>9.96404933929443</v>
+        <v>9.96405029296875</v>
       </c>
       <c r="H1233" t="n">
         <v>3042467</v>
@@ -36184,7 +36184,7 @@
         <v>12.1850004196167</v>
       </c>
       <c r="G1235" t="n">
-        <v>9.73242092132568</v>
+        <v>9.73241996765137</v>
       </c>
       <c r="H1235" t="n">
         <v>10965888</v>
@@ -36213,7 +36213,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1236" t="n">
-        <v>9.61660480499268</v>
+        <v>9.61660575866699</v>
       </c>
       <c r="H1236" t="n">
         <v>10407305</v>
@@ -36242,7 +36242,7 @@
         <v>12.1450004577637</v>
       </c>
       <c r="G1237" t="n">
-        <v>9.70046997070312</v>
+        <v>9.70047187805176</v>
       </c>
       <c r="H1237" t="n">
         <v>4914667</v>
@@ -36329,7 +36329,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>9.83226108551025</v>
+        <v>9.83226013183594</v>
       </c>
       <c r="H1240" t="n">
         <v>3900718</v>
@@ -36358,7 +36358,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1241" t="n">
-        <v>9.88817119598389</v>
+        <v>9.88817024230957</v>
       </c>
       <c r="H1241" t="n">
         <v>2451860</v>
@@ -36387,7 +36387,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.119800567627</v>
+        <v>10.1197996139526</v>
       </c>
       <c r="H1242" t="n">
         <v>4296989</v>
@@ -36445,7 +36445,7 @@
         <v>12.5550003051758</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.0279474258423</v>
+        <v>10.0279455184937</v>
       </c>
       <c r="H1244" t="n">
         <v>1426258</v>
@@ -36503,7 +36503,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.2555818557739</v>
+        <v>10.2555809020996</v>
       </c>
       <c r="H1246" t="n">
         <v>2608186</v>
@@ -36532,7 +36532,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1247" t="n">
-        <v>10.4073390960693</v>
+        <v>10.407338142395</v>
       </c>
       <c r="H1247" t="n">
         <v>3387027</v>
@@ -36561,7 +36561,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.3594169616699</v>
+        <v>10.3594160079956</v>
       </c>
       <c r="H1248" t="n">
         <v>4401443</v>
@@ -36590,7 +36590,7 @@
         <v>13.1149997711182</v>
       </c>
       <c r="G1249" t="n">
-        <v>10.4752292633057</v>
+        <v>10.47523021698</v>
       </c>
       <c r="H1249" t="n">
         <v>2631291</v>
@@ -36619,7 +36619,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G1250" t="n">
-        <v>10.4912052154541</v>
+        <v>10.4912042617798</v>
       </c>
       <c r="H1250" t="n">
         <v>3814049</v>
@@ -36793,7 +36793,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G1256" t="n">
-        <v>10.4352931976318</v>
+        <v>10.4352941513062</v>
       </c>
       <c r="H1256" t="n">
         <v>1797366</v>
@@ -36967,7 +36967,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.3953590393066</v>
+        <v>10.3953580856323</v>
       </c>
       <c r="H1262" t="n">
         <v>2331252</v>
@@ -36996,7 +36996,7 @@
         <v>13.0749998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.4432811737061</v>
+        <v>10.4432821273804</v>
       </c>
       <c r="H1263" t="n">
         <v>1578583</v>
@@ -37112,7 +37112,7 @@
         <v>13.2349996566772</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.5710773468018</v>
+        <v>10.5710763931274</v>
       </c>
       <c r="H1267" t="n">
         <v>1882160</v>
@@ -37141,7 +37141,7 @@
         <v>13.4250001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.7228345870972</v>
+        <v>10.7228336334229</v>
       </c>
       <c r="H1268" t="n">
         <v>1985023</v>
@@ -37257,7 +37257,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>10.7348146438599</v>
+        <v>10.7348136901855</v>
       </c>
       <c r="H1272" t="n">
         <v>2318767</v>
@@ -37315,7 +37315,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>10.9704370498657</v>
+        <v>10.9704360961914</v>
       </c>
       <c r="H1274" t="n">
         <v>2651348</v>
@@ -37373,7 +37373,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1276" t="n">
-        <v>10.9704370498657</v>
+        <v>10.9704360961914</v>
       </c>
       <c r="H1276" t="n">
         <v>2545763</v>
@@ -37402,7 +37402,7 @@
         <v>14</v>
       </c>
       <c r="G1277" t="n">
-        <v>11.1820993423462</v>
+        <v>11.1820983886719</v>
       </c>
       <c r="H1277" t="n">
         <v>2470000</v>
@@ -37431,7 +37431,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1278" t="n">
-        <v>11.0942401885986</v>
+        <v>11.0942392349243</v>
       </c>
       <c r="H1278" t="n">
         <v>1878203</v>
@@ -37460,7 +37460,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>11.0543050765991</v>
+        <v>11.0543041229248</v>
       </c>
       <c r="H1279" t="n">
         <v>2276701</v>
@@ -37489,7 +37489,7 @@
         <v>13.6850004196167</v>
       </c>
       <c r="G1280" t="n">
-        <v>10.9305019378662</v>
+        <v>10.9305009841919</v>
       </c>
       <c r="H1280" t="n">
         <v>2944954</v>
@@ -37518,7 +37518,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1281" t="n">
-        <v>11.0543050765991</v>
+        <v>11.0543041229248</v>
       </c>
       <c r="H1281" t="n">
         <v>1350537</v>
@@ -37576,7 +37576,7 @@
         <v>13.4650001525879</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.7547817230225</v>
+        <v>10.7547826766968</v>
       </c>
       <c r="H1283" t="n">
         <v>1402695</v>
@@ -37634,7 +37634,7 @@
         <v>13.3050003051758</v>
       </c>
       <c r="G1285" t="n">
-        <v>10.6269884109497</v>
+        <v>10.6269874572754</v>
       </c>
       <c r="H1285" t="n">
         <v>1995436</v>
@@ -37692,7 +37692,7 @@
         <v>13.1949996948242</v>
       </c>
       <c r="G1287" t="n">
-        <v>10.5391283035278</v>
+        <v>10.5391292572021</v>
       </c>
       <c r="H1287" t="n">
         <v>1130799</v>
@@ -37721,7 +37721,7 @@
         <v>12.9549999237061</v>
       </c>
       <c r="G1288" t="n">
-        <v>10.3474349975586</v>
+        <v>10.3474359512329</v>
       </c>
       <c r="H1288" t="n">
         <v>2182575</v>
@@ -37750,7 +37750,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G1289" t="n">
-        <v>10.4912052154541</v>
+        <v>10.4912042617798</v>
       </c>
       <c r="H1289" t="n">
         <v>1661895</v>
@@ -37924,7 +37924,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1295" t="n">
-        <v>11.6613321304321</v>
+        <v>11.6613311767578</v>
       </c>
       <c r="H1295" t="n">
         <v>2883119</v>
@@ -38011,7 +38011,7 @@
         <v>15.0050001144409</v>
       </c>
       <c r="G1298" t="n">
-        <v>11.9848146438599</v>
+        <v>11.9848136901855</v>
       </c>
       <c r="H1298" t="n">
         <v>3158259</v>
@@ -38069,7 +38069,7 @@
         <v>15.0649995803833</v>
       </c>
       <c r="G1300" t="n">
-        <v>12.032735824585</v>
+        <v>12.0327367782593</v>
       </c>
       <c r="H1300" t="n">
         <v>2233779</v>
@@ -38214,7 +38214,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>11.8610134124756</v>
+        <v>11.861011505127</v>
       </c>
       <c r="H1305" t="n">
         <v>1878355</v>
@@ -38243,7 +38243,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1306" t="n">
-        <v>11.7332172393799</v>
+        <v>11.7332162857056</v>
       </c>
       <c r="H1306" t="n">
         <v>1508288</v>
@@ -38272,7 +38272,7 @@
         <v>14.5349998474121</v>
       </c>
       <c r="G1307" t="n">
-        <v>11.6094160079956</v>
+        <v>11.6094150543213</v>
       </c>
       <c r="H1307" t="n">
         <v>1927439</v>
@@ -38301,7 +38301,7 @@
         <v>14.875</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.8809795379639</v>
+        <v>11.8809804916382</v>
       </c>
       <c r="H1308" t="n">
         <v>1942114</v>
@@ -38330,7 +38330,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412042617798</v>
       </c>
       <c r="H1309" t="n">
         <v>1874170</v>
@@ -38359,7 +38359,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.6373701095581</v>
+        <v>11.6373691558838</v>
       </c>
       <c r="H1310" t="n">
         <v>2259876</v>
@@ -38388,7 +38388,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.8330554962158</v>
+        <v>11.8330564498901</v>
       </c>
       <c r="H1311" t="n">
         <v>1577299</v>
@@ -38417,7 +38417,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.6174011230469</v>
+        <v>11.6174020767212</v>
       </c>
       <c r="H1312" t="n">
         <v>1617916</v>
@@ -38446,7 +38446,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.5894479751587</v>
+        <v>11.5894460678101</v>
       </c>
       <c r="H1313" t="n">
         <v>1721144</v>
@@ -38504,7 +38504,7 @@
         <v>14.4449996948242</v>
       </c>
       <c r="G1315" t="n">
-        <v>11.5375299453735</v>
+        <v>11.5375289916992</v>
       </c>
       <c r="H1315" t="n">
         <v>3249636</v>
@@ -38620,7 +38620,7 @@
         <v>14.8950004577637</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.8969554901123</v>
+        <v>11.896954536438</v>
       </c>
       <c r="H1319" t="n">
         <v>3011119</v>
@@ -38678,7 +38678,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G1321" t="n">
-        <v>11.5295429229736</v>
+        <v>11.5295438766479</v>
       </c>
       <c r="H1321" t="n">
         <v>2559551</v>
@@ -38794,7 +38794,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>11.5015869140625</v>
+        <v>11.5015878677368</v>
       </c>
       <c r="H1325" t="n">
         <v>3849807</v>
@@ -38939,7 +38939,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>11.1261892318726</v>
+        <v>11.1261901855469</v>
       </c>
       <c r="H1330" t="n">
         <v>1672330</v>
@@ -38997,7 +38997,7 @@
         <v>14</v>
       </c>
       <c r="G1332" t="n">
-        <v>11.1820993423462</v>
+        <v>11.1820983886719</v>
       </c>
       <c r="H1332" t="n">
         <v>1446546</v>
@@ -39026,7 +39026,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G1333" t="n">
-        <v>11.1461572647095</v>
+        <v>11.1461563110352</v>
       </c>
       <c r="H1333" t="n">
         <v>2952767</v>
@@ -39055,7 +39055,7 @@
         <v>13.9549999237061</v>
       </c>
       <c r="G1334" t="n">
-        <v>11.1461572647095</v>
+        <v>11.1461563110352</v>
       </c>
       <c r="H1334" t="n">
         <v>1405236</v>
@@ -39084,7 +39084,7 @@
         <v>13.8450002670288</v>
       </c>
       <c r="G1335" t="n">
-        <v>11.0582981109619</v>
+        <v>11.0582971572876</v>
       </c>
       <c r="H1335" t="n">
         <v>1961062</v>
@@ -39113,7 +39113,7 @@
         <v>13.9750003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>11.1621313095093</v>
+        <v>11.162130355835</v>
       </c>
       <c r="H1336" t="n">
         <v>2194077</v>
@@ -39200,7 +39200,7 @@
         <v>14.085000038147</v>
       </c>
       <c r="G1339" t="n">
-        <v>11.2499904632568</v>
+        <v>11.2499895095825</v>
       </c>
       <c r="H1339" t="n">
         <v>1667008</v>
@@ -39258,7 +39258,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1341" t="n">
-        <v>11.5175638198853</v>
+        <v>11.5175619125366</v>
       </c>
       <c r="H1341" t="n">
         <v>3085071</v>
@@ -39345,7 +39345,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G1344" t="n">
-        <v>11.5095748901367</v>
+        <v>11.509575843811</v>
       </c>
       <c r="H1344" t="n">
         <v>1687195</v>
@@ -39374,7 +39374,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>11.118200302124</v>
+        <v>11.1182012557983</v>
       </c>
       <c r="H1345" t="n">
         <v>2254848</v>
@@ -39432,7 +39432,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1347" t="n">
-        <v>11.0303421020508</v>
+        <v>11.0303430557251</v>
       </c>
       <c r="H1347" t="n">
         <v>1361313</v>
@@ -39635,7 +39635,7 @@
         <v>14.4849996566772</v>
       </c>
       <c r="G1354" t="n">
-        <v>11.5694770812988</v>
+        <v>11.5694799423218</v>
       </c>
       <c r="H1354" t="n">
         <v>1444441</v>
@@ -39693,7 +39693,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G1356" t="n">
-        <v>11.4336967468262</v>
+        <v>11.4336948394775</v>
       </c>
       <c r="H1356" t="n">
         <v>2211552</v>
@@ -39722,7 +39722,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1357" t="n">
-        <v>11.2300224304199</v>
+        <v>11.2300214767456</v>
       </c>
       <c r="H1357" t="n">
         <v>2197571</v>
@@ -39751,7 +39751,7 @@
         <v>14.1450004577637</v>
       </c>
       <c r="G1358" t="n">
-        <v>11.2979145050049</v>
+        <v>11.2979135513306</v>
       </c>
       <c r="H1358" t="n">
         <v>2141691</v>
@@ -39983,7 +39983,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1366" t="n">
-        <v>10.7507905960083</v>
+        <v>10.7507886886597</v>
       </c>
       <c r="H1366" t="n">
         <v>3014854</v>
@@ -40041,7 +40041,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1368" t="n">
-        <v>10.8865728378296</v>
+        <v>10.8865718841553</v>
       </c>
       <c r="H1368" t="n">
         <v>2489945</v>
@@ -40099,7 +40099,7 @@
         <v>13.7849998474121</v>
       </c>
       <c r="G1370" t="n">
-        <v>11.0103750228882</v>
+        <v>11.0103731155396</v>
       </c>
       <c r="H1370" t="n">
         <v>2270082</v>
@@ -40128,7 +40128,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1371" t="n">
-        <v>10.9105339050293</v>
+        <v>10.910532951355</v>
       </c>
       <c r="H1371" t="n">
         <v>1884972</v>
@@ -40186,7 +40186,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G1373" t="n">
-        <v>10.9185209274292</v>
+        <v>10.9185199737549</v>
       </c>
       <c r="H1373" t="n">
         <v>1919959</v>
@@ -40215,7 +40215,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G1374" t="n">
-        <v>10.9704370498657</v>
+        <v>10.9704360961914</v>
       </c>
       <c r="H1374" t="n">
         <v>1062371</v>
@@ -40302,7 +40302,7 @@
         <v>13.8549995422363</v>
       </c>
       <c r="G1377" t="n">
-        <v>11.0662832260132</v>
+        <v>11.0662841796875</v>
       </c>
       <c r="H1377" t="n">
         <v>1646430</v>
@@ -40331,7 +40331,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1378" t="n">
-        <v>11.0862531661987</v>
+        <v>11.0862522125244</v>
       </c>
       <c r="H1378" t="n">
         <v>1411505</v>
@@ -40418,7 +40418,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1381" t="n">
-        <v>11.1341753005981</v>
+        <v>11.1341743469238</v>
       </c>
       <c r="H1381" t="n">
         <v>1518297</v>
@@ -40476,7 +40476,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1383" t="n">
-        <v>11.1661233901978</v>
+        <v>11.1661243438721</v>
       </c>
       <c r="H1383" t="n">
         <v>997000</v>
@@ -40505,7 +40505,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G1384" t="n">
-        <v>11.1221952438354</v>
+        <v>11.1221942901611</v>
       </c>
       <c r="H1384" t="n">
         <v>1149509</v>
@@ -40563,7 +40563,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1386" t="n">
-        <v>11.4896068572998</v>
+        <v>11.4896078109741</v>
       </c>
       <c r="H1386" t="n">
         <v>4000594</v>
@@ -40592,7 +40592,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1387" t="n">
-        <v>11.4217157363892</v>
+        <v>11.4217147827148</v>
       </c>
       <c r="H1387" t="n">
         <v>2321321</v>
@@ -40679,7 +40679,7 @@
         <v>14.5</v>
       </c>
       <c r="G1390" t="n">
-        <v>11.5814590454102</v>
+        <v>11.5814599990845</v>
       </c>
       <c r="H1390" t="n">
         <v>2904755</v>
@@ -40708,7 +40708,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G1391" t="n">
-        <v>11.6533432006836</v>
+        <v>11.6533451080322</v>
       </c>
       <c r="H1391" t="n">
         <v>2668942</v>
@@ -40737,7 +40737,7 @@
         <v>14.7250003814697</v>
       </c>
       <c r="G1392" t="n">
-        <v>11.7611722946167</v>
+        <v>11.761173248291</v>
       </c>
       <c r="H1392" t="n">
         <v>1871889</v>
@@ -40795,7 +40795,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1394" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412042617798</v>
       </c>
       <c r="H1394" t="n">
         <v>1395345</v>
@@ -40824,7 +40824,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1395" t="n">
-        <v>11.7891273498535</v>
+        <v>11.7891283035278</v>
       </c>
       <c r="H1395" t="n">
         <v>1136188</v>
@@ -40853,7 +40853,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1396" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412042617798</v>
       </c>
       <c r="H1396" t="n">
         <v>2499043</v>
@@ -40882,7 +40882,7 @@
         <v>14.7049999237061</v>
       </c>
       <c r="G1397" t="n">
-        <v>11.7451972961426</v>
+        <v>11.7451982498169</v>
       </c>
       <c r="H1397" t="n">
         <v>2503933</v>
@@ -40911,7 +40911,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1398" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412042617798</v>
       </c>
       <c r="H1398" t="n">
         <v>1445021</v>
@@ -40940,7 +40940,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1399" t="n">
-        <v>11.8530254364014</v>
+        <v>11.8530244827271</v>
       </c>
       <c r="H1399" t="n">
         <v>900318</v>
@@ -40969,7 +40969,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>11.7412033081055</v>
+        <v>11.7412042617798</v>
       </c>
       <c r="H1400" t="n">
         <v>2955995</v>
@@ -40998,7 +40998,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1401" t="n">
-        <v>11.7891273498535</v>
+        <v>11.7891283035278</v>
       </c>
       <c r="H1401" t="n">
         <v>2541193</v>
@@ -41114,7 +41114,7 @@
         <v>14.7049999237061</v>
       </c>
       <c r="G1405" t="n">
-        <v>11.7451972961426</v>
+        <v>11.7451982498169</v>
       </c>
       <c r="H1405" t="n">
         <v>3201643</v>
@@ -41259,7 +41259,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1410" t="n">
-        <v>11.0543050765991</v>
+        <v>11.0543041229248</v>
       </c>
       <c r="H1410" t="n">
         <v>1386695</v>
@@ -41346,7 +41346,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1413" t="n">
-        <v>11.5175638198853</v>
+        <v>11.5175619125366</v>
       </c>
       <c r="H1413" t="n">
         <v>1751209</v>
@@ -41375,7 +41375,7 @@
         <v>14.6149997711182</v>
       </c>
       <c r="G1414" t="n">
-        <v>11.6733121871948</v>
+        <v>11.6733112335205</v>
       </c>
       <c r="H1414" t="n">
         <v>1166228</v>
@@ -41433,7 +41433,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1416" t="n">
-        <v>11.8769865036011</v>
+        <v>11.8769845962524</v>
       </c>
       <c r="H1416" t="n">
         <v>1671385</v>
@@ -41462,7 +41462,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>12.2443971633911</v>
+        <v>12.2443981170654</v>
       </c>
       <c r="H1417" t="n">
         <v>2895897</v>
@@ -41491,7 +41491,7 @@
         <v>15.1149997711182</v>
       </c>
       <c r="G1418" t="n">
-        <v>12.0726737976074</v>
+        <v>12.0726728439331</v>
       </c>
       <c r="H1418" t="n">
         <v>2580461</v>
@@ -41549,7 +41549,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1420" t="n">
-        <v>11.9129285812378</v>
+        <v>11.9129276275635</v>
       </c>
       <c r="H1420" t="n">
         <v>2494707</v>
@@ -41578,7 +41578,7 @@
         <v>15.4049997329712</v>
       </c>
       <c r="G1421" t="n">
-        <v>12.3043022155762</v>
+        <v>12.3043012619019</v>
       </c>
       <c r="H1421" t="n">
         <v>3606884</v>
@@ -41607,7 +41607,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.4201164245605</v>
+        <v>12.4201173782349</v>
       </c>
       <c r="H1422" t="n">
         <v>2549177</v>
@@ -41636,7 +41636,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.7396059036255</v>
+        <v>12.7396049499512</v>
       </c>
       <c r="H1423" t="n">
         <v>2715997</v>
@@ -41665,7 +41665,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G1424" t="n">
-        <v>12.8873682022095</v>
+        <v>12.8873701095581</v>
       </c>
       <c r="H1424" t="n">
         <v>1332826</v>
@@ -41694,7 +41694,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1425" t="n">
-        <v>12.9552612304688</v>
+        <v>12.9552602767944</v>
       </c>
       <c r="H1425" t="n">
         <v>1568736</v>
@@ -41752,7 +41752,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1427" t="n">
-        <v>12.9712352752686</v>
+        <v>12.9712362289429</v>
       </c>
       <c r="H1427" t="n">
         <v>1658401</v>
@@ -41781,7 +41781,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1428" t="n">
-        <v>12.9233121871948</v>
+        <v>12.9233131408691</v>
       </c>
       <c r="H1428" t="n">
         <v>1592846</v>
@@ -41810,7 +41810,7 @@
         <v>16.0949993133545</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.8554201126099</v>
+        <v>12.8554182052612</v>
       </c>
       <c r="H1429" t="n">
         <v>2654714</v>
@@ -41839,7 +41839,7 @@
         <v>15.9449996948242</v>
       </c>
       <c r="G1430" t="n">
-        <v>12.7356128692627</v>
+        <v>12.7356119155884</v>
       </c>
       <c r="H1430" t="n">
         <v>1600785</v>
@@ -41868,7 +41868,7 @@
         <v>16.25</v>
       </c>
       <c r="G1431" t="n">
-        <v>12.9792222976685</v>
+        <v>12.9792213439941</v>
       </c>
       <c r="H1431" t="n">
         <v>2489968</v>
@@ -41926,7 +41926,7 @@
         <v>15.7349996566772</v>
       </c>
       <c r="G1433" t="n">
-        <v>12.5678806304932</v>
+        <v>12.5678796768188</v>
       </c>
       <c r="H1433" t="n">
         <v>1618942</v>
@@ -41955,7 +41955,7 @@
         <v>15.8649997711182</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.6717138290405</v>
+        <v>12.6717147827148</v>
       </c>
       <c r="H1434" t="n">
         <v>919515</v>
@@ -41984,7 +41984,7 @@
         <v>15.8950004577637</v>
       </c>
       <c r="G1435" t="n">
-        <v>12.6956768035889</v>
+        <v>12.6956777572632</v>
       </c>
       <c r="H1435" t="n">
         <v>1183165</v>
@@ -42013,7 +42013,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G1436" t="n">
-        <v>12.7675609588623</v>
+        <v>12.767560005188</v>
       </c>
       <c r="H1436" t="n">
         <v>1011161</v>
@@ -42158,7 +42158,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G1441" t="n">
-        <v>12.3881673812866</v>
+        <v>12.3881683349609</v>
       </c>
       <c r="H1441" t="n">
         <v>2136237</v>
@@ -42187,7 +42187,7 @@
         <v>15.5150003433228</v>
       </c>
       <c r="G1442" t="n">
-        <v>12.392162322998</v>
+        <v>12.3921613693237</v>
       </c>
       <c r="H1442" t="n">
         <v>1547130</v>
@@ -42274,7 +42274,7 @@
         <v>15.5950002670288</v>
       </c>
       <c r="G1445" t="n">
-        <v>12.4560585021973</v>
+        <v>12.4560604095459</v>
       </c>
       <c r="H1445" t="n">
         <v>1585753</v>
@@ -42303,7 +42303,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G1446" t="n">
-        <v>12.3562202453613</v>
+        <v>12.356219291687</v>
       </c>
       <c r="H1446" t="n">
         <v>1126431</v>
@@ -42477,7 +42477,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1452" t="n">
-        <v>12.7475929260254</v>
+        <v>12.7475938796997</v>
       </c>
       <c r="H1452" t="n">
         <v>2430932</v>
@@ -42593,7 +42593,7 @@
         <v>15.6850004196167</v>
       </c>
       <c r="G1456" t="n">
-        <v>12.5279445648193</v>
+        <v>12.5279455184937</v>
       </c>
       <c r="H1456" t="n">
         <v>1260691</v>
@@ -42622,7 +42622,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G1457" t="n">
-        <v>12.7515859603882</v>
+        <v>12.7515869140625</v>
       </c>
       <c r="H1457" t="n">
         <v>1567852</v>
@@ -42651,7 +42651,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1458" t="n">
-        <v>12.7396059036255</v>
+        <v>12.7396049499512</v>
       </c>
       <c r="H1458" t="n">
         <v>1335880</v>
@@ -42680,7 +42680,7 @@
         <v>16.0450000762939</v>
       </c>
       <c r="G1459" t="n">
-        <v>12.8154830932617</v>
+        <v>12.815484046936</v>
       </c>
       <c r="H1459" t="n">
         <v>1882601</v>
@@ -42709,7 +42709,7 @@
         <v>15.6049995422363</v>
       </c>
       <c r="G1460" t="n">
-        <v>12.4640464782715</v>
+        <v>12.4640455245972</v>
       </c>
       <c r="H1460" t="n">
         <v>2177254</v>
@@ -42738,7 +42738,7 @@
         <v>15.5249996185303</v>
       </c>
       <c r="G1461" t="n">
-        <v>12.4001493453979</v>
+        <v>12.4001483917236</v>
       </c>
       <c r="H1461" t="n">
         <v>1841211</v>
@@ -42941,7 +42941,7 @@
         <v>15.8050003051758</v>
       </c>
       <c r="G1468" t="n">
-        <v>12.6237897872925</v>
+        <v>12.6237916946411</v>
       </c>
       <c r="H1468" t="n">
         <v>1308809</v>
@@ -42970,7 +42970,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G1469" t="n">
-        <v>12.5119695663452</v>
+        <v>12.5119705200195</v>
       </c>
       <c r="H1469" t="n">
         <v>998564</v>
@@ -42999,7 +42999,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1470" t="n">
-        <v>12.7156438827515</v>
+        <v>12.7156429290771</v>
       </c>
       <c r="H1470" t="n">
         <v>1136614</v>
@@ -43028,7 +43028,7 @@
         <v>15.8149995803833</v>
       </c>
       <c r="G1471" t="n">
-        <v>12.6317768096924</v>
+        <v>12.6317777633667</v>
       </c>
       <c r="H1471" t="n">
         <v>1311446</v>
@@ -43057,7 +43057,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1472" t="n">
-        <v>13.0990304946899</v>
+        <v>13.0990285873413</v>
       </c>
       <c r="H1472" t="n">
         <v>3176373</v>
@@ -43173,7 +43173,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1476" t="n">
-        <v>13.2907238006592</v>
+        <v>13.2907218933105</v>
       </c>
       <c r="H1476" t="n">
         <v>1193898</v>
@@ -43202,7 +43202,7 @@
         <v>16.6049995422363</v>
       </c>
       <c r="G1477" t="n">
-        <v>13.2627668380737</v>
+        <v>13.262767791748</v>
       </c>
       <c r="H1477" t="n">
         <v>1049924</v>
@@ -43231,7 +43231,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G1478" t="n">
-        <v>13.2867288589478</v>
+        <v>13.2867298126221</v>
       </c>
       <c r="H1478" t="n">
         <v>1057708</v>
@@ -43260,7 +43260,7 @@
         <v>16.7849998474121</v>
       </c>
       <c r="G1479" t="n">
-        <v>13.4065380096436</v>
+        <v>13.4065389633179</v>
       </c>
       <c r="H1479" t="n">
         <v>1867478</v>
@@ -43318,7 +43318,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1481" t="n">
-        <v>13.122992515564</v>
+        <v>13.1229915618896</v>
       </c>
       <c r="H1481" t="n">
         <v>1908408</v>
@@ -43376,7 +43376,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G1483" t="n">
-        <v>13.190881729126</v>
+        <v>13.1908836364746</v>
       </c>
       <c r="H1483" t="n">
         <v>2049036</v>
@@ -43405,7 +43405,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1484" t="n">
-        <v>13.4864101409912</v>
+        <v>13.4864110946655</v>
       </c>
       <c r="H1484" t="n">
         <v>1652168</v>
@@ -43434,7 +43434,7 @@
         <v>16.5949993133545</v>
       </c>
       <c r="G1485" t="n">
-        <v>13.2547798156738</v>
+        <v>13.2547807693481</v>
       </c>
       <c r="H1485" t="n">
         <v>2137623</v>
@@ -43463,7 +43463,7 @@
         <v>16.9850006103516</v>
       </c>
       <c r="G1486" t="n">
-        <v>13.5662822723389</v>
+        <v>13.5662813186646</v>
       </c>
       <c r="H1486" t="n">
         <v>1958921</v>
@@ -43492,7 +43492,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1487" t="n">
-        <v>13.4983911514282</v>
+        <v>13.4983901977539</v>
       </c>
       <c r="H1487" t="n">
         <v>1790777</v>
@@ -43521,7 +43521,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>13.698070526123</v>
+        <v>13.6980714797974</v>
       </c>
       <c r="H1488" t="n">
         <v>1698562</v>
@@ -43550,7 +43550,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1489" t="n">
-        <v>13.8019037246704</v>
+        <v>13.801905632019</v>
       </c>
       <c r="H1489" t="n">
         <v>1634220</v>
@@ -43637,7 +43637,7 @@
         <v>17.2350006103516</v>
       </c>
       <c r="G1492" t="n">
-        <v>13.7659616470337</v>
+        <v>13.7659635543823</v>
       </c>
       <c r="H1492" t="n">
         <v>1101791</v>
@@ -43666,7 +43666,7 @@
         <v>17.3050003051758</v>
       </c>
       <c r="G1493" t="n">
-        <v>13.8218727111816</v>
+        <v>13.821873664856</v>
       </c>
       <c r="H1493" t="n">
         <v>1148182</v>
@@ -43695,7 +43695,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1494" t="n">
-        <v>13.8019037246704</v>
+        <v>13.801905632019</v>
       </c>
       <c r="H1494" t="n">
         <v>1276201</v>
@@ -43724,7 +43724,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G1495" t="n">
-        <v>13.7340126037598</v>
+        <v>13.7340135574341</v>
       </c>
       <c r="H1495" t="n">
         <v>1671596</v>
@@ -43753,7 +43753,7 @@
         <v>17.25</v>
       </c>
       <c r="G1496" t="n">
-        <v>13.7779445648193</v>
+        <v>13.777943611145</v>
       </c>
       <c r="H1496" t="n">
         <v>1532165</v>
@@ -43782,7 +43782,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1497" t="n">
-        <v>13.6900844573975</v>
+        <v>13.6900835037231</v>
       </c>
       <c r="H1497" t="n">
         <v>1392449</v>
@@ -43869,7 +43869,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1500" t="n">
-        <v>13.3136911392212</v>
+        <v>13.3136920928955</v>
       </c>
       <c r="H1500" t="n">
         <v>1774165</v>
@@ -43898,7 +43898,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G1501" t="n">
-        <v>13.3466691970825</v>
+        <v>13.3466682434082</v>
       </c>
       <c r="H1501" t="n">
         <v>1345940</v>
@@ -43927,7 +43927,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>13.1488170623779</v>
+        <v>13.1488161087036</v>
       </c>
       <c r="H1502" t="n">
         <v>1269802</v>
@@ -43985,7 +43985,7 @@
         <v>15.5550003051758</v>
       </c>
       <c r="G1504" t="n">
-        <v>12.8231897354126</v>
+        <v>12.8231887817383</v>
       </c>
       <c r="H1504" t="n">
         <v>1690016</v>
@@ -44130,7 +44130,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1509" t="n">
-        <v>13.0498924255371</v>
+        <v>13.0498914718628</v>
       </c>
       <c r="H1509" t="n">
         <v>1519304</v>
@@ -44246,7 +44246,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G1513" t="n">
-        <v>12.9221143722534</v>
+        <v>12.9221134185791</v>
       </c>
       <c r="H1513" t="n">
         <v>947323</v>
@@ -44333,7 +44333,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G1516" t="n">
-        <v>12.9468441009521</v>
+        <v>12.9468450546265</v>
       </c>
       <c r="H1516" t="n">
         <v>853574</v>
@@ -44594,7 +44594,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1525" t="n">
-        <v>12.7613592147827</v>
+        <v>12.761360168457</v>
       </c>
       <c r="H1525" t="n">
         <v>680503</v>
@@ -44623,7 +44623,7 @@
         <v>15.4350004196167</v>
       </c>
       <c r="G1526" t="n">
-        <v>12.7242641448975</v>
+        <v>12.7242631912231</v>
       </c>
       <c r="H1526" t="n">
         <v>598379</v>
@@ -44768,7 +44768,7 @@
         <v>15.6049995422363</v>
       </c>
       <c r="G1531" t="n">
-        <v>12.8644065856934</v>
+        <v>12.864405632019</v>
       </c>
       <c r="H1531" t="n">
         <v>1917623</v>
@@ -44913,7 +44913,7 @@
         <v>15.8050003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>13.0292825698853</v>
+        <v>13.0292835235596</v>
       </c>
       <c r="H1536" t="n">
         <v>1754748</v>
@@ -44942,7 +44942,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1537" t="n">
-        <v>13.1075983047485</v>
+        <v>13.1075973510742</v>
       </c>
       <c r="H1537" t="n">
         <v>985261</v>
@@ -45145,7 +45145,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1544" t="n">
-        <v>12.0853710174561</v>
+        <v>12.0853700637817</v>
       </c>
       <c r="H1544" t="n">
         <v>1509739</v>
@@ -45290,7 +45290,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G1549" t="n">
-        <v>12.4233646392822</v>
+        <v>12.4233655929565</v>
       </c>
       <c r="H1549" t="n">
         <v>1472435</v>
@@ -45493,7 +45493,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G1556" t="n">
-        <v>12.9468441009521</v>
+        <v>12.9468450546265</v>
       </c>
       <c r="H1556" t="n">
         <v>1905297</v>
@@ -45667,7 +45667,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G1562" t="n">
-        <v>12.9138708114624</v>
+        <v>12.9138698577881</v>
       </c>
       <c r="H1562" t="n">
         <v>1531379</v>
@@ -45696,7 +45696,7 @@
         <v>15.5550003051758</v>
       </c>
       <c r="G1563" t="n">
-        <v>12.8231897354126</v>
+        <v>12.8231887817383</v>
       </c>
       <c r="H1563" t="n">
         <v>2000209</v>
@@ -45754,7 +45754,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1565" t="n">
-        <v>11.9699573516846</v>
+        <v>11.9699583053589</v>
       </c>
       <c r="H1565" t="n">
         <v>4647565</v>
@@ -45812,7 +45812,7 @@
         <v>14.9250001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>12.3038311004639</v>
+        <v>12.3038301467896</v>
       </c>
       <c r="H1567" t="n">
         <v>3030485</v>
@@ -45841,7 +45841,7 @@
         <v>14.0450000762939</v>
       </c>
       <c r="G1568" t="n">
-        <v>11.5783786773682</v>
+        <v>11.5783777236938</v>
       </c>
       <c r="H1568" t="n">
         <v>3205124</v>
@@ -45870,7 +45870,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1569" t="n">
-        <v>11.590744972229</v>
+        <v>11.5907440185547</v>
       </c>
       <c r="H1569" t="n">
         <v>2348018</v>
@@ -45957,7 +45957,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.4695911407471</v>
+        <v>10.4695920944214</v>
       </c>
       <c r="H1572" t="n">
         <v>5012765</v>
@@ -45986,7 +45986,7 @@
         <v>12.3050003051758</v>
       </c>
       <c r="G1573" t="n">
-        <v>10.1439619064331</v>
+        <v>10.1439628601074</v>
       </c>
       <c r="H1573" t="n">
         <v>3131711</v>
@@ -46015,7 +46015,7 @@
         <v>13.7650003433228</v>
       </c>
       <c r="G1574" t="n">
-        <v>11.3475532531738</v>
+        <v>11.3475542068481</v>
       </c>
       <c r="H1574" t="n">
         <v>3082206</v>
@@ -46160,7 +46160,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G1579" t="n">
-        <v>12.052393913269</v>
+        <v>12.0523948669434</v>
       </c>
       <c r="H1579" t="n">
         <v>2696184</v>
@@ -46189,7 +46189,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G1580" t="n">
-        <v>11.5454034805298</v>
+        <v>11.5454044342041</v>
       </c>
       <c r="H1580" t="n">
         <v>2851617</v>
@@ -46218,7 +46218,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1581" t="n">
-        <v>11.5660133361816</v>
+        <v>11.5660123825073</v>
       </c>
       <c r="H1581" t="n">
         <v>3825166</v>
@@ -46247,7 +46247,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G1582" t="n">
-        <v>11.5454034805298</v>
+        <v>11.5454044342041</v>
       </c>
       <c r="H1582" t="n">
         <v>1865620</v>
@@ -46421,7 +46421,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1588" t="n">
-        <v>11.8586683273315</v>
+        <v>11.8586673736572</v>
       </c>
       <c r="H1588" t="n">
         <v>3015569</v>
@@ -46450,7 +46450,7 @@
         <v>14.25</v>
       </c>
       <c r="G1589" t="n">
-        <v>11.7473764419556</v>
+        <v>11.7473754882812</v>
       </c>
       <c r="H1589" t="n">
         <v>1722196</v>
@@ -46595,7 +46595,7 @@
         <v>13.9650001525879</v>
       </c>
       <c r="G1594" t="n">
-        <v>11.5124292373657</v>
+        <v>11.5124282836914</v>
       </c>
       <c r="H1594" t="n">
         <v>2213985</v>
@@ -46624,7 +46624,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G1595" t="n">
-        <v>11.677303314209</v>
+        <v>11.6773023605347</v>
       </c>
       <c r="H1595" t="n">
         <v>1654206</v>
@@ -46653,7 +46653,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G1596" t="n">
-        <v>11.8627891540527</v>
+        <v>11.8627882003784</v>
       </c>
       <c r="H1596" t="n">
         <v>1215368</v>
@@ -46885,7 +46885,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1604" t="n">
-        <v>11.4258689880371</v>
+        <v>11.4258680343628</v>
       </c>
       <c r="H1604" t="n">
         <v>1692881</v>
@@ -46914,7 +46914,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G1605" t="n">
-        <v>11.0548992156982</v>
+        <v>11.0548982620239</v>
       </c>
       <c r="H1605" t="n">
         <v>1485626</v>
@@ -47088,7 +47088,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1611" t="n">
-        <v>10.9559736251831</v>
+        <v>10.9559726715088</v>
       </c>
       <c r="H1611" t="n">
         <v>1272146</v>
@@ -47117,7 +47117,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1612" t="n">
-        <v>10.6674404144287</v>
+        <v>10.667441368103</v>
       </c>
       <c r="H1612" t="n">
         <v>1483287</v>
@@ -47233,7 +47233,7 @@
         <v>11.7749996185303</v>
       </c>
       <c r="G1616" t="n">
-        <v>9.70704174041748</v>
+        <v>9.70704078674316</v>
       </c>
       <c r="H1616" t="n">
         <v>2686537</v>
@@ -47320,7 +47320,7 @@
         <v>12.375</v>
       </c>
       <c r="G1619" t="n">
-        <v>10.2016687393188</v>
+        <v>10.2016696929932</v>
       </c>
       <c r="H1619" t="n">
         <v>1395068</v>
@@ -47378,7 +47378,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1621" t="n">
-        <v>10.4283723831177</v>
+        <v>10.428373336792</v>
       </c>
       <c r="H1621" t="n">
         <v>1833576</v>
@@ -47639,7 +47639,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1630" t="n">
-        <v>11.2639560699463</v>
+        <v>11.263955116272</v>
       </c>
       <c r="H1630" t="n">
         <v>1215053</v>
@@ -47668,7 +47668,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G1631" t="n">
-        <v>11.204402923584</v>
+        <v>11.2044019699097</v>
       </c>
       <c r="H1631" t="n">
         <v>4664229</v>
@@ -47726,7 +47726,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G1633" t="n">
-        <v>11.204402923584</v>
+        <v>11.2044019699097</v>
       </c>
       <c r="H1633" t="n">
         <v>962421</v>
@@ -47784,7 +47784,7 @@
         <v>13.0050001144409</v>
       </c>
       <c r="G1635" t="n">
-        <v>11.0640287399292</v>
+        <v>11.0640277862549</v>
       </c>
       <c r="H1635" t="n">
         <v>2181026</v>
@@ -47813,7 +47813,7 @@
         <v>12.875</v>
       </c>
       <c r="G1636" t="n">
-        <v>10.9534301757812</v>
+        <v>10.9534311294556</v>
       </c>
       <c r="H1636" t="n">
         <v>1545532</v>
@@ -47871,7 +47871,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1638" t="n">
-        <v>10.2430534362793</v>
+        <v>10.243052482605</v>
       </c>
       <c r="H1638" t="n">
         <v>2772279</v>
@@ -47900,7 +47900,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1639" t="n">
-        <v>9.27319526672363</v>
+        <v>9.27319622039795</v>
       </c>
       <c r="H1639" t="n">
         <v>5390717</v>
@@ -48016,7 +48016,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G1643" t="n">
-        <v>9.09453678131104</v>
+        <v>9.09453773498535</v>
       </c>
       <c r="H1643" t="n">
         <v>2043275</v>
@@ -48045,7 +48045,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.2221508026123</v>
+        <v>9.22214984893799</v>
       </c>
       <c r="H1644" t="n">
         <v>3311840</v>
@@ -48074,7 +48074,7 @@
         <v>11.1949996948242</v>
       </c>
       <c r="G1645" t="n">
-        <v>9.52416801452637</v>
+        <v>9.52416706085205</v>
       </c>
       <c r="H1645" t="n">
         <v>1463179</v>
@@ -48132,7 +48132,7 @@
         <v>11.5249996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>9.80491638183594</v>
+        <v>9.80491542816162</v>
       </c>
       <c r="H1647" t="n">
         <v>2294733</v>
@@ -48190,7 +48190,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.226037979126</v>
+        <v>10.2260370254517</v>
       </c>
       <c r="H1649" t="n">
         <v>2123166</v>
@@ -48219,7 +48219,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1650" t="n">
-        <v>10.0814094543457</v>
+        <v>10.08141040802</v>
       </c>
       <c r="H1650" t="n">
         <v>1491980</v>
@@ -48248,7 +48248,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1651" t="n">
-        <v>10.0899171829224</v>
+        <v>10.089916229248</v>
       </c>
       <c r="H1651" t="n">
         <v>1228940</v>
@@ -48364,7 +48364,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G1655" t="n">
-        <v>9.84745311737061</v>
+        <v>9.84745216369629</v>
       </c>
       <c r="H1655" t="n">
         <v>907814</v>
@@ -48422,7 +48422,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G1657" t="n">
-        <v>9.83894443511963</v>
+        <v>9.83894538879395</v>
       </c>
       <c r="H1657" t="n">
         <v>1418382</v>
@@ -48509,7 +48509,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1660" t="n">
-        <v>10.0814094543457</v>
+        <v>10.08141040802</v>
       </c>
       <c r="H1660" t="n">
         <v>1285391</v>
@@ -48683,7 +48683,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1666" t="n">
-        <v>10.1749925613403</v>
+        <v>10.1749935150146</v>
       </c>
       <c r="H1666" t="n">
         <v>2561593</v>
@@ -48741,7 +48741,7 @@
         <v>11.4250001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>9.71984004974365</v>
+        <v>9.71984100341797</v>
       </c>
       <c r="H1668" t="n">
         <v>3841006</v>
@@ -48915,7 +48915,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1674" t="n">
-        <v>10.2855911254883</v>
+        <v>10.285590171814</v>
       </c>
       <c r="H1674" t="n">
         <v>2727334</v>
@@ -48944,7 +48944,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1675" t="n">
-        <v>10.2855911254883</v>
+        <v>10.285590171814</v>
       </c>
       <c r="H1675" t="n">
         <v>2299722</v>
@@ -49089,7 +49089,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>10.3111124038696</v>
+        <v>10.3111133575439</v>
       </c>
       <c r="H1680" t="n">
         <v>990232</v>
@@ -49118,7 +49118,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1681" t="n">
-        <v>10.166485786438</v>
+        <v>10.1664848327637</v>
       </c>
       <c r="H1681" t="n">
         <v>876754</v>
@@ -49205,7 +49205,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1684" t="n">
-        <v>10.5833539962769</v>
+        <v>10.5833530426025</v>
       </c>
       <c r="H1684" t="n">
         <v>821558</v>
@@ -49263,7 +49263,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1686" t="n">
-        <v>10.140962600708</v>
+        <v>10.1409635543823</v>
       </c>
       <c r="H1686" t="n">
         <v>1285151</v>
@@ -49524,7 +49524,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1695" t="n">
-        <v>9.18812084197998</v>
+        <v>9.18811988830566</v>
       </c>
       <c r="H1695" t="n">
         <v>1611228</v>
@@ -49582,7 +49582,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G1697" t="n">
-        <v>9.07752227783203</v>
+        <v>9.07752323150635</v>
       </c>
       <c r="H1697" t="n">
         <v>2037350</v>
@@ -49640,7 +49640,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G1699" t="n">
-        <v>9.19662761688232</v>
+        <v>9.19662857055664</v>
       </c>
       <c r="H1699" t="n">
         <v>984421</v>
@@ -49727,7 +49727,7 @@
         <v>11.164999961853</v>
       </c>
       <c r="G1702" t="n">
-        <v>9.49864482879639</v>
+        <v>9.4986457824707</v>
       </c>
       <c r="H1702" t="n">
         <v>2016046</v>
@@ -49785,7 +49785,7 @@
         <v>12.3149995803833</v>
       </c>
       <c r="G1704" t="n">
-        <v>10.4770088195801</v>
+        <v>10.4770097732544</v>
       </c>
       <c r="H1704" t="n">
         <v>2823150</v>
@@ -50017,7 +50017,7 @@
         <v>12.8149995803833</v>
       </c>
       <c r="G1712" t="n">
-        <v>10.9023866653442</v>
+        <v>10.9023857116699</v>
       </c>
       <c r="H1712" t="n">
         <v>4501639</v>
@@ -50162,7 +50162,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1717" t="n">
-        <v>10.4472341537476</v>
+        <v>10.4472332000732</v>
       </c>
       <c r="H1717" t="n">
         <v>2772550</v>
@@ -50249,7 +50249,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G1720" t="n">
-        <v>11.4085826873779</v>
+        <v>11.4085836410522</v>
       </c>
       <c r="H1720" t="n">
         <v>3237292</v>
@@ -50278,7 +50278,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1721" t="n">
-        <v>11.1108207702637</v>
+        <v>11.1108198165894</v>
       </c>
       <c r="H1721" t="n">
         <v>1779630</v>
@@ -50452,7 +50452,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1727" t="n">
-        <v>10.5833539962769</v>
+        <v>10.5833530426025</v>
       </c>
       <c r="H1727" t="n">
         <v>2812751</v>
@@ -50481,7 +50481,7 @@
         <v>12.3649997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>10.5195465087891</v>
+        <v>10.5195474624634</v>
       </c>
       <c r="H1728" t="n">
         <v>2086873</v>
@@ -50539,7 +50539,7 @@
         <v>12.7150001525879</v>
       </c>
       <c r="G1730" t="n">
-        <v>10.817310333252</v>
+        <v>10.8173112869263</v>
       </c>
       <c r="H1730" t="n">
         <v>2510534</v>
@@ -50684,7 +50684,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1735" t="n">
-        <v>11.5191793441772</v>
+        <v>11.5191802978516</v>
       </c>
       <c r="H1735" t="n">
         <v>1887133</v>
@@ -50800,7 +50800,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1739" t="n">
-        <v>11.6042566299438</v>
+        <v>11.6042556762695</v>
       </c>
       <c r="H1739" t="n">
         <v>1829304</v>
@@ -50974,7 +50974,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G1745" t="n">
-        <v>11.9190330505371</v>
+        <v>11.9190340042114</v>
       </c>
       <c r="H1745" t="n">
         <v>4469352</v>
@@ -51003,7 +51003,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G1746" t="n">
-        <v>12.157244682312</v>
+        <v>12.1572456359863</v>
       </c>
       <c r="H1746" t="n">
         <v>2467245</v>
@@ -51090,7 +51090,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1749" t="n">
-        <v>12.3529167175293</v>
+        <v>12.3529176712036</v>
       </c>
       <c r="H1749" t="n">
         <v>2201920</v>
@@ -51206,7 +51206,7 @@
         <v>15</v>
       </c>
       <c r="G1753" t="n">
-        <v>12.7612791061401</v>
+        <v>12.7612781524658</v>
       </c>
       <c r="H1753" t="n">
         <v>2578689</v>
@@ -51235,7 +51235,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1754" t="n">
-        <v>12.6932182312012</v>
+        <v>12.6932191848755</v>
       </c>
       <c r="H1754" t="n">
         <v>1326342</v>
@@ -51264,7 +51264,7 @@
         <v>15.0349998474121</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.791054725647</v>
+        <v>12.7910537719727</v>
       </c>
       <c r="H1755" t="n">
         <v>1061746</v>
@@ -51322,7 +51322,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G1757" t="n">
-        <v>12.9441909790039</v>
+        <v>12.9441900253296</v>
       </c>
       <c r="H1757" t="n">
         <v>962149</v>
@@ -51351,7 +51351,7 @@
         <v>15.3649997711182</v>
       </c>
       <c r="G1758" t="n">
-        <v>13.0718021392822</v>
+        <v>13.0718030929565</v>
       </c>
       <c r="H1758" t="n">
         <v>1166639</v>
@@ -51438,7 +51438,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1761" t="n">
-        <v>13.1356086730957</v>
+        <v>13.13560962677</v>
       </c>
       <c r="H1761" t="n">
         <v>6758399</v>
@@ -51496,7 +51496,7 @@
         <v>15.75</v>
       </c>
       <c r="G1763" t="n">
-        <v>13.3993434906006</v>
+        <v>13.3993425369263</v>
       </c>
       <c r="H1763" t="n">
         <v>1857607</v>
@@ -51612,7 +51612,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1767" t="n">
-        <v>13.237699508667</v>
+        <v>13.2377004623413</v>
       </c>
       <c r="H1767" t="n">
         <v>1506278</v>
@@ -51641,7 +51641,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1768" t="n">
-        <v>13.1696395874023</v>
+        <v>13.169638633728</v>
       </c>
       <c r="H1768" t="n">
         <v>1995902</v>
@@ -51815,7 +51815,7 @@
         <v>14.875</v>
       </c>
       <c r="G1774" t="n">
-        <v>12.6549339294434</v>
+        <v>12.6549348831177</v>
       </c>
       <c r="H1774" t="n">
         <v>1522073</v>
@@ -51989,7 +51989,7 @@
         <v>15.375</v>
       </c>
       <c r="G1780" t="n">
-        <v>13.0803108215332</v>
+        <v>13.0803098678589</v>
       </c>
       <c r="H1780" t="n">
         <v>563453</v>
@@ -52018,7 +52018,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1781" t="n">
-        <v>13.322774887085</v>
+        <v>13.3227739334106</v>
       </c>
       <c r="H1781" t="n">
         <v>1055718</v>
@@ -52105,7 +52105,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1784" t="n">
-        <v>13.6630764007568</v>
+        <v>13.6630754470825</v>
       </c>
       <c r="H1784" t="n">
         <v>1883290</v>
@@ -52192,7 +52192,7 @@
         <v>16.4950008392334</v>
       </c>
       <c r="G1787" t="n">
-        <v>14.0331535339355</v>
+        <v>14.0331544876099</v>
       </c>
       <c r="H1787" t="n">
         <v>1311331</v>
@@ -52250,7 +52250,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1789" t="n">
-        <v>14.318154335022</v>
+        <v>14.3181552886963</v>
       </c>
       <c r="H1789" t="n">
         <v>1992330</v>
@@ -52308,7 +52308,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G1791" t="n">
-        <v>14.2203187942505</v>
+        <v>14.2203178405762</v>
       </c>
       <c r="H1791" t="n">
         <v>2225422</v>
@@ -52366,7 +52366,7 @@
         <v>16.7450008392334</v>
       </c>
       <c r="G1793" t="n">
-        <v>14.2458400726318</v>
+        <v>14.2458410263062</v>
       </c>
       <c r="H1793" t="n">
         <v>986355</v>
@@ -52453,7 +52453,7 @@
         <v>16.2350006103516</v>
       </c>
       <c r="G1796" t="n">
-        <v>13.811957359314</v>
+        <v>13.8119564056396</v>
       </c>
       <c r="H1796" t="n">
         <v>1934638</v>
@@ -52482,7 +52482,7 @@
         <v>16.4349994659424</v>
       </c>
       <c r="G1797" t="n">
-        <v>13.9821071624756</v>
+        <v>13.9821062088013</v>
       </c>
       <c r="H1797" t="n">
         <v>1100115</v>
@@ -52540,7 +52540,7 @@
         <v>16.0149993896484</v>
       </c>
       <c r="G1799" t="n">
-        <v>13.624792098999</v>
+        <v>13.6247911453247</v>
       </c>
       <c r="H1799" t="n">
         <v>2043334</v>
@@ -52598,7 +52598,7 @@
         <v>16.3549995422363</v>
       </c>
       <c r="G1801" t="n">
-        <v>13.9140472412109</v>
+        <v>13.9140481948853</v>
       </c>
       <c r="H1801" t="n">
         <v>1769467</v>
@@ -52627,7 +52627,7 @@
         <v>16.4249992370605</v>
       </c>
       <c r="G1802" t="n">
-        <v>13.9735984802246</v>
+        <v>13.9735994338989</v>
       </c>
       <c r="H1802" t="n">
         <v>1570176</v>
@@ -52714,7 +52714,7 @@
         <v>16.4449996948242</v>
       </c>
       <c r="G1805" t="n">
-        <v>13.9906139373779</v>
+        <v>13.9906148910522</v>
       </c>
       <c r="H1805" t="n">
         <v>1467688</v>
@@ -52743,7 +52743,7 @@
         <v>16.5049991607666</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.0416603088379</v>
+        <v>14.0416593551636</v>
       </c>
       <c r="H1806" t="n">
         <v>1946632</v>
@@ -52946,7 +52946,7 @@
         <v>16.5949993133545</v>
       </c>
       <c r="G1813" t="n">
-        <v>14.1182279586792</v>
+        <v>14.1182270050049</v>
       </c>
       <c r="H1813" t="n">
         <v>1504272</v>
@@ -53120,7 +53120,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1819" t="n">
-        <v>14.1012134552002</v>
+        <v>14.1012125015259</v>
       </c>
       <c r="H1819" t="n">
         <v>1445138</v>
@@ -53178,7 +53178,7 @@
         <v>16.0049991607666</v>
       </c>
       <c r="G1821" t="n">
-        <v>13.616283416748</v>
+        <v>13.6162843704224</v>
       </c>
       <c r="H1821" t="n">
         <v>2311806</v>
@@ -53294,7 +53294,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1825" t="n">
-        <v>13.6971054077148</v>
+        <v>13.6971063613892</v>
       </c>
       <c r="H1825" t="n">
         <v>1198518</v>
@@ -53410,7 +53410,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1829" t="n">
-        <v>13.7226276397705</v>
+        <v>13.7226266860962</v>
       </c>
       <c r="H1829" t="n">
         <v>1292941</v>
@@ -53555,7 +53555,7 @@
         <v>14.0950002670288</v>
       </c>
       <c r="G1834" t="n">
-        <v>11.9913473129272</v>
+        <v>11.9913482666016</v>
       </c>
       <c r="H1834" t="n">
         <v>6189357</v>
@@ -53584,7 +53584,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1835" t="n">
-        <v>11.076789855957</v>
+        <v>11.0767908096313</v>
       </c>
       <c r="H1835" t="n">
         <v>6617771</v>
@@ -53729,7 +53729,7 @@
         <v>14.0550003051758</v>
       </c>
       <c r="G1840" t="n">
-        <v>11.9573173522949</v>
+        <v>11.9573183059692</v>
       </c>
       <c r="H1840" t="n">
         <v>3930666</v>
@@ -53787,7 +53787,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G1842" t="n">
-        <v>11.5787324905396</v>
+        <v>11.5787334442139</v>
       </c>
       <c r="H1842" t="n">
         <v>3434857</v>
@@ -53874,7 +53874,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>12.0381383895874</v>
+        <v>12.0381393432617</v>
       </c>
       <c r="H1845" t="n">
         <v>1729467</v>
@@ -53961,7 +53961,7 @@
         <v>13.914999961853</v>
       </c>
       <c r="G1848" t="n">
-        <v>11.8382120132446</v>
+        <v>11.8382129669189</v>
       </c>
       <c r="H1848" t="n">
         <v>2952972</v>
@@ -54019,7 +54019,7 @@
         <v>13.6549997329712</v>
       </c>
       <c r="G1850" t="n">
-        <v>11.6170167922974</v>
+        <v>11.6170177459717</v>
       </c>
       <c r="H1850" t="n">
         <v>2542949</v>
@@ -54048,7 +54048,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G1851" t="n">
-        <v>11.9147806167603</v>
+        <v>11.9147815704346</v>
       </c>
       <c r="H1851" t="n">
         <v>2391436</v>
@@ -54106,7 +54106,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G1853" t="n">
-        <v>12.259334564209</v>
+        <v>12.2593355178833</v>
       </c>
       <c r="H1853" t="n">
         <v>3308275</v>
@@ -54135,7 +54135,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G1854" t="n">
-        <v>12.0509004592896</v>
+        <v>12.0509014129639</v>
       </c>
       <c r="H1854" t="n">
         <v>2270868</v>
@@ -54338,7 +54338,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G1861" t="n">
-        <v>12.072169303894</v>
+        <v>12.0721683502197</v>
       </c>
       <c r="H1861" t="n">
         <v>1150810</v>
@@ -54454,7 +54454,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1865" t="n">
-        <v>11.6808242797852</v>
+        <v>11.6808233261108</v>
       </c>
       <c r="H1865" t="n">
         <v>3201725</v>
@@ -54483,7 +54483,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G1866" t="n">
-        <v>11.3235082626343</v>
+        <v>11.32350730896</v>
       </c>
       <c r="H1866" t="n">
         <v>2253898</v>
@@ -54512,7 +54512,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G1867" t="n">
-        <v>11.6638088226318</v>
+        <v>11.6638078689575</v>
       </c>
       <c r="H1867" t="n">
         <v>1852658</v>
@@ -54570,7 +54570,7 @@
         <v>13.5150003433228</v>
       </c>
       <c r="G1869" t="n">
-        <v>11.4979124069214</v>
+        <v>11.4979133605957</v>
       </c>
       <c r="H1869" t="n">
         <v>2327193</v>
@@ -54773,7 +54773,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1876" t="n">
-        <v>10.8768615722656</v>
+        <v>10.8768625259399</v>
       </c>
       <c r="H1876" t="n">
         <v>2656906</v>
@@ -55121,7 +55121,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1888" t="n">
-        <v>11.0128221511841</v>
+        <v>11.0128231048584</v>
       </c>
       <c r="H1888" t="n">
         <v>2981675</v>
@@ -55295,7 +55295,7 @@
         <v>12.5</v>
       </c>
       <c r="G1894" t="n">
-        <v>11.0659399032593</v>
+        <v>11.0659408569336</v>
       </c>
       <c r="H1894" t="n">
         <v>2070672</v>
@@ -55382,7 +55382,7 @@
         <v>12.4650001525879</v>
       </c>
       <c r="G1897" t="n">
-        <v>11.0349559783936</v>
+        <v>11.0349550247192</v>
       </c>
       <c r="H1897" t="n">
         <v>3755807</v>
@@ -55411,7 +55411,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1898" t="n">
-        <v>11.3182430267334</v>
+        <v>11.3182420730591</v>
       </c>
       <c r="H1898" t="n">
         <v>4023127</v>
@@ -55585,7 +55585,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G1904" t="n">
-        <v>10.5967435836792</v>
+        <v>10.5967445373535</v>
       </c>
       <c r="H1904" t="n">
         <v>1985036</v>
@@ -55614,7 +55614,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1905" t="n">
-        <v>10.5878915786743</v>
+        <v>10.587890625</v>
       </c>
       <c r="H1905" t="n">
         <v>2112945</v>
@@ -55788,7 +55788,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1911" t="n">
-        <v>10.6764183044434</v>
+        <v>10.6764192581177</v>
       </c>
       <c r="H1911" t="n">
         <v>2465453</v>
@@ -55846,7 +55846,7 @@
         <v>12.4750003814697</v>
       </c>
       <c r="G1913" t="n">
-        <v>11.0438089370728</v>
+        <v>11.0438079833984</v>
       </c>
       <c r="H1913" t="n">
         <v>13122628</v>
@@ -55962,7 +55962,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1917" t="n">
-        <v>11.8626871109009</v>
+        <v>11.8626880645752</v>
       </c>
       <c r="H1917" t="n">
         <v>3249165</v>
@@ -55991,7 +55991,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G1918" t="n">
-        <v>11.8715400695801</v>
+        <v>11.8715410232544</v>
       </c>
       <c r="H1918" t="n">
         <v>3310722</v>
@@ -56078,7 +56078,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1921" t="n">
-        <v>12.0663003921509</v>
+        <v>12.0663013458252</v>
       </c>
       <c r="H1921" t="n">
         <v>2571170</v>
@@ -56368,7 +56368,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G1931" t="n">
-        <v>12.2920455932617</v>
+        <v>12.292046546936</v>
       </c>
       <c r="H1931" t="n">
         <v>4864850</v>
@@ -56426,7 +56426,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G1933" t="n">
-        <v>11.9821996688843</v>
+        <v>11.98219871521</v>
       </c>
       <c r="H1933" t="n">
         <v>2208640</v>
@@ -56455,7 +56455,7 @@
         <v>13.625</v>
       </c>
       <c r="G1934" t="n">
-        <v>12.0618743896484</v>
+        <v>12.0618734359741</v>
       </c>
       <c r="H1934" t="n">
         <v>1791107</v>
@@ -56513,7 +56513,7 @@
         <v>12.2250003814697</v>
       </c>
       <c r="G1936" t="n">
-        <v>10.82248878479</v>
+        <v>10.8224897384644</v>
       </c>
       <c r="H1936" t="n">
         <v>11207002</v>
@@ -56658,7 +56658,7 @@
         <v>13.0050001144409</v>
       </c>
       <c r="G1941" t="n">
-        <v>11.5130043029785</v>
+        <v>11.5130033493042</v>
       </c>
       <c r="H1941" t="n">
         <v>1763618</v>
@@ -56774,7 +56774,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G1945" t="n">
-        <v>11.1234827041626</v>
+        <v>11.1234817504883</v>
       </c>
       <c r="H1945" t="n">
         <v>1482371</v>
@@ -56890,7 +56890,7 @@
         <v>12.7349996566772</v>
       </c>
       <c r="G1949" t="n">
-        <v>11.2739791870117</v>
+        <v>11.273980140686</v>
       </c>
       <c r="H1949" t="n">
         <v>1139561</v>
@@ -56919,7 +56919,7 @@
         <v>12.7950000762939</v>
       </c>
       <c r="G1950" t="n">
-        <v>11.3270959854126</v>
+        <v>11.3270950317383</v>
       </c>
       <c r="H1950" t="n">
         <v>1951759</v>
@@ -56977,7 +56977,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1952" t="n">
-        <v>11.2075834274292</v>
+        <v>11.2075843811035</v>
       </c>
       <c r="H1952" t="n">
         <v>3774889</v>
@@ -57093,7 +57093,7 @@
         <v>12.6350002288818</v>
       </c>
       <c r="G1956" t="n">
-        <v>11.1854524612427</v>
+        <v>11.1854515075684</v>
       </c>
       <c r="H1956" t="n">
         <v>2588441</v>
@@ -57122,7 +57122,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G1957" t="n">
-        <v>10.5436267852783</v>
+        <v>10.5436277389526</v>
       </c>
       <c r="H1957" t="n">
         <v>7793962</v>
@@ -57180,7 +57180,7 @@
         <v>11.8249998092651</v>
       </c>
       <c r="G1959" t="n">
-        <v>10.4683780670166</v>
+        <v>10.4683790206909</v>
       </c>
       <c r="H1959" t="n">
         <v>3458215</v>
@@ -57209,7 +57209,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1960" t="n">
-        <v>10.4551010131836</v>
+        <v>10.4551000595093</v>
       </c>
       <c r="H1960" t="n">
         <v>2768890</v>
@@ -57325,7 +57325,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1964" t="n">
-        <v>10.3311614990234</v>
+        <v>10.3311624526978</v>
       </c>
       <c r="H1964" t="n">
         <v>2704871</v>
@@ -57441,7 +57441,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G1968" t="n">
-        <v>10.2603397369385</v>
+        <v>10.2603406906128</v>
       </c>
       <c r="H1968" t="n">
         <v>2203369</v>
@@ -57557,7 +57557,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G1972" t="n">
-        <v>10.2603397369385</v>
+        <v>10.2603406906128</v>
       </c>
       <c r="H1972" t="n">
         <v>2361185</v>
@@ -57586,7 +57586,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G1973" t="n">
-        <v>10.193943977356</v>
+        <v>10.1939449310303</v>
       </c>
       <c r="H1973" t="n">
         <v>3005626</v>
@@ -57673,7 +57673,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G1976" t="n">
-        <v>9.74688053131104</v>
+        <v>9.74687957763672</v>
       </c>
       <c r="H1976" t="n">
         <v>2130085</v>
@@ -57760,7 +57760,7 @@
         <v>10.6549997329712</v>
       </c>
       <c r="G1979" t="n">
-        <v>9.43260765075684</v>
+        <v>9.43260669708252</v>
       </c>
       <c r="H1979" t="n">
         <v>2652336</v>
@@ -57789,7 +57789,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G1980" t="n">
-        <v>9.7645845413208</v>
+        <v>9.76458549499512</v>
       </c>
       <c r="H1980" t="n">
         <v>3974217</v>
@@ -57905,7 +57905,7 @@
         <v>10.8450002670288</v>
       </c>
       <c r="G1984" t="n">
-        <v>9.60081005096436</v>
+        <v>9.60080909729004</v>
       </c>
       <c r="H1984" t="n">
         <v>2019740</v>
@@ -57934,7 +57934,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G1985" t="n">
-        <v>9.7645845413208</v>
+        <v>9.76458549499512</v>
       </c>
       <c r="H1985" t="n">
         <v>3516275</v>
@@ -58050,7 +58050,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G1989" t="n">
-        <v>9.71146965026855</v>
+        <v>9.71146869659424</v>
       </c>
       <c r="H1989" t="n">
         <v>1932634</v>
@@ -58079,7 +58079,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1990" t="n">
-        <v>9.66720485687256</v>
+        <v>9.66720581054688</v>
       </c>
       <c r="H1990" t="n">
         <v>2767724</v>
@@ -58195,7 +58195,7 @@
         <v>11.0550003051758</v>
       </c>
       <c r="G1994" t="n">
-        <v>9.78671741485596</v>
+        <v>9.78671646118164</v>
       </c>
       <c r="H1994" t="n">
         <v>1494144</v>
@@ -58311,7 +58311,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G1998" t="n">
-        <v>10.5436267852783</v>
+        <v>10.5436277389526</v>
       </c>
       <c r="H1998" t="n">
         <v>5882314</v>
@@ -58514,7 +58514,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G2005" t="n">
-        <v>10.9729871749878</v>
+        <v>10.9729862213135</v>
       </c>
       <c r="H2005" t="n">
         <v>6408248</v>
@@ -58717,7 +58717,7 @@
         <v>11.9650001525879</v>
       </c>
       <c r="G2012" t="n">
-        <v>10.5923166275024</v>
+        <v>10.5923175811768</v>
       </c>
       <c r="H2012" t="n">
         <v>1403887</v>
@@ -58775,7 +58775,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G2014" t="n">
-        <v>10.5878915786743</v>
+        <v>10.587890625</v>
       </c>
       <c r="H2014" t="n">
         <v>1195621</v>
@@ -58804,7 +58804,7 @@
         <v>11.9549999237061</v>
       </c>
       <c r="G2015" t="n">
-        <v>10.5834646224976</v>
+        <v>10.5834636688232</v>
       </c>
       <c r="H2015" t="n">
         <v>1372665</v>
@@ -58833,7 +58833,7 @@
         <v>12.2349996566772</v>
       </c>
       <c r="G2016" t="n">
-        <v>10.8313417434692</v>
+        <v>10.8313407897949</v>
       </c>
       <c r="H2016" t="n">
         <v>2641847</v>
@@ -58949,7 +58949,7 @@
         <v>12.5</v>
       </c>
       <c r="G2020" t="n">
-        <v>11.0659399032593</v>
+        <v>11.0659408569336</v>
       </c>
       <c r="H2020" t="n">
         <v>1638378</v>
@@ -59007,7 +59007,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G2022" t="n">
-        <v>11.3403749465942</v>
+        <v>11.3403759002686</v>
       </c>
       <c r="H2022" t="n">
         <v>3651366</v>
@@ -59094,7 +59094,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G2025" t="n">
-        <v>11.9069499969482</v>
+        <v>11.9069509506226</v>
       </c>
       <c r="H2025" t="n">
         <v>3154851</v>
@@ -59152,7 +59152,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2027" t="n">
-        <v>11.9689197540283</v>
+        <v>11.9689207077026</v>
       </c>
       <c r="H2027" t="n">
         <v>4153108</v>
@@ -59210,7 +59210,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G2029" t="n">
-        <v>11.942361831665</v>
+        <v>11.9423627853394</v>
       </c>
       <c r="H2029" t="n">
         <v>1889820</v>
@@ -59268,7 +59268,7 @@
         <v>13.4549999237061</v>
       </c>
       <c r="G2031" t="n">
-        <v>11.9113779067993</v>
+        <v>11.911376953125</v>
       </c>
       <c r="H2031" t="n">
         <v>1553104</v>
@@ -59297,7 +59297,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>11.8626871109009</v>
+        <v>11.8626880645752</v>
       </c>
       <c r="H2032" t="n">
         <v>1016892</v>
@@ -59471,7 +59471,7 @@
         <v>13.3249998092651</v>
       </c>
       <c r="G2038" t="n">
-        <v>11.7962913513184</v>
+        <v>11.7962923049927</v>
       </c>
       <c r="H2038" t="n">
         <v>2032720</v>
@@ -59587,7 +59587,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G2042" t="n">
-        <v>11.9954795837402</v>
+        <v>11.9954786300659</v>
       </c>
       <c r="H2042" t="n">
         <v>2251868</v>
@@ -59616,7 +59616,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G2043" t="n">
-        <v>12.2787656784058</v>
+        <v>12.2787666320801</v>
       </c>
       <c r="H2043" t="n">
         <v>3824472</v>
@@ -59674,7 +59674,7 @@
         <v>13.9750003814697</v>
       </c>
       <c r="G2045" t="n">
-        <v>12.3717212677002</v>
+        <v>12.3717203140259</v>
       </c>
       <c r="H2045" t="n">
         <v>2169431</v>
@@ -59732,7 +59732,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G2047" t="n">
-        <v>12.4248361587524</v>
+        <v>12.4248371124268</v>
       </c>
       <c r="H2047" t="n">
         <v>1920068</v>
@@ -59761,7 +59761,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2048" t="n">
-        <v>12.3053255081177</v>
+        <v>12.3053245544434</v>
       </c>
       <c r="H2048" t="n">
         <v>2995667</v>
@@ -59848,7 +59848,7 @@
         <v>13.7250003814697</v>
       </c>
       <c r="G2051" t="n">
-        <v>12.1504020690918</v>
+        <v>12.1504030227661</v>
       </c>
       <c r="H2051" t="n">
         <v>2295970</v>
@@ -59935,7 +59935,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G2054" t="n">
-        <v>12.190239906311</v>
+        <v>12.1902389526367</v>
       </c>
       <c r="H2054" t="n">
         <v>1101459</v>
@@ -59964,7 +59964,7 @@
         <v>13.9650001525879</v>
       </c>
       <c r="G2055" t="n">
-        <v>12.3628673553467</v>
+        <v>12.362868309021</v>
       </c>
       <c r="H2055" t="n">
         <v>1910347</v>
@@ -60254,7 +60254,7 @@
         <v>12.8850002288818</v>
       </c>
       <c r="G2065" t="n">
-        <v>11.4067707061768</v>
+        <v>11.4067716598511</v>
       </c>
       <c r="H2065" t="n">
         <v>1287041</v>
@@ -60544,7 +60544,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G2075" t="n">
-        <v>11.6413688659668</v>
+        <v>11.6413679122925</v>
       </c>
       <c r="H2075" t="n">
         <v>2479047</v>
@@ -60718,7 +60718,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2081" t="n">
-        <v>11.4554605484009</v>
+        <v>11.4554595947266</v>
       </c>
       <c r="H2081" t="n">
         <v>1655448</v>
@@ -60805,7 +60805,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G2084" t="n">
-        <v>11.7033386230469</v>
+        <v>11.7033376693726</v>
       </c>
       <c r="H2084" t="n">
         <v>1944721</v>
@@ -60921,7 +60921,7 @@
         <v>13.25</v>
       </c>
       <c r="G2088" t="n">
-        <v>11.7298955917358</v>
+        <v>11.7298965454102</v>
       </c>
       <c r="H2088" t="n">
         <v>2350431</v>
@@ -60950,7 +60950,7 @@
         <v>13.2250003814697</v>
       </c>
       <c r="G2089" t="n">
-        <v>11.7077655792236</v>
+        <v>11.7077646255493</v>
       </c>
       <c r="H2089" t="n">
         <v>1582393</v>
@@ -60979,7 +60979,7 @@
         <v>13.3249998092651</v>
       </c>
       <c r="G2090" t="n">
-        <v>11.7962913513184</v>
+        <v>11.7962923049927</v>
       </c>
       <c r="H2090" t="n">
         <v>5178441</v>
@@ -61095,7 +61095,7 @@
         <v>13.7349996566772</v>
       </c>
       <c r="G2094" t="n">
-        <v>12.159255027771</v>
+        <v>12.1592540740967</v>
       </c>
       <c r="H2094" t="n">
         <v>4057351</v>
@@ -61153,7 +61153,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2096" t="n">
-        <v>12.3584413528442</v>
+        <v>12.3584423065186</v>
       </c>
       <c r="H2096" t="n">
         <v>2883561</v>
@@ -61240,7 +61240,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G2099" t="n">
-        <v>12.2920455932617</v>
+        <v>12.292046546936</v>
       </c>
       <c r="H2099" t="n">
         <v>2494940</v>
@@ -61298,7 +61298,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G2101" t="n">
-        <v>12.7346830368042</v>
+        <v>12.7346839904785</v>
       </c>
       <c r="H2101" t="n">
         <v>10177983</v>
@@ -61414,7 +61414,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G2105" t="n">
-        <v>12.7789468765259</v>
+        <v>12.7789478302002</v>
       </c>
       <c r="H2105" t="n">
         <v>3631338</v>
@@ -61588,7 +61588,7 @@
         <v>13.7950000762939</v>
       </c>
       <c r="G2111" t="n">
-        <v>12.2123708724976</v>
+        <v>12.2123718261719</v>
       </c>
       <c r="H2111" t="n">
         <v>1964436</v>
@@ -61646,7 +61646,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G2113" t="n">
-        <v>12.5177917480469</v>
+        <v>12.5177907943726</v>
       </c>
       <c r="H2113" t="n">
         <v>1944456</v>
@@ -61791,7 +61791,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2118" t="n">
-        <v>12.5709066390991</v>
+        <v>12.5709075927734</v>
       </c>
       <c r="H2118" t="n">
         <v>1791428</v>
@@ -61820,7 +61820,7 @@
         <v>14.2049999237061</v>
       </c>
       <c r="G2119" t="n">
-        <v>12.5753345489502</v>
+        <v>12.5753335952759</v>
       </c>
       <c r="H2119" t="n">
         <v>1609008</v>
@@ -61878,7 +61878,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2121" t="n">
-        <v>12.6594362258911</v>
+        <v>12.6594352722168</v>
       </c>
       <c r="H2121" t="n">
         <v>3195732</v>
@@ -62023,7 +62023,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G2126" t="n">
-        <v>13.2702741622925</v>
+        <v>13.2702751159668</v>
       </c>
       <c r="H2126" t="n">
         <v>3027426</v>
@@ -62052,7 +62052,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G2127" t="n">
-        <v>13.4119186401367</v>
+        <v>13.411919593811</v>
       </c>
       <c r="H2127" t="n">
         <v>2318284</v>
@@ -62081,7 +62081,7 @@
         <v>15.125</v>
       </c>
       <c r="G2128" t="n">
-        <v>13.3897876739502</v>
+        <v>13.3897867202759</v>
       </c>
       <c r="H2128" t="n">
         <v>2635433</v>
@@ -80200,7 +80200,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="E2753" t="n">
-        <v>20.8199996948242</v>
+        <v>20.8099994659424</v>
       </c>
       <c r="F2753" t="n">
         <v>20.8700008392334</v>
@@ -80212,6 +80212,35 @@
         <v>2277897</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>20.8799991607666</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>20.9699993133545</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>20.6800003051758</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>20.7199993133545</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>20.7199993133545</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>2575258</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
